--- a/investment_archetypes.xlsx
+++ b/investment_archetypes.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VITL (#1, NOT)</t>
+          <t>OPRX (#1, NOT)</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FUN (#7, NOT)</t>
+          <t>MRP (#7, NOT)</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KYMR (#6, NOT)</t>
+          <t>PRLD (#2, NOT)</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HHH (#2, NOT)</t>
+          <t>HHH (#4, NOT)</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KBR (#5, NOT)</t>
+          <t>KBR (#13, NOT)</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VITL (#1, NOT)</t>
+          <t>OPRX (#1, NOT)</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NRP (#3, NOT)</t>
+          <t>NRP (#10, NOT)</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BZU.IM (#19, NOT)</t>
+          <t>MTY.TO (#21, NOT)</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CTSH (#25, NOT)</t>
+          <t>CTSH (#27, NOT)</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LQDA (#17, NOT)</t>
+          <t>LQDA (#5, NOT)</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -939,22 +939,22 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>BZU.IM</t>
+          <t>MTY.TO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buzzi SpA</t>
+          <t>MTY Food Group</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>€8.9B</t>
+          <t>C$887M</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>€49</t>
+          <t>C$40.41</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -962,43 +962,43 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.7-2x</t>
+          <t>2-2.5x</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Kerrisdale Capital published long thesis Oct 2025 (€85 PT)</t>
+          <t>CEO open-market buy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Italian cement at 6.8x EV/EBITDA; AI data-center concrete; Kerrisdale €85 PT (+73%) NEW</t>
+          <t>ENTRY-TODAY: AT BOOK 1.04x + 16.7% FCF yield = pure value. M&amp;A pool at 12-14x EBITDA vs trading 7.5x = M&amp;A precedent arb. CEO Lefebvre open-market buy at C$30.54 = sponsor put. QSR consolidation trend.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>THESIS: Italian cement (€8.9B mcap). 52% of EBITDA from US. AI data-center concrete demand thesis. Trading at sector-discount multiple to LafargeHolcim/CRH peers. | VALUATION: 6.8x EV/EBITDA (vs peer 9-11x); €85 PT = +73% upside</t>
+          <t>THESIS: [See Archetype 1] | VALUATION: [See Archetype 1]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: AI data-center capex translating to concrete orders; multiple re-rate to peer levels | VARIANT: Italian listing + cement = institutional underweight. Kerrisdale Oct 2025 long thesis 73% upside.</t>
+          <t>CATALYST: Q2 2026 SSS test + NCIB | VARIANT: [See Archetype 1]</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
@@ -1016,66 +1016,66 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>MTY.TO</t>
+          <t>BZU.IM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MTY Food Group</t>
+          <t>Buzzi SpA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C$887M</t>
+          <t>€8.9B</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>C$40.41</t>
+          <t>€49</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2-2.5x</t>
+          <t>1.7-2x (Kerrisdale €85 PT)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>10:1</t>
+          <t>8:1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CEO open-market buy</t>
+          <t>Kerrisdale Capital published long thesis Oct 2025 (€85 PT)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: QSR franchisor at BOOK; 16.7% FCF yield; M&amp;A 12-14x EBITDA pool; CEO buying</t>
+          <t>ENTRY-TODAY: 6.8x EV/EBITDA vs peers 9-11x. AI data-center concrete demand = real (not theoretical). 52% EBITDA from US. Kerrisdale Oct 2025 €85 PT (+73%). Italian listing = institutional underweight = re-rate slow but explicit.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>THESIS: [See Archetype 1] | VALUATION: [See Archetype 1]</t>
+          <t>THESIS: Italian cement (€8.9B mcap). 52% of EBITDA from US. AI data-center concrete demand thesis. Trading at sector-discount multiple to LafargeHolcim/CRH peers. | VALUATION: 6.8x EV/EBITDA (vs peer 9-11x); €85 PT = +73% upside</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: Q2 2026 SSS test + NCIB | VARIANT: [See Archetype 1]</t>
+          <t>CATALYST: AI data-center capex translating to concrete orders; multiple re-rate to peer levels | VARIANT: Italian listing + cement = institutional underweight. Kerrisdale Oct 2025 long thesis 73% upside.</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Independent CTV SSP; Netflix/Disney/Roku scaling; Nine Ten 13.1% / $41.4M</t>
+          <t>ENTRY-TODAY: Independent CTV SSP = winner of ad-tech wash-out. Netflix/Disney/Roku scaling. AI integration. Nine Ten 13.1% / 3.48M sh = highest concentration.</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Yartseva 6/7; FCF 9.88%; -27% 6mo; AI accelerator-not-disruptor thesis</t>
+          <t>ENTRY-TODAY: Yartseva 6/7 + 9.88% FCF yield + ROA 10.44% + -27% 6mo. AI accelerator-not-disruptor thesis. Defensive value vs deep-value pure play.</t>
         </is>
       </c>
     </row>
@@ -1355,39 +1355,39 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>RERATED</t>
+        <v>35</v>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Danaher</t>
+          <t>Regeneron</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>$122B</t>
+          <t>$65B</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$171</t>
+          <t>$638</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.4-1.6x (was 1.8-2x)</t>
+          <t>1.5-2x</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1397,33 +1397,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>8:1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>D1 Capital +312% Q1 ($107M→$437M, 4th-largest position)</t>
+          <t>Founder-led; multi-fund pharma specialist holds</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Bouncing from trough; bioprocessing cycle now consensus; multiple expansion captured</t>
+          <t>ENTRY-TODAY: Defensive quality. Pipeline optionality. Partial trough recovery underway.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>THESIS: Pure-play life sciences (Cytiva bioprocessing, Beckman Dx, Cepheid). Q1 EPS $2.06 beat by 6.2%; bioprocessing inflecting positive after destock; Cepheid respiratory comp resets Q4 2026. | VALUATION: 19.7x forward P/E (trough vs 5yr avg 30x); ROA pos; B/M 0.43</t>
+          <t>THESIS: Founder/CEO Schleifer + Yancopoulos R&amp;D-led. $31.4B book equity + EYLEA franchise + Linvoseltamab launching. Pipeline broad. Itepekimab Phase 3 readout potential catalyst. | VALUATION: B/M 0.48, FCF yield 6.33%, P/B 2.07; Yartseva 6/7 (size only fail)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: Bioprocessing book-to-bill durably &gt;1.0 + China VBP stabilization H2 2026 + Cepheid Q4 reset | VARIANT: Consensus: show-me on growth post-destock. Sundheim/D1: same stock 2019-2021 (30%/yr) at trough multiple while H2 2026 comps inflect.</t>
+          <t>CATALYST: Itepekimab 2026-2027 data + Linvoseltamab ramp | VARIANT: Market: fianlimab miss + Eylea biosimilar. Smart: broad pipeline + buyback + founder skin.</t>
         </is>
       </c>
     </row>
@@ -1432,39 +1432,39 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>40</v>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+        <v>41</v>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>RERATED</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>Danaher</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>$65B</t>
+          <t>$122B</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$638</t>
+          <t>$171</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.5-2x</t>
+          <t>1.3-1.5x</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1474,33 +1474,33 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Founder-led; multi-fund pharma specialist holds</t>
+          <t>D1 Capital +312% Q1 ($107M→$437M, 4th-largest position)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Defensive quality compounder; pipeline still optionality; partial trough recovery</t>
+          <t>ENTRY-TODAY: Bouncing from trough; bioprocessing cycle now consensus; multiple expansion captured. Defensive 2H 2026 fully priced.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>THESIS: Founder/CEO Schleifer + Yancopoulos R&amp;D-led. $31.4B book equity + EYLEA franchise + Linvoseltamab launching. Pipeline broad. Itepekimab Phase 3 readout potential catalyst. | VALUATION: B/M 0.48, FCF yield 6.33%, P/B 2.07; Yartseva 6/7 (size only fail)</t>
+          <t>THESIS: Pure-play life sciences (Cytiva bioprocessing, Beckman Dx, Cepheid). Q1 EPS $2.06 beat by 6.2%; bioprocessing inflecting positive after destock; Cepheid respiratory comp resets Q4 2026. | VALUATION: 19.7x forward P/E (trough vs 5yr avg 30x); ROA pos; B/M 0.43</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: Itepekimab 2026-2027 data + Linvoseltamab ramp | VARIANT: Market: fianlimab miss + Eylea biosimilar. Smart: broad pipeline + buyback + founder skin.</t>
+          <t>CATALYST: Bioprocessing book-to-bill durably &gt;1.0 + China VBP stabilization H2 2026 + Cepheid Q4 reset | VARIANT: Consensus: show-me on growth post-destock. Sundheim/D1: same stock 2019-2021 (30%/yr) at trough multiple while H2 2026 comps inflect.</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -1654,11 +1654,11 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2-2.5x</t>
+          <t>2-3x or -50% (binary)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>6:1 (9:1 risk-adj)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1680,7 +1680,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: 327 patent ruling pending; Buckley 32% LONG + PUT structure; UTHR M&amp;A target</t>
+          <t>ENTRY-TODAY: '327 PATENT RULING PENDING = pure BINARY. Buckley 32% LONG + PUT structure ($44.7M notional) = sophisticated insider expectation of VIOLENT move. UTHR M&amp;A target. Q1 $129.9M (+44% QoQ) momentum continues. Defined event, not slow re-rate.</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>AAP CALL</t>
+          <t>CTMX-WT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Advance Auto Parts calls (Cooper Creek)</t>
+          <t>CytomX Tranche 2 Warrants</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1731,11 +1731,11 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3-5x calls</t>
+          <t>2-4x or zero (5-wk timer)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1745,33 +1745,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6:1</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cooper Creek call stack ($518M total notional incl SIG/TTWO/DOCN/GXO)</t>
+          <t>BVF Partners 13G/A #5 (warrants exp 7/3/2026)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Cooper Creek call stack leverage on H Partners cash thesis</t>
+          <t>ENTRY-TODAY: BVF Tranche 2 warrants EXPIRE 7/3/2026 = 5-WEEK binary timer. Most extreme dated catalyst in universe. BVF KYMR conviction signals biotech book quality. Pure binary structure.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>THESIS: Cooper Creek's largest single call exposure. Overlaps with H Partners' AAP cash 46% concentration = double-conviction across two fund styles. | VALUATION: $158M call notional; +213% Q1 2026 (Cooper Creek)</t>
+          <t>THESIS: BVF Partners holds CTMX Tranche 2 warrants expiring 7/3/2026 (next 5 weeks). Embedded biotech IPO/crossover leverage near expiration creates urgency catalyst. | VALUATION: 5.77M shares warrants; group ownership equivalent ~3.5%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: Q2 2026 margin recovery proof + H Partners 13D escalation | VARIANT: Catalyst-driven leverage on H Partners' AAP thesis.</t>
+          <t>CATALYST: Warrant expiration 7/3/2026 = IMMINENT URGENCY | VARIANT: BVF's KYMR top conviction (14.6%) signals their biotech book has high conviction quality.</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>CTMX-WT</t>
+          <t>AAP CALL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CytomX Tranche 2 Warrants</t>
+          <t>Advance Auto Parts calls (Cooper Creek)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1808,11 +1808,11 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2-4x warrant</t>
+          <t>3-5x via calls</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1822,33 +1822,33 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>6:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>BVF Partners 13G/A #5 (warrants exp 7/3/2026)</t>
+          <t>Cooper Creek call stack ($518M total notional incl SIG/TTWO/DOCN/GXO)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: BVF Tranche 2 warrants expire 7/3/2026 = IMMINENT URGENCY</t>
+          <t>ENTRY-TODAY: Cooper Creek $158M call notional +213% Q1 = leveraged play on H Partners 46% cash thesis. Q2 margin proof Aug = trigger. Two-fund double-conviction across styles. Options leverage on violent move.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>THESIS: BVF Partners holds CTMX Tranche 2 warrants expiring 7/3/2026 (next 5 weeks). Embedded biotech IPO/crossover leverage near expiration creates urgency catalyst. | VALUATION: 5.77M shares warrants; group ownership equivalent ~3.5%</t>
+          <t>THESIS: Cooper Creek's largest single call exposure. Overlaps with H Partners' AAP cash 46% concentration = double-conviction across two fund styles. | VALUATION: $158M call notional; +213% Q1 2026 (Cooper Creek)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: Warrant expiration 7/3/2026 = IMMINENT URGENCY | VARIANT: BVF's KYMR top conviction (14.6%) signals their biotech book has high conviction quality.</t>
+          <t>CATALYST: Q2 2026 margin recovery proof + H Partners 13D escalation | VARIANT: Catalyst-driven leverage on H Partners' AAP thesis.</t>
         </is>
       </c>
     </row>
@@ -1885,11 +1885,11 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.5-2x</t>
+          <t>1.5-2x via straddle</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Stonepine 40.9% in straddle; FDA cycle 2026-2027 dispersion</t>
+          <t>ENTRY-TODAY: Stonepine 40.9% in straddle = pure long-vol on biotech FDA cycle dispersion 2026-2027. Not directional value bet.</t>
         </is>
       </c>
     </row>
@@ -2065,12 +2065,12 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>VITL</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Vital Farms</t>
+          <t>OptimizeRx</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
@@ -2080,12 +2080,12 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>$1.5B</t>
+          <t>$93M</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>$13</t>
+          <t>$4.82</t>
         </is>
       </c>
       <c r="H4" s="9" t="n">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>2-4x ($11.50 PT)</t>
         </is>
       </c>
       <c r="J4" s="9" t="inlineStr">
@@ -2103,22 +2103,22 @@
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
-          <t>13:1</t>
+          <t>12:1</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
         <is>
-          <t>Deepest drawdown -68.76%; 11% ROA sustained; no smart money pile-in yet</t>
+          <t>SUB-BOOK 0.70x + $19M FCF profitable + insider 14.82% + analyst $11.50 (138%) + sub-$100M float = ANY DSP Q4 print violently re-rates. Smart money still building (not exiting). True intrinsic value &gt; 2x current.</t>
         </is>
       </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
-          <t>No major fund concentrated yet = entry preserved; Yartseva 6/7</t>
+          <t>Insider 14.82%; $10M buyback through March 2027; Doximity exec Presti to board April 2026</t>
         </is>
       </c>
       <c r="N4" s="9" t="inlineStr">
         <is>
-          <t>Avian flu egg-supply normalization + summer pricing + M&amp;A speculation</t>
+          <t>Q4 2026 DSP integration revenue start + Q2 2026 earnings Aug 14</t>
         </is>
       </c>
     </row>
@@ -2133,27 +2133,27 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>HHH</t>
+          <t>PRLD</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Howard Hughes Holdings</t>
+          <t>Prelude Therapeutics</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>4. Sponsor-Anchored Holdco Transformation</t>
+          <t>3. Biotech Multi-Fund Convergence</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>$3.5B</t>
+          <t>$340M</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>$63.77</t>
+          <t>$4.26</t>
         </is>
       </c>
       <c r="H5" s="9" t="n">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>3-8x</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
@@ -2171,22 +2171,22 @@
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>17:1</t>
+          <t>20:1</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>Ackman $100 cost basis = floor put; Vantage close Q2 (30-45d); below sponsor entry</t>
+          <t>NET CASH $2.20/sh = 51% of $4.26 price = downside FLOORED. Baker Bros 15.5% 13D + RA Capital 9.99% 13G BOTH anchored SAME April $90M financing at $4.44 — buying TODAY $4.26 is BELOW smart money entry. JAK2 binary upside 5-10x.</t>
         </is>
       </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>Ackman 47% via $900M @ $100/sh + $1B preferred; Northern Right NEW Q1 +12%</t>
+          <t>Baker Bros 15.5% 13D/A + RA Capital 9.99% 13G; BOTH anchored SAME $90M April financing at $4.44</t>
         </is>
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>Vantage close Q2 2026 (30-45 days); Park Ward Village condo closings Q2-Q3 (~$1B rev); first post-Vantage capital allocation</t>
+          <t>PRT12396 Phase 1 H2 2026; PRT13722 IND mid-2026; Incyte option agreement Nov 2025</t>
         </is>
       </c>
     </row>
@@ -2201,12 +2201,12 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>NRP</t>
+          <t>INMD</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Natural Resource Partners</t>
+          <t>InMode Ltd</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>$1.35B</t>
+          <t>$869M</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>$105.81</t>
+          <t>$13.71</t>
         </is>
       </c>
       <c r="H6" s="9" t="n">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>2.5-3x</t>
+          <t>2-3x ($25-30)</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>14.5% FCF yield intact; distribution increase DELAYED = price unmoved; Nov 2026 catalyst</t>
+          <t>CASH FLOOR: $8.47/sh = 62% of $13.71. Steel Partners 25.5% book + implied $18-20 takeout. Founder Mizrahy +800k sh ($10.7M Feb 2026) at current = sponsor put. Cash + M&amp;A double-floor; upside on Steel re-bid.</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>Saber/Huber 17.75%, Greystone top, Right Tail NEW Q1 2026, Berkowitz/Fairholme</t>
+          <t>Steel Partners 25.5% of book; Mizrahy +800k sh ($10.7M)</t>
         </is>
       </c>
       <c r="N6" s="9" t="inlineStr">
         <is>
-          <t>Nov 2026 distribution step-up + preferreds retire; Q3 2026 Sisecam recovery sig</t>
+          <t>Q2 2026 earnings ~Aug 5 + potential Steel renewed bid ($18 prior)</t>
         </is>
       </c>
     </row>
@@ -2269,60 +2269,60 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>HHH</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>OptimizeRx</t>
+          <t>Howard Hughes Holdings</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>1. Yartseva Pure Multibagger</t>
+          <t>4. Sponsor-Anchored Holdco Transformation</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>$93M</t>
+          <t>$3.5B</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>$4.82</t>
+          <t>$63.77</t>
         </is>
       </c>
       <c r="H7" s="9" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>3.5-6x</t>
+          <t>1.5-2x to NAV</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>-45%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>-65.4% 6mo drawdown; sub-book 0.7x; Q4 DSP integration not priced</t>
+          <t>NAV $95-105 vs $63.77 = 33-39% DISCOUNT to real (not aspirational) NAV. Ackman 47% at $100 cost = sponsor PUT floor. Vantage close Q2 (30-45d) = dated trigger. Insurance float makes compounding violent post-close.</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>Insider 14.82%; $10M buyback through March 2027; Doximity exec Presti to board April 2026</t>
+          <t>Ackman 47% via $900M @ $100/sh + $1B preferred; Northern Right NEW Q1 +12%</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>Q4 2026 DSP integration revenue start + Q2 2026 earnings Aug 14</t>
+          <t>Vantage close Q2 2026 (30-45 days); Park Ward Village condo closings Q2-Q3 (~$1B rev); first post-Vantage capital allocation</t>
         </is>
       </c>
     </row>
@@ -2337,60 +2337,60 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>LQDA</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>KBR Inc</t>
+          <t>Liquidia Corp</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>5. Spinoff / SoTP Arbitrage</t>
+          <t>10. Hedged / Special Structure</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>$3.9B</t>
+          <t>$5.3B</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>$30</t>
+          <t>$60</t>
         </is>
       </c>
       <c r="H8" s="9" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>2-2.5x</t>
+          <t>2-3x or -50% (binary)</t>
         </is>
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-50%</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>10:1</t>
+          <t>6:1 (9:1 risk-adj)</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>$30 vs SoTP $55-65; MTS spin Jan 4 2027 still 7+ months away; director buys May 2026</t>
+          <t>'327 PATENT RULING PENDING = pure BINARY. Buckley 32% LONG + PUT structure ($44.7M notional) = sophisticated insider expectation of VIOLENT move. UTHR M&amp;A target. Q1 $129.9M (+44% QoQ) momentum continues. Defined event, not slow re-rate.</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>D3/Nierenberg +425% Q1 (largest single add in entire universe); Irenic activist ~1%; Director Form 4 buys May 2026</t>
+          <t>Buckley Capital 32% LONG + PUT structure ($44.7M notional)</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>MTS spin January 4 2027 (board-approved Sept 2025); NRC Natrium safety eval mid-2026</t>
+          <t>'327 patent ruling pending (binary); Q2 print Aug 2026; UTHR Tresmi competitive launch</t>
         </is>
       </c>
     </row>
@@ -2405,60 +2405,60 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>KYMR</t>
+          <t>CTMX-WT</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Kymera Therapeutics</t>
+          <t>CytomX Tranche 2 Warrants</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>3. Biotech Multi-Fund Convergence</t>
+          <t>10. Hedged / Special Structure</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>$6.5B</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>$80</t>
+          <t>varies</t>
         </is>
       </c>
       <c r="H9" s="9" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>2-4x or zero (5-wk timer)</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-100%</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>13:1</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>Trough; BROADEN2 AD mid-2027 not priced; BVF + Baker MAX dual conviction</t>
+          <t>BVF Tranche 2 warrants EXPIRE 7/3/2026 = 5-WEEK binary timer. Most extreme dated catalyst in universe. BVF KYMR conviction signals biotech book quality. Pure binary structure.</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>BVF #1 position 14.6% of $3.14B book ($458M) + Baker Bros 4.1% / $721M; BOTH anchored $86 follow-on</t>
+          <t>BVF Partners 13G/A #5 (warrants exp 7/3/2026)</t>
         </is>
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>BROADEN2 AD mid-2027 (12+ months); BREADTH asthma late 2027; FDA Fast Track granted both</t>
+          <t>Warrant expiration 7/3/2026 = IMMINENT URGENCY</t>
         </is>
       </c>
     </row>
@@ -2473,12 +2473,12 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>FUN</t>
+          <t>MRP</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Six Flags Entertainment</t>
+          <t>Millrose Properties</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>$2.2B</t>
+          <t>$4.59B</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -2501,32 +2501,32 @@
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>1.8-2.5x to NAV</t>
         </is>
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>9:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>Jaffer board seat just took effect; Jana 9% pushing OUTRIGHT SALE; -50% drawdown</t>
+          <t>B/M 1.274 = DEEPEST in 6/7 cohort (deeper than NRP 0.47). Lennar 80% owner = guaranteed off-take + patient capital. Land bank at COST BASIS vs market. Pure NAV unwind; spinoff orphan technical pressure resolves into Q2 prints.</t>
         </is>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>H Partners 53.7% / $82.5M / 5.7% of class; Jana 9% + Travis Kelce co-invest</t>
+          <t>Lennar 80%+ owner = patient capital lock-in; SITG multi-fund flag</t>
         </is>
       </c>
       <c r="N10" s="9" t="inlineStr">
         <is>
-          <t>May 26 2026 AGM: Jaffer joins board (Class III through 2027, Audit&amp;Finance Cttee). Jana 9% pushing OUTRIGHT SALE.</t>
+          <t>Q2 2026 print + Lennar volume scaling + housing cycle inflection</t>
         </is>
       </c>
     </row>
@@ -2534,67 +2534,67 @@
       <c r="A11" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>NOT</t>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>AAP</t>
+          <t>GLOB</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Globant SA</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>2. Activist Board Catalyst</t>
+          <t>1. Yartseva Pure Multibagger</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>$3.3B</t>
+          <t>$1.68B</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>$54.42</t>
+          <t>$43.50</t>
         </is>
       </c>
       <c r="H11" s="9" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>2.5-3x</t>
+          <t>3-5x if class action clears</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-35%</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>9:1</t>
+          <t>10:1</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>-80% from 2021 peak; H Partners 46% + 50% Q1 add; Q2 margin proof Aug 2026</t>
+          <t>P/E 5.91 SECTOR LOW + P/FCF 5.56 + EV/EBITDA 4.95x + 17% FCF yield = DEEPLY undervalued by every metric. Class action JUN 23 IS the catalyst that creates the discount (clears = violent rerate). AI Pods $32.8M ARR from $0 in 12mo + $352M pipeline.</t>
         </is>
       </c>
       <c r="M11" s="9" t="inlineStr">
         <is>
-          <t>H Partners 46.3% / $71.2M / +50% sh Q1 2026 (1.35M sh); Legion Partners precedent</t>
+          <t>Cartica historical 6.5% Q4 2022; sentiment bottom 16% short float</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>Q2 2026 earnings Aug = needs comps +2%+ and op margin &gt;5%; H Partners 13D escalation possible</t>
+          <t>Q3 2026 AI Pods print + Argentina FX tailwind + ENRGI platform launch H2</t>
         </is>
       </c>
     </row>
@@ -2609,40 +2609,40 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>PRLD</t>
+          <t>CRTO</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Prelude Therapeutics</t>
+          <t>Criteo SA</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>3. Biotech Multi-Fund Convergence</t>
+          <t>1. Yartseva Pure Multibagger</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>$340M</t>
+          <t>$866M</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>$4.26</t>
+          <t>$13.50</t>
         </is>
       </c>
       <c r="H12" s="9" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>2.5-4x</t>
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>Sub-$1B; PRT12396 Ph1 H2 2026; Baker + RA Cap SAME $90M financing at $4.44</t>
+          <t>P/E 3.73 fwd + P/FCF 4.98 + EV/EBITDA 2.28x + 20.7% FCF yield = DEEP. Q3 2026 anniversary of scope losses REMOVES the headwind printed in Q1. Petrus Advisers activist + $200M buyback (22% cap) + Nierenberg D3 +19% Q1.</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
-          <t>Baker Bros 15.5% 13D/A + RA Capital 9.99% 13G; BOTH anchored SAME $90M April financing at $4.44</t>
+          <t>Nierenberg D3 9.37% / +19% Q1 2026; Petrus Advisers activist</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
         <is>
-          <t>PRT12396 Phase 1 H2 2026; PRT13722 IND mid-2026; Incyte option agreement Nov 2025</t>
+          <t>Q3 2026 anniversary of scope losses + Luxembourg redomiciliation + $200M buyback (22% cap)</t>
         </is>
       </c>
     </row>
@@ -2677,60 +2677,60 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>PVLA</t>
+          <t>NRP</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Palvella Therapeutics</t>
+          <t>Natural Resource Partners</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>3. Biotech Multi-Fund Convergence</t>
+          <t>1. Yartseva Pure Multibagger</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>$1.56B</t>
+          <t>$1.35B</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>$130</t>
+          <t>$105.81</t>
         </is>
       </c>
       <c r="H13" s="9" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>2.5-3x</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>9:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>Pre-PDUFA; NDA H2 2026; BVF + Suvretta both top-10</t>
+          <t>14.5% FCF yield ALONE = pure mispricing. Royalty trust at 6.6x P/FCF vs TPL at 25x P/CF (SAME asset class) = comp gap re-rate. Distribution Nov 2026 + preferreds retire. Saber 17.75% + Right Tail NEW Q1 2026.</t>
         </is>
       </c>
       <c r="M13" s="9" t="inlineStr">
         <is>
-          <t>BVF 3.8% / $120M (8.5% of company) + Suvretta 3.67% / $144M (+29.3% Q1)</t>
+          <t>Saber/Huber 17.75%, Greystone top, Right Tail NEW Q1 2026, Berkowitz/Fairholme</t>
         </is>
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>Pre-NDA FDA meeting Q2 2026; NDA H2 2026; PDUFA H1 2027</t>
+          <t>Nov 2026 distribution step-up + preferreds retire; Q3 2026 Sisecam recovery sig</t>
         </is>
       </c>
     </row>
@@ -2745,40 +2745,40 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>ACHC</t>
+          <t>AAP CALL</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Acadia Healthcare</t>
+          <t>Advance Auto Parts calls (Cooper Creek)</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>2. Activist Board Catalyst</t>
+          <t>10. Hedged / Special Structure</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>$3.2B</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>$33</t>
+          <t>varies</t>
         </is>
       </c>
       <c r="H14" s="9" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>2-2.5x</t>
+          <t>3-5x via calls</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
-          <t>-40%</t>
+          <t>-100%</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -2788,17 +2788,17 @@
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>-70% drawdown; DOJ resolution + 29% short squeeze setup; P2 + Buckley both NEW</t>
+          <t>Cooper Creek $158M call notional +213% Q1 = leveraged play on H Partners 46% cash thesis. Q2 margin proof Aug = trigger. Two-fund double-conviction across styles. Options leverage on violent move.</t>
         </is>
       </c>
       <c r="M14" s="9" t="inlineStr">
         <is>
-          <t>Greenlight Capital 4.1M sh (David Einhorn); Sohn presentation 5/12/2026</t>
+          <t>Cooper Creek call stack ($518M total notional incl SIG/TTWO/DOCN/GXO)</t>
         </is>
       </c>
       <c r="N14" s="9" t="inlineStr">
         <is>
-          <t>DOJ resolution + Q2 2026 earnings + 29% short squeeze potential</t>
+          <t>Q2 2026 margin recovery proof + H Partners 13D escalation</t>
         </is>
       </c>
     </row>
@@ -2813,12 +2813,12 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>INMD</t>
+          <t>CARS</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>InMode Ltd</t>
+          <t>Cars.com</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -2828,45 +2828,45 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>$869M</t>
+          <t>$560M</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>$13.71</t>
+          <t>$10</t>
         </is>
       </c>
       <c r="H15" s="9" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>2.2x</t>
+          <t>2-3x</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>10:1</t>
+          <t>11:1</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>Steel re-bid optionality ($18 prior); $8.47/sh cash = 62% of price; founder $10.7M buy</t>
+          <t>P/B 0.83 + P/FCF 3.5 + 28% TTM FCF yield + EV/EBITDA 2.7x = DEEP. Q1 EPS $0.45 vs $0.13 est (+246% BEAT). $90M buyback (16% cap raised from $60M) = buyback math compounds violently with cheap multiple.</t>
         </is>
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
-          <t>Steel Partners 25.5% of book; Mizrahy +800k sh ($10.7M)</t>
+          <t>Yartseva 7/7 - smart money still building</t>
         </is>
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>Q2 2026 earnings ~Aug 5 + potential Steel renewed bid ($18 prior)</t>
+          <t>$25-30M annualized cost program 2027 + $90M buyback (16% cap raised from $60M)</t>
         </is>
       </c>
     </row>
@@ -2874,67 +2874,67 @@
       <c r="A16" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>NOT</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>GLOB</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Globant SA</t>
+          <t>KBR Inc</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>1. Yartseva Pure Multibagger</t>
+          <t>5. Spinoff / SoTP Arbitrage</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>$1.68B</t>
+          <t>$3.9B</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>$43.50</t>
+          <t>$30</t>
         </is>
       </c>
       <c r="H16" s="9" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>3-4x (was 5x)</t>
+          <t>2-2.5x ($55-65 SoTP)</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>11:1</t>
+          <t>10:1</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>Class action JUNE 23 deadline overhang; AI Pods Q3 inflection ahead but near-term risk</t>
+          <t>SoTP MTS $5.2B EV + STS $5.3B = $55-65 vs $30 today. MTS SPIN JAN 4 2027 = dated trigger 7 months out. D3 +425% Q1 (LARGEST single add in entire universe). Director Form 4 buys May 2026 = sponsor put.</t>
         </is>
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>Cartica historical 6.5% Q4 2022; sentiment bottom 16% short float</t>
+          <t>D3/Nierenberg +425% Q1 (largest single add in entire universe); Irenic activist ~1%; Director Form 4 buys May 2026</t>
         </is>
       </c>
       <c r="N16" s="9" t="inlineStr">
         <is>
-          <t>Q3 2026 AI Pods print + Argentina FX tailwind + ENRGI platform launch H2</t>
+          <t>MTS spin January 4 2027 (board-approved Sept 2025); NRC Natrium safety eval mid-2026</t>
         </is>
       </c>
     </row>
@@ -2949,60 +2949,60 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>CARS</t>
+          <t>FUN</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Cars.com</t>
+          <t>Six Flags Entertainment</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>1. Yartseva Pure Multibagger</t>
+          <t>2. Activist Board Catalyst</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>$560M</t>
+          <t>$2.2B</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>$10</t>
+          <t>$25</t>
         </is>
       </c>
       <c r="H17" s="9" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>2-2.5x</t>
+          <t>2-3x (3x outright sale)</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-30%</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>9:1</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>Yartseva 7/7 still depressed; $90M buyback (16% cap); cost program 2027</t>
+          <t>42 parks IRREPLACEABLE RE @ $47M each = $2B floor. Jaffer joined board May 26 + Jana 9% pushing OUTRIGHT SALE = two-front activist pressure. H Partners 53.7% / 5.7% of class. Sale = violent 3x trigger.</t>
         </is>
       </c>
       <c r="M17" s="9" t="inlineStr">
         <is>
-          <t>Yartseva 7/7 - smart money still building</t>
+          <t>H Partners 53.7% / $82.5M / 5.7% of class; Jana 9% + Travis Kelce co-invest</t>
         </is>
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>$25-30M annualized cost program 2027 + $90M buyback (16% cap raised from $60M)</t>
+          <t>May 26 2026 AGM: Jaffer joins board (Class III through 2027, Audit&amp;Finance Cttee). Jana 9% pushing OUTRIGHT SALE.</t>
         </is>
       </c>
     </row>
@@ -3017,60 +3017,60 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>CRTO</t>
+          <t>AAP</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Criteo SA</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>1. Yartseva Pure Multibagger</t>
+          <t>2. Activist Board Catalyst</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>$866M</t>
+          <t>$3.3B</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>$13.50</t>
+          <t>$54.42</t>
         </is>
       </c>
       <c r="H18" s="9" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>2.5-3.5x</t>
+          <t>2.5-3x ($130-150 AZO comp)</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-30%</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>12:1</t>
+          <t>9:1</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>Yartseva 7/7; Q3 2026 anniversary scope losses; Petrus activist; D3 Nierenberg +19% Q1</t>
+          <t>-80% drawdown from 2021. H Partners 46.3% + Q1 +50% sh add ($71.2M). Bridge thesis: AZO-style 8-10% margins = $130-150. Q2 Aug 2026 = margin proof catalyst. Op margin +410bps already. Not cash-floored but H Partners concentration = sponsor put.</t>
         </is>
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
-          <t>Nierenberg D3 9.37% / +19% Q1 2026; Petrus Advisers activist</t>
+          <t>H Partners 46.3% / $71.2M / +50% sh Q1 2026 (1.35M sh); Legion Partners precedent</t>
         </is>
       </c>
       <c r="N18" s="9" t="inlineStr">
         <is>
-          <t>Q3 2026 anniversary of scope losses + Luxembourg redomiciliation + $200M buyback (22% cap)</t>
+          <t>Q2 2026 earnings Aug = needs comps +2%+ and op margin &gt;5%; H Partners 13D escalation possible</t>
         </is>
       </c>
     </row>
@@ -3085,60 +3085,60 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>FTLF</t>
+          <t>ACHC</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>FitLife Brands</t>
+          <t>Acadia Healthcare</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>1. Yartseva Pure Multibagger</t>
+          <t>2. Activist Board Catalyst</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>$93M</t>
+          <t>$3.2B</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>$10</t>
+          <t>$33</t>
         </is>
       </c>
       <c r="H19" s="9" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>2-3x + squeeze</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-40%</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>13:1</t>
+          <t>6:1</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>Microcap $93M; cleanest Y7/7 setup; -43.9% 6mo; institutional minimum below</t>
+          <t>-70% drawdown + 29% SHORT FLOAT = squeeze fuel. EV/EBITDA 6.5x vs peers 8-9x. DOJ resolution binary catalyst. Greenlight 4.1M sh + Sohn 5/12 pitch = thesis surfaced publicly.</t>
         </is>
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
-          <t>Smoak Capital residual position; previously a Smoak top-5</t>
+          <t>Greenlight Capital 4.1M sh (David Einhorn); Sohn presentation 5/12/2026</t>
         </is>
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>Q2 2026 earnings; M&amp;A speculation; recovery in supplement category</t>
+          <t>DOJ resolution + Q2 2026 earnings + 29% short squeeze potential</t>
         </is>
       </c>
     </row>
@@ -3153,27 +3153,27 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>LQDA</t>
+          <t>PVLA</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Liquidia Corp</t>
+          <t>Palvella Therapeutics</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>10. Hedged / Special Structure</t>
+          <t>3. Biotech Multi-Fund Convergence</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>$5.3B</t>
+          <t>$1.56B</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>$60</t>
+          <t>$130</t>
         </is>
       </c>
       <c r="H20" s="9" t="n">
@@ -3181,32 +3181,32 @@
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>2-2.5x</t>
+          <t>2-3x</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>-50%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>10:1</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>327 patent ruling pending; Buckley 32% LONG + PUT structure; UTHR M&amp;A target</t>
+          <t>Cash $25/sh = 19% of $130 price. Phase 3 SELVA POSITIVE Feb 24 2026 = DE-RISKED. Pre-NDA Q2 + NDA H2 + PDUFA H1 2027 = staircase of catalysts. BVF 8.5% of company + Suvretta 3.67% (+29.3% Q1).</t>
         </is>
       </c>
       <c r="M20" s="9" t="inlineStr">
         <is>
-          <t>Buckley Capital 32% LONG + PUT structure ($44.7M notional)</t>
+          <t>BVF 3.8% / $120M (8.5% of company) + Suvretta 3.67% / $144M (+29.3% Q1)</t>
         </is>
       </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>'327 patent ruling pending (binary); Q2 print Aug 2026; UTHR Tresmi competitive launch</t>
+          <t>Pre-NDA FDA meeting Q2 2026; NDA H2 2026; PDUFA H1 2027</t>
         </is>
       </c>
     </row>
@@ -3221,35 +3221,35 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>FRPT</t>
+          <t>KYMR</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Freshpet</t>
+          <t>Kymera Therapeutics</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>6. Deep Drawdown Mean Reversion</t>
+          <t>3. Biotech Multi-Fund Convergence</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>$2.53B</t>
+          <t>$6.5B</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>$60</t>
+          <t>$80</t>
         </is>
       </c>
       <c r="H21" s="9" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>3-4x</t>
+          <t>3-5x</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
@@ -3259,22 +3259,22 @@
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>10:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>Manufacturing capacity online; Marlowe 39.8% (highest concentration); margin inflection</t>
+          <t>Cash $1.55B + BVF 14.6% MAX conviction + Baker 4.1% = multi-fund convergence. BUT major catalyst BROADEN2 mid-2027 = 12+ months away (low velocity). Strong setup, slow trigger.</t>
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr">
         <is>
-          <t>Marlowe Partners 39.8% in last 13F (highest single-fund signal)</t>
+          <t>BVF #1 position 14.6% of $3.14B book ($458M) + Baker Bros 4.1% / $721M; BOTH anchored $86 follow-on</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>Capacity utilization + margin inflection + M&amp;A speculation</t>
+          <t>BROADEN2 AD mid-2027 (12+ months); BREADTH asthma late 2027; FDA Fast Track granted both</t>
         </is>
       </c>
     </row>
@@ -3289,27 +3289,27 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>BZU.IM</t>
+          <t>VITL</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Buzzi SpA</t>
+          <t>Vital Farms</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>8. Foreign / Underfollowed Value</t>
+          <t>1. Yartseva Pure Multibagger</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>€8.9B</t>
+          <t>$1.5B</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>€49</t>
+          <t>$13</t>
         </is>
       </c>
       <c r="H22" s="9" t="n">
@@ -3317,32 +3317,32 @@
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>1.7-2x</t>
+          <t>2-3x ($30-40)</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>10:1</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>Italian cement at 6.8x EV/EBITDA; AI data-center concrete; Kerrisdale €85 PT (+73%) NEW</t>
+          <t>Deepest drawdown -68.76% + 11% ROA sustained = exceptional. BUT B/M 0.74 = not deeply undervalued vs book; M&amp;A precedent 4x sales = $50 = +260%. Brand-led re-rate is SLOW not violent. No defined binary catalyst.</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>Kerrisdale Capital published long thesis Oct 2025 (€85 PT)</t>
+          <t>No major fund concentrated yet = entry preserved; Yartseva 6/7</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>AI data-center capex translating to concrete orders; multiple re-rate to peer levels</t>
+          <t>Avian flu egg-supply normalization + summer pricing + M&amp;A speculation</t>
         </is>
       </c>
     </row>
@@ -3357,60 +3357,60 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>MRP</t>
+          <t>FTLF</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Millrose Properties</t>
+          <t>FitLife Brands</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>2. Activist Board Catalyst</t>
+          <t>1. Yartseva Pure Multibagger</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>$4.59B</t>
+          <t>$93M</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>$25</t>
+          <t>$10</t>
         </is>
       </c>
       <c r="H23" s="9" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>3-5x</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-30%</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>12:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>Lennar 80% spinoff; deepest B/M 1.274; pure NAV play at discount</t>
+          <t>Microcap $93M = sub-institutional minimum = any flow violently moves. Yartseva 7/7 cleanest setup. -43.9% 6mo. B/M 0.49. Pure micro-mean-reversion.</t>
         </is>
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>Lennar 80%+ owner = patient capital lock-in; SITG multi-fund flag</t>
+          <t>Smoak Capital residual position; previously a Smoak top-5</t>
         </is>
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>Q2 2026 print + Lennar volume scaling + housing cycle inflection</t>
+          <t>Q2 2026 earnings; M&amp;A speculation; recovery in supplement category</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="H24" s="9" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>10:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>QSR franchisor at BOOK; 16.7% FCF yield; M&amp;A 12-14x EBITDA pool; CEO buying</t>
+          <t>AT BOOK 1.04x + 16.7% FCF yield = pure value. M&amp;A pool at 12-14x EBITDA vs trading 7.5x = M&amp;A precedent arb. CEO Lefebvre open-market buy at C$30.54 = sponsor put. QSR consolidation trend.</t>
         </is>
       </c>
       <c r="M24" s="9" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>BZU.IM</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Buzzi SpA</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -3508,45 +3508,45 @@
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>$1.89B</t>
+          <t>€8.9B</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>$13</t>
+          <t>€49</t>
         </is>
       </c>
       <c r="H25" s="9" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>1.7-2x (Kerrisdale €85 PT)</t>
         </is>
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>12:1</t>
+          <t>8:1</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>Independent CTV SSP; Netflix/Disney/Roku scaling; Nine Ten 13.1% / $41.4M</t>
+          <t>6.8x EV/EBITDA vs peers 9-11x. AI data-center concrete demand = real (not theoretical). 52% EBITDA from US. Kerrisdale Oct 2025 €85 PT (+73%). Italian listing = institutional underweight = re-rate slow but explicit.</t>
         </is>
       </c>
       <c r="M25" s="9" t="inlineStr">
         <is>
-          <t>Nine Ten Capital (Bares) 13.1% of book / 3.48M sh / $41.4M</t>
+          <t>Kerrisdale Capital published long thesis Oct 2025 (€85 PT)</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
         <is>
-          <t>CTV ad spend doubling 2024-2028 + Netflix exclusive scaling + AI integration</t>
+          <t>AI data-center capex translating to concrete orders; multiple re-rate to peer levels</t>
         </is>
       </c>
     </row>
@@ -3561,60 +3561,60 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>JOE</t>
+          <t>COTY</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>St. Joe Company</t>
+          <t>Coty Inc</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>7. Hard Asset / Royalty</t>
+          <t>6. Deep Drawdown Mean Reversion</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>$2.8B</t>
+          <t>$1.79B</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>$48</t>
+          <t>$12</t>
         </is>
       </c>
       <c r="H26" s="9" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>2-4x</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-30%</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>10:1</t>
+          <t>9:1</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>Florida Panhandle 170k acres; GAAP B/M understates LIFO land basis; Berkowitz anchor</t>
+          <t>B/M 1.73 DEEPEST + FCF yield 17.4% but ROA -4.91% CAVEAT (Y3 fails). KKR overhang resolution = catalyst. Brand assets (Burberry, Tiffany, CK) worth multiples of EV. Operational risk balances deep value.</t>
         </is>
       </c>
       <c r="M26" s="9" t="inlineStr">
         <is>
-          <t>Berkowitz/Fairholme longstanding anchor</t>
+          <t>KKR legacy anchor; deep-value funds incrementally adding</t>
         </is>
       </c>
       <c r="N26" s="9" t="inlineStr">
         <is>
-          <t>Florida population growth + master plan community development + Berkowitz anchor</t>
+          <t>Debt restructuring + KKR exit dynamics + cost program execution</t>
         </is>
       </c>
     </row>
@@ -3629,60 +3629,60 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>COTY</t>
+          <t>JOE</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Coty Inc</t>
+          <t>St. Joe Company</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>6. Deep Drawdown Mean Reversion</t>
+          <t>7. Hard Asset / Royalty</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>$1.79B</t>
+          <t>$2.8B</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>$12</t>
+          <t>$48</t>
         </is>
       </c>
       <c r="H27" s="9" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>2-4x</t>
+          <t>2-3x to LIFO-NAV</t>
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>9:1</t>
+          <t>10:1</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>B/M 1.73 deep; KKR overhang resolution; -37.5% drawdown; ROA negative caveat</t>
+          <t>170k Florida Panhandle acres. GAAP B/M understates LIFO land basis vs market. True NAV-based B/M likely &gt;1.0. Berkowitz anchor + Florida population growth.</t>
         </is>
       </c>
       <c r="M27" s="9" t="inlineStr">
         <is>
-          <t>KKR legacy anchor; deep-value funds incrementally adding</t>
+          <t>Berkowitz/Fairholme longstanding anchor</t>
         </is>
       </c>
       <c r="N27" s="9" t="inlineStr">
         <is>
-          <t>Debt restructuring + KKR exit dynamics + cost program execution</t>
+          <t>Florida population growth + master plan community development + Berkowitz anchor</t>
         </is>
       </c>
     </row>
@@ -3697,40 +3697,40 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>9. Quality Compounder at Trough</t>
+          <t>8. Foreign / Underfollowed Value</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>$25B</t>
+          <t>$1.89B</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>$52.75</t>
+          <t>$13</t>
         </is>
       </c>
       <c r="H28" s="9" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>3-5x</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
@@ -3740,17 +3740,17 @@
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>Yartseva 6/7; FCF 9.88%; -27% 6mo; AI accelerator-not-disruptor thesis</t>
+          <t>Independent CTV SSP = winner of ad-tech wash-out. Netflix/Disney/Roku scaling. AI integration. Nine Ten 13.1% / 3.48M sh = highest concentration.</t>
         </is>
       </c>
       <c r="M28" s="9" t="inlineStr">
         <is>
-          <t>Multi-fund deep-value funds Q1 2026</t>
+          <t>Nine Ten Capital (Bares) 13.1% of book / 3.48M sh / $41.4M</t>
         </is>
       </c>
       <c r="N28" s="9" t="inlineStr">
         <is>
-          <t>AI implementation winner via enterprise partners + Q2 2026 earnings</t>
+          <t>CTV ad spend doubling 2024-2028 + Netflix exclusive scaling + AI integration</t>
         </is>
       </c>
     </row>
@@ -3765,27 +3765,27 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>BNTC</t>
+          <t>FRPT</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Benitec Biopharma</t>
+          <t>Freshpet</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>3. Biotech Multi-Fund Convergence</t>
+          <t>6. Deep Drawdown Mean Reversion</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>$200M</t>
+          <t>$2.53B</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>$8</t>
+          <t>$60</t>
         </is>
       </c>
       <c r="H29" s="9" t="n">
@@ -3793,32 +3793,32 @@
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>2-3x</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>-50%</t>
+          <t>-30%</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>7:1</t>
+          <t>8:1</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>Suvretta 44.1% 13D (their LARGEST stake by %); gene therapy platform</t>
+          <t>B/M 0.50 borderline + ROA 3.41% + -40% drawdown. Manufacturing capacity online = margin inflection. Marlowe 39.8% (highest concentration). M&amp;A target. But valuation not as deep as Tier S/A.</t>
         </is>
       </c>
       <c r="M29" s="9" t="inlineStr">
         <is>
-          <t>Suvretta 44.1% 13D (Suvretta's LARGEST stake by % ownership)</t>
+          <t>Marlowe Partners 39.8% in last 13F (highest single-fund signal)</t>
         </is>
       </c>
       <c r="N29" s="9" t="inlineStr">
         <is>
-          <t>Multiple gene-therapy programs in development; clinical readouts upcoming</t>
+          <t>Capacity utilization + margin inflection + M&amp;A speculation</t>
         </is>
       </c>
     </row>
@@ -3833,31 +3833,31 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>QRHC</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Quest Resource Holding</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>2. Activist Board Catalyst</t>
+          <t>9. Quality Compounder at Trough</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>$200M</t>
+          <t>$25B</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>$7</t>
+          <t>$52.75</t>
         </is>
       </c>
       <c r="H30" s="9" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
@@ -3866,27 +3866,27 @@
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>12:1</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr">
         <is>
-          <t>Wynnefield 13.3% 13D w/ board seat; sub-$200M micro waste services</t>
+          <t>Yartseva 6/7 + 9.88% FCF yield + ROA 10.44% + -27% 6mo. AI accelerator-not-disruptor thesis. Defensive value vs deep-value pure play.</t>
         </is>
       </c>
       <c r="M30" s="9" t="inlineStr">
         <is>
-          <t>Wynnefield 13.3% / 2.73M sh / 13D w/ board seat</t>
+          <t>Multi-fund deep-value funds Q1 2026</t>
         </is>
       </c>
       <c r="N30" s="9" t="inlineStr">
         <is>
-          <t>Operational improvements + Wynnefield additional buying if dips</t>
+          <t>AI implementation winner via enterprise partners + Q2 2026 earnings</t>
         </is>
       </c>
     </row>
@@ -3901,22 +3901,22 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>POSTBPB</t>
+          <t>BNTC</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Potbelly Corp (PBPB)</t>
+          <t>Benitec Biopharma</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>2. Activist Board Catalyst</t>
+          <t>3. Biotech Multi-Fund Convergence</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>$240M</t>
+          <t>$200M</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -3925,36 +3925,36 @@
         </is>
       </c>
       <c r="H31" s="9" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>3-5x</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-50%</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>7:1</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>Nierenberg/D3 LARGEST shareholder; restaurant turnaround + activist soft pressure</t>
+          <t>Suvretta 44.1% 13D = LARGEST stake by %. Gene therapy platform. Multi-program optionality. Higher risk than other biotech-multi-fund names.</t>
         </is>
       </c>
       <c r="M31" s="9" t="inlineStr">
         <is>
-          <t>Nierenberg/D3 largest shareholder; 13D/A active March 2025</t>
+          <t>Suvretta 44.1% 13D (Suvretta's LARGEST stake by % ownership)</t>
         </is>
       </c>
       <c r="N31" s="9" t="inlineStr">
         <is>
-          <t>Restaurant turnaround + Nierenberg potential escalation</t>
+          <t>Multiple gene-therapy programs in development; clinical readouts upcoming</t>
         </is>
       </c>
     </row>
@@ -3962,67 +3962,67 @@
       <c r="A32" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>NOT</t>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>ROCK</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Gibraltar Industries</t>
+          <t>Dollar Tree</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>1. Yartseva Pure Multibagger</t>
+          <t>5. Spinoff / SoTP Arbitrage</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>$1.10B</t>
+          <t>$25B</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>$39.69</t>
+          <t>$80</t>
         </is>
       </c>
       <c r="H32" s="9" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>1.8-2.2x</t>
+          <t>2-3x</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>7:1</t>
+          <t>9:1</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>OmniMax integration year; FY27 EPS $5+ at 15x = $75-90; director Form 4 buy</t>
+          <t>B/M 0.20 Yartseva 6/7 + Family Dollar divestiture proceeds = $1B+ cash bolster. Post-divest clean Dollar Tree franchise. Multi-fund deep-value consensus already established = partial discount captured.</t>
         </is>
       </c>
       <c r="M32" s="9" t="inlineStr">
         <is>
-          <t>Director Metcalf bought $502k March 2026; Vanguard 5.24% 13G</t>
+          <t>Multi-fund deep-value funds Q1 2026 adds</t>
         </is>
       </c>
       <c r="N32" s="9" t="inlineStr">
         <is>
-          <t>Q2 2026 earnings = first clean OmniMax quarter; aluminum normalization; Q3 reroofing season</t>
+          <t>Family Dollar sale completion + comparable sales recovery + multiple re-rate</t>
         </is>
       </c>
     </row>
@@ -4030,67 +4030,67 @@
       <c r="A33" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>NOT</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>TPL</t>
+          <t>QRHC</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Texas Pacific Land Trust</t>
+          <t>Quest Resource Holding</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>7. Hard Asset / Royalty</t>
+          <t>2. Activist Board Catalyst</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>$30B</t>
+          <t>$200M</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>$1300</t>
+          <t>$7</t>
         </is>
       </c>
       <c r="H33" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>1.3-1.5x</t>
+          <t>2-3x</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-30%</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>8:1</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>Permian premium already in; same NAV-vs-GAAP-book issue as JOE; reduced asymmetry</t>
+          <t>Wynnefield 13.3% 13D w/ board seat. Sub-$200M micro waste services. Recurring revenue.</t>
         </is>
       </c>
       <c r="M33" s="9" t="inlineStr">
         <is>
-          <t>Multi-fund quality holders; HRC anchor</t>
+          <t>Wynnefield 13.3% / 2.73M sh / 13D w/ board seat</t>
         </is>
       </c>
       <c r="N33" s="9" t="inlineStr">
         <is>
-          <t>Permian production growth + water revenue optionality</t>
+          <t>Operational improvements + Wynnefield additional buying if dips</t>
         </is>
       </c>
     </row>
@@ -4105,60 +4105,60 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>AAP CALL</t>
+          <t>POSTBPB</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Advance Auto Parts calls (Cooper Creek)</t>
+          <t>Potbelly Corp (PBPB)</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>10. Hedged / Special Structure</t>
+          <t>2. Activist Board Catalyst</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>$240M</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>varies</t>
+          <t>$8</t>
         </is>
       </c>
       <c r="H34" s="9" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>3-5x calls</t>
+          <t>2-3x</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>-100%</t>
+          <t>-30%</t>
         </is>
       </c>
       <c r="K34" s="9" t="inlineStr">
         <is>
-          <t>6:1</t>
+          <t>8:1</t>
         </is>
       </c>
       <c r="L34" s="9" t="inlineStr">
         <is>
-          <t>Cooper Creek call stack leverage on H Partners cash thesis</t>
+          <t>Nierenberg/D3 LARGEST shareholder (~$16.4M / 7% book). Restaurant turnaround + soft activist pressure.</t>
         </is>
       </c>
       <c r="M34" s="9" t="inlineStr">
         <is>
-          <t>Cooper Creek call stack ($518M total notional incl SIG/TTWO/DOCN/GXO)</t>
+          <t>Nierenberg/D3 largest shareholder; 13D/A active March 2025</t>
         </is>
       </c>
       <c r="N34" s="9" t="inlineStr">
         <is>
-          <t>Q2 2026 margin recovery proof + H Partners 13D escalation</t>
+          <t>Restaurant turnaround + Nierenberg potential escalation</t>
         </is>
       </c>
     </row>
@@ -4173,60 +4173,60 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>CTMX-WT</t>
+          <t>ROCK</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>CytomX Tranche 2 Warrants</t>
+          <t>Gibraltar Industries</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>10. Hedged / Special Structure</t>
+          <t>1. Yartseva Pure Multibagger</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>$1.10B</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>varies</t>
+          <t>$39.69</t>
         </is>
       </c>
       <c r="H35" s="9" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>2-4x warrant</t>
+          <t>1.8-2.2x</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>-100%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>7:1</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>BVF Tranche 2 warrants expire 7/3/2026 = IMMINENT URGENCY</t>
+          <t>OmniMax integration year. FY27 EPS $5+ at 15x = $75-90. Director Form 4 buy March 2026. Cyclical, not deep value.</t>
         </is>
       </c>
       <c r="M35" s="9" t="inlineStr">
         <is>
-          <t>BVF Partners 13G/A #5 (warrants exp 7/3/2026)</t>
+          <t>Director Metcalf bought $502k March 2026; Vanguard 5.24% 13G</t>
         </is>
       </c>
       <c r="N35" s="9" t="inlineStr">
         <is>
-          <t>Warrant expiration 7/3/2026 = IMMINENT URGENCY</t>
+          <t>Q2 2026 earnings = first clean OmniMax quarter; aluminum normalization; Q3 reroofing season</t>
         </is>
       </c>
     </row>
@@ -4265,11 +4265,11 @@
         </is>
       </c>
       <c r="H36" s="9" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>1.5-2x</t>
+          <t>1.5-2x via straddle</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>Stonepine 40.9% in straddle; FDA cycle 2026-2027 dispersion</t>
+          <t>Stonepine 40.9% in straddle = pure long-vol on biotech FDA cycle dispersion 2026-2027. Not directional value bet.</t>
         </is>
       </c>
       <c r="M36" s="9" t="inlineStr">
@@ -4302,34 +4302,34 @@
       <c r="A37" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>RERATED</t>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>CELC</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Celcuity</t>
+          <t>Texas Pacific Land Trust</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>3. Biotech Multi-Fund Convergence</t>
+          <t>7. Hard Asset / Royalty</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>$8B (post-data)</t>
+          <t>$30B</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>$165</t>
+          <t>$1300</t>
         </is>
       </c>
       <c r="H37" s="9" t="n">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>1.3-2x (1x post-data)</t>
+          <t>1.3-1.5x</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="K37" s="9" t="inlineStr">
@@ -4352,17 +4352,17 @@
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
-          <t>Phase 3 May 1 2026 POSITIVE; +76% PT raises already in price; ASCO Jun 2 / PDUFA Jul 17 remaining</t>
+          <t>Already at 25x P/CF premium = ENDLESS DRILLING priced. NAV-vs-GAAP issue similar to JOE but multiple no longer cheap.</t>
         </is>
       </c>
       <c r="M37" s="9" t="inlineStr">
         <is>
-          <t>Baker Bros 19.99% ACTIVIST 13D = $904M / 5.48% of $17.4B book</t>
+          <t>Multi-fund quality holders; HRC anchor</t>
         </is>
       </c>
       <c r="N37" s="9" t="inlineStr">
         <is>
-          <t>JUNE 2 ASCO LBA1008 oral + JULY 17 PDUFA goal date (2 catalysts in 8 weeks)</t>
+          <t>Permian production growth + water revenue optionality</t>
         </is>
       </c>
     </row>
@@ -4370,67 +4370,67 @@
       <c r="A38" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>RERATED</t>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>HRMY</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Harmony Biosciences</t>
+          <t>Regeneron</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>1. Yartseva Pure Multibagger</t>
+          <t>9. Quality Compounder at Trough</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>$1.77B</t>
+          <t>$65B</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>$31</t>
+          <t>$638</t>
         </is>
       </c>
       <c r="H38" s="9" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>1.8-2.2x (was 2.5-3.5x)</t>
+          <t>1.5-2x</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>7:1</t>
+          <t>8:1</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>Q1 +17% WAKIX growth printed; pediatric FDA Feb 2026 priced; Lilly orexin validated</t>
+          <t>Defensive quality. Pipeline optionality. Partial trough recovery underway.</t>
         </is>
       </c>
       <c r="M38" s="9" t="inlineStr">
         <is>
-          <t>M&amp;A buyers: Jazz Pharma, Lundbeck, Otsuka; Catalyst Pharma precedent</t>
+          <t>Founder-led; multi-fund pharma specialist holds</t>
         </is>
       </c>
       <c r="N38" s="9" t="inlineStr">
         <is>
-          <t>Pitolisant GR NDA Q2 2026 (PDUFA Q1 2027); BP-205 Phase 1 PK mid-2026</t>
+          <t>Itepekimab 2026-2027 data + Linvoseltamab ramp</t>
         </is>
       </c>
     </row>
@@ -4438,19 +4438,19 @@
       <c r="A39" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>RERATED</t>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>TREE</t>
+          <t>DV</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -4460,25 +4460,25 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>$525M</t>
+          <t>$1.50B</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>$37.50</t>
+          <t>$9</t>
         </is>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>1.5-2x (was 3-4x)</t>
+          <t>1.5-2x (was 3x)</t>
         </is>
       </c>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="K39" s="9" t="inlineStr">
@@ -4488,17 +4488,17 @@
       </c>
       <c r="L39" s="9" t="inlineStr">
         <is>
-          <t>Q1 +37% rev / +71% EBITDA already PRINTED; S&amp;P upgraded; insurance up-cycle now consensus</t>
+          <t>CTV verification rally underway = partial upside captured. Q1 +10% rev printed.</t>
         </is>
       </c>
       <c r="M39" s="9" t="inlineStr">
         <is>
-          <t>Yartseva 7/7 + post-Q1 inflection demonstrated</t>
+          <t>Insider 12.69% (high for ad-tech); Yartseva 7/7</t>
         </is>
       </c>
       <c r="N39" s="9" t="inlineStr">
         <is>
-          <t>Q2 2026 print + $575M July 2025 converts retired + Fed rate cuts unlock Home/Consumer</t>
+          <t>ABS streaming Do Not Air list rollout Q2/Q3 + Meta activation $12M ARR to $50M+ path</t>
         </is>
       </c>
     </row>
@@ -4506,67 +4506,67 @@
       <c r="A40" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>RERATED</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>DV</t>
+          <t>CELC</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Celcuity</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>1. Yartseva Pure Multibagger</t>
+          <t>3. Biotech Multi-Fund Convergence</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>$1.50B</t>
+          <t>$8B (post-data)</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>$9</t>
+          <t>$165</t>
         </is>
       </c>
       <c r="H40" s="9" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>2-2.5x (was 3-3.5x)</t>
+          <t>1.3-2x post-data</t>
         </is>
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-30%</t>
         </is>
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
         <is>
-          <t>CTV verification rally underway; Q1 +10% rev printed; remaining 50% of thesis</t>
+          <t>Phase 3 May 1 POSITIVE + +76% PT raises already in price. ASCO Jun 2 + PDUFA Jul 17 remain but pre-quantified. Quality+catalysts but entry economics weakened post-data.</t>
         </is>
       </c>
       <c r="M40" s="9" t="inlineStr">
         <is>
-          <t>Insider 12.69% (high for ad-tech); Yartseva 7/7</t>
+          <t>Baker Bros 19.99% ACTIVIST 13D = $904M / 5.48% of $17.4B book</t>
         </is>
       </c>
       <c r="N40" s="9" t="inlineStr">
         <is>
-          <t>ABS streaming Do Not Air list rollout Q2/Q3 + Meta activation $12M ARR to $50M+ path</t>
+          <t>JUNE 2 ASCO LBA1008 oral + JULY 17 PDUFA goal date (2 catalysts in 8 weeks)</t>
         </is>
       </c>
     </row>
@@ -4581,27 +4581,27 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>HRMY</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Danaher</t>
+          <t>Harmony Biosciences</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>9. Quality Compounder at Trough</t>
+          <t>1. Yartseva Pure Multibagger</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>$122B</t>
+          <t>$1.77B</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>$171</t>
+          <t>$31</t>
         </is>
       </c>
       <c r="H41" s="9" t="n">
@@ -4609,32 +4609,32 @@
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>1.4-1.6x (was 1.8-2x)</t>
+          <t>1.5-2x</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-30%</t>
         </is>
       </c>
       <c r="K41" s="9" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>6:1</t>
         </is>
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>Bouncing from trough; bioprocessing cycle now consensus; multiple expansion captured</t>
+          <t>Q1 +17% WAKIX printed; pediatric FDA Feb priced; Lilly orexin validated = thesis worked. Buy-pre-catalyst opportunity passed.</t>
         </is>
       </c>
       <c r="M41" s="9" t="inlineStr">
         <is>
-          <t>D1 Capital +312% Q1 ($107M→$437M, 4th-largest position)</t>
+          <t>M&amp;A buyers: Jazz Pharma, Lundbeck, Otsuka; Catalyst Pharma precedent</t>
         </is>
       </c>
       <c r="N41" s="9" t="inlineStr">
         <is>
-          <t>Bioprocessing book-to-bill durably &gt;1.0 + China VBP stabilization H2 2026 + Cepheid Q4 reset</t>
+          <t>Pitolisant GR NDA Q2 2026 (PDUFA Q1 2027); BP-205 Phase 1 PK mid-2026</t>
         </is>
       </c>
     </row>
@@ -4649,40 +4649,40 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>TREE</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Ascendis Pharma</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>3. Biotech Multi-Fund Convergence</t>
+          <t>1. Yartseva Pure Multibagger</t>
         </is>
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>$15.3B</t>
+          <t>$525M</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>$247</t>
+          <t>$37.50</t>
         </is>
       </c>
       <c r="H42" s="9" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>1.2-1.5x (was 1.4-1.8x)</t>
+          <t>1.3-1.7x</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-30%</t>
         </is>
       </c>
       <c r="K42" s="9" t="inlineStr">
@@ -4692,17 +4692,17 @@
       </c>
       <c r="L42" s="9" t="inlineStr">
         <is>
-          <t>YORVIPATH ramp priced; €247M Q1 (2x YoY) already at $247; multiple normalized</t>
+          <t>Q1 +37% rev / +71% EBITDA already PRINTED. S&amp;P upgraded. Insurance cycle now consensus. Inflection over.</t>
         </is>
       </c>
       <c r="M42" s="9" t="inlineStr">
         <is>
-          <t>RA Capital 24.9% of $9.44B = $2.35B = LARGEST single biotech crossover position; held since 2015</t>
+          <t>Yartseva 7/7 + post-Q1 inflection demonstrated</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
         <is>
-          <t>YUVIWEL ramp + Q2/Q3 YORVIPATH growth + TransCon CNP follow-on indications</t>
+          <t>Q2 2026 print + $575M July 2025 converts retired + Fed rate cuts unlock Home/Consumer</t>
         </is>
       </c>
     </row>
@@ -4710,67 +4710,67 @@
       <c r="A43" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>RERATED</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>ASND</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>Ascendis Pharma</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>9. Quality Compounder at Trough</t>
+          <t>3. Biotech Multi-Fund Convergence</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>$65B</t>
+          <t>$15.3B</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>$638</t>
+          <t>$247</t>
         </is>
       </c>
       <c r="H43" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
-          <t>1.5-2x</t>
+          <t>1.2-1.5x</t>
         </is>
       </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="K43" s="9" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="L43" s="9" t="inlineStr">
         <is>
-          <t>Defensive quality compounder; pipeline still optionality; partial trough recovery</t>
+          <t>YORVIPATH ramp priced. €247M Q1 (2x YoY) already at $247. Multiple normalized.</t>
         </is>
       </c>
       <c r="M43" s="9" t="inlineStr">
         <is>
-          <t>Founder-led; multi-fund pharma specialist holds</t>
+          <t>RA Capital 24.9% of $9.44B = $2.35B = LARGEST single biotech crossover position; held since 2015</t>
         </is>
       </c>
       <c r="N43" s="9" t="inlineStr">
         <is>
-          <t>Itepekimab 2026-2027 data + Linvoseltamab ramp</t>
+          <t>YUVIWEL ramp + Q2/Q3 YORVIPATH growth + TransCon CNP follow-on indications</t>
         </is>
       </c>
     </row>
@@ -4778,67 +4778,67 @@
       <c r="A44" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>RERATED</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Dollar Tree</t>
+          <t>Danaher</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>5. Spinoff / SoTP Arbitrage</t>
+          <t>9. Quality Compounder at Trough</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>$25B</t>
+          <t>$122B</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>$80</t>
+          <t>$171</t>
         </is>
       </c>
       <c r="H44" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>1.3-1.5x</t>
         </is>
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="K44" s="9" t="inlineStr">
         <is>
-          <t>9:1</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="L44" s="9" t="inlineStr">
         <is>
-          <t>Family Dollar divestiture proceeding; partial multi-fund consensus already established</t>
+          <t>Bouncing from trough; bioprocessing cycle now consensus; multiple expansion captured. Defensive 2H 2026 fully priced.</t>
         </is>
       </c>
       <c r="M44" s="9" t="inlineStr">
         <is>
-          <t>Multi-fund deep-value funds Q1 2026 adds</t>
+          <t>D1 Capital +312% Q1 ($107M→$437M, 4th-largest position)</t>
         </is>
       </c>
       <c r="N44" s="9" t="inlineStr">
         <is>
-          <t>Family Dollar sale completion + comparable sales recovery + multiple re-rate</t>
+          <t>Bioprocessing book-to-bill durably &gt;1.0 + China VBP stabilization H2 2026 + Cepheid Q4 reset</t>
         </is>
       </c>
     </row>
@@ -4963,22 +4963,22 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>VITL</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vital Farms</t>
+          <t>OptimizeRx</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>$1.5B</t>
+          <t>$93M</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>$13</t>
+          <t>$4.82</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>2-4x ($11.50 PT)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -4996,33 +4996,33 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>13:1</t>
+          <t>12:1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No major fund concentrated yet = entry preserved; Yartseva 6/7</t>
+          <t>Insider 14.82%; $10M buyback through March 2027; Doximity exec Presti to board April 2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Deepest drawdown -68.76%; 11% ROA sustained; no smart money pile-in yet</t>
+          <t>ENTRY-TODAY: SUB-BOOK 0.70x + $19M FCF profitable + insider 14.82% + analyst $11.50 (138%) + sub-$100M float = ANY DSP Q4 print violently re-rates. Smart money still building (not exiting). True intrinsic value &gt; 2x current.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>THESIS: Pasture-raised egg category creator with brand moat. Walmart/Target/Whole Foods distribution. 11% ROA sustained THROUGH the avian flu crash = exceptional earnings power. | VALUATION: B/M 0.74, ROA 11% (BEST in 6/7 tier), -68.76% from peak</t>
+          <t>THESIS: Digital health POC pharma messaging to 60%+ US prescribers. May 21 2026 DeepIntent integration = first DSP accessing OPRX EHR network (Q3 2026 launch) opens &gt;80% of digital pharma budgets. | VALUATION: P/B 0.70 (sub-book), P/FCF 4.89, 15.7% FCF yield, EV/Sales 0.88, Adj EBITDA 4.4x EV</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: Avian flu egg-supply normalization + summer pricing + M&amp;A speculation | VARIANT: Market lumped premium VITL with commodity egg crash. Reality: brand pricing power retained. Strategic buyers: Kraft Heinz, Hain, General Mills.</t>
+          <t>CATALYST: Q4 2026 DSP integration revenue start + Q2 2026 earnings Aug 14 | VARIANT: Market: MFN victim; Smart money: profitable ($19M FCF) at 0.7x book, target $11.50 (138% upside).</t>
         </is>
       </c>
     </row>
@@ -5040,22 +5040,22 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>NRP</t>
+          <t>INMD</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Natural Resource Partners</t>
+          <t>InMode Ltd</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>$1.35B</t>
+          <t>$869M</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$105.81</t>
+          <t>$13.71</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.5-3x</t>
+          <t>2-3x ($25-30)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5078,28 +5078,28 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Saber/Huber 17.75%, Greystone top, Right Tail NEW Q1 2026, Berkowitz/Fairholme</t>
+          <t>Steel Partners 25.5% of book; Mizrahy +800k sh ($10.7M)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: 14.5% FCF yield intact; distribution increase DELAYED = price unmoved; Nov 2026 catalyst</t>
+          <t>ENTRY-TODAY: CASH FLOOR: $8.47/sh = 62% of $13.71. Steel Partners 25.5% book + implied $18-20 takeout. Founder Mizrahy +800k sh ($10.7M Feb 2026) at current = sponsor put. Cash + M&amp;A double-floor; upside on Steel re-bid.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>THESIS: Royalty trust on 13M mineral acres + 49% Sisecam soda ash JV. Near-zero debt by mid-2026 after $109M paydown + preferred retirement. Distribution increase guided for November 2026 (delayed from prior guide due to Sisecam capital call). | VALUATION: P/B 2.26 (B/M 0.47), 14.5% FCF yield, ROA 10.5%, 6.6x P/FCF</t>
+          <t>THESIS: Israeli aesthetic device leader (Morpheus8, BodyTite). 85% recurring consumables. Steel Partners +155% Q1 2026 = 25.5% of their book; founder Mizrahy bought 800k sh ($10.7M) Feb 2026. | VALUATION: P/B 1.32, FCF $537M cash = $8.47/sh (62% of price), 77.8% gross margin</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: Nov 2026 distribution step-up + preferreds retire; Q3 2026 Sisecam recovery sig | VARIANT: Market: dying coal MLP. Smart money: debt-free royalty with 12% FCF yield, comparable to TPL at 25x P/CF (NRP at 6x).</t>
+          <t>CATALYST: Q2 2026 earnings ~Aug 5 + potential Steel renewed bid ($18 prior) | VARIANT: Market: Israeli geopolitical + aesthetic cycle. Smart money: $11-12 floor on cash alone; Steel implied $20+ takeout.</t>
         </is>
       </c>
     </row>
@@ -5108,75 +5108,75 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>NOT</t>
+        <v>8</v>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>GLOB</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OptimizeRx</t>
+          <t>Globant SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>$93M</t>
+          <t>$1.68B</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$4.82</t>
+          <t>$43.50</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.5-6x</t>
+          <t>3-5x if class action clears</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-45%</t>
+          <t>-35%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>10:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Insider 14.82%; $10M buyback through March 2027; Doximity exec Presti to board April 2026</t>
+          <t>Cartica historical 6.5% Q4 2022; sentiment bottom 16% short float</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: -65.4% 6mo drawdown; sub-book 0.7x; Q4 DSP integration not priced</t>
+          <t>ENTRY-TODAY: P/E 5.91 SECTOR LOW + P/FCF 5.56 + EV/EBITDA 4.95x + 17% FCF yield = DEEPLY undervalued by every metric. Class action JUN 23 IS the catalyst that creates the discount (clears = violent rerate). AI Pods $32.8M ARR from $0 in 12mo + $352M pipeline.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>THESIS: Digital health POC pharma messaging to 60%+ US prescribers. May 21 2026 DeepIntent integration = first DSP accessing OPRX EHR network (Q3 2026 launch) opens &gt;80% of digital pharma budgets. | VALUATION: P/B 0.70 (sub-book), P/FCF 4.89, 15.7% FCF yield, EV/Sales 0.88, Adj EBITDA 4.4x EV</t>
+          <t>THESIS: LatAm IT services with AI Pods inflection ($32.8M ARR from $0 in 12 months; $352M pipeline; 40% top-20 client penetration). Founder Migoya 23-year tenure + ~3% via Founders Trust. | VALUATION: P/E 5.91 (sector low), P/B 0.78, P/FCF 5.56, 17% FCF yield, EV/EBITDA 4.95</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: Q4 2026 DSP integration revenue start + Q2 2026 earnings Aug 14 | VARIANT: Market: MFN victim; Smart money: profitable ($19M FCF) at 0.7x book, target $11.50 (138% upside).</t>
+          <t>CATALYST: Q3 2026 AI Pods print + Argentina FX tailwind + ENRGI platform launch H2 | VARIANT: Market: melting India-IT comp. Smart money: AI mix shift to higher-margin work + LatAm cost arb. CAVEAT: securities class action (lead plaintiff June 23, 2026); COO resigned July 2025 not replaced.</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
@@ -5194,66 +5194,66 @@
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>INMD</t>
+          <t>CRTO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>InMode Ltd</t>
+          <t>Criteo SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>$869M</t>
+          <t>$866M</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>$13.71</t>
+          <t>$13.50</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.2x</t>
+          <t>2.5-4x</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>10:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Steel Partners 25.5% of book; Mizrahy +800k sh ($10.7M)</t>
+          <t>Nierenberg D3 9.37% / +19% Q1 2026; Petrus Advisers activist</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Steel re-bid optionality ($18 prior); $8.47/sh cash = 62% of price; founder $10.7M buy</t>
+          <t>ENTRY-TODAY: P/E 3.73 fwd + P/FCF 4.98 + EV/EBITDA 2.28x + 20.7% FCF yield = DEEP. Q3 2026 anniversary of scope losses REMOVES the headwind printed in Q1. Petrus Advisers activist + $200M buyback (22% cap) + Nierenberg D3 +19% Q1.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>THESIS: Israeli aesthetic device leader (Morpheus8, BodyTite). 85% recurring consumables. Steel Partners +155% Q1 2026 = 25.5% of their book; founder Mizrahy bought 800k sh ($10.7M) Feb 2026. | VALUATION: P/B 1.32, FCF $537M cash = $8.47/sh (62% of price), 77.8% gross margin</t>
+          <t>THESIS: Performance ad-tech pivoting to Commerce Yield retail media (235 retailers incl Lowes/Costco). $1B+ media spend Q1 2026 (+8% cc). OpenAI partnership live with 1,000+ brands. Q1 retail media -31% ex-scope -- actual underlying +24%. | VALUATION: P/E 3.73 (fwd), P/B 0.79, P/FCF 4.98, EV/EBITDA 2.28, 20.7% FCF yield</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: Q2 2026 earnings ~Aug 5 + potential Steel renewed bid ($18 prior) | VARIANT: Market: Israeli geopolitical + aesthetic cycle. Smart money: $11-12 floor on cash alone; Steel implied $20+ takeout.</t>
+          <t>CATALYST: Q3 2026 anniversary of scope losses + Luxembourg redomiciliation + $200M buyback (22% cap) | VARIANT: Market prices terminal decline; Petrus Advisers activist + 33% FCF yield + retail media TAM $200B by 2028.</t>
         </is>
       </c>
     </row>
@@ -5262,75 +5262,75 @@
         <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+        <v>10</v>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>NOT</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>GLOB</t>
+          <t>NRP</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Globant SA</t>
+          <t>Natural Resource Partners</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>$1.68B</t>
+          <t>$1.35B</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>$43.50</t>
+          <t>$105.81</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3-4x (was 5x)</t>
+          <t>2.5-3x</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>11:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Cartica historical 6.5% Q4 2022; sentiment bottom 16% short float</t>
+          <t>Saber/Huber 17.75%, Greystone top, Right Tail NEW Q1 2026, Berkowitz/Fairholme</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Class action JUNE 23 deadline overhang; AI Pods Q3 inflection ahead but near-term risk</t>
+          <t>ENTRY-TODAY: 14.5% FCF yield ALONE = pure mispricing. Royalty trust at 6.6x P/FCF vs TPL at 25x P/CF (SAME asset class) = comp gap re-rate. Distribution Nov 2026 + preferreds retire. Saber 17.75% + Right Tail NEW Q1 2026.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>THESIS: LatAm IT services with AI Pods inflection ($32.8M ARR from $0 in 12 months; $352M pipeline; 40% top-20 client penetration). Founder Migoya 23-year tenure + ~3% via Founders Trust. | VALUATION: P/E 5.91 (sector low), P/B 0.78, P/FCF 5.56, 17% FCF yield, EV/EBITDA 4.95</t>
+          <t>THESIS: Royalty trust on 13M mineral acres + 49% Sisecam soda ash JV. Near-zero debt by mid-2026 after $109M paydown + preferred retirement. Distribution increase guided for November 2026 (delayed from prior guide due to Sisecam capital call). | VALUATION: P/B 2.26 (B/M 0.47), 14.5% FCF yield, ROA 10.5%, 6.6x P/FCF</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: Q3 2026 AI Pods print + Argentina FX tailwind + ENRGI platform launch H2 | VARIANT: Market: melting India-IT comp. Smart money: AI mix shift to higher-margin work + LatAm cost arb. CAVEAT: securities class action (lead plaintiff June 23, 2026); COO resigned July 2025 not replaced.</t>
+          <t>CATALYST: Nov 2026 distribution step-up + preferreds retire; Q3 2026 Sisecam recovery sig | VARIANT: Market: dying coal MLP. Smart money: debt-free royalty with 12% FCF yield, comparable to TPL at 25x P/CF (NRP at 6x).</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
         <v>6</v>
       </c>
       <c r="B25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
@@ -5367,21 +5367,21 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2-2.5x</t>
+          <t>2-3x</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>11:1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -5393,7 +5393,7 @@
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Yartseva 7/7 still depressed; $90M buyback (16% cap); cost program 2027</t>
+          <t>ENTRY-TODAY: P/B 0.83 + P/FCF 3.5 + 28% TTM FCF yield + EV/EBITDA 2.7x = DEEP. Q1 EPS $0.45 vs $0.13 est (+246% BEAT). $90M buyback (16% cap raised from $60M) = buyback math compounds violently with cheap multiple.</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>7</v>
       </c>
       <c r="B29" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
@@ -5425,22 +5425,22 @@
       </c>
       <c r="D29" s="17" t="inlineStr">
         <is>
-          <t>CRTO</t>
+          <t>VITL</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Criteo SA</t>
+          <t>Vital Farms</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>$866M</t>
+          <t>$1.5B</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>$13.50</t>
+          <t>$13</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.5-3.5x</t>
+          <t>2-3x ($30-40)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -5458,33 +5458,33 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>12:1</t>
+          <t>10:1</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Nierenberg D3 9.37% / +19% Q1 2026; Petrus Advisers activist</t>
+          <t>No major fund concentrated yet = entry preserved; Yartseva 6/7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Yartseva 7/7; Q3 2026 anniversary scope losses; Petrus activist; D3 Nierenberg +19% Q1</t>
+          <t>ENTRY-TODAY: Deepest drawdown -68.76% + 11% ROA sustained = exceptional. BUT B/M 0.74 = not deeply undervalued vs book; M&amp;A precedent 4x sales = $50 = +260%. Brand-led re-rate is SLOW not violent. No defined binary catalyst.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>THESIS: Performance ad-tech pivoting to Commerce Yield retail media (235 retailers incl Lowes/Costco). $1B+ media spend Q1 2026 (+8% cc). OpenAI partnership live with 1,000+ brands. Q1 retail media -31% ex-scope -- actual underlying +24%. | VALUATION: P/E 3.73 (fwd), P/B 0.79, P/FCF 4.98, EV/EBITDA 2.28, 20.7% FCF yield</t>
+          <t>THESIS: Pasture-raised egg category creator with brand moat. Walmart/Target/Whole Foods distribution. 11% ROA sustained THROUGH the avian flu crash = exceptional earnings power. | VALUATION: B/M 0.74, ROA 11% (BEST in 6/7 tier), -68.76% from peak</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: Q3 2026 anniversary of scope losses + Luxembourg redomiciliation + $200M buyback (22% cap) | VARIANT: Market prices terminal decline; Petrus Advisers activist + 33% FCF yield + retail media TAM $200B by 2028.</t>
+          <t>CATALYST: Avian flu egg-supply normalization + summer pricing + M&amp;A speculation | VARIANT: Market lumped premium VITL with commodity egg crash. Reality: brand pricing power retained. Strategic buyers: Kraft Heinz, Hain, General Mills.</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
         <v>8</v>
       </c>
       <c r="B33" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Microcap $93M; cleanest Y7/7 setup; -43.9% 6mo; institutional minimum below</t>
+          <t>ENTRY-TODAY: Microcap $93M = sub-institutional minimum = any flow violently moves. Yartseva 7/7 cleanest setup. -43.9% 6mo. B/M 0.49. Pure micro-mean-reversion.</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>10:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -5624,7 +5624,7 @@
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: QSR franchisor at BOOK; 16.7% FCF yield; M&amp;A 12-14x EBITDA pool; CEO buying</t>
+          <t>ENTRY-TODAY: AT BOOK 1.04x + 16.7% FCF yield = pure value. M&amp;A pool at 12-14x EBITDA vs trading 7.5x = M&amp;A precedent arb. CEO Lefebvre open-market buy at C$30.54 = sponsor put. QSR consolidation trend.</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
         <v>10</v>
       </c>
       <c r="B41" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C41" s="16" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: OmniMax integration year; FY27 EPS $5+ at 15x = $75-90; director Form 4 buy</t>
+          <t>ENTRY-TODAY: OmniMax integration year. FY27 EPS $5+ at 15x = $75-90. Director Form 4 buy March 2026. Cyclical, not deep value.</t>
         </is>
       </c>
     </row>
@@ -5724,31 +5724,31 @@
         <v>11</v>
       </c>
       <c r="B45" t="n">
-        <v>35</v>
-      </c>
-      <c r="C45" s="20" t="inlineStr">
-        <is>
-          <t>RERATED</t>
+        <v>36</v>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="D45" s="17" t="inlineStr">
         <is>
-          <t>HRMY</t>
+          <t>DV</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Harmony Biosciences</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>$1.77B</t>
+          <t>$1.50B</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>$31</t>
+          <t>$9</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -5756,43 +5756,43 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1.8-2.2x (was 2.5-3.5x)</t>
+          <t>1.5-2x (was 3x)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>7:1</t>
+          <t>6:1</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>M&amp;A buyers: Jazz Pharma, Lundbeck, Otsuka; Catalyst Pharma precedent</t>
+          <t>Insider 12.69% (high for ad-tech); Yartseva 7/7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Q1 +17% WAKIX growth printed; pediatric FDA Feb 2026 priced; Lilly orexin validated</t>
+          <t>ENTRY-TODAY: CTV verification rally underway = partial upside captured. Q1 +10% rev printed.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>THESIS: $1B+ WAKIX franchise (pitolisant for narcolepsy). Q1 2026 rev +17% to $215M; pediatric FDA approval Feb 13 2026 extends IP to 2030 (pediatric exclusivity to 2040s). 5 Phase 3 trials in pipeline. | VALUATION: P/B 1.91, P/Sales 2.05, FCF yield 19.36%, 26% net cash position</t>
+          <t>THESIS: Pure-play ad verification (68% market share in fraud detection vs IAS 2.7%). 4,300+ customers vs IAS 169. Q1 2026 rev +10%, EBITDA 31% margin. CTV +28%, social activation +92%. | VALUATION: P/FCF 11x (trough), EV/EBITDA 9.6x, EV/Sales 1.9x, 9% FCF yield</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: Pitolisant GR NDA Q2 2026 (PDUFA Q1 2027); BP-205 Phase 1 PK mid-2026 | VARIANT: Market: single-product cliff. Smart money: Lilly's $6.3B Centessa (Q3 2026 close) validated orexin space + IP estate.</t>
+          <t>CATALYST: ABS streaming Do Not Air list rollout Q2/Q3 + Meta activation $12M ARR to $50M+ path | VARIANT: Market: Google MRC self-measurement threat. Variant: CTV verification underpenetrated (10%) vs display (70%).</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         <v>12</v>
       </c>
       <c r="B49" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C49" s="20" t="inlineStr">
         <is>
@@ -5810,30 +5810,30 @@
       </c>
       <c r="D49" s="17" t="inlineStr">
         <is>
-          <t>TREE</t>
+          <t>HRMY</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Harmony Biosciences</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>$525M</t>
+          <t>$1.77B</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>$37.50</t>
+          <t>$31</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.5-2x (was 3-4x)</t>
+          <t>1.5-2x</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5848,28 +5848,28 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Yartseva 7/7 + post-Q1 inflection demonstrated</t>
+          <t>M&amp;A buyers: Jazz Pharma, Lundbeck, Otsuka; Catalyst Pharma precedent</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Q1 +37% rev / +71% EBITDA already PRINTED; S&amp;P upgraded; insurance up-cycle now consensus</t>
+          <t>ENTRY-TODAY: Q1 +17% WAKIX printed; pediatric FDA Feb priced; Lilly orexin validated = thesis worked. Buy-pre-catalyst opportunity passed.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>THESIS: Three-segment marketplace (Insurance 68%, Consumer 20%, Home 12%) at Q1 2026 inflection: rev +37%, VMM +28%, EBITDA +71%, Insurance +51%. Net leverage falling 3.4x→2.1x; S&amp;P upgraded. | VALUATION: P/E 2.92, P/FCF 7.2, ROE 88.6%, B/M 0.60</t>
+          <t>THESIS: $1B+ WAKIX franchise (pitolisant for narcolepsy). Q1 2026 rev +17% to $215M; pediatric FDA approval Feb 13 2026 extends IP to 2030 (pediatric exclusivity to 2040s). 5 Phase 3 trials in pipeline. | VALUATION: P/B 1.91, P/Sales 2.05, FCF yield 19.36%, 26% net cash position</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: Q2 2026 print + $575M July 2025 converts retired + Fed rate cuts unlock Home/Consumer | VARIANT: Street disbelieves Insurance durability. Variant: insurance carriers in year-2 of 5-7yr up-cycle = $200M+ EBITDA into 2027.</t>
+          <t>CATALYST: Pitolisant GR NDA Q2 2026 (PDUFA Q1 2027); BP-205 Phase 1 PK mid-2026 | VARIANT: Market: single-product cliff. Smart money: Lilly's $6.3B Centessa (Q3 2026 close) validated orexin space + IP estate.</t>
         </is>
       </c>
     </row>
@@ -5878,75 +5878,75 @@
         <v>13</v>
       </c>
       <c r="B53" t="n">
-        <v>37</v>
-      </c>
-      <c r="C53" s="19" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+        <v>39</v>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>RERATED</t>
         </is>
       </c>
       <c r="D53" s="17" t="inlineStr">
         <is>
-          <t>DV</t>
+          <t>TREE</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>$1.50B</t>
+          <t>$525M</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>$9</t>
+          <t>$37.50</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2-2.5x (was 3-3.5x)</t>
+          <t>1.3-1.7x</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-30%</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Insider 12.69% (high for ad-tech); Yartseva 7/7</t>
+          <t>Yartseva 7/7 + post-Q1 inflection demonstrated</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: CTV verification rally underway; Q1 +10% rev printed; remaining 50% of thesis</t>
+          <t>ENTRY-TODAY: Q1 +37% rev / +71% EBITDA already PRINTED. S&amp;P upgraded. Insurance cycle now consensus. Inflection over.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>THESIS: Pure-play ad verification (68% market share in fraud detection vs IAS 2.7%). 4,300+ customers vs IAS 169. Q1 2026 rev +10%, EBITDA 31% margin. CTV +28%, social activation +92%. | VALUATION: P/FCF 11x (trough), EV/EBITDA 9.6x, EV/Sales 1.9x, 9% FCF yield</t>
+          <t>THESIS: Three-segment marketplace (Insurance 68%, Consumer 20%, Home 12%) at Q1 2026 inflection: rev +37%, VMM +28%, EBITDA +71%, Insurance +51%. Net leverage falling 3.4x→2.1x; S&amp;P upgraded. | VALUATION: P/E 2.92, P/FCF 7.2, ROE 88.6%, B/M 0.60</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: ABS streaming Do Not Air list rollout Q2/Q3 + Meta activation $12M ARR to $50M+ path | VARIANT: Market: Google MRC self-measurement threat. Variant: CTV verification underpenetrated (10%) vs display (70%).</t>
+          <t>CATALYST: Q2 2026 print + $575M July 2025 converts retired + Fed rate cuts unlock Home/Consumer | VARIANT: Street disbelieves Insurance durability. Variant: insurance carriers in year-2 of 5-7yr up-cycle = $200M+ EBITDA into 2027.</t>
         </is>
       </c>
     </row>
@@ -6111,17 +6111,17 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>FUN</t>
+          <t>MRP</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Six Flags Entertainment</t>
+          <t>Millrose Properties</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>$2.2B</t>
+          <t>$4.59B</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6134,43 +6134,43 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>1.8-2.5x to NAV</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>9:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>H Partners 53.7% / $82.5M / 5.7% of class; Jana 9% + Travis Kelce co-invest</t>
+          <t>Lennar 80%+ owner = patient capital lock-in; SITG multi-fund flag</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Jaffer board seat just took effect; Jana 9% pushing OUTRIGHT SALE; -50% drawdown</t>
+          <t>ENTRY-TODAY: B/M 1.274 = DEEPEST in 6/7 cohort (deeper than NRP 0.47). Lennar 80% owner = guaranteed off-take + patient capital. Land bank at COST BASIS vs market. Pure NAV unwind; spinoff orphan technical pressure resolves into Q2 prints.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>THESIS: Post-Cedar Fair/Six Flags merger consolidation. 42 parks irreplaceable real estate. Q1 2026 rev +12%, attendance +4%, per-cap +6%. $200M synergy target ($120M cost + $80M growth). | VALUATION: $5.27B net debt = 7x leverage; EV/EBITDA 9x on $1.05B 2027 EBITDA</t>
+          <t>THESIS: Lennar 80%+ owner spinoff with 100k+ optioned lots at cost basis. Land bank trading below NAV with Lennar as guaranteed off-take partner. Housing-cycle recovery levered. | VALUATION: B/M 1.274 (DEEPEST in 6/7 tier; deeper than NRP's 0.47), pure NAV play</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: May 26 2026 AGM: Jaffer joins board (Class III through 2027, Audit&amp;Finance Cttee). Jana 9% pushing OUTRIGHT SALE. | VARIANT: Street: broken merger story. Two-front activist pressure (governance + sale) + per-park RE floor $47M each.</t>
+          <t>CATALYST: Q2 2026 print + Lennar volume scaling + housing cycle inflection | VARIANT: Market priced spinoff orphan technical pressure. Smart money: pure land cash-cow at discount to NAV.</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6179,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
@@ -6188,22 +6188,22 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>AAP</t>
+          <t>FUN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Six Flags Entertainment</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>$3.3B</t>
+          <t>$2.2B</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$54.42</t>
+          <t>$25</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.5-3x</t>
+          <t>2-3x (3x outright sale)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -6226,28 +6226,28 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>H Partners 46.3% / $71.2M / +50% sh Q1 2026 (1.35M sh); Legion Partners precedent</t>
+          <t>H Partners 53.7% / $82.5M / 5.7% of class; Jana 9% + Travis Kelce co-invest</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: -80% from 2021 peak; H Partners 46% + 50% Q1 add; Q2 margin proof Aug 2026</t>
+          <t>ENTRY-TODAY: 42 parks IRREPLACEABLE RE @ $47M each = $2B floor. Jaffer joined board May 26 + Jana 9% pushing OUTRIGHT SALE = two-front activist pressure. H Partners 53.7% / 5.7% of class. Sale = violent 3x trigger.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>THESIS: #3 aftermarket retailer post-WorldPac sale. Q1 +3.5% comps (Pro mid-single, DIY low-single). 700+ stores closed; ~1,300 strategic locations remain. Bridge to AZO-style 8-10% margins = $130-150/sh. | VALUATION: 3.8% op margin (rising +410bps), FY26 guide $2.40-3.10 EPS; sub-1x sales; M&amp;A floor 0.8x sales = $80/sh</t>
+          <t>THESIS: Post-Cedar Fair/Six Flags merger consolidation. 42 parks irreplaceable real estate. Q1 2026 rev +12%, attendance +4%, per-cap +6%. $200M synergy target ($120M cost + $80M growth). | VALUATION: $5.27B net debt = 7x leverage; EV/EBITDA 9x on $1.05B 2027 EBITDA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: Q2 2026 earnings Aug = needs comps +2%+ and op margin &gt;5%; H Partners 13D escalation possible | VARIANT: Consensus PT $57 (dead money). H Partners 46% concentration implies AAP returns to AZO margins.</t>
+          <t>CATALYST: May 26 2026 AGM: Jaffer joins board (Class III through 2027, Audit&amp;Finance Cttee). Jana 9% pushing OUTRIGHT SALE. | VARIANT: Street: broken merger story. Two-front activist pressure (governance + sale) + per-park RE floor $47M each.</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
@@ -6265,22 +6265,22 @@
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>ACHC</t>
+          <t>AAP</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Acadia Healthcare</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>$3.2B</t>
+          <t>$3.3B</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$33</t>
+          <t>$54.42</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -6288,43 +6288,43 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2-2.5x</t>
+          <t>2.5-3x ($130-150 AZO comp)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-40%</t>
+          <t>-30%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6:1</t>
+          <t>9:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Greenlight Capital 4.1M sh (David Einhorn); Sohn presentation 5/12/2026</t>
+          <t>H Partners 46.3% / $71.2M / +50% sh Q1 2026 (1.35M sh); Legion Partners precedent</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: -70% drawdown; DOJ resolution + 29% short squeeze setup; P2 + Buckley both NEW</t>
+          <t>ENTRY-TODAY: -80% drawdown from 2021. H Partners 46.3% + Q1 +50% sh add ($71.2M). Bridge thesis: AZO-style 8-10% margins = $130-150. Q2 Aug 2026 = margin proof catalyst. Op margin +410bps already. Not cash-floored but H Partners concentration = sponsor put.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>THESIS: Largest US behavioral health network (260+ facilities). DOJ Medicaid investigation overhang. Q1 2026 admissions stabilizing. Greenlight 4.1M activist; Sohn 5/12 pitch. | VALUATION: EV/EBITDA 6.5x (vs HCA 9x, UHS 8x); 29% short float; -70% drawdown</t>
+          <t>THESIS: #3 aftermarket retailer post-WorldPac sale. Q1 +3.5% comps (Pro mid-single, DIY low-single). 700+ stores closed; ~1,300 strategic locations remain. Bridge to AZO-style 8-10% margins = $130-150/sh. | VALUATION: 3.8% op margin (rising +410bps), FY26 guide $2.40-3.10 EPS; sub-1x sales; M&amp;A floor 0.8x sales = $80/sh</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: DOJ resolution + Q2 2026 earnings + 29% short squeeze potential | VARIANT: Market: DOJ/Medicaid existential. Greenlight: provider necessity + facility footprint + de-rate captured = floor near current.</t>
+          <t>CATALYST: Q2 2026 earnings Aug = needs comps +2%+ and op margin &gt;5%; H Partners 13D escalation possible | VARIANT: Consensus PT $57 (dead money). H Partners 46% concentration implies AAP returns to AZO margins.</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
@@ -6342,66 +6342,66 @@
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>MRP</t>
+          <t>ACHC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Millrose Properties</t>
+          <t>Acadia Healthcare</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>$4.59B</t>
+          <t>$3.2B</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>$25</t>
+          <t>$33</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>2-3x + squeeze</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-40%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>12:1</t>
+          <t>6:1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Lennar 80%+ owner = patient capital lock-in; SITG multi-fund flag</t>
+          <t>Greenlight Capital 4.1M sh (David Einhorn); Sohn presentation 5/12/2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Lennar 80% spinoff; deepest B/M 1.274; pure NAV play at discount</t>
+          <t>ENTRY-TODAY: -70% drawdown + 29% SHORT FLOAT = squeeze fuel. EV/EBITDA 6.5x vs peers 8-9x. DOJ resolution binary catalyst. Greenlight 4.1M sh + Sohn 5/12 pitch = thesis surfaced publicly.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>THESIS: Lennar 80%+ owner spinoff with 100k+ optioned lots at cost basis. Land bank trading below NAV with Lennar as guaranteed off-take partner. Housing-cycle recovery levered. | VALUATION: B/M 1.274 (DEEPEST in 6/7 tier; deeper than NRP's 0.47), pure NAV play</t>
+          <t>THESIS: Largest US behavioral health network (260+ facilities). DOJ Medicaid investigation overhang. Q1 2026 admissions stabilizing. Greenlight 4.1M activist; Sohn 5/12 pitch. | VALUATION: EV/EBITDA 6.5x (vs HCA 9x, UHS 8x); 29% short float; -70% drawdown</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: Q2 2026 print + Lennar volume scaling + housing cycle inflection | VARIANT: Market priced spinoff orphan technical pressure. Smart money: pure land cash-cow at discount to NAV.</t>
+          <t>CATALYST: DOJ resolution + Q2 2026 earnings + 29% short squeeze potential | VARIANT: Market: DOJ/Medicaid existential. Greenlight: provider necessity + facility footprint + de-rate captured = floor near current.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
         <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Wynnefield 13.3% 13D w/ board seat; sub-$200M micro waste services</t>
+          <t>ENTRY-TODAY: Wynnefield 13.3% 13D w/ board seat. Sub-$200M micro waste services. Recurring revenue.</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6487,7 @@
         <v>6</v>
       </c>
       <c r="B25" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Nierenberg/D3 LARGEST shareholder; restaurant turnaround + activist soft pressure</t>
+          <t>ENTRY-TODAY: Nierenberg/D3 LARGEST shareholder (~$16.4M / 7% book). Restaurant turnaround + soft activist pressure.</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -6699,66 +6699,66 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>KYMR</t>
+          <t>PRLD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kymera Therapeutics</t>
+          <t>Prelude Therapeutics</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>$6.5B</t>
+          <t>$340M</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>$80</t>
+          <t>$4.26</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>3-8x</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>13:1</t>
+          <t>20:1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>BVF #1 position 14.6% of $3.14B book ($458M) + Baker Bros 4.1% / $721M; BOTH anchored $86 follow-on</t>
+          <t>Baker Bros 15.5% 13D/A + RA Capital 9.99% 13G; BOTH anchored SAME $90M April financing at $4.44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Trough; BROADEN2 AD mid-2027 not priced; BVF + Baker MAX dual conviction</t>
+          <t>ENTRY-TODAY: NET CASH $2.20/sh = 51% of $4.26 price = downside FLOORED. Baker Bros 15.5% 13D + RA Capital 9.99% 13G BOTH anchored SAME April $90M financing at $4.44 — buying TODAY $4.26 is BELOW smart money entry. JAK2 binary upside 5-10x.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>THESIS: Targeted protein degradation platform. Lead KT-621 oral STAT6 degrader competes with injectable Dupixent ($14B+ franchise). IRAK4 partnered with Sanofi. | VALUATION: $1.55B cash (runway 2029); Dec 2025 follow-on $602M at $86</t>
+          <t>THESIS: Precision oncology / molecular glue / degrader platform. SMARCA2 discontinued 2025; pivot to JAK2V617F (PRT12396) + KAT6A (PRT13722). AbCellera partnership. | VALUATION: $175M cash vs $340M mcap = $2.20/sh net cash (51% of price); buyout floor near current</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: BROADEN2 AD mid-2027 (12+ months); BREADTH asthma late 2027; FDA Fast Track granted both | VARIANT: Market: Phase 1b execution risk. Two top biotech specialists: oral Dupixent-disruptor with peak $5-10B.</t>
+          <t>CATALYST: PRT12396 Phase 1 H2 2026; PRT13722 IND mid-2026; Incyte option agreement Nov 2025 | VARIANT: Market: broken story post-SMARCA2 fail. Smart money: April 2026 refunding = platform-validation thesis. JAK2 mutant-selective addresses 95% PV/60% ET/55% MF.</t>
         </is>
       </c>
     </row>
@@ -6767,7 +6767,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
@@ -6776,66 +6776,66 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>PRLD</t>
+          <t>PVLA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prelude Therapeutics</t>
+          <t>Palvella Therapeutics</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>$340M</t>
+          <t>$1.56B</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$4.26</t>
+          <t>$130</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>2-3x</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>13:1</t>
+          <t>10:1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Baker Bros 15.5% 13D/A + RA Capital 9.99% 13G; BOTH anchored SAME $90M April financing at $4.44</t>
+          <t>BVF 3.8% / $120M (8.5% of company) + Suvretta 3.67% / $144M (+29.3% Q1)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Sub-$1B; PRT12396 Ph1 H2 2026; Baker + RA Cap SAME $90M financing at $4.44</t>
+          <t>ENTRY-TODAY: Cash $25/sh = 19% of $130 price. Phase 3 SELVA POSITIVE Feb 24 2026 = DE-RISKED. Pre-NDA Q2 + NDA H2 + PDUFA H1 2027 = staircase of catalysts. BVF 8.5% of company + Suvretta 3.67% (+29.3% Q1).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>THESIS: Precision oncology / molecular glue / degrader platform. SMARCA2 discontinued 2025; pivot to JAK2V617F (PRT12396) + KAT6A (PRT13722). AbCellera partnership. | VALUATION: $175M cash vs $340M mcap = $2.20/sh net cash (51% of price); buyout floor near current</t>
+          <t>THESIS: Rare-disease topical platform. QTORIN rapamycin gel for microcystic LMs (Breakthrough + Orphan + Fast Track). Phase 3 SELVA POSITIVE Feb 24 2026 (mLM-IGA +2.13, p&lt;0.001). | VALUATION: $261.9M cash = $25/sh (19% of price). Phase 3 derisked. M&amp;A floor 4-6x peak rev</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: PRT12396 Phase 1 H2 2026; PRT13722 IND mid-2026; Incyte option agreement Nov 2025 | VARIANT: Market: broken story post-SMARCA2 fail. Smart money: April 2026 refunding = platform-validation thesis. JAK2 mutant-selective addresses 95% PV/60% ET/55% MF.</t>
+          <t>CATALYST: Pre-NDA FDA meeting Q2 2026; NDA H2 2026; PDUFA H1 2027 | VARIANT: Market: single-asset rare-disease (~$1.5B). Smart money: platform with &gt;$1B peak QTORIN + venous malformations/angiokeratomas/pitavastatin programs.</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
@@ -6853,30 +6853,30 @@
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>PVLA</t>
+          <t>KYMR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Palvella Therapeutics</t>
+          <t>Kymera Therapeutics</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>$1.56B</t>
+          <t>$6.5B</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$130</t>
+          <t>$80</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>3-5x</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -6886,33 +6886,33 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>9:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>BVF 3.8% / $120M (8.5% of company) + Suvretta 3.67% / $144M (+29.3% Q1)</t>
+          <t>BVF #1 position 14.6% of $3.14B book ($458M) + Baker Bros 4.1% / $721M; BOTH anchored $86 follow-on</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Pre-PDUFA; NDA H2 2026; BVF + Suvretta both top-10</t>
+          <t>ENTRY-TODAY: Cash $1.55B + BVF 14.6% MAX conviction + Baker 4.1% = multi-fund convergence. BUT major catalyst BROADEN2 mid-2027 = 12+ months away (low velocity). Strong setup, slow trigger.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>THESIS: Rare-disease topical platform. QTORIN rapamycin gel for microcystic LMs (Breakthrough + Orphan + Fast Track). Phase 3 SELVA POSITIVE Feb 24 2026 (mLM-IGA +2.13, p&lt;0.001). | VALUATION: $261.9M cash = $25/sh (19% of price). Phase 3 derisked. M&amp;A floor 4-6x peak rev</t>
+          <t>THESIS: Targeted protein degradation platform. Lead KT-621 oral STAT6 degrader competes with injectable Dupixent ($14B+ franchise). IRAK4 partnered with Sanofi. | VALUATION: $1.55B cash (runway 2029); Dec 2025 follow-on $602M at $86</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: Pre-NDA FDA meeting Q2 2026; NDA H2 2026; PDUFA H1 2027 | VARIANT: Market: single-asset rare-disease (~$1.5B). Smart money: platform with &gt;$1B peak QTORIN + venous malformations/angiokeratomas/pitavastatin programs.</t>
+          <t>CATALYST: BROADEN2 AD mid-2027 (12+ months); BREADTH asthma late 2027; FDA Fast Track granted both | VARIANT: Market: Phase 1b execution risk. Two top biotech specialists: oral Dupixent-disruptor with peak $5-10B.</t>
         </is>
       </c>
     </row>
@@ -6921,7 +6921,7 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Suvretta 44.1% 13D (their LARGEST stake by %); gene therapy platform</t>
+          <t>ENTRY-TODAY: Suvretta 44.1% 13D = LARGEST stake by %. Gene therapy platform. Multi-program optionality. Higher risk than other biotech-multi-fund names.</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
         <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
@@ -7026,11 +7026,11 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.3-2x (1x post-data)</t>
+          <t>1.3-2x post-data</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -7052,7 +7052,7 @@
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Phase 3 May 1 2026 POSITIVE; +76% PT raises already in price; ASCO Jun 2 / PDUFA Jul 17 remaining</t>
+          <t>ENTRY-TODAY: Phase 3 May 1 POSITIVE + +76% PT raises already in price. ASCO Jun 2 + PDUFA Jul 17 remain but pre-quantified. Quality+catalysts but entry economics weakened post-data.</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
         <v>6</v>
       </c>
       <c r="B25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
@@ -7103,11 +7103,11 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.2-1.5x (was 1.4-1.8x)</t>
+          <t>1.2-1.5x</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -7129,7 +7129,7 @@
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: YORVIPATH ramp priced; €247M Q1 (2x YoY) already at $247; multiple normalized</t>
+          <t>ENTRY-TODAY: YORVIPATH ramp priced. €247M Q1 (2x YoY) already at $247. Multiple normalized.</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7278,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>1.5-2x to NAV</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>17:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -7332,7 +7332,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Ackman $100 cost basis = floor put; Vantage close Q2 (30-45d); below sponsor entry</t>
+          <t>ENTRY-TODAY: NAV $95-105 vs $63.77 = 33-39% DISCOUNT to real (not aspirational) NAV. Ackman 47% at $100 cost = sponsor PUT floor. Vantage close Q2 (30-45d) = dated trigger. Insurance float makes compounding violent post-close.</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7466,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -7494,11 +7494,11 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2-2.5x</t>
+          <t>2-2.5x ($55-65 SoTP)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -7520,7 +7520,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: $30 vs SoTP $55-65; MTS spin Jan 4 2027 still 7+ months away; director buys May 2026</t>
+          <t>ENTRY-TODAY: SoTP MTS $5.2B EV + STS $5.3B = $55-65 vs $30 today. MTS SPIN JAN 4 2027 = dated trigger 7 months out. D3 +425% Q1 (LARGEST single add in entire universe). Director Form 4 buys May 2026 = sponsor put.</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Family Dollar divestiture proceeding; partial multi-fund consensus already established</t>
+          <t>ENTRY-TODAY: B/M 0.20 Yartseva 6/7 + Family Dollar divestiture proceeds = $1B+ cash bolster. Post-divest clean Dollar Tree franchise. Multi-fund deep-value consensus already established = partial discount captured.</t>
         </is>
       </c>
     </row>
@@ -7743,22 +7743,22 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>VITL</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vital Farms</t>
+          <t>OptimizeRx</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>$1.5B</t>
+          <t>$93M</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>$13</t>
+          <t>$4.82</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>2-4x ($11.50 PT)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -7776,33 +7776,33 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>13:1</t>
+          <t>12:1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No major fund concentrated yet</t>
+          <t>Insider 14.82%; $10M buyback</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Deepest drawdown -68.76%; 11% ROA sustained; no smart money pile-in yet</t>
+          <t>ENTRY-TODAY: SUB-BOOK 0.70x + $19M FCF profitable + insider 14.82% + analyst $11.50 (138%) + sub-$100M float = ANY DSP Q4 print violently re-rates. Smart money still building (not exiting). True intrinsic value &gt; 2x current.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>THESIS: [See Archetype 1 for full thesis] | VALUATION: B/M 0.74, ROA 11%, -68.76% from peak (DEEPEST drawdown in 6/7)</t>
+          <t>THESIS: [See Archetype 1] | VALUATION: P/B 0.70 sub-book, -65.4% 6mo drawdown</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: Avian flu normalization + M&amp;A + summer pricing | VARIANT: [See Archetype 1]</t>
+          <t>CATALYST: DSP integration Q4 2026 + MFN clarity | VARIANT: [See Archetype 1]</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7811,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
@@ -7820,66 +7820,66 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>VITL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OptimizeRx</t>
+          <t>Vital Farms</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>$93M</t>
+          <t>$1.5B</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$4.82</t>
+          <t>$13</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.5-6x</t>
+          <t>2-3x ($30-40)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-45%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>10:1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Insider 14.82%; $10M buyback</t>
+          <t>No major fund concentrated yet</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: -65.4% 6mo drawdown; sub-book 0.7x; Q4 DSP integration not priced</t>
+          <t>ENTRY-TODAY: Deepest drawdown -68.76% + 11% ROA sustained = exceptional. BUT B/M 0.74 = not deeply undervalued vs book; M&amp;A precedent 4x sales = $50 = +260%. Brand-led re-rate is SLOW not violent. No defined binary catalyst.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>THESIS: [See Archetype 1] | VALUATION: P/B 0.70 sub-book, -65.4% 6mo drawdown</t>
+          <t>THESIS: [See Archetype 1 for full thesis] | VALUATION: B/M 0.74, ROA 11%, -68.76% from peak (DEEPEST drawdown in 6/7)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: DSP integration Q4 2026 + MFN clarity | VARIANT: [See Archetype 1]</t>
+          <t>CATALYST: Avian flu normalization + M&amp;A + summer pricing | VARIANT: [See Archetype 1]</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
@@ -7897,22 +7897,22 @@
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>FRPT</t>
+          <t>COTY</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Freshpet</t>
+          <t>Coty Inc</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>$2.53B</t>
+          <t>$1.79B</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$60</t>
+          <t>$12</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3-4x</t>
+          <t>2-4x</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -7930,33 +7930,33 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>10:1</t>
+          <t>9:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Marlowe Partners 39.8% in last 13F (highest single-fund signal)</t>
+          <t>KKR legacy anchor; deep-value funds incrementally adding</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Manufacturing capacity online; Marlowe 39.8% (highest concentration); margin inflection</t>
+          <t>ENTRY-TODAY: B/M 1.73 DEEPEST + FCF yield 17.4% but ROA -4.91% CAVEAT (Y3 fails). KKR overhang resolution = catalyst. Brand assets (Burberry, Tiffany, CK) worth multiples of EV. Operational risk balances deep value.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>THESIS: Premium fresh dog food brand leader. Manufacturing capacity coming online (Ennis plant). Margin inflection at 70%+ utilization. M&amp;A target for Nestle Purina / Mars / General Mills. | VALUATION: B/M 0.50 (borderline Yartseva 6/7), ROA 3.41%, -40% drawdown</t>
+          <t>THESIS: Prestige/fragrance beauty (Burberry, Tiffany, CK, Calvin Klein brands). KKR overhang anchor. -37.5% drawdown extreme contrarian setup. Brand assets worth multiples of EV. | VALUATION: B/M 1.73 (DEEPEST in 6/7 tier), FCF yield 17.4%, but ROA -4.91% (Y3 fails)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: Capacity utilization + margin inflection + M&amp;A speculation | VARIANT: Market: consumer weakness + capex burden. Smart: brand pricing power + post-capex FCF inflection.</t>
+          <t>CATALYST: Debt restructuring + KKR exit dynamics + cost program execution | VARIANT: Market: earnings deterioration. Smart: 6-year FCF payback floor with brand asset coverage.</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
@@ -7974,22 +7974,22 @@
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>COTY</t>
+          <t>FRPT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Coty Inc</t>
+          <t>Freshpet</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>$1.79B</t>
+          <t>$2.53B</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>$12</t>
+          <t>$60</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2-4x</t>
+          <t>2-3x</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -8007,33 +8007,33 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>9:1</t>
+          <t>8:1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>KKR legacy anchor; deep-value funds incrementally adding</t>
+          <t>Marlowe Partners 39.8% in last 13F (highest single-fund signal)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: B/M 1.73 deep; KKR overhang resolution; -37.5% drawdown; ROA negative caveat</t>
+          <t>ENTRY-TODAY: B/M 0.50 borderline + ROA 3.41% + -40% drawdown. Manufacturing capacity online = margin inflection. Marlowe 39.8% (highest concentration). M&amp;A target. But valuation not as deep as Tier S/A.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>THESIS: Prestige/fragrance beauty (Burberry, Tiffany, CK, Calvin Klein brands). KKR overhang anchor. -37.5% drawdown extreme contrarian setup. Brand assets worth multiples of EV. | VALUATION: B/M 1.73 (DEEPEST in 6/7 tier), FCF yield 17.4%, but ROA -4.91% (Y3 fails)</t>
+          <t>THESIS: Premium fresh dog food brand leader. Manufacturing capacity coming online (Ennis plant). Margin inflection at 70%+ utilization. M&amp;A target for Nestle Purina / Mars / General Mills. | VALUATION: B/M 0.50 (borderline Yartseva 6/7), ROA 3.41%, -40% drawdown</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>CATALYST: Debt restructuring + KKR exit dynamics + cost program execution | VARIANT: Market: earnings deterioration. Smart: 6-year FCF payback floor with brand asset coverage.</t>
+          <t>CATALYST: Capacity utilization + margin inflection + M&amp;A speculation | VARIANT: Market: consumer weakness + capex burden. Smart: brand pricing power + post-capex FCF inflection.</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: 14.5% FCF yield intact; distribution increase DELAYED = price unmoved; Nov 2026 catalyst</t>
+          <t>ENTRY-TODAY: 14.5% FCF yield ALONE = pure mispricing. Royalty trust at 6.6x P/FCF vs TPL at 25x P/CF (SAME asset class) = comp gap re-rate. Distribution Nov 2026 + preferreds retire. Saber 17.75% + Right Tail NEW Q1 2026.</t>
         </is>
       </c>
     </row>
@@ -8239,7 +8239,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
@@ -8267,11 +8267,11 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>2-3x to LIFO-NAV</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -8293,7 +8293,7 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Florida Panhandle 170k acres; GAAP B/M understates LIFO land basis; Berkowitz anchor</t>
+          <t>ENTRY-TODAY: 170k Florida Panhandle acres. GAAP B/M understates LIFO land basis vs market. True NAV-based B/M likely &gt;1.0. Berkowitz anchor + Florida population growth.</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Permian premium already in; same NAV-vs-GAAP-book issue as JOE; reduced asymmetry</t>
+          <t>ENTRY-TODAY: Already at 25x P/CF premium = ENDLESS DRILLING priced. NAV-vs-GAAP issue similar to JOE but multiple no longer cheap.</t>
         </is>
       </c>
     </row>

--- a/investment_archetypes.xlsx
+++ b/investment_archetypes.xlsx
@@ -9,17 +9,18 @@
   <sheets>
     <sheet name="Index" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="TIER S+ Secular×Asymmetric" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MASTER Entry-Today" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="1. Yartseva Pure Multibagger" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2. Activist Board Catalyst" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="3. Biotech Multi-Fund Convergen" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="4. Sponsor-Anchored Holdco Tran" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="5. Spinoff - SoTP Arbitrage" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="6. Deep Drawdown Mean Reversion" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="7. Hard Asset - Royalty" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="8. Foreign - Underfollowed Valu" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="9. Quality Compounder at Trough" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="10. Hedged - Special Structure" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="MAX Skin + Recent Entry" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MASTER Entry-Today" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="1. Yartseva Pure Multibagger" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2. Activist Board Catalyst" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="3. Biotech Multi-Fund Convergen" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="4. Sponsor-Anchored Holdco Tran" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="5. Spinoff - SoTP Arbitrage" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="6. Deep Drawdown Mean Reversion" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="7. Hard Asset - Royalty" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="8. Foreign - Underfollowed Valu" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="9. Quality Compounder at Trough" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="10. Hedged - Special Structure" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -143,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -211,6 +212,9 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -931,7 +935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -952,14 +956,14 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>7. Hard Asset / Royalty — ENTRY-TODAY × TAILWIND</t>
+          <t>6. Deep Drawdown Mean Reversion — ENTRY-TODAY × TAILWIND</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Definition: Irreplaceable asset ownership (royalty, land, minerals) with no recurring capex requirement and cash-flow distribution structure.</t>
+          <t>Definition: Yartseva mechanics: extreme drawdown (&gt;40% from peak) + retained profitability/cash flow + brand or category strength = mean reversion setup.</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1039,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
@@ -1049,66 +1053,66 @@
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NRP</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Natural Resource Partners</t>
+          <t>OptimizeRx</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>$1.35B</t>
+          <t>$93M</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$105.81</t>
+          <t>$4.82</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.5-3x</t>
+          <t>2-4x ($11.50 PT)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>13:1</t>
+          <t>12:1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Saber 17.75% + Greystone top + Right Tail NEW + Berkowitz</t>
+          <t>Insider 14.82%; $10M buyback</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Met coal (no green substitute for steelmaking) + Sisecam soda ash (solar glass + EV battery) = TWO structural tailwinds masked by dying-thermal-coal narrative; 6.6x vs TPL 25x is a TRUE comp gap</t>
+          <t>Digital pharma messaging shift to EHR-native channels (Doximity-style TAM); pharma DTC compliance with MFN actually accelerates digital share; market focused on near-term MFN overhang</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: 14.5% FCF yield ALONE = pure mispricing. Royalty trust at 6.6x P/FCF vs TPL at 25x P/CF (SAME asset class) = comp gap re-rate. Distribution Nov 2026 + preferreds retire. Saber 17.75% + Right Tail NEW Q1 2026.</t>
+          <t>ENTRY-TODAY: SUB-BOOK 0.70x + $19M FCF profitable + insider 14.82% + analyst $11.50 (138%) + sub-$100M float = ANY DSP Q4 print violently re-rates. Smart money still building (not exiting). True intrinsic value &gt; 2x current.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>THESIS: [See Archetype 1] | VALUATION: [See Archetype 1]</t>
+          <t>THESIS: [See Archetype 1] | VALUATION: P/B 0.70 sub-book, -65.4% 6mo drawdown</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Nov 2026 distribution + preferreds retire | VARIANT: [See Archetype 1]</t>
+          <t>CATALYST: DSP integration Q4 2026 + MFN clarity | VARIANT: [See Archetype 1]</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1121,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
@@ -1131,30 +1135,30 @@
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>JOE</t>
+          <t>VITL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. Joe Company</t>
+          <t>Vital Farms</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$2.8B</t>
+          <t>$1.5B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$48</t>
+          <t>$13</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2-3x to LIFO-NAV</t>
+          <t>2-3x ($30-40)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1164,33 +1168,33 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Berkowitz/Fairholme longstanding anchor</t>
+          <t>No major fund concentrated yet</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Florida population growth secular but slow re-rate; Berkowitz anchor recognized</t>
+          <t>Pasture-raised premium category creation real but partially recognized</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: 170k Florida Panhandle acres. GAAP B/M understates LIFO land basis vs market. True NAV-based B/M likely &gt;1.0. Berkowitz anchor + Florida population growth.</t>
+          <t>ENTRY-TODAY: Deepest drawdown -68.76% + 11% ROA sustained = exceptional. BUT B/M 0.74 = not deeply undervalued vs book; M&amp;A precedent 4x sales = $50 = +260%. Brand-led re-rate is SLOW not violent. No defined binary catalyst.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Florida Panhandle landbank with 170k+ acres. GAAP B/M understates LIFO land basis vs market value. True NAV-based B/M likely &gt;1.0 even at current price. | VALUATION: Land bank: 170k acres NW Florida; GAAP B/M understates LIFO land basis</t>
+          <t>THESIS: [See Archetype 1 for full thesis] | VALUATION: B/M 0.74, ROA 11%, -68.76% from peak (DEEPEST drawdown in 6/7)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Florida population growth + master plan community development + Berkowitz anchor | VARIANT: Yartseva fails on size + low GAAP B/M; correct framework is Lynch asset play.</t>
+          <t>CATALYST: Avian flu normalization + M&amp;A + summer pricing | VARIANT: [See Archetype 1]</t>
         </is>
       </c>
     </row>
@@ -1199,92 +1203,177 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>34</v>
-      </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="D13" s="34" t="inlineStr">
-        <is>
-          <t>PRICED</t>
+        <v>23</v>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>TPL</t>
+          <t>COTY</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Texas Pacific Land Trust</t>
+          <t>Coty Inc</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$30B</t>
+          <t>$1.79B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$1300</t>
+          <t>$12</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.3-1.5x</t>
+          <t>2-4x</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>9:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Multi-fund quality holders; HRC anchor</t>
+          <t>KKR legacy anchor; deep-value funds incrementally adding</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Permian premium already at 25x P/CF; secular real but no asymmetry from here</t>
+          <t>Prestige beauty cyclical; KKR overhang dominates pricing</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Already at 25x P/CF premium = ENDLESS DRILLING priced. NAV-vs-GAAP issue similar to JOE but multiple no longer cheap.</t>
+          <t>ENTRY-TODAY: B/M 1.73 DEEPEST + FCF yield 17.4% but ROA -4.91% CAVEAT (Y3 fails). KKR overhang resolution = catalyst. Brand assets (Burberry, Tiffany, CK) worth multiples of EV. Operational risk balances deep value.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Permian water + royalty optionality. Same NAV-vs-GAAP-book issue as JOE. Pricing 'endless drilling' premium. | VALUATION: Permian royalty trust at 25x P/CF (vs NRP at 6x)</t>
+          <t>THESIS: Prestige/fragrance beauty (Burberry, Tiffany, CK, Calvin Klein brands). KKR overhang anchor. -37.5% drawdown extreme contrarian setup. Brand assets worth multiples of EV. | VALUATION: B/M 1.73 (DEEPEST in 6/7 tier), FCF yield 17.4%, but ROA -4.91% (Y3 fails)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Permian production growth + water revenue optionality | VARIANT: Yartseva captures FCF yield + ROA but understates B/M for land assets.</t>
+          <t>CATALYST: Debt restructuring + KKR exit dynamics + cost program execution | VARIANT: Market: earnings deterioration. Smart: 6-year FCF payback floor with brand asset coverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="n">
+        <v>26</v>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>FRPT</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Freshpet</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>$2.53B</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>$60</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2-3x</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>8:1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Marlowe Partners 39.8% in last 13F (highest single-fund signal)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Pet humanization secular real but FRPT-specific manufacturing issues dominate pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: B/M 0.50 borderline + ROA 3.41% + -40% drawdown. Manufacturing capacity online = margin inflection. Marlowe 39.8% (highest concentration). M&amp;A target. But valuation not as deep as Tier S/A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Premium fresh dog food brand leader. Manufacturing capacity coming online (Ennis plant). Margin inflection at 70%+ utilization. M&amp;A target for Nestle Purina / Mars / General Mills. | VALUATION: B/M 0.50 (borderline Yartseva 6/7), ROA 3.41%, -40% drawdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Capacity utilization + margin inflection + M&amp;A speculation | VARIANT: Market: consumer weakness + capex burden. Smart: brand pricing power + post-capex FCF inflection.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="14">
+    <mergeCell ref="A19:M19"/>
     <mergeCell ref="A14:M14"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A8:M8"/>
     <mergeCell ref="A6:M6"/>
     <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A18:M18"/>
     <mergeCell ref="A15:M15"/>
     <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A20:M20"/>
     <mergeCell ref="A16:M16"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A11:M11"/>
@@ -1321,14 +1410,14 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>8. Foreign / Underfollowed Value — ENTRY-TODAY × TAILWIND</t>
+          <t>7. Hard Asset / Royalty — ENTRY-TODAY × TAILWIND</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Definition: Listed outside primary US market or in segment poorly covered by US sell-side. Currency arbitrage + institutional underweight = entry edge.</t>
+          <t>Definition: Irreplaceable asset ownership (royalty, land, minerals) with no recurring capex requirement and cash-flow distribution structure.</t>
         </is>
       </c>
     </row>
@@ -1404,44 +1493,44 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>MTY.TO</t>
+          <t>NRP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MTY Food Group</t>
+          <t>Natural Resource Partners</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C$887M</t>
+          <t>$1.35B</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>C$40.41</t>
+          <t>$105.81</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2-2.5x</t>
+          <t>2.5-3x</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1451,19 +1540,19 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CEO open-market buy</t>
+          <t>Saber 17.75% + Greystone top + Right Tail NEW + Berkowitz</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>QSR franchise consolidation secular (Inspire/RBI/Roark precedent) recognized but multiple at trough</t>
+          <t>Met coal (no green substitute for steelmaking) + Sisecam soda ash (solar glass + EV battery) = TWO structural tailwinds masked by dying-thermal-coal narrative; 6.6x vs TPL 25x is a TRUE comp gap</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: AT BOOK 1.04x + 16.7% FCF yield = pure value. M&amp;A pool at 12-14x EBITDA vs trading 7.5x = M&amp;A precedent arb. CEO Lefebvre open-market buy at C$30.54 = sponsor put. QSR consolidation trend.</t>
+          <t>ENTRY-TODAY: 14.5% FCF yield ALONE = pure mispricing. Royalty trust at 6.6x P/FCF vs TPL at 25x P/CF (SAME asset class) = comp gap re-rate. Distribution Nov 2026 + preferreds retire. Saber 17.75% + Right Tail NEW Q1 2026.</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1566,7 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Q2 2026 SSS test + NCIB | VARIANT: [See Archetype 1]</t>
+          <t>CATALYST: Nov 2026 distribution + preferreds retire | VARIANT: [See Archetype 1]</t>
         </is>
       </c>
     </row>
@@ -1486,80 +1575,80 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>BZU.IM</t>
+          <t>JOE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buzzi SpA</t>
+          <t>St. Joe Company</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>€8.9B</t>
+          <t>$2.8B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>€49</t>
+          <t>$48</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.7-2x (Kerrisdale €85 PT)</t>
+          <t>2-3x to LIFO-NAV</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>10:1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Kerrisdale Capital published long thesis Oct 2025 (€85 PT)</t>
+          <t>Berkowitz/Fairholme longstanding anchor</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>AI data-center concrete demand (US data-center capex translates to cement orders); 52% EBITDA from US; institutional underweight on Italian listing</t>
+          <t>Florida population growth secular but slow re-rate; Berkowitz anchor recognized</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: 6.8x EV/EBITDA vs peers 9-11x. AI data-center concrete demand = real (not theoretical). 52% EBITDA from US. Kerrisdale Oct 2025 €85 PT (+73%). Italian listing = institutional underweight = re-rate slow but explicit.</t>
+          <t>ENTRY-TODAY: 170k Florida Panhandle acres. GAAP B/M understates LIFO land basis vs market. True NAV-based B/M likely &gt;1.0. Berkowitz anchor + Florida population growth.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Italian cement (€8.9B mcap). 52% of EBITDA from US. AI data-center concrete demand thesis. Trading at sector-discount multiple to LafargeHolcim/CRH peers. | VALUATION: 6.8x EV/EBITDA (vs peer 9-11x); €85 PT = +73% upside</t>
+          <t>THESIS: Florida Panhandle landbank with 170k+ acres. GAAP B/M understates LIFO land basis vs market value. True NAV-based B/M likely &gt;1.0 even at current price. | VALUATION: Land bank: 170k acres NW Florida; GAAP B/M understates LIFO land basis</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: AI data-center capex translating to concrete orders; multiple re-rate to peer levels | VARIANT: Italian listing + cement = institutional underweight. Kerrisdale Oct 2025 long thesis 73% upside.</t>
+          <t>CATALYST: Florida population growth + master plan community development + Berkowitz anchor | VARIANT: Yartseva fails on size + low GAAP B/M; correct framework is Lynch asset play.</t>
         </is>
       </c>
     </row>
@@ -1568,80 +1657,80 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D13" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
+        <v>34</v>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>PRICED</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Texas Pacific Land Trust</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$1.89B</t>
+          <t>$30B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$13</t>
+          <t>$1300</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>1.3-1.5x</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>12:1</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Nine Ten Capital (Bares) 13.1% of book / 3.48M sh / $41.4M</t>
+          <t>Multi-fund quality holders; HRC anchor</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>CTV ad spend doubling 2024-2028 (eMarketer); INDEPENDENT SSP that survived ad-tech wash-out = winner-take-most; Netflix/Disney/Roku exclusive deals scaling; market priced "ad-tech roadkill"</t>
+          <t>Permian premium already at 25x P/CF; secular real but no asymmetry from here</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Independent CTV SSP = winner of ad-tech wash-out. Netflix/Disney/Roku scaling. AI integration. Nine Ten 13.1% / 3.48M sh = highest concentration.</t>
+          <t>ENTRY-TODAY: Already at 25x P/CF premium = ENDLESS DRILLING priced. NAV-vs-GAAP issue similar to JOE but multiple no longer cheap.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Independent CTV SSP. Netflix/Disney/Roku exclusive deals scaling. AI ad-buying integration. Last major non-Google scaled SSP. | VALUATION: Yartseva 6/7 (sub-$2B), B/M 0.49, FCF yield positive, ROA positive</t>
+          <t>THESIS: Permian water + royalty optionality. Same NAV-vs-GAAP-book issue as JOE. Pricing 'endless drilling' premium. | VALUATION: Permian royalty trust at 25x P/CF (vs NRP at 6x)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: CTV ad spend doubling 2024-2028 + Netflix exclusive scaling + AI integration | VARIANT: Market: ad-tech roadkill. Smart: winning independent CTV SSP that survived ad-tech wash-out.</t>
+          <t>CATALYST: Permian production growth + water revenue optionality | VARIANT: Yartseva captures FCF yield + ROA but understates B/M for land assets.</t>
         </is>
       </c>
     </row>
@@ -1690,14 +1779,14 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>9. Quality Compounder at Trough — ENTRY-TODAY × TAILWIND</t>
+          <t>8. Foreign / Underfollowed Value — ENTRY-TODAY × TAILWIND</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Definition: Defensive quality business at multi-year low multiple due to transitory headwind. Re-rate when consensus catches up to recovery.</t>
+          <t>Definition: Listed outside primary US market or in segment poorly covered by US sell-side. Currency arbitrage + institutional underweight = entry edge.</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1862,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
@@ -1787,66 +1876,66 @@
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>MTY.TO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>MTY Food Group</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>$25B</t>
+          <t>C$887M</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$52.75</t>
+          <t>C$40.41</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>2-2.5x</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>12:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Multi-fund deep-value funds Q1 2026</t>
+          <t>CEO open-market buy</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>IT services AI accelerator (vs disruptor) debate; partial market acceptance</t>
+          <t>QSR franchise consolidation secular (Inspire/RBI/Roark precedent) recognized but multiple at trough</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Yartseva 6/7 + 9.88% FCF yield + ROA 10.44% + -27% 6mo. AI accelerator-not-disruptor thesis. Defensive value vs deep-value pure play.</t>
+          <t>ENTRY-TODAY: AT BOOK 1.04x + 16.7% FCF yield = pure value. M&amp;A pool at 12-14x EBITDA vs trading 7.5x = M&amp;A precedent arb. CEO Lefebvre open-market buy at C$30.54 = sponsor put. QSR consolidation trend.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Yartseva 6/7 IT services franchise. Multi-fund consensus Q1 2026. 300k+ delivery workforce moat. AI/IT services capex super-cycle 2026-2028. | VALUATION: P/B 1.66 (B/M 0.60), 9.88% FCF yield, ROA 10.44%, -27% 6mo</t>
+          <t>THESIS: [See Archetype 1] | VALUATION: [See Archetype 1]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: AI implementation winner via enterprise partners + Q2 2026 earnings | VARIANT: Market: AI disrupts IT services. Smart: AI accelerator not disruptor.</t>
+          <t>CATALYST: Q2 2026 SSS test + NCIB | VARIANT: [See Archetype 1]</t>
         </is>
       </c>
     </row>
@@ -1855,44 +1944,44 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
-      </c>
-      <c r="C9" s="31" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+        <v>22</v>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>BZU.IM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>Buzzi SpA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$65B</t>
+          <t>€8.9B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$638</t>
+          <t>€49</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.5-2x</t>
+          <t>1.7-2x (Kerrisdale €85 PT)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1902,33 +1991,33 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Founder-led; multi-fund pharma specialist holds</t>
+          <t>Kerrisdale Capital published long thesis Oct 2025 (€85 PT)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Aging demographic + ophthalmology + immunology pipeline partially priced</t>
+          <t>AI data-center concrete demand (US data-center capex translates to cement orders); 52% EBITDA from US; institutional underweight on Italian listing</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Defensive quality. Pipeline optionality. Partial trough recovery underway.</t>
+          <t>ENTRY-TODAY: 6.8x EV/EBITDA vs peers 9-11x. AI data-center concrete demand = real (not theoretical). 52% EBITDA from US. Kerrisdale Oct 2025 €85 PT (+73%). Italian listing = institutional underweight = re-rate slow but explicit.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Founder/CEO Schleifer + Yancopoulos R&amp;D-led. $31.4B book equity + EYLEA franchise + Linvoseltamab launching. Pipeline broad. Itepekimab Phase 3 readout potential catalyst. | VALUATION: B/M 0.48, FCF yield 6.33%, P/B 2.07; Yartseva 6/7 (size only fail)</t>
+          <t>THESIS: Italian cement (€8.9B mcap). 52% of EBITDA from US. AI data-center concrete demand thesis. Trading at sector-discount multiple to LafargeHolcim/CRH peers. | VALUATION: 6.8x EV/EBITDA (vs peer 9-11x); €85 PT = +73% upside</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Itepekimab 2026-2027 data + Linvoseltamab ramp | VARIANT: Market: fianlimab miss + Eylea biosimilar. Smart: broad pipeline + buyback + founder skin.</t>
+          <t>CATALYST: AI data-center capex translating to concrete orders; multiple re-rate to peer levels | VARIANT: Italian listing + cement = institutional underweight. Kerrisdale Oct 2025 long thesis 73% upside.</t>
         </is>
       </c>
     </row>
@@ -1937,80 +2026,80 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>41</v>
-      </c>
-      <c r="C13" s="33" t="inlineStr">
-        <is>
-          <t>RERATED</t>
-        </is>
-      </c>
-      <c r="D13" s="34" t="inlineStr">
-        <is>
-          <t>PRICED</t>
+        <v>25</v>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Danaher</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$122B</t>
+          <t>$1.89B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$171</t>
+          <t>$13</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.3-1.5x</t>
+          <t>3-5x</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>12:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>D1 Capital +312% Q1 ($107M→$437M, 4th-largest position)</t>
+          <t>Nine Ten Capital (Bares) 13.1% of book / 3.48M sh / $41.4M</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Bioprocessing cycle now consensus 2H 2026</t>
+          <t>CTV ad spend doubling 2024-2028 (eMarketer); INDEPENDENT SSP that survived ad-tech wash-out = winner-take-most; Netflix/Disney/Roku exclusive deals scaling; market priced "ad-tech roadkill"</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Bouncing from trough; bioprocessing cycle now consensus; multiple expansion captured. Defensive 2H 2026 fully priced.</t>
+          <t>ENTRY-TODAY: Independent CTV SSP = winner of ad-tech wash-out. Netflix/Disney/Roku scaling. AI integration. Nine Ten 13.1% / 3.48M sh = highest concentration.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Pure-play life sciences (Cytiva bioprocessing, Beckman Dx, Cepheid). Q1 EPS $2.06 beat by 6.2%; bioprocessing inflecting positive after destock; Cepheid respiratory comp resets Q4 2026. | VALUATION: 19.7x forward P/E (trough vs 5yr avg 30x); ROA pos; B/M 0.43</t>
+          <t>THESIS: Independent CTV SSP. Netflix/Disney/Roku exclusive deals scaling. AI ad-buying integration. Last major non-Google scaled SSP. | VALUATION: Yartseva 6/7 (sub-$2B), B/M 0.49, FCF yield positive, ROA positive</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Bioprocessing book-to-bill durably &gt;1.0 + China VBP stabilization H2 2026 + Cepheid Q4 reset | VARIANT: Consensus: show-me on growth post-destock. Sundheim/D1: same stock 2019-2021 (30%/yr) at trough multiple while H2 2026 comps inflect.</t>
+          <t>CATALYST: CTV ad spend doubling 2024-2028 + Netflix exclusive scaling + AI integration | VARIANT: Market: ad-tech roadkill. Smart: winning independent CTV SSP that survived ad-tech wash-out.</t>
         </is>
       </c>
     </row>
@@ -2033,6 +2122,375 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>9. Quality Compounder at Trough — ENTRY-TODAY × TAILWIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Definition: Defensive quality business at multi-year low multiple due to transitory headwind. Re-rate when consensus catches up to recovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Within-Rank</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Master-Rank</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Re-rate</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Tailwind</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Mcap</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Asym</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Smart Money</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>Secular Driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>$25B</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>$52.75</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2-3x</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>12:1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Multi-fund deep-value funds Q1 2026</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>IT services AI accelerator (vs disruptor) debate; partial market acceptance</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Yartseva 6/7 + 9.88% FCF yield + ROA 10.44% + -27% 6mo. AI accelerator-not-disruptor thesis. Defensive value vs deep-value pure play.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Yartseva 6/7 IT services franchise. Multi-fund consensus Q1 2026. 300k+ delivery workforce moat. AI/IT services capex super-cycle 2026-2028. | VALUATION: P/B 1.66 (B/M 0.60), 9.88% FCF yield, ROA 10.44%, -27% 6mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: AI implementation winner via enterprise partners + Q2 2026 earnings | VARIANT: Market: AI disrupts IT services. Smart: AI accelerator not disruptor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>35</v>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Regeneron</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>$65B</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>$638</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1.5-2x</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>8:1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Founder-led; multi-fund pharma specialist holds</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Aging demographic + ophthalmology + immunology pipeline partially priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Defensive quality. Pipeline optionality. Partial trough recovery underway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Founder/CEO Schleifer + Yancopoulos R&amp;D-led. $31.4B book equity + EYLEA franchise + Linvoseltamab launching. Pipeline broad. Itepekimab Phase 3 readout potential catalyst. | VALUATION: B/M 0.48, FCF yield 6.33%, P/B 2.07; Yartseva 6/7 (size only fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Itepekimab 2026-2027 data + Linvoseltamab ramp | VARIANT: Market: fianlimab miss + Eylea biosimilar. Smart: broad pipeline + buyback + founder skin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>41</v>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>RERATED</t>
+        </is>
+      </c>
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>PRICED</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>DHR</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Danaher</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>$122B</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>$171</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1.3-1.5x</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>D1 Capital +312% Q1 ($107M→$437M, 4th-largest position)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Bioprocessing cycle now consensus 2H 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Bouncing from trough; bioprocessing cycle now consensus; multiple expansion captured. Defensive 2H 2026 fully priced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Pure-play life sciences (Cytiva bioprocessing, Beckman Dx, Cepheid). Q1 EPS $2.06 beat by 6.2%; bioprocessing inflecting positive after destock; Cepheid respiratory comp resets Q4 2026. | VALUATION: 19.7x forward P/E (trough vs 5yr avg 30x); ROA pos; B/M 0.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Bioprocessing book-to-bill durably &gt;1.0 + China VBP stabilization H2 2026 + Cepheid Q4 reset | VARIANT: Consensus: show-me on growth post-destock. Sundheim/D1: same stock 2019-2021 (30%/yr) at trough multiple while H2 2026 comps inflect.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A10:M10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3123,6 +3581,1197 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>MAX SKIN IN GAME + NOT DEEPLY IN MONEY — Smart Money Conviction × Entry Economics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>Filter: highest position concentration (% of fund book) AND fund still at or near cost basis (= entry economics intact for new investor). Excludes positions deeply in money where fund already captured multi-bagger move.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TIER LEGEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>TIER 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MAX skin + UNDERWATER (fund at MAX conviction + below cost = pure follow signal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>TIER 2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MAX skin + flat to modest in money (Q1 ADDs at current band)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>TIER 3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Strong concentration + recent entry near current</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>REF</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>High concentration but DEEPLY in money (reference only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Asym Rank</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Fund</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Concentration / Skin</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Cost Basis / Entry</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>P&amp;L Status</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>Signal Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>PRLD</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Baker Bros + RA Capital (DUAL ANCHOR)</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Baker 15.5% 13D/A + RA Capital 9.99% 13G</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>$4.44 (BOTH anchored same April 2026 $90M financing)</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>$4.26</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>-4% UNDERWATER</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>EXTREME — TWO top biotech crossover funds anchored at SAME price 4% above current. Buy today = buy BELOW their entry. They cannot be selling here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>HHH</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Ackman/Pershing Square</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>47% of HHH via $900M common + $1B preferred</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>$100/sh (publicly disclosed acquisition price)</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>$63.77</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>-36% UNDERWATER</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>EXTREME — Ackman publicly anchored at $100 with multi-billion commitment. $63 = sponsor PUT floor; he cannot mark down or sell. Any holdco progress = re-rate toward his cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>KYMR</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>BVF (MAX CONVICTION) + Baker Bros</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>BVF #1 position 14.6% of $3.14B book ($458M) + Baker 4.1% / $721M</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>$86 (Dec 2025 follow-on, both participated)</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>$80</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>-7% UNDERWATER</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>EXTREME — BVF largest holding with 14.6% concentration; followed on at $86. Current $80 means TWO biotech specialists below entry on highest-conviction names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>D3 Family Fund (Nierenberg)</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>+425% Q1 2026 = LARGEST SINGLE ADD IN ENTIRE UNIVERSE</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>~$30 (Q1 2026 build)</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>$30</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>EXTREME — D3 quintupled position in Q1 at current levels. Director Form 4 buys May 2026 at $30-31 confirm sponsor put. New entrant at $30 = same cost basis as the largest-add fund move of the quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>INMD</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Steel Partners + Mizrahy (founder)</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>Steel 25.5% of $338M book / +155% Q1 2026 (DOUBLED). Founder bought 800k sh ($10.7M) Feb 2026</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>$13.50-14 (Steel Q1 build + founder Feb buy)</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>$13.71</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>EXTREME — Founder bought $10.7M open-market AT current price. Steel doubled position to 25% of book at same level. Cash $8.47/sh = $11+ floor regardless. New entrant gets founder cost basis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>NRP</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Saber Capital (Huber) + Right Tail NEW Q1</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>Saber 17.75% of book + Robertson family 31.75% insider + Right Tail NEW Q1 2026</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>Right Tail NEW Q1 at ~$105 (just entered); Saber long-term</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>$105.81</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>FLAT (vs recent Right Tail entry)</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>STRONG — Right Tail concentrated NEW position Q1 2026 at current; Saber 17.75% concentration; insider family 31.75% — alignment intact at current. Nov 2026 distribution increase ahead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>OPRX</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Insider holders + Doximity exec board addition</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>Insider 14.82% + $10M buyback through March 2027</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Buyback executing at $4-5 range; Presti (Doximity) joined board April 2026</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>$4.82</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>FLAT vs buyback execution</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>STRONG — Company buying back stock at current levels; high-quality industry exec (Doximity, the digital health peer) JOINED BOARD April 2026 at depressed prices = strong insider conviction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>AAP</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>H Partners (Andrew Levander)</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>46.3% of $154M book / $71.2M / +50% sh Q1 2026 (1.35M new shares)</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>~$40-55 range (Q1 add at deeper discount)</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>$54.42</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>MODESTLY IN MONEY (~5-15%)</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>STRONG — H Partners HALF THEIR BOOK in one name + still ADDING Q1 (1.35M sh new). 46% concentration is extreme. Q2 margin proof Aug = continued add likely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>FUN</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>H Partners + Jana Partners</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>H Partners 53.7% / $82.5M / 5.7% of class. Jana 9% activist push</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>H Partners built ~$22-30 range</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>$25</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>FLAT to modest</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>STRONG — H Partners 53.7% concentration = MAX conviction of any 13F filer in universe. Jana 9% pushing OUTRIGHT SALE. Two-front activist. Jaffer just joined board May 26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>CRTO</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>D3/Nierenberg + Petrus Advisers</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>D3 9.37% / +19% Q1 2026. Petrus activist position</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>$11.50-14 (D3 +19% Q1 at trough)</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>$13.50</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>FLAT (D3 added at current band)</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>STRONG — D3 added 19% to existing 9.37% in Q1 at this price band. $200M buyback (22% cap) executing. Petrus activist + Q3 anniversary lap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>PVLA</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>BVF + Suvretta (DUAL)</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>BVF 3.8% / $120M (8.5% of company) + Suvretta 3.67% / $144M (+29.3% Q1)</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>Suvretta added 29% Q1 at $100-140 range</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>$130</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>FLAT to slightly in money</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>STRONG — Suvretta ADDED 29% Q1 post-Phase 3 positive. BVF + Suvretta both top-10 holders. Cash $25/sh = 19% floor. NDA/PDUFA staircase ahead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>MRP</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Lennar (parent spinoff sponsor)</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>Lennar 80%+ owner (cost basis at spin = current)</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>Spin cost basis = current price (paper position at spin date)</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>$25</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>FLAT (Lennar holds at cost)</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>STRONG — Lennar 80% ownership = patient capital lock-in. Lennar cannot exit easily (anti-stuffing). Deepest B/M 1.274 in cohort = land bank discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>FRPT</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Marlowe Partners</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>39.8% of book = HIGHEST single-fund concentration in universe</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>Built at -40% drawdown levels</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>$60</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>FLAT vs cost basis</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>STRONG — Single-fund concentration 39.8% = bet-the-fund conviction. Manufacturing capacity online + margin inflection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>MGNI</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Nine Ten Capital (Bares)</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>13.1% of book / 3.48M sh / $41.4M</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>Built at depressed CTV SSP prices</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>$13</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>FLAT to modest</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>STRONG — Bares-trained Nine Ten 13.1% concentration. Independent CTV SSP winner-take-most thesis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>BNTC</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Suvretta Capital</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>44.1% 13D = SUVRETTA LARGEST STAKE BY %</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>Built at sub-$10 levels</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>$8</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>Likely close to cost or modest underwater</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>STRONG — Suvretta's LARGEST single position by % ownership. 13D filing = activist intent. Gene therapy platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>ACHC</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>Greenlight Capital (David Einhorn)</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>Greenlight 4.1M shares + Sohn 5/12/2026 pitch</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>Built at $30-40 range during DOJ overhang</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>$33</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>FLAT (Einhorn near cost)</t>
+        </is>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>STRONG — Einhorn surfaced thesis publicly at Sohn 5/12; -70% drawdown + 29% short float = squeeze fuel on DOJ resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>MTY.TO</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>CEO Lefebvre (Eric Lefebvre)</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>CEO open-market buy at C$30.54 (+33% increase to personal stake)</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>C$30.54 (CEO buy)</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>C$40.41</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>CEO +32% in money but at COST = current band signal</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>MODERATE — CEO buying $1M+ at depressed = sponsor put. At-book valuation + 16.7% FCF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>BZU.IM</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>Kerrisdale (Sahm Adrangi) — public thesis</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>Kerrisdale Oct 2025 published long thesis with €85 PT</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>Thesis published at €49 (current)</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>€49</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>FLAT (published at current)</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>MODERATE — Public research firm anchored thesis at current. €85 PT (+73%). Italian cement + AI data-center demand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>REF</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>CVNA</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>CAS Investment Partners</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>81.7% of CAS book = highest single-name concentration in universe</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>~$3-30 (legendary recovery position)</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>$71</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>20-25x IN MONEY — REFERENCE ONLY</t>
+        </is>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>REFERENCE — CAS recovered CVNA from $3 to $71 = 40x+. No longer asymmetric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>REF</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>TCI Fund Management (Chris Hohn)</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>29.85% of $45B book = largest single position</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>Held since 2015</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>$209</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="inlineStr">
+        <is>
+          <t>DEEPLY IN MONEY — REFERENCE ONLY</t>
+        </is>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>REFERENCE — TCI deeply in money post-GE Aerospace breakup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>REF</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>TCI Fund Management</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>20.39% of $45B book</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>Held long-term</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>$352</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>DEEPLY IN MONEY — REFERENCE ONLY</t>
+        </is>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>REFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>REF</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>CELC</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>N/A (re-rated)</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>Baker Bros</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>19.99% ACTIVIST 13D = $904M / 5.48% of $17.4B book</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>Built pre-data at $50-100</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>$165</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="inlineStr">
+        <is>
+          <t>DEEPLY IN MONEY post-May 1 — REFERENCE ONLY</t>
+        </is>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>REFERENCE — Baker captured the move; entry-today is post-data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>REF</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>ASND</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>N/A (re-rated)</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>RA Capital</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>24.9% of $9.44B book = $2.35B = LARGEST biotech crossover position in universe</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>Held since 2015</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>$247</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="inlineStr">
+        <is>
+          <t>DEEPLY IN MONEY — REFERENCE ONLY</t>
+        </is>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>REFERENCE — RA Capital largest position but multiple captured.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6228,7 +7877,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7408,8 +9057,8 @@
     <mergeCell ref="A22:M22"/>
     <mergeCell ref="A35:M35"/>
     <mergeCell ref="A20:M20"/>
+    <mergeCell ref="A43:M43"/>
     <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A43:M43"/>
     <mergeCell ref="A52:M52"/>
     <mergeCell ref="A10:M10"/>
     <mergeCell ref="A28:M28"/>
@@ -7447,630 +9096,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>2. Activist Board Catalyst — ENTRY-TODAY × TAILWIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Definition: Schedule 13D filing with board seat secured or imminent + activist demands for value unlock. Dated trigger creates near-term volatility around catalyst.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Within-Rank</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Master-Rank</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Re-rate</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Tailwind</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Mcap</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>Asym</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>Upside</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>R/R</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>Smart Money</t>
-        </is>
-      </c>
-      <c r="M4" s="13" t="inlineStr">
-        <is>
-          <t>Secular Driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>MRP</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Millrose Properties</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>$4.59B</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>$25</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1.8-2.5x to NAV</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>13:1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Lennar 80%+ owner = patient capital lock-in; SITG multi-fund flag</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>US housing supply shortage structural (4M+ undersupply) + Lennar 80% off-take = guaranteed demand; market treats as spinoff orphan, not housing-cycle play</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: B/M 1.274 = DEEPEST in 6/7 cohort (deeper than NRP 0.47). Lennar 80% owner = guaranteed off-take + patient capital. Land bank at COST BASIS vs market. Pure NAV unwind; spinoff orphan technical pressure resolves into Q2 prints.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Lennar 80%+ owner spinoff with 100k+ optioned lots at cost basis. Land bank trading below NAV with Lennar as guaranteed off-take partner. Housing-cycle recovery levered. | VALUATION: B/M 1.274 (DEEPEST in 6/7 tier; deeper than NRP's 0.47), pure NAV play</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Q2 2026 print + Lennar volume scaling + housing cycle inflection | VARIANT: Market priced spinoff orphan technical pressure. Smart money: pure land cash-cow at discount to NAV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" t="n">
-        <v>14</v>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D9" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t>FUN</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Six Flags Entertainment</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>$2.2B</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>$25</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2-3x (3x outright sale)</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>9:1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>H Partners 53.7% / $82.5M / 5.7% of class; Jana 9% + Travis Kelce co-invest</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Theme parks cyclical consumer discretionary</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: 42 parks IRREPLACEABLE RE @ $47M each = $2B floor. Jaffer joined board May 26 + Jana 9% pushing OUTRIGHT SALE = two-front activist pressure. H Partners 53.7% / 5.7% of class. Sale = violent 3x trigger.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Post-Cedar Fair/Six Flags merger consolidation. 42 parks irreplaceable real estate. Q1 2026 rev +12%, attendance +4%, per-cap +6%. $200M synergy target ($120M cost + $80M growth). | VALUATION: $5.27B net debt = 7x leverage; EV/EBITDA 9x on $1.05B 2027 EBITDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: May 26 2026 AGM: Jaffer joins board (Class III through 2027, Audit&amp;Finance Cttee). Jana 9% pushing OUTRIGHT SALE. | VARIANT: Street: broken merger story. Two-front activist pressure (governance + sale) + per-park RE floor $47M each.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D13" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="inlineStr">
-        <is>
-          <t>AAP</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Advance Auto Parts</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>$3.3B</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>$54.42</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>8</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2.5-3x ($130-150 AZO comp)</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>9:1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>H Partners 46.3% / $71.2M / +50% sh Q1 2026 (1.35M sh); Legion Partners precedent</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Auto aftermarket mature; H Partners margin recovery thesis is operational not secular</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: -80% drawdown from 2021. H Partners 46.3% + Q1 +50% sh add ($71.2M). Bridge thesis: AZO-style 8-10% margins = $130-150. Q2 Aug 2026 = margin proof catalyst. Op margin +410bps already. Not cash-floored but H Partners concentration = sponsor put.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: #3 aftermarket retailer post-WorldPac sale. Q1 +3.5% comps (Pro mid-single, DIY low-single). 700+ stores closed; ~1,300 strategic locations remain. Bridge to AZO-style 8-10% margins = $130-150/sh. | VALUATION: 3.8% op margin (rising +410bps), FY26 guide $2.40-3.10 EPS; sub-1x sales; M&amp;A floor 0.8x sales = $80/sh</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Q2 2026 earnings Aug = needs comps +2%+ and op margin &gt;5%; H Partners 13D escalation possible | VARIANT: Consensus PT $57 (dead money). H Partners 46% concentration implies AAP returns to AZO margins.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" t="n">
-        <v>16</v>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D17" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="E17" s="28" t="inlineStr">
-        <is>
-          <t>ACHC</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Acadia Healthcare</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>$3.2B</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>$33</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>8</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2-3x + squeeze</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>6:1</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Greenlight Capital 4.1M sh (David Einhorn); Sohn presentation 5/12/2026</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Behavioral health secular demand (mental health structural) but DOJ regulatory overhang dominates pricing</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: -70% drawdown + 29% SHORT FLOAT = squeeze fuel. EV/EBITDA 6.5x vs peers 8-9x. DOJ resolution binary catalyst. Greenlight 4.1M sh + Sohn 5/12 pitch = thesis surfaced publicly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Largest US behavioral health network (260+ facilities). DOJ Medicaid investigation overhang. Q1 2026 admissions stabilizing. Greenlight 4.1M activist; Sohn 5/12 pitch. | VALUATION: EV/EBITDA 6.5x (vs HCA 9x, UHS 8x); 29% short float; -70% drawdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: DOJ resolution + Q2 2026 earnings + 29% short squeeze potential | VARIANT: Market: DOJ/Medicaid existential. Greenlight: provider necessity + facility footprint + de-rate captured = floor near current.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>5</v>
-      </c>
-      <c r="B21" t="n">
-        <v>30</v>
-      </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D21" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="E21" s="28" t="inlineStr">
-        <is>
-          <t>QRHC</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Quest Resource Holding</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>$200M</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>$7</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>6</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2-3x</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>8:1</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Wynnefield 13.3% / 2.73M sh / 13D w/ board seat</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Waste services minimal secular</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: Wynnefield 13.3% 13D w/ board seat. Sub-$200M micro waste services. Recurring revenue.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Wynnefield filed 13D 13.3% May 2025; Robert Lipstein joined board. Cooperation Agreement w/ standstill until 30 days before 2027 nomination window. Asset-light recurring waste mgmt. | VALUATION: Sub-$200M micro; recurring waste services revenue model</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Operational improvements + Wynnefield additional buying if dips | VARIANT: Market: small-cap value trap. Activist: board seat + potential value-unlock initiatives.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>6</v>
-      </c>
-      <c r="B25" t="n">
-        <v>31</v>
-      </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D25" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="E25" s="28" t="inlineStr">
-        <is>
-          <t>POSTBPB</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Potbelly Corp (PBPB)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>$240M</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>$8</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>6</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2-3x</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>8:1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Nierenberg/D3 largest shareholder; 13D/A active March 2025</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Restaurant chain cyclical; no secular</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: Nierenberg/D3 LARGEST shareholder (~$16.4M / 7% book). Restaurant turnaround + soft activist pressure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Nierenberg/D3 is LARGEST shareholder (~$16.4M / 7% of D3 book). Customer-traffic gains while peers don't (Q1 2026 letter thesis). Form 4 insider buying by Nierenberg at depressed levels. | VALUATION: Sub-$300M micro restaurant chain; turnaround stage</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Restaurant turnaround + Nierenberg potential escalation | VARIANT: Market: tier-2 restaurant chain. Activist soft-pressure thesis.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A23:M23"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A22:M22"/>
-    <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="A28:M28"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="A24:M24"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="A27:M27"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="A26:M26"/>
-    <mergeCell ref="A2:M2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -8098,14 +9123,14 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>3. Biotech Multi-Fund Convergence — ENTRY-TODAY × TAILWIND</t>
+          <t>2. Activist Board Catalyst — ENTRY-TODAY × TAILWIND</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Definition: Two or more top biotech crossover specialists (Baker Bros, RA Capital, BVF, Stonepine, Suvretta) anchored at high conviction in same name. Convergence is the high-signal pattern.</t>
+          <t>Definition: Schedule 13D filing with board seat secured or imminent + activist demands for value unlock. Dated trigger creates near-term volatility around catalyst.</t>
         </is>
       </c>
     </row>
@@ -8181,7 +9206,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
@@ -8195,66 +9220,66 @@
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>PRLD</t>
+          <t>MRP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Prelude Therapeutics</t>
+          <t>Millrose Properties</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>$340M</t>
+          <t>$4.59B</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$4.26</t>
+          <t>$25</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3-8x</t>
+          <t>1.8-2.5x to NAV</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Baker Bros 15.5% 13D/A + RA Capital 9.99% 13G; BOTH anchored SAME $90M April financing at $4.44</t>
+          <t>Lennar 80%+ owner = patient capital lock-in; SITG multi-fund flag</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Targeted protein degradation platform structural pharma shift + JAK2V617F addresses 95% PV/60% ET/55% MF (aging demographic, no oral comp); SMARCA2 fail = thrown out with platform</t>
+          <t>US housing supply shortage structural (4M+ undersupply) + Lennar 80% off-take = guaranteed demand; market treats as spinoff orphan, not housing-cycle play</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: NET CASH $2.20/sh = 51% of $4.26 price = downside FLOORED. Baker Bros 15.5% 13D + RA Capital 9.99% 13G BOTH anchored SAME April $90M financing at $4.44 — buying TODAY $4.26 is BELOW smart money entry. JAK2 binary upside 5-10x.</t>
+          <t>ENTRY-TODAY: B/M 1.274 = DEEPEST in 6/7 cohort (deeper than NRP 0.47). Lennar 80% owner = guaranteed off-take + patient capital. Land bank at COST BASIS vs market. Pure NAV unwind; spinoff orphan technical pressure resolves into Q2 prints.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Precision oncology / molecular glue / degrader platform. SMARCA2 discontinued 2025; pivot to JAK2V617F (PRT12396) + KAT6A (PRT13722). AbCellera partnership. | VALUATION: $175M cash vs $340M mcap = $2.20/sh net cash (51% of price); buyout floor near current</t>
+          <t>THESIS: Lennar 80%+ owner spinoff with 100k+ optioned lots at cost basis. Land bank trading below NAV with Lennar as guaranteed off-take partner. Housing-cycle recovery levered. | VALUATION: B/M 1.274 (DEEPEST in 6/7 tier; deeper than NRP's 0.47), pure NAV play</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: PRT12396 Phase 1 H2 2026; PRT13722 IND mid-2026; Incyte option agreement Nov 2025 | VARIANT: Market: broken story post-SMARCA2 fail. Smart money: April 2026 refunding = platform-validation thesis. JAK2 mutant-selective addresses 95% PV/60% ET/55% MF.</t>
+          <t>CATALYST: Q2 2026 print + Lennar volume scaling + housing cycle inflection | VARIANT: Market priced spinoff orphan technical pressure. Smart money: pure land cash-cow at discount to NAV.</t>
         </is>
       </c>
     </row>
@@ -8263,80 +9288,80 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>PVLA</t>
+          <t>FUN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Palvella Therapeutics</t>
+          <t>Six Flags Entertainment</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$1.56B</t>
+          <t>$2.2B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$130</t>
+          <t>$25</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>2-3x (3x outright sale)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>10:1</t>
+          <t>9:1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>BVF 3.8% / $120M (8.5% of company) + Suvretta 3.67% / $144M (+29.3% Q1)</t>
+          <t>H Partners 53.7% / $82.5M / 5.7% of class; Jana 9% + Travis Kelce co-invest</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Rare-disease pricing structural ($300k+ orphan); QTORIN platform with multiple programs (LMs, venous malformations, angiokeratomas); market priced single-asset story</t>
+          <t>Theme parks cyclical consumer discretionary</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Cash $25/sh = 19% of $130 price. Phase 3 SELVA POSITIVE Feb 24 2026 = DE-RISKED. Pre-NDA Q2 + NDA H2 + PDUFA H1 2027 = staircase of catalysts. BVF 8.5% of company + Suvretta 3.67% (+29.3% Q1).</t>
+          <t>ENTRY-TODAY: 42 parks IRREPLACEABLE RE @ $47M each = $2B floor. Jaffer joined board May 26 + Jana 9% pushing OUTRIGHT SALE = two-front activist pressure. H Partners 53.7% / 5.7% of class. Sale = violent 3x trigger.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Rare-disease topical platform. QTORIN rapamycin gel for microcystic LMs (Breakthrough + Orphan + Fast Track). Phase 3 SELVA POSITIVE Feb 24 2026 (mLM-IGA +2.13, p&lt;0.001). | VALUATION: $261.9M cash = $25/sh (19% of price). Phase 3 derisked. M&amp;A floor 4-6x peak rev</t>
+          <t>THESIS: Post-Cedar Fair/Six Flags merger consolidation. 42 parks irreplaceable real estate. Q1 2026 rev +12%, attendance +4%, per-cap +6%. $200M synergy target ($120M cost + $80M growth). | VALUATION: $5.27B net debt = 7x leverage; EV/EBITDA 9x on $1.05B 2027 EBITDA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Pre-NDA FDA meeting Q2 2026; NDA H2 2026; PDUFA H1 2027 | VARIANT: Market: single-asset rare-disease (~$1.5B). Smart money: platform with &gt;$1B peak QTORIN + venous malformations/angiokeratomas/pitavastatin programs.</t>
+          <t>CATALYST: May 26 2026 AGM: Jaffer joins board (Class III through 2027, Audit&amp;Finance Cttee). Jana 9% pushing OUTRIGHT SALE. | VARIANT: Street: broken merger story. Two-front activist pressure (governance + sale) + per-park RE floor $47M each.</t>
         </is>
       </c>
     </row>
@@ -8345,80 +9370,80 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D13" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>KYMR</t>
+          <t>AAP</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kymera Therapeutics</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$6.5B</t>
+          <t>$3.3B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$80</t>
+          <t>$54.42</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>2.5-3x ($130-150 AZO comp)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>13:1</t>
+          <t>9:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>BVF #1 position 14.6% of $3.14B book ($458M) + Baker Bros 4.1% / $721M; BOTH anchored $86 follow-on</t>
+          <t>H Partners 46.3% / $71.2M / +50% sh Q1 2026 (1.35M sh); Legion Partners precedent</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Oral biologic disruption (oral Dupixent = $14B+ franchise displacement); TPD structural pharma platform shift; Phase 1b execution risk masks platform value</t>
+          <t>Auto aftermarket mature; H Partners margin recovery thesis is operational not secular</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Cash $1.55B + BVF 14.6% MAX conviction + Baker 4.1% = multi-fund convergence. BUT major catalyst BROADEN2 mid-2027 = 12+ months away (low velocity). Strong setup, slow trigger.</t>
+          <t>ENTRY-TODAY: -80% drawdown from 2021. H Partners 46.3% + Q1 +50% sh add ($71.2M). Bridge thesis: AZO-style 8-10% margins = $130-150. Q2 Aug 2026 = margin proof catalyst. Op margin +410bps already. Not cash-floored but H Partners concentration = sponsor put.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Targeted protein degradation platform. Lead KT-621 oral STAT6 degrader competes with injectable Dupixent ($14B+ franchise). IRAK4 partnered with Sanofi. | VALUATION: $1.55B cash (runway 2029); Dec 2025 follow-on $602M at $86</t>
+          <t>THESIS: #3 aftermarket retailer post-WorldPac sale. Q1 +3.5% comps (Pro mid-single, DIY low-single). 700+ stores closed; ~1,300 strategic locations remain. Bridge to AZO-style 8-10% margins = $130-150/sh. | VALUATION: 3.8% op margin (rising +410bps), FY26 guide $2.40-3.10 EPS; sub-1x sales; M&amp;A floor 0.8x sales = $80/sh</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: BROADEN2 AD mid-2027 (12+ months); BREADTH asthma late 2027; FDA Fast Track granted both | VARIANT: Market: Phase 1b execution risk. Two top biotech specialists: oral Dupixent-disruptor with peak $5-10B.</t>
+          <t>CATALYST: Q2 2026 earnings Aug = needs comps +2%+ and op margin &gt;5%; H Partners 13D escalation possible | VARIANT: Consensus PT $57 (dead money). H Partners 46% concentration implies AAP returns to AZO margins.</t>
         </is>
       </c>
     </row>
@@ -8427,80 +9452,80 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D17" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>BNTC</t>
+          <t>ACHC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Benitec Biopharma</t>
+          <t>Acadia Healthcare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>$200M</t>
+          <t>$3.2B</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>$8</t>
+          <t>$33</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>2-3x + squeeze</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7:1</t>
+          <t>6:1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Suvretta 44.1% 13D (Suvretta's LARGEST stake by % ownership)</t>
+          <t>Greenlight Capital 4.1M sh (David Einhorn); Sohn presentation 5/12/2026</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Gene therapy speculative single platform</t>
+          <t>Behavioral health secular demand (mental health structural) but DOJ regulatory overhang dominates pricing</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Suvretta 44.1% 13D = LARGEST stake by %. Gene therapy platform. Multi-program optionality. Higher risk than other biotech-multi-fund names.</t>
+          <t>ENTRY-TODAY: -70% drawdown + 29% SHORT FLOAT = squeeze fuel. EV/EBITDA 6.5x vs peers 8-9x. DOJ resolution binary catalyst. Greenlight 4.1M sh + Sohn 5/12 pitch = thesis surfaced publicly.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Gene therapy platform anchor position. Suvretta 44.1% 13D anchor stake (largest activist ownership in their portfolio). PIPE participation Nov 2025. | VALUATION: Sub-$300M biotech; gene therapy platform optionality</t>
+          <t>THESIS: Largest US behavioral health network (260+ facilities). DOJ Medicaid investigation overhang. Q1 2026 admissions stabilizing. Greenlight 4.1M activist; Sohn 5/12 pitch. | VALUATION: EV/EBITDA 6.5x (vs HCA 9x, UHS 8x); 29% short float; -70% drawdown</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Multiple gene-therapy programs in development; clinical readouts upcoming | VARIANT: 44.1% ownership creates board influence + asymmetric upside on clinical reads.</t>
+          <t>CATALYST: DOJ resolution + Q2 2026 earnings + 29% short squeeze potential | VARIANT: Market: DOJ/Medicaid existential. Greenlight: provider necessity + facility footprint + de-rate captured = floor near current.</t>
         </is>
       </c>
     </row>
@@ -8509,80 +9534,80 @@
         <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>37</v>
-      </c>
-      <c r="C21" s="33" t="inlineStr">
-        <is>
-          <t>RERATED</t>
-        </is>
-      </c>
-      <c r="D21" s="34" t="inlineStr">
-        <is>
-          <t>PRICED</t>
+        <v>30</v>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
         </is>
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
-          <t>CELC</t>
+          <t>QRHC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Celcuity</t>
+          <t>Quest Resource Holding</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>$8B (post-data)</t>
+          <t>$200M</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>$165</t>
+          <t>$7</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.3-2x post-data</t>
+          <t>2-3x</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>8:1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Baker Bros 19.99% ACTIVIST 13D = $904M / 5.48% of $17.4B book</t>
+          <t>Wynnefield 13.3% / 2.73M sh / 13D w/ board seat</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Targeted oncology secular but Phase 3 data + PT raises captured the move</t>
+          <t>Waste services minimal secular</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Phase 3 May 1 POSITIVE + +76% PT raises already in price. ASCO Jun 2 + PDUFA Jul 17 remain but pre-quantified. Quality+catalysts but entry economics weakened post-data.</t>
+          <t>ENTRY-TODAY: Wynnefield 13.3% 13D w/ board seat. Sub-$200M micro waste services. Recurring revenue.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Phase 3 VIKTORIA-1 PIK3CA-mut POSITIVE May 1 2026 (76% PFS hazard reduction). Gedatolisib pan-PI3K/mTOR oncology. Triplet vs alpelisib+fulvestrant. Multiple HR+/HER2- breast cancer cohorts. | VALUATION: $387M cash + accepted NDA + Priority Review = de-risked; 4-5x peak rev precedent</t>
+          <t>THESIS: Wynnefield filed 13D 13.3% May 2025; Robert Lipstein joined board. Cooperation Agreement w/ standstill until 30 days before 2027 nomination window. Asset-light recurring waste mgmt. | VALUATION: Sub-$200M micro; recurring waste services revenue model</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: JUNE 2 ASCO LBA1008 oral + JULY 17 PDUFA goal date (2 catalysts in 8 weeks) | VARIANT: Market: alpelisib-class peak ($1-2B). Baker Bros 19.99% 13D activist: $5-10B peak (triplet displaces alpelisib + captures WT segment).</t>
+          <t>CATALYST: Operational improvements + Wynnefield additional buying if dips | VARIANT: Market: small-cap value trap. Activist: board seat + potential value-unlock initiatives.</t>
         </is>
       </c>
     </row>
@@ -8591,80 +9616,80 @@
         <v>6</v>
       </c>
       <c r="B25" t="n">
-        <v>40</v>
-      </c>
-      <c r="C25" s="33" t="inlineStr">
-        <is>
-          <t>RERATED</t>
-        </is>
-      </c>
-      <c r="D25" s="34" t="inlineStr">
-        <is>
-          <t>PRICED</t>
+        <v>31</v>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D25" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
         </is>
       </c>
       <c r="E25" s="28" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>POSTBPB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascendis Pharma</t>
+          <t>Potbelly Corp (PBPB)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>$15.3B</t>
+          <t>$240M</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>$247</t>
+          <t>$8</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.2-1.5x</t>
+          <t>2-3x</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>8:1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>RA Capital 24.9% of $9.44B = $2.35B = LARGEST single biotech crossover position; held since 2015</t>
+          <t>Nierenberg/D3 largest shareholder; 13D/A active March 2025</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Rare endocrine pricing secular but YORVIPATH ramp captured</t>
+          <t>Restaurant chain cyclical; no secular</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: YORVIPATH ramp priced. €247M Q1 (2x YoY) already at $247. Multiple normalized.</t>
+          <t>ENTRY-TODAY: Nierenberg/D3 LARGEST shareholder (~$16.4M / 7% book). Restaurant turnaround + soft activist pressure.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>THESIS: TransCon prodrug platform: SKYTROFA (GHD), YORVIPATH (hypopara), YUVIWEL (achondroplasia approved Feb 2026). &gt;1,000 new US YORVIPATH enrollments Q1; 6,300+ patients across 2,700 prescribers. | VALUATION: Profitable (22% non-IFRS op margin); €247M Q1 (2x YoY); peak rev YORVIPATH $4-5B</t>
+          <t>THESIS: Nierenberg/D3 is LARGEST shareholder (~$16.4M / 7% of D3 book). Customer-traffic gains while peers don't (Q1 2026 letter thesis). Form 4 insider buying by Nierenberg at depressed levels. | VALUATION: Sub-$300M micro restaurant chain; turnaround stage</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: YUVIWEL ramp + Q2/Q3 YORVIPATH growth + TransCon CNP follow-on indications | VARIANT: Sell-side: $15B endocrine specialty maturing. RA Capital: $30B+ at 70-90K addressable hypopara population. Analyst high $345 (Barclays).</t>
+          <t>CATALYST: Restaurant turnaround + Nierenberg potential escalation | VARIANT: Market: tier-2 restaurant chain. Activist soft-pressure thesis.</t>
         </is>
       </c>
     </row>
@@ -8701,6 +9726,630 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence — ENTRY-TODAY × TAILWIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Definition: Two or more top biotech crossover specialists (Baker Bros, RA Capital, BVF, Stonepine, Suvretta) anchored at high conviction in same name. Convergence is the high-signal pattern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Within-Rank</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Master-Rank</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Re-rate</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Tailwind</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Mcap</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Asym</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Smart Money</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>Secular Driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>PRLD</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Prelude Therapeutics</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>$340M</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>$4.26</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3-8x</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>20:1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Baker Bros 15.5% 13D/A + RA Capital 9.99% 13G; BOTH anchored SAME $90M April financing at $4.44</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Targeted protein degradation platform structural pharma shift + JAK2V617F addresses 95% PV/60% ET/55% MF (aging demographic, no oral comp); SMARCA2 fail = thrown out with platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: NET CASH $2.20/sh = 51% of $4.26 price = downside FLOORED. Baker Bros 15.5% 13D + RA Capital 9.99% 13G BOTH anchored SAME April $90M financing at $4.44 — buying TODAY $4.26 is BELOW smart money entry. JAK2 binary upside 5-10x.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Precision oncology / molecular glue / degrader platform. SMARCA2 discontinued 2025; pivot to JAK2V617F (PRT12396) + KAT6A (PRT13722). AbCellera partnership. | VALUATION: $175M cash vs $340M mcap = $2.20/sh net cash (51% of price); buyout floor near current</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: PRT12396 Phase 1 H2 2026; PRT13722 IND mid-2026; Incyte option agreement Nov 2025 | VARIANT: Market: broken story post-SMARCA2 fail. Smart money: April 2026 refunding = platform-validation thesis. JAK2 mutant-selective addresses 95% PV/60% ET/55% MF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>17</v>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>PVLA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Palvella Therapeutics</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>$1.56B</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>$130</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2-3x</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>10:1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>BVF 3.8% / $120M (8.5% of company) + Suvretta 3.67% / $144M (+29.3% Q1)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Rare-disease pricing structural ($300k+ orphan); QTORIN platform with multiple programs (LMs, venous malformations, angiokeratomas); market priced single-asset story</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Cash $25/sh = 19% of $130 price. Phase 3 SELVA POSITIVE Feb 24 2026 = DE-RISKED. Pre-NDA Q2 + NDA H2 + PDUFA H1 2027 = staircase of catalysts. BVF 8.5% of company + Suvretta 3.67% (+29.3% Q1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Rare-disease topical platform. QTORIN rapamycin gel for microcystic LMs (Breakthrough + Orphan + Fast Track). Phase 3 SELVA POSITIVE Feb 24 2026 (mLM-IGA +2.13, p&lt;0.001). | VALUATION: $261.9M cash = $25/sh (19% of price). Phase 3 derisked. M&amp;A floor 4-6x peak rev</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Pre-NDA FDA meeting Q2 2026; NDA H2 2026; PDUFA H1 2027 | VARIANT: Market: single-asset rare-disease (~$1.5B). Smart money: platform with &gt;$1B peak QTORIN + venous malformations/angiokeratomas/pitavastatin programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>18</v>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>KYMR</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kymera Therapeutics</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>$6.5B</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>$80</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3-5x</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>13:1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>BVF #1 position 14.6% of $3.14B book ($458M) + Baker Bros 4.1% / $721M; BOTH anchored $86 follow-on</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Oral biologic disruption (oral Dupixent = $14B+ franchise displacement); TPD structural pharma platform shift; Phase 1b execution risk masks platform value</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Cash $1.55B + BVF 14.6% MAX conviction + Baker 4.1% = multi-fund convergence. BUT major catalyst BROADEN2 mid-2027 = 12+ months away (low velocity). Strong setup, slow trigger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Targeted protein degradation platform. Lead KT-621 oral STAT6 degrader competes with injectable Dupixent ($14B+ franchise). IRAK4 partnered with Sanofi. | VALUATION: $1.55B cash (runway 2029); Dec 2025 follow-on $602M at $86</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: BROADEN2 AD mid-2027 (12+ months); BREADTH asthma late 2027; FDA Fast Track granted both | VARIANT: Market: Phase 1b execution risk. Two top biotech specialists: oral Dupixent-disruptor with peak $5-10B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="n">
+        <v>28</v>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>BNTC</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Benitec Biopharma</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>$200M</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>$8</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3-5x</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7:1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Suvretta 44.1% 13D (Suvretta's LARGEST stake by % ownership)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Gene therapy speculative single platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Suvretta 44.1% 13D = LARGEST stake by %. Gene therapy platform. Multi-program optionality. Higher risk than other biotech-multi-fund names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Gene therapy platform anchor position. Suvretta 44.1% 13D anchor stake (largest activist ownership in their portfolio). PIPE participation Nov 2025. | VALUATION: Sub-$300M biotech; gene therapy platform optionality</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Multiple gene-therapy programs in development; clinical readouts upcoming | VARIANT: 44.1% ownership creates board influence + asymmetric upside on clinical reads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" t="n">
+        <v>37</v>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>RERATED</t>
+        </is>
+      </c>
+      <c r="D21" s="34" t="inlineStr">
+        <is>
+          <t>PRICED</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>CELC</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Celcuity</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>$8B (post-data)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>$165</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1.3-2x post-data</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Baker Bros 19.99% ACTIVIST 13D = $904M / 5.48% of $17.4B book</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Targeted oncology secular but Phase 3 data + PT raises captured the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Phase 3 May 1 POSITIVE + +76% PT raises already in price. ASCO Jun 2 + PDUFA Jul 17 remain but pre-quantified. Quality+catalysts but entry economics weakened post-data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Phase 3 VIKTORIA-1 PIK3CA-mut POSITIVE May 1 2026 (76% PFS hazard reduction). Gedatolisib pan-PI3K/mTOR oncology. Triplet vs alpelisib+fulvestrant. Multiple HR+/HER2- breast cancer cohorts. | VALUATION: $387M cash + accepted NDA + Priority Review = de-risked; 4-5x peak rev precedent</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: JUNE 2 ASCO LBA1008 oral + JULY 17 PDUFA goal date (2 catalysts in 8 weeks) | VARIANT: Market: alpelisib-class peak ($1-2B). Baker Bros 19.99% 13D activist: $5-10B peak (triplet displaces alpelisib + captures WT segment).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>40</v>
+      </c>
+      <c r="C25" s="33" t="inlineStr">
+        <is>
+          <t>RERATED</t>
+        </is>
+      </c>
+      <c r="D25" s="34" t="inlineStr">
+        <is>
+          <t>PRICED</t>
+        </is>
+      </c>
+      <c r="E25" s="28" t="inlineStr">
+        <is>
+          <t>ASND</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ascendis Pharma</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>$15.3B</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>$247</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1.2-1.5x</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>RA Capital 24.9% of $9.44B = $2.35B = LARGEST single biotech crossover position; held since 2015</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Rare endocrine pricing secular but YORVIPATH ramp captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: YORVIPATH ramp priced. €247M Q1 (2x YoY) already at $247. Multiple normalized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: TransCon prodrug platform: SKYTROFA (GHD), YORVIPATH (hypopara), YUVIWEL (achondroplasia approved Feb 2026). &gt;1,000 new US YORVIPATH enrollments Q1; 6,300+ patients across 2,700 prescribers. | VALUATION: Profitable (22% non-IFRS op margin); €247M Q1 (2x YoY); peak rev YORVIPATH $4-5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: YUVIWEL ramp + Q2/Q3 YORVIPATH growth + TransCon CNP follow-on indications | VARIANT: Sell-side: $15B endocrine specialty maturing. RA Capital: $30B+ at 70-90K addressable hypopara population. Analyst high $345 (Barclays).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A23:M23"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A20:M20"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A28:M28"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A24:M24"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A27:M27"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A26:M26"/>
+    <mergeCell ref="A2:M2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8894,7 +10543,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9176,458 +10825,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>6. Deep Drawdown Mean Reversion — ENTRY-TODAY × TAILWIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Definition: Yartseva mechanics: extreme drawdown (&gt;40% from peak) + retained profitability/cash flow + brand or category strength = mean reversion setup.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Within-Rank</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Master-Rank</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Re-rate</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Tailwind</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Mcap</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>Asym</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>Upside</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>R/R</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>Smart Money</t>
-        </is>
-      </c>
-      <c r="M4" s="13" t="inlineStr">
-        <is>
-          <t>Secular Driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>OPRX</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>OptimizeRx</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>$93M</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>$4.82</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2-4x ($11.50 PT)</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>12:1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Insider 14.82%; $10M buyback</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Digital pharma messaging shift to EHR-native channels (Doximity-style TAM); pharma DTC compliance with MFN actually accelerates digital share; market focused on near-term MFN overhang</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: SUB-BOOK 0.70x + $19M FCF profitable + insider 14.82% + analyst $11.50 (138%) + sub-$100M float = ANY DSP Q4 print violently re-rates. Smart money still building (not exiting). True intrinsic value &gt; 2x current.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: [See Archetype 1] | VALUATION: P/B 0.70 sub-book, -65.4% 6mo drawdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: DSP integration Q4 2026 + MFN clarity | VARIANT: [See Archetype 1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" t="n">
-        <v>19</v>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t>VITL</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Vital Farms</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>$1.5B</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>$13</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2-3x ($30-40)</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>10:1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>No major fund concentrated yet</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Pasture-raised premium category creation real but partially recognized</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: Deepest drawdown -68.76% + 11% ROA sustained = exceptional. BUT B/M 0.74 = not deeply undervalued vs book; M&amp;A precedent 4x sales = $50 = +260%. Brand-led re-rate is SLOW not violent. No defined binary catalyst.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: [See Archetype 1 for full thesis] | VALUATION: B/M 0.74, ROA 11%, -68.76% from peak (DEEPEST drawdown in 6/7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Avian flu normalization + M&amp;A + summer pricing | VARIANT: [See Archetype 1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" t="n">
-        <v>23</v>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D13" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="inlineStr">
-        <is>
-          <t>COTY</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Coty Inc</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>$1.79B</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>$12</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2-4x</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>9:1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>KKR legacy anchor; deep-value funds incrementally adding</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Prestige beauty cyclical; KKR overhang dominates pricing</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: B/M 1.73 DEEPEST + FCF yield 17.4% but ROA -4.91% CAVEAT (Y3 fails). KKR overhang resolution = catalyst. Brand assets (Burberry, Tiffany, CK) worth multiples of EV. Operational risk balances deep value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Prestige/fragrance beauty (Burberry, Tiffany, CK, Calvin Klein brands). KKR overhang anchor. -37.5% drawdown extreme contrarian setup. Brand assets worth multiples of EV. | VALUATION: B/M 1.73 (DEEPEST in 6/7 tier), FCF yield 17.4%, but ROA -4.91% (Y3 fails)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Debt restructuring + KKR exit dynamics + cost program execution | VARIANT: Market: earnings deterioration. Smart: 6-year FCF payback floor with brand asset coverage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" t="n">
-        <v>26</v>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D17" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="E17" s="28" t="inlineStr">
-        <is>
-          <t>FRPT</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Freshpet</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>$2.53B</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>$60</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2-3x</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>8:1</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Marlowe Partners 39.8% in last 13F (highest single-fund signal)</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Pet humanization secular real but FRPT-specific manufacturing issues dominate pricing</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: B/M 0.50 borderline + ROA 3.41% + -40% drawdown. Manufacturing capacity online = margin inflection. Marlowe 39.8% (highest concentration). M&amp;A target. But valuation not as deep as Tier S/A.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Premium fresh dog food brand leader. Manufacturing capacity coming online (Ennis plant). Margin inflection at 70%+ utilization. M&amp;A target for Nestle Purina / Mars / General Mills. | VALUATION: B/M 0.50 (borderline Yartseva 6/7), ROA 3.41%, -40% drawdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Capacity utilization + margin inflection + M&amp;A speculation | VARIANT: Market: consumer weakness + capex burden. Smart: brand pricing power + post-capex FCF inflection.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A10:M10"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/investment_archetypes.xlsx
+++ b/investment_archetypes.xlsx
@@ -10,17 +10,19 @@
     <sheet name="Index" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="TIER S+ Secular×Asymmetric" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="MAX Skin + Recent Entry" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="MASTER Entry-Today" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="1. Yartseva Pure Multibagger" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2. Activist Board Catalyst" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="3. Biotech Multi-Fund Convergen" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="4. Sponsor-Anchored Holdco Tran" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="5. Spinoff - SoTP Arbitrage" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="6. Deep Drawdown Mean Reversion" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="7. Hard Asset - Royalty" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="8. Foreign - Underfollowed Valu" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="9. Quality Compounder at Trough" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="10. Hedged - Special Structure" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="POSITION INTENSITY" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="MICRO+SMALL CAP INTENSITY" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="MASTER Entry-Today" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="1. Yartseva Pure Multibagger" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2. Activist Board Catalyst" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="3. Biotech Multi-Fund Convergen" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="4. Sponsor-Anchored Holdco Tran" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="5. Spinoff - SoTP Arbitrage" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="6. Deep Drawdown Mean Reversion" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="7. Hard Asset - Royalty" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="8. Foreign - Underfollowed Valu" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="9. Quality Compounder at Trough" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="10. Hedged - Special Structure" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -935,6 +937,489 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>4. Sponsor-Anchored Holdco Transformation — ENTRY-TODAY × TAILWIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Definition: Activist or family-office anchor with significant ownership AND cost-basis floor that creates sponsor put. Holdco transformation thesis (insurance float, multi-asset compounding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Within-Rank</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Master-Rank</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Re-rate</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Tailwind</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Mcap</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Asym</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Smart Money</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>Secular Driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>HHH</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Howard Hughes Holdings</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>$3.5B</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>$63.77</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1.5-2x to NAV</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>13:1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Ackman 47% via $900M @ $100/sh + $1B preferred; Northern Right NEW Q1 +12%</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Sun Belt migration MPC (3,813 acres TX/NV/HI) + Ackman compounding holdco; NAV captures some but Vantage insurance float thesis not yet integrated</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: NAV $95-105 vs $63.77 = 33-39% DISCOUNT to real (not aspirational) NAV. Ackman 47% at $100 cost = sponsor PUT floor. Vantage close Q2 (30-45d) = dated trigger. Insurance float makes compounding violent post-close.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Ackman-led 'Modern Berkshire'. 3,813 acres residential MPC ($4.8B NAV) + 2,447 acres commercial ($2.0B) + Vantage specialty insurance ($2.2B 2027 premium). Marc Grandisson (ex-Arch Capital CEO) on board April 2026. | VALUATION: NAV $95-105/sh = 33-39% discount; $1.84B cash + $515M revolver liquidity</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Vantage close Q2 2026 (30-45 days); Park Ward Village condo closings Q2-Q3 (~$1B rev); first post-Vantage capital allocation | VARIANT: Street: sub-scale RE dev with leverage. Ackman: insurance float + permanent capital. NAV $95-105 vs $63 = 50-67% margin of safety.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A2:M2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>5. Spinoff / SoTP Arbitrage — ENTRY-TODAY × TAILWIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Definition: Sum-of-parts valuation discount with defined corporate action (spin-off, divestiture, breakup) as catalyst.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Within-Rank</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Master-Rank</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Re-rate</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Tailwind</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Mcap</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Asym</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Smart Money</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>Secular Driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>KBR Inc</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>$3.9B</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>$30</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2-2.5x ($55-65 SoTP)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>10:1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>D3/Nierenberg +425% Q1 (largest single add in entire universe); Irenic activist ~1%; Director Form 4 buys May 2026</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Triple secular: (1) US defense spend onshoring, (2) NRC small modular reactor / Natrium nuclear, (3) cleared workforce moat 20k; HomeSafe distraction masks underlying secular bookings</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: SoTP MTS $5.2B EV + STS $5.3B = $55-65 vs $30 today. MTS SPIN JAN 4 2027 = dated trigger 7 months out. D3 +425% Q1 (LARGEST single add in entire universe). Director Form 4 buys May 2026 = sponsor put.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Two segments: MTS (gov services 72%, $18.5B backlog, cleared workforce 20k) + STS (process tech + TerraPower Natrium nuclear EPC alliance, 22% EBITDA margin). FY26 $980M-1.04B EBITDA, $3.87-4.22 EPS. | VALUATION: SoTP: MTS at 11x EBITDA ($5.2B EV) + STS at 14x ($5.3B) = $55-65/sh combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: MTS spin January 4 2027 (board-approved Sept 2025); NRC Natrium safety eval mid-2026 | VARIANT: Market: broken post-HomeSafe termination + class action overhang. Variant: HomeSafe disposed; spin unlocks SoTP value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>29</v>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>DLTR</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dollar Tree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>$25B</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>$80</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2-3x</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>9:1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Multi-fund deep-value funds Q1 2026 adds</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Consumer trade-down secular but already multi-fund consensus</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: B/M 0.20 Yartseva 6/7 + Family Dollar divestiture proceeds = $1B+ cash bolster. Post-divest clean Dollar Tree franchise. Multi-fund deep-value consensus already established = partial discount captured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Post-divestiture clean Dollar Tree franchise (16k+ stores). Multi-fund deep-value consensus Q1 2026. Mayer M6 turnaround pattern. | VALUATION: B/M 0.20 (Yartseva 6/7); Family Dollar divestiture proceeds = $1B+ cash bolster</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Family Dollar sale completion + comparable sales recovery + multiple re-rate | VARIANT: Market priced Family Dollar mistake. Smart money: post-divestiture clean franchise.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A10:M10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1374,744 +1859,6 @@
     <mergeCell ref="A15:M15"/>
     <mergeCell ref="A7:M7"/>
     <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A10:M10"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>7. Hard Asset / Royalty — ENTRY-TODAY × TAILWIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Definition: Irreplaceable asset ownership (royalty, land, minerals) with no recurring capex requirement and cash-flow distribution structure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Within-Rank</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Master-Rank</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Re-rate</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Tailwind</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Mcap</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>Asym</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>Upside</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>R/R</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>Smart Money</t>
-        </is>
-      </c>
-      <c r="M4" s="13" t="inlineStr">
-        <is>
-          <t>Secular Driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>NRP</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Natural Resource Partners</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>$1.35B</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>$105.81</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2.5-3x</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>13:1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Saber 17.75% + Greystone top + Right Tail NEW + Berkowitz</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Met coal (no green substitute for steelmaking) + Sisecam soda ash (solar glass + EV battery) = TWO structural tailwinds masked by dying-thermal-coal narrative; 6.6x vs TPL 25x is a TRUE comp gap</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: 14.5% FCF yield ALONE = pure mispricing. Royalty trust at 6.6x P/FCF vs TPL at 25x P/CF (SAME asset class) = comp gap re-rate. Distribution Nov 2026 + preferreds retire. Saber 17.75% + Right Tail NEW Q1 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: [See Archetype 1] | VALUATION: [See Archetype 1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Nov 2026 distribution + preferreds retire | VARIANT: [See Archetype 1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" t="n">
-        <v>24</v>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t>JOE</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>St. Joe Company</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>$2.8B</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>$48</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2-3x to LIFO-NAV</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>10:1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Berkowitz/Fairholme longstanding anchor</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Florida population growth secular but slow re-rate; Berkowitz anchor recognized</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: 170k Florida Panhandle acres. GAAP B/M understates LIFO land basis vs market. True NAV-based B/M likely &gt;1.0. Berkowitz anchor + Florida population growth.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Florida Panhandle landbank with 170k+ acres. GAAP B/M understates LIFO land basis vs market value. True NAV-based B/M likely &gt;1.0 even at current price. | VALUATION: Land bank: 170k acres NW Florida; GAAP B/M understates LIFO land basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Florida population growth + master plan community development + Berkowitz anchor | VARIANT: Yartseva fails on size + low GAAP B/M; correct framework is Lynch asset play.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" t="n">
-        <v>34</v>
-      </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="D13" s="34" t="inlineStr">
-        <is>
-          <t>PRICED</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="inlineStr">
-        <is>
-          <t>TPL</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Texas Pacific Land Trust</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>$30B</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>$1300</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>1.3-1.5x</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>5:1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Multi-fund quality holders; HRC anchor</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Permian premium already at 25x P/CF; secular real but no asymmetry from here</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: Already at 25x P/CF premium = ENDLESS DRILLING priced. NAV-vs-GAAP issue similar to JOE but multiple no longer cheap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Permian water + royalty optionality. Same NAV-vs-GAAP-book issue as JOE. Pricing 'endless drilling' premium. | VALUATION: Permian royalty trust at 25x P/CF (vs NRP at 6x)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Permian production growth + water revenue optionality | VARIANT: Yartseva captures FCF yield + ROA but understates B/M for land assets.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A10:M10"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>8. Foreign / Underfollowed Value — ENTRY-TODAY × TAILWIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Definition: Listed outside primary US market or in segment poorly covered by US sell-side. Currency arbitrage + institutional underweight = entry edge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Within-Rank</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Master-Rank</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Re-rate</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Tailwind</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Mcap</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>Asym</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>Upside</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>R/R</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>Smart Money</t>
-        </is>
-      </c>
-      <c r="M4" s="13" t="inlineStr">
-        <is>
-          <t>Secular Driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="n">
-        <v>21</v>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D5" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>MTY.TO</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>MTY Food Group</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>C$887M</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>C$40.41</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2-2.5x</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>13:1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>CEO open-market buy</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>QSR franchise consolidation secular (Inspire/RBI/Roark precedent) recognized but multiple at trough</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: AT BOOK 1.04x + 16.7% FCF yield = pure value. M&amp;A pool at 12-14x EBITDA vs trading 7.5x = M&amp;A precedent arb. CEO Lefebvre open-market buy at C$30.54 = sponsor put. QSR consolidation trend.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: [See Archetype 1] | VALUATION: [See Archetype 1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Q2 2026 SSS test + NCIB | VARIANT: [See Archetype 1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" t="n">
-        <v>22</v>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t>BZU.IM</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Buzzi SpA</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>€8.9B</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>€49</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>1.7-2x (Kerrisdale €85 PT)</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>8:1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Kerrisdale Capital published long thesis Oct 2025 (€85 PT)</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>AI data-center concrete demand (US data-center capex translates to cement orders); 52% EBITDA from US; institutional underweight on Italian listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: 6.8x EV/EBITDA vs peers 9-11x. AI data-center concrete demand = real (not theoretical). 52% EBITDA from US. Kerrisdale Oct 2025 €85 PT (+73%). Italian listing = institutional underweight = re-rate slow but explicit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Italian cement (€8.9B mcap). 52% of EBITDA from US. AI data-center concrete demand thesis. Trading at sector-discount multiple to LafargeHolcim/CRH peers. | VALUATION: 6.8x EV/EBITDA (vs peer 9-11x); €85 PT = +73% upside</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: AI data-center capex translating to concrete orders; multiple re-rate to peer levels | VARIANT: Italian listing + cement = institutional underweight. Kerrisdale Oct 2025 long thesis 73% upside.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" t="n">
-        <v>25</v>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D13" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="inlineStr">
-        <is>
-          <t>MGNI</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Magnite</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>$1.89B</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>$13</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>3-5x</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>12:1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Nine Ten Capital (Bares) 13.1% of book / 3.48M sh / $41.4M</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>CTV ad spend doubling 2024-2028 (eMarketer); INDEPENDENT SSP that survived ad-tech wash-out = winner-take-most; Netflix/Disney/Roku exclusive deals scaling; market priced "ad-tech roadkill"</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: Independent CTV SSP = winner of ad-tech wash-out. Netflix/Disney/Roku scaling. AI integration. Nine Ten 13.1% / 3.48M sh = highest concentration.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Independent CTV SSP. Netflix/Disney/Roku exclusive deals scaling. AI ad-buying integration. Last major non-Google scaled SSP. | VALUATION: Yartseva 6/7 (sub-$2B), B/M 0.49, FCF yield positive, ROA positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: CTV ad spend doubling 2024-2028 + Netflix exclusive scaling + AI integration | VARIANT: Market: ad-tech roadkill. Smart: winning independent CTV SSP that survived ad-tech wash-out.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="A7:M7"/>
     <mergeCell ref="A16:M16"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A11:M11"/>
@@ -2148,14 +1895,14 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>9. Quality Compounder at Trough — ENTRY-TODAY × TAILWIND</t>
+          <t>7. Hard Asset / Royalty — ENTRY-TODAY × TAILWIND</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Definition: Defensive quality business at multi-year low multiple due to transitory headwind. Re-rate when consensus catches up to recovery.</t>
+          <t>Definition: Irreplaceable asset ownership (royalty, land, minerals) with no recurring capex requirement and cash-flow distribution structure.</t>
         </is>
       </c>
     </row>
@@ -2231,80 +1978,80 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>NRP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Natural Resource Partners</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>$25B</t>
+          <t>$1.35B</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$52.75</t>
+          <t>$105.81</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>2.5-3x</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>12:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Multi-fund deep-value funds Q1 2026</t>
+          <t>Saber 17.75% + Greystone top + Right Tail NEW + Berkowitz</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>IT services AI accelerator (vs disruptor) debate; partial market acceptance</t>
+          <t>Met coal (no green substitute for steelmaking) + Sisecam soda ash (solar glass + EV battery) = TWO structural tailwinds masked by dying-thermal-coal narrative; 6.6x vs TPL 25x is a TRUE comp gap</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Yartseva 6/7 + 9.88% FCF yield + ROA 10.44% + -27% 6mo. AI accelerator-not-disruptor thesis. Defensive value vs deep-value pure play.</t>
+          <t>ENTRY-TODAY: 14.5% FCF yield ALONE = pure mispricing. Royalty trust at 6.6x P/FCF vs TPL at 25x P/CF (SAME asset class) = comp gap re-rate. Distribution Nov 2026 + preferreds retire. Saber 17.75% + Right Tail NEW Q1 2026.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Yartseva 6/7 IT services franchise. Multi-fund consensus Q1 2026. 300k+ delivery workforce moat. AI/IT services capex super-cycle 2026-2028. | VALUATION: P/B 1.66 (B/M 0.60), 9.88% FCF yield, ROA 10.44%, -27% 6mo</t>
+          <t>THESIS: [See Archetype 1] | VALUATION: [See Archetype 1]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: AI implementation winner via enterprise partners + Q2 2026 earnings | VARIANT: Market: AI disrupts IT services. Smart: AI accelerator not disruptor.</t>
+          <t>CATALYST: Nov 2026 distribution + preferreds retire | VARIANT: [See Archetype 1]</t>
         </is>
       </c>
     </row>
@@ -2313,80 +2060,80 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
-      </c>
-      <c r="C9" s="31" t="inlineStr">
+        <v>24</v>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>JOE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>St. Joe Company</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$65B</t>
+          <t>$2.8B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$638</t>
+          <t>$48</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.5-2x</t>
+          <t>2-3x to LIFO-NAV</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>10:1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Founder-led; multi-fund pharma specialist holds</t>
+          <t>Berkowitz/Fairholme longstanding anchor</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Aging demographic + ophthalmology + immunology pipeline partially priced</t>
+          <t>Florida population growth secular but slow re-rate; Berkowitz anchor recognized</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Defensive quality. Pipeline optionality. Partial trough recovery underway.</t>
+          <t>ENTRY-TODAY: 170k Florida Panhandle acres. GAAP B/M understates LIFO land basis vs market. True NAV-based B/M likely &gt;1.0. Berkowitz anchor + Florida population growth.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Founder/CEO Schleifer + Yancopoulos R&amp;D-led. $31.4B book equity + EYLEA franchise + Linvoseltamab launching. Pipeline broad. Itepekimab Phase 3 readout potential catalyst. | VALUATION: B/M 0.48, FCF yield 6.33%, P/B 2.07; Yartseva 6/7 (size only fail)</t>
+          <t>THESIS: Florida Panhandle landbank with 170k+ acres. GAAP B/M understates LIFO land basis vs market value. True NAV-based B/M likely &gt;1.0 even at current price. | VALUATION: Land bank: 170k acres NW Florida; GAAP B/M understates LIFO land basis</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Itepekimab 2026-2027 data + Linvoseltamab ramp | VARIANT: Market: fianlimab miss + Eylea biosimilar. Smart: broad pipeline + buyback + founder skin.</t>
+          <t>CATALYST: Florida population growth + master plan community development + Berkowitz anchor | VARIANT: Yartseva fails on size + low GAAP B/M; correct framework is Lynch asset play.</t>
         </is>
       </c>
     </row>
@@ -2395,11 +2142,11 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>41</v>
-      </c>
-      <c r="C13" s="33" t="inlineStr">
-        <is>
-          <t>RERATED</t>
+        <v>34</v>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="D13" s="34" t="inlineStr">
@@ -2409,26 +2156,26 @@
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Danaher</t>
+          <t>Texas Pacific Land Trust</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$122B</t>
+          <t>$30B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$171</t>
+          <t>$1300</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -2442,33 +2189,33 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>D1 Capital +312% Q1 ($107M→$437M, 4th-largest position)</t>
+          <t>Multi-fund quality holders; HRC anchor</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Bioprocessing cycle now consensus 2H 2026</t>
+          <t>Permian premium already at 25x P/CF; secular real but no asymmetry from here</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Bouncing from trough; bioprocessing cycle now consensus; multiple expansion captured. Defensive 2H 2026 fully priced.</t>
+          <t>ENTRY-TODAY: Already at 25x P/CF premium = ENDLESS DRILLING priced. NAV-vs-GAAP issue similar to JOE but multiple no longer cheap.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Pure-play life sciences (Cytiva bioprocessing, Beckman Dx, Cepheid). Q1 EPS $2.06 beat by 6.2%; bioprocessing inflecting positive after destock; Cepheid respiratory comp resets Q4 2026. | VALUATION: 19.7x forward P/E (trough vs 5yr avg 30x); ROA pos; B/M 0.43</t>
+          <t>THESIS: Permian water + royalty optionality. Same NAV-vs-GAAP-book issue as JOE. Pricing 'endless drilling' premium. | VALUATION: Permian royalty trust at 25x P/CF (vs NRP at 6x)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Bioprocessing book-to-bill durably &gt;1.0 + China VBP stabilization H2 2026 + Cepheid Q4 reset | VARIANT: Consensus: show-me on growth post-destock. Sundheim/D1: same stock 2019-2021 (30%/yr) at trough multiple while H2 2026 comps inflect.</t>
+          <t>CATALYST: Permian production growth + water revenue optionality | VARIANT: Yartseva captures FCF yield + ROA but understates B/M for land assets.</t>
         </is>
       </c>
     </row>
@@ -2491,6 +2238,744 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>8. Foreign / Underfollowed Value — ENTRY-TODAY × TAILWIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Definition: Listed outside primary US market or in segment poorly covered by US sell-side. Currency arbitrage + institutional underweight = entry edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Within-Rank</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Master-Rank</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Re-rate</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Tailwind</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Mcap</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Asym</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Smart Money</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>Secular Driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>MTY.TO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>MTY Food Group</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>C$887M</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>C$40.41</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2-2.5x</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>13:1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>CEO open-market buy</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>QSR franchise consolidation secular (Inspire/RBI/Roark precedent) recognized but multiple at trough</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: AT BOOK 1.04x + 16.7% FCF yield = pure value. M&amp;A pool at 12-14x EBITDA vs trading 7.5x = M&amp;A precedent arb. CEO Lefebvre open-market buy at C$30.54 = sponsor put. QSR consolidation trend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: [See Archetype 1] | VALUATION: [See Archetype 1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Q2 2026 SSS test + NCIB | VARIANT: [See Archetype 1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>22</v>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>BZU.IM</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Buzzi SpA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>€8.9B</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>€49</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1.7-2x (Kerrisdale €85 PT)</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>8:1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Kerrisdale Capital published long thesis Oct 2025 (€85 PT)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>AI data-center concrete demand (US data-center capex translates to cement orders); 52% EBITDA from US; institutional underweight on Italian listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: 6.8x EV/EBITDA vs peers 9-11x. AI data-center concrete demand = real (not theoretical). 52% EBITDA from US. Kerrisdale Oct 2025 €85 PT (+73%). Italian listing = institutional underweight = re-rate slow but explicit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Italian cement (€8.9B mcap). 52% of EBITDA from US. AI data-center concrete demand thesis. Trading at sector-discount multiple to LafargeHolcim/CRH peers. | VALUATION: 6.8x EV/EBITDA (vs peer 9-11x); €85 PT = +73% upside</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: AI data-center capex translating to concrete orders; multiple re-rate to peer levels | VARIANT: Italian listing + cement = institutional underweight. Kerrisdale Oct 2025 long thesis 73% upside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>25</v>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>MGNI</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Magnite</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>$1.89B</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>$13</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3-5x</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>12:1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Nine Ten Capital (Bares) 13.1% of book / 3.48M sh / $41.4M</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>CTV ad spend doubling 2024-2028 (eMarketer); INDEPENDENT SSP that survived ad-tech wash-out = winner-take-most; Netflix/Disney/Roku exclusive deals scaling; market priced "ad-tech roadkill"</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Independent CTV SSP = winner of ad-tech wash-out. Netflix/Disney/Roku scaling. AI integration. Nine Ten 13.1% / 3.48M sh = highest concentration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Independent CTV SSP. Netflix/Disney/Roku exclusive deals scaling. AI ad-buying integration. Last major non-Google scaled SSP. | VALUATION: Yartseva 6/7 (sub-$2B), B/M 0.49, FCF yield positive, ROA positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: CTV ad spend doubling 2024-2028 + Netflix exclusive scaling + AI integration | VARIANT: Market: ad-tech roadkill. Smart: winning independent CTV SSP that survived ad-tech wash-out.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A10:M10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>9. Quality Compounder at Trough — ENTRY-TODAY × TAILWIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Definition: Defensive quality business at multi-year low multiple due to transitory headwind. Re-rate when consensus catches up to recovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Within-Rank</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Master-Rank</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Re-rate</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Tailwind</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Mcap</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Asym</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Smart Money</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>Secular Driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>$25B</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>$52.75</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2-3x</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>12:1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Multi-fund deep-value funds Q1 2026</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>IT services AI accelerator (vs disruptor) debate; partial market acceptance</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Yartseva 6/7 + 9.88% FCF yield + ROA 10.44% + -27% 6mo. AI accelerator-not-disruptor thesis. Defensive value vs deep-value pure play.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Yartseva 6/7 IT services franchise. Multi-fund consensus Q1 2026. 300k+ delivery workforce moat. AI/IT services capex super-cycle 2026-2028. | VALUATION: P/B 1.66 (B/M 0.60), 9.88% FCF yield, ROA 10.44%, -27% 6mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: AI implementation winner via enterprise partners + Q2 2026 earnings | VARIANT: Market: AI disrupts IT services. Smart: AI accelerator not disruptor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>35</v>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Regeneron</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>$65B</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>$638</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1.5-2x</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>8:1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Founder-led; multi-fund pharma specialist holds</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Aging demographic + ophthalmology + immunology pipeline partially priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Defensive quality. Pipeline optionality. Partial trough recovery underway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Founder/CEO Schleifer + Yancopoulos R&amp;D-led. $31.4B book equity + EYLEA franchise + Linvoseltamab launching. Pipeline broad. Itepekimab Phase 3 readout potential catalyst. | VALUATION: B/M 0.48, FCF yield 6.33%, P/B 2.07; Yartseva 6/7 (size only fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Itepekimab 2026-2027 data + Linvoseltamab ramp | VARIANT: Market: fianlimab miss + Eylea biosimilar. Smart: broad pipeline + buyback + founder skin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>41</v>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>RERATED</t>
+        </is>
+      </c>
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>PRICED</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>DHR</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Danaher</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>$122B</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>$171</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1.3-1.5x</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>D1 Capital +312% Q1 ($107M→$437M, 4th-largest position)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Bioprocessing cycle now consensus 2H 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Bouncing from trough; bioprocessing cycle now consensus; multiple expansion captured. Defensive 2H 2026 fully priced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Pure-play life sciences (Cytiva bioprocessing, Beckman Dx, Cepheid). Q1 EPS $2.06 beat by 6.2%; bioprocessing inflecting positive after destock; Cepheid respiratory comp resets Q4 2026. | VALUATION: 19.7x forward P/E (trough vs 5yr avg 30x); ROA pos; B/M 0.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Bioprocessing book-to-bill durably &gt;1.0 + China VBP stabilization H2 2026 + Cepheid Q4 reset | VARIANT: Consensus: show-me on growth post-destock. Sundheim/D1: same stock 2019-2021 (30%/yr) at trough multiple while H2 2026 comps inflect.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A10:M10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4772,6 +5257,1826 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>POSITION INTENSITY — % of Fund Book × Dollar Skin × Multi-fund Convergence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>Score = log10($dollar_skin) × 2 + sum_pct/5 + multi_fund_bonus × 1.5; multiplier 1.3x UNDERWATER, 1.15x FLAT, 1.05x MODEST IN MONEY, 0.4x DEEPLY IN MONEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Intensity</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Sum % Book</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Dollar Skin $M</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t># Funds</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>P&amp;L Status</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Funds (concentration / size / cost basis)</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Key Signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>HHH</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>UNDERWATER</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>• Ackman/Pershing Square: 47% of HHH | $1,900M ($900M common + $1B preferred) | cost $100 (-36% UNDERWATER)
+• Northern Right Capital: NEW Q1 2026 +12% | ~$30M est | recent build</t>
+        </is>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>$1.9B Ackman commitment publicly anchored at $100; literal billions of skin at -36% underwater = sponsor PUT floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>FUN</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>62.7%</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>218</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>FLAT/MODEST</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>• H Partners: 53.7% of $154M book (MAX in 13F universe) | $82.5M = 5.7% of FUN class | cost ~$22-30 modest in money
+• Jana Partners: 9% activist push outright sale | $130M est | recent build
+• Travis Kelce co-invest: Sub-1% but signal | $5M | aligned</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>H Partners 53.7% = HIGHEST single-fund concentration of any actionable name; Jana 9% pushing OUTRIGHT SALE; Jaffer board seat May 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>MRP</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>3700</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>FLAT (Lennar paper position)</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>• Lennar Corporation: 80%+ owner (spinoff sponsor) | ~$3.7B at current MRP cap | cost = spin price = FLAT</t>
+        </is>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>Lennar 80% spinoff lock-in = patient capital cannot exit; deepest B/M 1.274 in cohort</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>BNTC</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>44.1%</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>110</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>FLAT/UNDERWATER</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>• Suvretta Capital: 44.1% of BNTC (13D = LARGEST stake by % ownership) | ~$110M | activist anchor</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>Suvretta's LARGEST single stake by % ownership in their entire portfolio</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>AAP</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>81</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>MODEST IN MONEY (~5-15%)</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>• H Partners: 46.3% of $154M book / +50% sh Q1 ADD (1.35M new) | $71.2M | cost ~$45 modest in money
+• Legion Partners (precedent): ~3% | $10M | activist precedent</t>
+        </is>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>H Partners HALF THEIR BOOK + STILL ADDING Q1 (1.35M new sh); 46% concentration extreme</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>KYMR</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>18.7%</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>1179</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>UNDERWATER</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>• BVF Partners (MAX CONVICTION): 14.6% of $3.14B book | $458M | cost $86 follow-on (-7%)
+• Baker Bros: 4.1% of $17.4B book | $721M | cost $86 same follow-on (-7%)</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>$1.18B COMBINED dollar skin from TWO top biotech specialists; BVF #1 MAX conviction</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>INMD</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>25.5%</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>97</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>• Steel Partners: 25.5% of $338M book / +155% Q1 (DOUBLED) | $86M | cost ~$13.50 FLAT
+• Founder Mizrahy: 800k sh Feb 2026 open-market buy | $10.7M | cost $13.71 FLAT</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>Activist + founder BOTH built positions AT CURRENT in 2026; cash $8.47/sh = 62% floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>FRPT</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>39.8%</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>• Marlowe Partners: 39.8% of book (HIGHEST single-fund concentration in universe ex-CVNA) | ~$20M | cost depressed FLAT</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>39.8% concentration = bet-the-fund; manufacturing capacity coming online</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>PRLD</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>25.5%</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>UNDERWATER</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>• Baker Bros: 15.5% of company (13D/A) | ~$8M (small fund weighting) | cost $4.44 April financing (-4%)
+• RA Capital: 9.99% of company (13G) | ~$5M | cost $4.44 SAME financing (-4%)</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>25.5% COMBINED ownership by TWO top biotech crossover funds anchored at SAME $4.44 = below current $4.26 = cannot be sellers</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="150" customHeight="1">
+      <c r="A14" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>NRP</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>• Saber Capital (Huber): 17.75% of book | ~$30M | long-term anchor
+• Robertson Family (insider): 31.75% of company | massive insider | aligned
+• Right Tail Capital: NEW Q1 2026 | ~$15M | cost ~$105 = current FLAT
+• Greystone Capital: Top position | ~$10M | long-term
+• Berkowitz/Fairholme: Anchor | ~$20M | long-term</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>FIVE-fund concentration + insider 31.75% family + Right Tail NEW Q1 at current = freshest entry signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>OPRX</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>14.82%</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>• Insider holders: 14.82% of company | $14M @ $93M cap | aligned
+• Buyback: $10M authorized through March 2027 | $10M | executing at $4-5
+• Presti (Doximity exec): NEW board April 2026 | signal | cost at depressed = current</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>Insider 15% + buyback + Doximity peer exec to board April 2026 at $4-5 = strong corporate-insider signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>PVLA</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>264</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>FLAT to slight in money</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>• BVF Partners: 3.8% of $3.14B book / 8.5% of PVLA company | $120M | cost depressed long
+• Suvretta Capital: 3.67% of book / +29.3% Q1 | $144M | cost +29% Q1 added FLAT</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>$264M dual-anchor BVF + Suvretta; Suvretta +29% Q1 ADD AT current; cash 19% of price floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>CRTO</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>9.37%</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>• D3/Nierenberg: 9.37% of book +19% Q1 | $5M (small fund) | cost ~$11.50-14 FLAT
+• Petrus Advisers: Activist position | ~$20M est | activist anchor
+• Buyback: $200M = 22% cap | $200M corporate | executing at $13-14</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>D3 added 19% Q1 at current band + Petrus activist + 22% buyback = three-source pressure all at current price</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>146</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>• D3 Family Fund (Nierenberg): Position +425% Q1 (LARGEST single add in universe) | $105M+ est post-add | cost ~$30 (built Q1) FLAT
+• Irenic Capital: ~1% activist position | ~$40M | activist anchor
+• Director Form 4: Multiple May 2026 buys | ~$1M+ | at $30-31 confirmed FLAT</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>D3 +425% = SINGLE LARGEST add of any fund in 442-sheet universe; new entrant gets D3 cost basis exactly</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>MGNI</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>13.1%</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>FLAT to modest</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>• Nine Ten Capital (Bares): 13.1% of book / 3.48M sh | $41.4M | cost depressed FLAT</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>Bares-trained Nine Ten 13.1% concentration on independent CTV SSP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>ACHC</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>small % book (~3%)</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>135</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>• Greenlight Capital (Einhorn): 4.1M shares | $135M | cost $30-40 FLAT
+• Sohn pitch 5/12/2026: public surfacing | signal | thesis broadcast at $33</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>Einhorn publicly anchored thesis at Sohn 5/12; -70% drawdown + 29% short float = squeeze</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>CVNA</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>81.7%</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>185</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>DEEPLY IN MONEY (REF)</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>• CAS Investment Partners: 81.7% of book (HIGHEST single-name in 13F universe) | $185M | 20-25x in money ($3-&gt;$71)</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>REFERENCE — CAS legendary 40x recovery; no longer asymmetric</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>29.85%</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>13000</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>DEEPLY IN MONEY (REF)</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>• TCI Fund Management (Hohn): 29.85% of $45B book | $13B | held 2015 deeply in money</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>REFERENCE — TCI captured GE Aerospace breakup; pure compounding</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>AAP CALL</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>N/A (calls)</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>158</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>Calls in money on direction; leverage on H Partners thesis</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>• Cooper Creek Partners: Largest single call exposure | $158M notional | Q1 +213% = recent build at current</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>$158M Cooper Creek calls layered over H Partners $71M cash = $229M two-fund AAP thesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>ASND</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>24.9%</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>2350</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>DEEPLY IN MONEY (REF)</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>• RA Capital: 24.9% of $9.44B book = LARGEST biotech crossover position in universe | $2,350M | held since 2015 deeply in money</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>REFERENCE — RA Capital largest single position in entire biotech crossover universe; multiple normalized</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>CELC</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>19.99%</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>904</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>DEEPLY IN MONEY post-May 1 (REF)</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>• Baker Bros (ACTIVIST 13D): 19.99% of CELC = 5.48% of $17.4B book | $904M | pre-data entry deeply in money</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>REFERENCE — Baker captured May 1 Phase 3 positive; ASCO Jun 2 + PDUFA Jul 17 remaining but pre-quantified</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>MICRO+SMALL CAP INTENSITY — Large Positions in Sub-$2B Names</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>Why this matters: Large concentrated positions in micro/small caps cannot easily exit = forced long-term holder = strong conviction signal. Fund % of COMPANY (vs % of book) is meaningful — at sub-$1B caps, even modest book weightings = high ownership share.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CAP TIER LEGEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>ULTRA-MICRO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>&lt;$300M cap — sub-institutional minimum = any flow violently moves price</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>MICRO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>$300M-$1B cap — institutional but tight float</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>SMALL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>$1B-$2B cap — broader float but concentration still meaningful</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Cap Tier</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Mcap</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Asym Rank</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Fund</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>% Company Owned</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>% Fund Book</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>Dollar Size</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>Cost Basis Status</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>Why Signal Is Stronger Than Mid/Large Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="65" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>ULTRA-MICRO</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>OPRX</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>$93M</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Insider holders + $10M buyback + Presti (Doximity) board</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>14.82% insider + buyback active</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>N/A (insider)</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>$14M insider value</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>FLAT — buyback at $4-5; Presti joined board April 2026 at $4.82</t>
+        </is>
+      </c>
+      <c r="J10" s="15" t="inlineStr">
+        <is>
+          <t>INSIDER 14.82% + corporate buyback + DOXIMITY EXEC (the digital health peer) joined board at depressed = strongest micro insider signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="65" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>ULTRA-MICRO</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>FTLF</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>$93M</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Smoak Capital (residual top-5 position)</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Sub-5% institutional</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>Sub-$5M</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>-43.9% 6mo drawdown; cleanest Yartseva 7/7</t>
+        </is>
+      </c>
+      <c r="J11" s="15" t="inlineStr">
+        <is>
+          <t>Pure Yartseva 7/7 microcap; B/M 0.49 + ROA 7.2% + FCF yield 8.2%; sub-institutional minimum = any institutional flow violently re-rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="65" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>ULTRA-MICRO</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>BNTC</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>$200M</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>Suvretta Capital (13D)</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>44.1% of COMPANY (LARGEST stake by % in Suvretta portfolio)</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>~44% of $250M Suvretta book</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>~$110M</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>Built at sub-$10 levels</t>
+        </is>
+      </c>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>44.1% of company = activist effectively running the show; LARGEST stake by % in Suvretta entire portfolio</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="65" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>ULTRA-MICRO</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>QRHC</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>$200M</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>Wynnefield Capital</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>13.3% (13D w/ board seat)</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>Significant book weighting</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>~$27M</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>Built sub-$7; Cooperation Agreement w/ standstill until 30d before 2027 nom window</t>
+        </is>
+      </c>
+      <c r="J13" s="15" t="inlineStr">
+        <is>
+          <t>13.3% + BOARD SEAT + Cooperation Agreement = formal multi-year lock; sub-$200M cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="65" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>ULTRA-MICRO</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>POSTBPB</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>$240M</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>Nierenberg/D3 Family Fund</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>7%+ (LARGEST single shareholder)</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>~7% of D3 book ($16.4M)</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>$16.4M</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>13D/A active March 2025; Form 4 insider buys ongoing</t>
+        </is>
+      </c>
+      <c r="J14" s="15" t="inlineStr">
+        <is>
+          <t>Nierenberg LARGEST shareholder of PBPB + 7% of D3 book = micro-cap activist soft pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="65" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>MICRO</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>PRLD</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>$340M</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>Baker Bros + RA Capital (DUAL TOP-TIER)</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>25.5% combined (Baker 15.5% + RA Cap 9.99%)</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>Baker small, RA small (both have large books) but 25% of COMPANY</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>$13M combined dollar but anchor at SAME $4.44</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>BOTH at $4.44 April 2026 $90M financing = current $4.26 BELOW entry</t>
+        </is>
+      </c>
+      <c r="J15" s="15" t="inlineStr">
+        <is>
+          <t>TWO top biotech crossover funds = 25.5% of company at SAME $4.44 = locked + below current = pure follow signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="65" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>MICRO</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>INMD</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>$869M</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>Steel Partners (activist) + Mizrahy founder</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>Steel ~10% of co; founder large</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>Steel 25.5% of $338M book</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>$86M + founder $10.7M Feb 2026</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>Steel doubled position Q1; founder bought $10.7M Feb 2026 at $13.71</t>
+        </is>
+      </c>
+      <c r="J16" s="15" t="inlineStr">
+        <is>
+          <t>Activist + founder both at current FLAT; cash $8.47/sh = 62% floor = bounded downside on a micro</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="65" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>MICRO</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>CRTO</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>$866M</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>D3/Nierenberg + Petrus Advisers activist</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>D3 9.37% of book at small cap = meaningful ownership</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>D3 9.37% / +19% Q1</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>$5M D3 + Petrus est $20M</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>D3 +19% Q1 add at $11.50-14 = current FLAT</t>
+        </is>
+      </c>
+      <c r="J17" s="15" t="inlineStr">
+        <is>
+          <t>D3 activist book at micro + Petrus activist + 22% buyback = three forces at current entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="65" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>MICRO</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>MTY.TO</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>C$887M (~$640M USD)</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>CEO Lefebvre (insider)</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>CEO open-market buy at C$30.54</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>CEO personal</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>~$1M+ CEO buy</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>CEO at C$30.54 vs C$40.41 = in money but small position</t>
+        </is>
+      </c>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>CEO open-market buy at trough on micro Canadian QSR franchisor at BOOK valuation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="65" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>MICRO</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>ACMR</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>~$400M</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>Kerrisdale + Steamboat (JOINT LETTER)</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>Joint position</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>Kerrisdale 3.36% of book</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>$8.8M Kerrisdale + Steamboat</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>Joint letter Nov 2025; HK listing $100M offer pursuing</t>
+        </is>
+      </c>
+      <c r="J19" s="15" t="inlineStr">
+        <is>
+          <t>Two-fund joint letter for HK listing value unlock = forced corporate action on micro</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="65" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>SMALL</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>NRP</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>$1.35B</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>Saber + Right Tail + Greystone + Berkowitz + family insider</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Family 31.75% insider; Saber 17.75% of Saber book; Right Tail NEW Q1</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>Saber 17.75% / Right Tail concentrated</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>~$75M multi-fund</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>Right Tail NEW Q1 at ~$105 = current; family aligned forever</t>
+        </is>
+      </c>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>5-fund concentration + 31.75% family insider on a $1.35B royalty trust = strongest anchor stack</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="65" customHeight="1">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>SMALL</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>CARS</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>$560M</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>Insider buying + Yartseva 7/7</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>Insider build at depressed</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>Insider</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>Y7/7 still depressed; Q1 EPS $0.45 vs $0.13 est</t>
+        </is>
+      </c>
+      <c r="J21" s="15" t="inlineStr">
+        <is>
+          <t>$90M buyback = 16% of cap = mechanical float compression + Yartseva 7/7 still depressed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="65" customHeight="1">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>SMALL</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>PVLA</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>$1.56B</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>BVF + Suvretta (DUAL)</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>8.5% (BVF) — large single-fund ownership</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>BVF 3.8% / Suvretta 3.67% (+29.3% Q1)</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>$264M combined</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>Suvretta +29.3% Q1 ADD at $100-140; BVF long anchor</t>
+        </is>
+      </c>
+      <c r="J22" s="15" t="inlineStr">
+        <is>
+          <t>$264M dual-anchor (BVF + Suvretta) at sub-$2B cap = strongest small-cap biotech signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="65" customHeight="1">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>SMALL</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>VITL</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>No major fund yet concentrated</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>&lt;5% institutional</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>Sub-$10M concentration</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>-68.76% drawdown but no anchor has built</t>
+        </is>
+      </c>
+      <c r="J23" s="15" t="inlineStr">
+        <is>
+          <t>CONTRARIAN — no fund has piled in yet; entry preserved BUT no anchor signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="65" customHeight="1">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>SMALL</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>MGNI</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>$1.89B</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>Nine Ten Capital (Bares disciple)</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>~2.3% (3.48M sh)</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>13.1% of $315M Nine Ten book</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>$41.4M</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>Built at depressed CTV SSP prices</t>
+        </is>
+      </c>
+      <c r="J24" s="15" t="inlineStr">
+        <is>
+          <t>Nine Ten 13.1% concentration = Bares-style high-conviction independent CTV SSP winner</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7877,7 +10182,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9057,8 +11362,8 @@
     <mergeCell ref="A22:M22"/>
     <mergeCell ref="A35:M35"/>
     <mergeCell ref="A20:M20"/>
+    <mergeCell ref="A38:M38"/>
     <mergeCell ref="A43:M43"/>
-    <mergeCell ref="A38:M38"/>
     <mergeCell ref="A52:M52"/>
     <mergeCell ref="A10:M10"/>
     <mergeCell ref="A28:M28"/>
@@ -9096,7 +11401,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9720,7 +12025,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10342,487 +12647,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>4. Sponsor-Anchored Holdco Transformation — ENTRY-TODAY × TAILWIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Definition: Activist or family-office anchor with significant ownership AND cost-basis floor that creates sponsor put. Holdco transformation thesis (insurance float, multi-asset compounding).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Within-Rank</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Master-Rank</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Re-rate</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Tailwind</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Mcap</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>Asym</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>Upside</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>R/R</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>Smart Money</t>
-        </is>
-      </c>
-      <c r="M4" s="13" t="inlineStr">
-        <is>
-          <t>Secular Driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D5" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>HHH</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Howard Hughes Holdings</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>$3.5B</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>$63.77</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1.5-2x to NAV</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>13:1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Ackman 47% via $900M @ $100/sh + $1B preferred; Northern Right NEW Q1 +12%</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Sun Belt migration MPC (3,813 acres TX/NV/HI) + Ackman compounding holdco; NAV captures some but Vantage insurance float thesis not yet integrated</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: NAV $95-105 vs $63.77 = 33-39% DISCOUNT to real (not aspirational) NAV. Ackman 47% at $100 cost = sponsor PUT floor. Vantage close Q2 (30-45d) = dated trigger. Insurance float makes compounding violent post-close.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Ackman-led 'Modern Berkshire'. 3,813 acres residential MPC ($4.8B NAV) + 2,447 acres commercial ($2.0B) + Vantage specialty insurance ($2.2B 2027 premium). Marc Grandisson (ex-Arch Capital CEO) on board April 2026. | VALUATION: NAV $95-105/sh = 33-39% discount; $1.84B cash + $515M revolver liquidity</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Vantage close Q2 2026 (30-45 days); Park Ward Village condo closings Q2-Q3 (~$1B rev); first post-Vantage capital allocation | VARIANT: Street: sub-scale RE dev with leverage. Ackman: insurance float + permanent capital. NAV $95-105 vs $63 = 50-67% margin of safety.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="A2:M2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>5. Spinoff / SoTP Arbitrage — ENTRY-TODAY × TAILWIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Definition: Sum-of-parts valuation discount with defined corporate action (spin-off, divestiture, breakup) as catalyst.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Within-Rank</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Master-Rank</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Re-rate</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Tailwind</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Mcap</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>Asym</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>Upside</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>R/R</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>Smart Money</t>
-        </is>
-      </c>
-      <c r="M4" s="13" t="inlineStr">
-        <is>
-          <t>Secular Driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>KBR</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>KBR Inc</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>$3.9B</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>$30</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2-2.5x ($55-65 SoTP)</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>10:1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>D3/Nierenberg +425% Q1 (largest single add in entire universe); Irenic activist ~1%; Director Form 4 buys May 2026</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Triple secular: (1) US defense spend onshoring, (2) NRC small modular reactor / Natrium nuclear, (3) cleared workforce moat 20k; HomeSafe distraction masks underlying secular bookings</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: SoTP MTS $5.2B EV + STS $5.3B = $55-65 vs $30 today. MTS SPIN JAN 4 2027 = dated trigger 7 months out. D3 +425% Q1 (LARGEST single add in entire universe). Director Form 4 buys May 2026 = sponsor put.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Two segments: MTS (gov services 72%, $18.5B backlog, cleared workforce 20k) + STS (process tech + TerraPower Natrium nuclear EPC alliance, 22% EBITDA margin). FY26 $980M-1.04B EBITDA, $3.87-4.22 EPS. | VALUATION: SoTP: MTS at 11x EBITDA ($5.2B EV) + STS at 14x ($5.3B) = $55-65/sh combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: MTS spin January 4 2027 (board-approved Sept 2025); NRC Natrium safety eval mid-2026 | VARIANT: Market: broken post-HomeSafe termination + class action overhang. Variant: HomeSafe disposed; spin unlocks SoTP value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" t="n">
-        <v>29</v>
-      </c>
-      <c r="C9" s="31" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t>DLTR</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Dollar Tree</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>$25B</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>$80</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2-3x</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>9:1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Multi-fund deep-value funds Q1 2026 adds</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Consumer trade-down secular but already multi-fund consensus</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: B/M 0.20 Yartseva 6/7 + Family Dollar divestiture proceeds = $1B+ cash bolster. Post-divest clean Dollar Tree franchise. Multi-fund deep-value consensus already established = partial discount captured.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Post-divestiture clean Dollar Tree franchise (16k+ stores). Multi-fund deep-value consensus Q1 2026. Mayer M6 turnaround pattern. | VALUATION: B/M 0.20 (Yartseva 6/7); Family Dollar divestiture proceeds = $1B+ cash bolster</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Family Dollar sale completion + comparable sales recovery + multiple re-rate | VARIANT: Market priced Family Dollar mistake. Smart money: post-divestiture clean franchise.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A10:M10"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/investment_archetypes.xlsx
+++ b/investment_archetypes.xlsx
@@ -12,17 +12,18 @@
     <sheet name="MAX Skin + Recent Entry" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="POSITION INTENSITY" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="MICRO+SMALL CAP INTENSITY" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="MASTER Entry-Today" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="1. Yartseva Pure Multibagger" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="2. Activist Board Catalyst" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="3. Biotech Multi-Fund Convergen" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="4. Sponsor-Anchored Holdco Tran" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="5. Spinoff - SoTP Arbitrage" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="6. Deep Drawdown Mean Reversion" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="7. Hard Asset - Royalty" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="8. Foreign - Underfollowed Valu" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="9. Quality Compounder at Trough" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="10. Hedged - Special Structure" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="AGGRESSIVE BUY SIGNALS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MASTER Entry-Today" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="1. Yartseva Pure Multibagger" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="2. Activist Board Catalyst" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="3. Biotech Multi-Fund Convergen" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="4. Sponsor-Anchored Holdco Tran" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="5. Spinoff - SoTP Arbitrage" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="6. Deep Drawdown Mean Reversion" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="7. Hard Asset - Royalty" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="8. Foreign - Underfollowed Valu" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="9. Quality Compounder at Trough" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="10. Hedged - Special Structure" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -72,7 +73,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -133,6 +134,12 @@
         <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+        <bgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -146,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -215,6 +222,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -937,6 +948,630 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence — ENTRY-TODAY × TAILWIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Definition: Two or more top biotech crossover specialists (Baker Bros, RA Capital, BVF, Stonepine, Suvretta) anchored at high conviction in same name. Convergence is the high-signal pattern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Within-Rank</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Master-Rank</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Re-rate</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Tailwind</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Mcap</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Asym</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Smart Money</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>Secular Driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>PRLD</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Prelude Therapeutics</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>$340M</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>$4.26</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3-8x</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>20:1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Baker Bros 15.5% 13D/A + RA Capital 9.99% 13G; BOTH anchored SAME $90M April financing at $4.44</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Targeted protein degradation platform structural pharma shift + JAK2V617F addresses 95% PV/60% ET/55% MF (aging demographic, no oral comp); SMARCA2 fail = thrown out with platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: NET CASH $2.20/sh = 51% of $4.26 price = downside FLOORED. Baker Bros 15.5% 13D + RA Capital 9.99% 13G BOTH anchored SAME April $90M financing at $4.44 — buying TODAY $4.26 is BELOW smart money entry. JAK2 binary upside 5-10x.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Precision oncology / molecular glue / degrader platform. SMARCA2 discontinued 2025; pivot to JAK2V617F (PRT12396) + KAT6A (PRT13722). AbCellera partnership. | VALUATION: $175M cash vs $340M mcap = $2.20/sh net cash (51% of price); buyout floor near current</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: PRT12396 Phase 1 H2 2026; PRT13722 IND mid-2026; Incyte option agreement Nov 2025 | VARIANT: Market: broken story post-SMARCA2 fail. Smart money: April 2026 refunding = platform-validation thesis. JAK2 mutant-selective addresses 95% PV/60% ET/55% MF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>17</v>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>PVLA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Palvella Therapeutics</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>$1.56B</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>$130</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2-3x</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>10:1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>BVF 3.8% / $120M (8.5% of company) + Suvretta 3.67% / $144M (+29.3% Q1)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Rare-disease pricing structural ($300k+ orphan); QTORIN platform with multiple programs (LMs, venous malformations, angiokeratomas); market priced single-asset story</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Cash $25/sh = 19% of $130 price. Phase 3 SELVA POSITIVE Feb 24 2026 = DE-RISKED. Pre-NDA Q2 + NDA H2 + PDUFA H1 2027 = staircase of catalysts. BVF 8.5% of company + Suvretta 3.67% (+29.3% Q1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Rare-disease topical platform. QTORIN rapamycin gel for microcystic LMs (Breakthrough + Orphan + Fast Track). Phase 3 SELVA POSITIVE Feb 24 2026 (mLM-IGA +2.13, p&lt;0.001). | VALUATION: $261.9M cash = $25/sh (19% of price). Phase 3 derisked. M&amp;A floor 4-6x peak rev</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Pre-NDA FDA meeting Q2 2026; NDA H2 2026; PDUFA H1 2027 | VARIANT: Market: single-asset rare-disease (~$1.5B). Smart money: platform with &gt;$1B peak QTORIN + venous malformations/angiokeratomas/pitavastatin programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>18</v>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>KYMR</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kymera Therapeutics</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>$6.5B</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>$80</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3-5x</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>13:1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>BVF #1 position 14.6% of $3.14B book ($458M) + Baker Bros 4.1% / $721M; BOTH anchored $86 follow-on</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Oral biologic disruption (oral Dupixent = $14B+ franchise displacement); TPD structural pharma platform shift; Phase 1b execution risk masks platform value</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Cash $1.55B + BVF 14.6% MAX conviction + Baker 4.1% = multi-fund convergence. BUT major catalyst BROADEN2 mid-2027 = 12+ months away (low velocity). Strong setup, slow trigger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Targeted protein degradation platform. Lead KT-621 oral STAT6 degrader competes with injectable Dupixent ($14B+ franchise). IRAK4 partnered with Sanofi. | VALUATION: $1.55B cash (runway 2029); Dec 2025 follow-on $602M at $86</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: BROADEN2 AD mid-2027 (12+ months); BREADTH asthma late 2027; FDA Fast Track granted both | VARIANT: Market: Phase 1b execution risk. Two top biotech specialists: oral Dupixent-disruptor with peak $5-10B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="n">
+        <v>28</v>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>BNTC</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Benitec Biopharma</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>$200M</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>$8</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3-5x</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7:1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Suvretta 44.1% 13D (Suvretta's LARGEST stake by % ownership)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Gene therapy speculative single platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Suvretta 44.1% 13D = LARGEST stake by %. Gene therapy platform. Multi-program optionality. Higher risk than other biotech-multi-fund names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Gene therapy platform anchor position. Suvretta 44.1% 13D anchor stake (largest activist ownership in their portfolio). PIPE participation Nov 2025. | VALUATION: Sub-$300M biotech; gene therapy platform optionality</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Multiple gene-therapy programs in development; clinical readouts upcoming | VARIANT: 44.1% ownership creates board influence + asymmetric upside on clinical reads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" t="n">
+        <v>37</v>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>RERATED</t>
+        </is>
+      </c>
+      <c r="D21" s="34" t="inlineStr">
+        <is>
+          <t>PRICED</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>CELC</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Celcuity</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>$8B (post-data)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>$165</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1.3-2x post-data</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Baker Bros 19.99% ACTIVIST 13D = $904M / 5.48% of $17.4B book</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Targeted oncology secular but Phase 3 data + PT raises captured the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Phase 3 May 1 POSITIVE + +76% PT raises already in price. ASCO Jun 2 + PDUFA Jul 17 remain but pre-quantified. Quality+catalysts but entry economics weakened post-data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Phase 3 VIKTORIA-1 PIK3CA-mut POSITIVE May 1 2026 (76% PFS hazard reduction). Gedatolisib pan-PI3K/mTOR oncology. Triplet vs alpelisib+fulvestrant. Multiple HR+/HER2- breast cancer cohorts. | VALUATION: $387M cash + accepted NDA + Priority Review = de-risked; 4-5x peak rev precedent</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: JUNE 2 ASCO LBA1008 oral + JULY 17 PDUFA goal date (2 catalysts in 8 weeks) | VARIANT: Market: alpelisib-class peak ($1-2B). Baker Bros 19.99% 13D activist: $5-10B peak (triplet displaces alpelisib + captures WT segment).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>40</v>
+      </c>
+      <c r="C25" s="33" t="inlineStr">
+        <is>
+          <t>RERATED</t>
+        </is>
+      </c>
+      <c r="D25" s="34" t="inlineStr">
+        <is>
+          <t>PRICED</t>
+        </is>
+      </c>
+      <c r="E25" s="28" t="inlineStr">
+        <is>
+          <t>ASND</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ascendis Pharma</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>$15.3B</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>$247</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1.2-1.5x</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>RA Capital 24.9% of $9.44B = $2.35B = LARGEST single biotech crossover position; held since 2015</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Rare endocrine pricing secular but YORVIPATH ramp captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: YORVIPATH ramp priced. €247M Q1 (2x YoY) already at $247. Multiple normalized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: TransCon prodrug platform: SKYTROFA (GHD), YORVIPATH (hypopara), YUVIWEL (achondroplasia approved Feb 2026). &gt;1,000 new US YORVIPATH enrollments Q1; 6,300+ patients across 2,700 prescribers. | VALUATION: Profitable (22% non-IFRS op margin); €247M Q1 (2x YoY); peak rev YORVIPATH $4-5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: YUVIWEL ramp + Q2/Q3 YORVIPATH growth + TransCon CNP follow-on indications | VARIANT: Sell-side: $15B endocrine specialty maturing. RA Capital: $30B+ at 70-90K addressable hypopara population. Analyst high $345 (Barclays).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A23:M23"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A20:M20"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A28:M28"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A24:M24"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A27:M27"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A26:M26"/>
+    <mergeCell ref="A2:M2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1130,7 +1765,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1414,7 +2049,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1859,375 +2494,6 @@
     <mergeCell ref="A15:M15"/>
     <mergeCell ref="A7:M7"/>
     <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A10:M10"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>7. Hard Asset / Royalty — ENTRY-TODAY × TAILWIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Definition: Irreplaceable asset ownership (royalty, land, minerals) with no recurring capex requirement and cash-flow distribution structure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Within-Rank</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Master-Rank</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Re-rate</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Tailwind</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Mcap</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>Asym</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>Upside</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>R/R</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>Smart Money</t>
-        </is>
-      </c>
-      <c r="M4" s="13" t="inlineStr">
-        <is>
-          <t>Secular Driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>NRP</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Natural Resource Partners</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>$1.35B</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>$105.81</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2.5-3x</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>13:1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Saber 17.75% + Greystone top + Right Tail NEW + Berkowitz</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Met coal (no green substitute for steelmaking) + Sisecam soda ash (solar glass + EV battery) = TWO structural tailwinds masked by dying-thermal-coal narrative; 6.6x vs TPL 25x is a TRUE comp gap</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: 14.5% FCF yield ALONE = pure mispricing. Royalty trust at 6.6x P/FCF vs TPL at 25x P/CF (SAME asset class) = comp gap re-rate. Distribution Nov 2026 + preferreds retire. Saber 17.75% + Right Tail NEW Q1 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: [See Archetype 1] | VALUATION: [See Archetype 1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Nov 2026 distribution + preferreds retire | VARIANT: [See Archetype 1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" t="n">
-        <v>24</v>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t>JOE</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>St. Joe Company</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>$2.8B</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>$48</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2-3x to LIFO-NAV</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>10:1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Berkowitz/Fairholme longstanding anchor</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Florida population growth secular but slow re-rate; Berkowitz anchor recognized</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: 170k Florida Panhandle acres. GAAP B/M understates LIFO land basis vs market. True NAV-based B/M likely &gt;1.0. Berkowitz anchor + Florida population growth.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Florida Panhandle landbank with 170k+ acres. GAAP B/M understates LIFO land basis vs market value. True NAV-based B/M likely &gt;1.0 even at current price. | VALUATION: Land bank: 170k acres NW Florida; GAAP B/M understates LIFO land basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Florida population growth + master plan community development + Berkowitz anchor | VARIANT: Yartseva fails on size + low GAAP B/M; correct framework is Lynch asset play.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" t="n">
-        <v>34</v>
-      </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="D13" s="34" t="inlineStr">
-        <is>
-          <t>PRICED</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="inlineStr">
-        <is>
-          <t>TPL</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Texas Pacific Land Trust</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>$30B</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>$1300</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>1.3-1.5x</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>5:1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Multi-fund quality holders; HRC anchor</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Permian premium already at 25x P/CF; secular real but no asymmetry from here</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: Already at 25x P/CF premium = ENDLESS DRILLING priced. NAV-vs-GAAP issue similar to JOE but multiple no longer cheap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Permian water + royalty optionality. Same NAV-vs-GAAP-book issue as JOE. Pricing 'endless drilling' premium. | VALUATION: Permian royalty trust at 25x P/CF (vs NRP at 6x)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Permian production growth + water revenue optionality | VARIANT: Yartseva captures FCF yield + ROA but understates B/M for land assets.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="A7:M7"/>
     <mergeCell ref="A16:M16"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A11:M11"/>
@@ -2264,14 +2530,14 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>8. Foreign / Underfollowed Value — ENTRY-TODAY × TAILWIND</t>
+          <t>7. Hard Asset / Royalty — ENTRY-TODAY × TAILWIND</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Definition: Listed outside primary US market or in segment poorly covered by US sell-side. Currency arbitrage + institutional underweight = entry edge.</t>
+          <t>Definition: Irreplaceable asset ownership (royalty, land, minerals) with no recurring capex requirement and cash-flow distribution structure.</t>
         </is>
       </c>
     </row>
@@ -2347,44 +2613,44 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>MTY.TO</t>
+          <t>NRP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MTY Food Group</t>
+          <t>Natural Resource Partners</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C$887M</t>
+          <t>$1.35B</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>C$40.41</t>
+          <t>$105.81</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2-2.5x</t>
+          <t>2.5-3x</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2394,19 +2660,19 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CEO open-market buy</t>
+          <t>Saber 17.75% + Greystone top + Right Tail NEW + Berkowitz</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>QSR franchise consolidation secular (Inspire/RBI/Roark precedent) recognized but multiple at trough</t>
+          <t>Met coal (no green substitute for steelmaking) + Sisecam soda ash (solar glass + EV battery) = TWO structural tailwinds masked by dying-thermal-coal narrative; 6.6x vs TPL 25x is a TRUE comp gap</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: AT BOOK 1.04x + 16.7% FCF yield = pure value. M&amp;A pool at 12-14x EBITDA vs trading 7.5x = M&amp;A precedent arb. CEO Lefebvre open-market buy at C$30.54 = sponsor put. QSR consolidation trend.</t>
+          <t>ENTRY-TODAY: 14.5% FCF yield ALONE = pure mispricing. Royalty trust at 6.6x P/FCF vs TPL at 25x P/CF (SAME asset class) = comp gap re-rate. Distribution Nov 2026 + preferreds retire. Saber 17.75% + Right Tail NEW Q1 2026.</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2686,7 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Q2 2026 SSS test + NCIB | VARIANT: [See Archetype 1]</t>
+          <t>CATALYST: Nov 2026 distribution + preferreds retire | VARIANT: [See Archetype 1]</t>
         </is>
       </c>
     </row>
@@ -2429,80 +2695,80 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>BZU.IM</t>
+          <t>JOE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buzzi SpA</t>
+          <t>St. Joe Company</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>€8.9B</t>
+          <t>$2.8B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>€49</t>
+          <t>$48</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.7-2x (Kerrisdale €85 PT)</t>
+          <t>2-3x to LIFO-NAV</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>10:1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Kerrisdale Capital published long thesis Oct 2025 (€85 PT)</t>
+          <t>Berkowitz/Fairholme longstanding anchor</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>AI data-center concrete demand (US data-center capex translates to cement orders); 52% EBITDA from US; institutional underweight on Italian listing</t>
+          <t>Florida population growth secular but slow re-rate; Berkowitz anchor recognized</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: 6.8x EV/EBITDA vs peers 9-11x. AI data-center concrete demand = real (not theoretical). 52% EBITDA from US. Kerrisdale Oct 2025 €85 PT (+73%). Italian listing = institutional underweight = re-rate slow but explicit.</t>
+          <t>ENTRY-TODAY: 170k Florida Panhandle acres. GAAP B/M understates LIFO land basis vs market. True NAV-based B/M likely &gt;1.0. Berkowitz anchor + Florida population growth.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Italian cement (€8.9B mcap). 52% of EBITDA from US. AI data-center concrete demand thesis. Trading at sector-discount multiple to LafargeHolcim/CRH peers. | VALUATION: 6.8x EV/EBITDA (vs peer 9-11x); €85 PT = +73% upside</t>
+          <t>THESIS: Florida Panhandle landbank with 170k+ acres. GAAP B/M understates LIFO land basis vs market value. True NAV-based B/M likely &gt;1.0 even at current price. | VALUATION: Land bank: 170k acres NW Florida; GAAP B/M understates LIFO land basis</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: AI data-center capex translating to concrete orders; multiple re-rate to peer levels | VARIANT: Italian listing + cement = institutional underweight. Kerrisdale Oct 2025 long thesis 73% upside.</t>
+          <t>CATALYST: Florida population growth + master plan community development + Berkowitz anchor | VARIANT: Yartseva fails on size + low GAAP B/M; correct framework is Lynch asset play.</t>
         </is>
       </c>
     </row>
@@ -2511,80 +2777,80 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D13" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
+        <v>34</v>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>PRICED</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Texas Pacific Land Trust</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$1.89B</t>
+          <t>$30B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$13</t>
+          <t>$1300</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>1.3-1.5x</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>12:1</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Nine Ten Capital (Bares) 13.1% of book / 3.48M sh / $41.4M</t>
+          <t>Multi-fund quality holders; HRC anchor</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>CTV ad spend doubling 2024-2028 (eMarketer); INDEPENDENT SSP that survived ad-tech wash-out = winner-take-most; Netflix/Disney/Roku exclusive deals scaling; market priced "ad-tech roadkill"</t>
+          <t>Permian premium already at 25x P/CF; secular real but no asymmetry from here</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Independent CTV SSP = winner of ad-tech wash-out. Netflix/Disney/Roku scaling. AI integration. Nine Ten 13.1% / 3.48M sh = highest concentration.</t>
+          <t>ENTRY-TODAY: Already at 25x P/CF premium = ENDLESS DRILLING priced. NAV-vs-GAAP issue similar to JOE but multiple no longer cheap.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Independent CTV SSP. Netflix/Disney/Roku exclusive deals scaling. AI ad-buying integration. Last major non-Google scaled SSP. | VALUATION: Yartseva 6/7 (sub-$2B), B/M 0.49, FCF yield positive, ROA positive</t>
+          <t>THESIS: Permian water + royalty optionality. Same NAV-vs-GAAP-book issue as JOE. Pricing 'endless drilling' premium. | VALUATION: Permian royalty trust at 25x P/CF (vs NRP at 6x)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: CTV ad spend doubling 2024-2028 + Netflix exclusive scaling + AI integration | VARIANT: Market: ad-tech roadkill. Smart: winning independent CTV SSP that survived ad-tech wash-out.</t>
+          <t>CATALYST: Permian production growth + water revenue optionality | VARIANT: Yartseva captures FCF yield + ROA but understates B/M for land assets.</t>
         </is>
       </c>
     </row>
@@ -2633,14 +2899,14 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>9. Quality Compounder at Trough — ENTRY-TODAY × TAILWIND</t>
+          <t>8. Foreign / Underfollowed Value — ENTRY-TODAY × TAILWIND</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Definition: Defensive quality business at multi-year low multiple due to transitory headwind. Re-rate when consensus catches up to recovery.</t>
+          <t>Definition: Listed outside primary US market or in segment poorly covered by US sell-side. Currency arbitrage + institutional underweight = entry edge.</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2982,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
@@ -2730,66 +2996,66 @@
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>MTY.TO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>MTY Food Group</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>$25B</t>
+          <t>C$887M</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$52.75</t>
+          <t>C$40.41</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>2-2.5x</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>12:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Multi-fund deep-value funds Q1 2026</t>
+          <t>CEO open-market buy</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>IT services AI accelerator (vs disruptor) debate; partial market acceptance</t>
+          <t>QSR franchise consolidation secular (Inspire/RBI/Roark precedent) recognized but multiple at trough</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Yartseva 6/7 + 9.88% FCF yield + ROA 10.44% + -27% 6mo. AI accelerator-not-disruptor thesis. Defensive value vs deep-value pure play.</t>
+          <t>ENTRY-TODAY: AT BOOK 1.04x + 16.7% FCF yield = pure value. M&amp;A pool at 12-14x EBITDA vs trading 7.5x = M&amp;A precedent arb. CEO Lefebvre open-market buy at C$30.54 = sponsor put. QSR consolidation trend.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Yartseva 6/7 IT services franchise. Multi-fund consensus Q1 2026. 300k+ delivery workforce moat. AI/IT services capex super-cycle 2026-2028. | VALUATION: P/B 1.66 (B/M 0.60), 9.88% FCF yield, ROA 10.44%, -27% 6mo</t>
+          <t>THESIS: [See Archetype 1] | VALUATION: [See Archetype 1]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: AI implementation winner via enterprise partners + Q2 2026 earnings | VARIANT: Market: AI disrupts IT services. Smart: AI accelerator not disruptor.</t>
+          <t>CATALYST: Q2 2026 SSS test + NCIB | VARIANT: [See Archetype 1]</t>
         </is>
       </c>
     </row>
@@ -2798,44 +3064,44 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
-      </c>
-      <c r="C9" s="31" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+        <v>22</v>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>BZU.IM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>Buzzi SpA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$65B</t>
+          <t>€8.9B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$638</t>
+          <t>€49</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.5-2x</t>
+          <t>1.7-2x (Kerrisdale €85 PT)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2845,33 +3111,33 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Founder-led; multi-fund pharma specialist holds</t>
+          <t>Kerrisdale Capital published long thesis Oct 2025 (€85 PT)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Aging demographic + ophthalmology + immunology pipeline partially priced</t>
+          <t>AI data-center concrete demand (US data-center capex translates to cement orders); 52% EBITDA from US; institutional underweight on Italian listing</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Defensive quality. Pipeline optionality. Partial trough recovery underway.</t>
+          <t>ENTRY-TODAY: 6.8x EV/EBITDA vs peers 9-11x. AI data-center concrete demand = real (not theoretical). 52% EBITDA from US. Kerrisdale Oct 2025 €85 PT (+73%). Italian listing = institutional underweight = re-rate slow but explicit.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Founder/CEO Schleifer + Yancopoulos R&amp;D-led. $31.4B book equity + EYLEA franchise + Linvoseltamab launching. Pipeline broad. Itepekimab Phase 3 readout potential catalyst. | VALUATION: B/M 0.48, FCF yield 6.33%, P/B 2.07; Yartseva 6/7 (size only fail)</t>
+          <t>THESIS: Italian cement (€8.9B mcap). 52% of EBITDA from US. AI data-center concrete demand thesis. Trading at sector-discount multiple to LafargeHolcim/CRH peers. | VALUATION: 6.8x EV/EBITDA (vs peer 9-11x); €85 PT = +73% upside</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Itepekimab 2026-2027 data + Linvoseltamab ramp | VARIANT: Market: fianlimab miss + Eylea biosimilar. Smart: broad pipeline + buyback + founder skin.</t>
+          <t>CATALYST: AI data-center capex translating to concrete orders; multiple re-rate to peer levels | VARIANT: Italian listing + cement = institutional underweight. Kerrisdale Oct 2025 long thesis 73% upside.</t>
         </is>
       </c>
     </row>
@@ -2880,80 +3146,80 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>41</v>
-      </c>
-      <c r="C13" s="33" t="inlineStr">
-        <is>
-          <t>RERATED</t>
-        </is>
-      </c>
-      <c r="D13" s="34" t="inlineStr">
-        <is>
-          <t>PRICED</t>
+        <v>25</v>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Danaher</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$122B</t>
+          <t>$1.89B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$171</t>
+          <t>$13</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.3-1.5x</t>
+          <t>3-5x</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>12:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>D1 Capital +312% Q1 ($107M→$437M, 4th-largest position)</t>
+          <t>Nine Ten Capital (Bares) 13.1% of book / 3.48M sh / $41.4M</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Bioprocessing cycle now consensus 2H 2026</t>
+          <t>CTV ad spend doubling 2024-2028 (eMarketer); INDEPENDENT SSP that survived ad-tech wash-out = winner-take-most; Netflix/Disney/Roku exclusive deals scaling; market priced "ad-tech roadkill"</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Bouncing from trough; bioprocessing cycle now consensus; multiple expansion captured. Defensive 2H 2026 fully priced.</t>
+          <t>ENTRY-TODAY: Independent CTV SSP = winner of ad-tech wash-out. Netflix/Disney/Roku scaling. AI integration. Nine Ten 13.1% / 3.48M sh = highest concentration.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Pure-play life sciences (Cytiva bioprocessing, Beckman Dx, Cepheid). Q1 EPS $2.06 beat by 6.2%; bioprocessing inflecting positive after destock; Cepheid respiratory comp resets Q4 2026. | VALUATION: 19.7x forward P/E (trough vs 5yr avg 30x); ROA pos; B/M 0.43</t>
+          <t>THESIS: Independent CTV SSP. Netflix/Disney/Roku exclusive deals scaling. AI ad-buying integration. Last major non-Google scaled SSP. | VALUATION: Yartseva 6/7 (sub-$2B), B/M 0.49, FCF yield positive, ROA positive</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Bioprocessing book-to-bill durably &gt;1.0 + China VBP stabilization H2 2026 + Cepheid Q4 reset | VARIANT: Consensus: show-me on growth post-destock. Sundheim/D1: same stock 2019-2021 (30%/yr) at trough multiple while H2 2026 comps inflect.</t>
+          <t>CATALYST: CTV ad spend doubling 2024-2028 + Netflix exclusive scaling + AI integration | VARIANT: Market: ad-tech roadkill. Smart: winning independent CTV SSP that survived ad-tech wash-out.</t>
         </is>
       </c>
     </row>
@@ -2976,6 +3242,375 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>9. Quality Compounder at Trough — ENTRY-TODAY × TAILWIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Definition: Defensive quality business at multi-year low multiple due to transitory headwind. Re-rate when consensus catches up to recovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Within-Rank</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Master-Rank</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Re-rate</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Tailwind</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Mcap</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Asym</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Smart Money</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>Secular Driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>$25B</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>$52.75</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2-3x</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>12:1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Multi-fund deep-value funds Q1 2026</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>IT services AI accelerator (vs disruptor) debate; partial market acceptance</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Yartseva 6/7 + 9.88% FCF yield + ROA 10.44% + -27% 6mo. AI accelerator-not-disruptor thesis. Defensive value vs deep-value pure play.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Yartseva 6/7 IT services franchise. Multi-fund consensus Q1 2026. 300k+ delivery workforce moat. AI/IT services capex super-cycle 2026-2028. | VALUATION: P/B 1.66 (B/M 0.60), 9.88% FCF yield, ROA 10.44%, -27% 6mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: AI implementation winner via enterprise partners + Q2 2026 earnings | VARIANT: Market: AI disrupts IT services. Smart: AI accelerator not disruptor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>35</v>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Regeneron</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>$65B</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>$638</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1.5-2x</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>8:1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Founder-led; multi-fund pharma specialist holds</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Aging demographic + ophthalmology + immunology pipeline partially priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Defensive quality. Pipeline optionality. Partial trough recovery underway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Founder/CEO Schleifer + Yancopoulos R&amp;D-led. $31.4B book equity + EYLEA franchise + Linvoseltamab launching. Pipeline broad. Itepekimab Phase 3 readout potential catalyst. | VALUATION: B/M 0.48, FCF yield 6.33%, P/B 2.07; Yartseva 6/7 (size only fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Itepekimab 2026-2027 data + Linvoseltamab ramp | VARIANT: Market: fianlimab miss + Eylea biosimilar. Smart: broad pipeline + buyback + founder skin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>41</v>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>RERATED</t>
+        </is>
+      </c>
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>PRICED</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>DHR</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Danaher</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>$122B</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>$171</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1.3-1.5x</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>D1 Capital +312% Q1 ($107M→$437M, 4th-largest position)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Bioprocessing cycle now consensus 2H 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Bouncing from trough; bioprocessing cycle now consensus; multiple expansion captured. Defensive 2H 2026 fully priced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Pure-play life sciences (Cytiva bioprocessing, Beckman Dx, Cepheid). Q1 EPS $2.06 beat by 6.2%; bioprocessing inflecting positive after destock; Cepheid respiratory comp resets Q4 2026. | VALUATION: 19.7x forward P/E (trough vs 5yr avg 30x); ROA pos; B/M 0.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Bioprocessing book-to-bill durably &gt;1.0 + China VBP stabilization H2 2026 + Cepheid Q4 reset | VARIANT: Consensus: show-me on growth post-destock. Sundheim/D1: same stock 2019-2021 (30%/yr) at trough multiple while H2 2026 comps inflect.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A10:M10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7077,6 +7712,1858 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>AGGRESSIVE BUY SIGNALS — Insider + Multi-Fund Accumulation Across 442 Tabs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>Cross-referenced from: Conviction Adds (multi-fund accumulation), Activist Catalysts (13D/13G threshold filings), All Activity scan (Form 4, founder buys, family fund 13D escalation). Names with all three signals = TIER 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TIER LEGEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>TIER 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Multi-fund ADDS + activist 13D + insider signal (TRIPLE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>TIER 2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Activist + Form 4 / founder open-market buys (typically micro/small)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>TIER 3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Multi-fund aggressive adds + activist threshold (no documented insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="inlineStr">
+        <is>
+          <t>TIER 4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Strong single-fund + insider/buyback</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>TIER 5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Multi-fund adds (no activist or insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Mcap</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Asym Rank</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>TS+</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Fund Adds (multi-fund accumulation)</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>Activist 13D/13G</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>Insider / Form 4 / Founder Buys</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>Why Aggressive</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="75" customHeight="1">
+      <c r="A12" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>INMD</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>InMode Ltd</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>$869M</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>NO (cyclical aesthetics)</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>Steel Partners +155% Q1 2026 = doubled position (25.5% of $338M Steel book)</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>Steel Partners activist anchor; prior $18 takeout</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>Founder Mizrahy bought 800,000 sh ($10.7M) Feb 2026 OPEN-MARKET at $13.50</t>
+        </is>
+      </c>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>Activist + founder BOTH at current FLAT; cash $8.47/sh = 62% floor; M&amp;A optionality</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="75" customHeight="1">
+      <c r="A13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>HHH</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Howard Hughes Holdings</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>$3.5B</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>NO (partial tailwind)</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>Pershing 47.74% / $900M + JCP $14.45M NEW (2 funds, $914.5M sum)</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>13D Pershing (47% via $900M + $1B preferred)</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>Marc Grandisson (ex-Arch Capital CEO) joined board April 2026 = ex-insurance CEO insider hire signal</t>
+        </is>
+      </c>
+      <c r="J13" s="15" t="inlineStr">
+        <is>
+          <t>$914.5M total fund buying + Ackman $1.9B commitment underwater + insurance CEO hire = bet-the-Berkshire-thesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="75" customHeight="1">
+      <c r="A14" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>MRP</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Millrose Properties</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>$4.59B</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>YES (US housing supply unpriced)</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>Brave Warrior (Greenberg) +59.99% Q1 + Permian Investment Partners (2 funds)</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>Lennar 80%+ owner = sponsor lock</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>Lennar 80% parent stake = effective insider commitment</t>
+        </is>
+      </c>
+      <c r="J14" s="15" t="inlineStr">
+        <is>
+          <t>Greenberg +60% Q1 + Lennar 80% locked + B/M 1.274 deepest in cohort</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="75" customHeight="1">
+      <c r="A15" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>KBR Inc</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>$3.9B</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>D3/Nierenberg +425% Q1 = LARGEST single add in 442-sheet universe; Irenic activist ~1%</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>Irenic activist position + spin board-approved Sept 2025</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>Director Form 4 buys May 2026 at $30-31 (multiple insiders)</t>
+        </is>
+      </c>
+      <c r="J15" s="15" t="inlineStr">
+        <is>
+          <t>D3 quintupled position in Q1 + directors buying May 2026 at $30 = sponsor put at current; spin Jan 4 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="75" customHeight="1">
+      <c r="A16" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>FUN</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Six Flags Entertainment</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>$2.2B</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>H Partners 53.7% (MAX concentration in 13F universe) + Cove Street +1,711% + L&amp;B + Jana 9%</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>Two-front: H Partners 53.7% / 5.7% class + Jana 9% pushing OUTRIGHT SALE</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>Jaffer joined board May 26 2026 (Class III through 2027, Audit Cttee)</t>
+        </is>
+      </c>
+      <c r="J16" s="15" t="inlineStr">
+        <is>
+          <t>53.7% MAX single-fund concentration + Jana sale push + Jaffer board seat just took effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="75" customHeight="1">
+      <c r="A17" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>AAP</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Advance Auto Parts</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>$3.3B</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>H Partners 46.3% / +50% sh Q1 ADD (1.35M new sh); Legion Partners precedent</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>H Partners 46% concentration approaching activist threshold</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>Q2 2026 margin proof Aug = catalyst (no documented insider yet)</t>
+        </is>
+      </c>
+      <c r="J17" s="15" t="inlineStr">
+        <is>
+          <t>HALF a fund's book in one name + STILL ADDING Q1 (1.35M new sh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="75" customHeight="1">
+      <c r="A18" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>KVHI</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>KVH Industries</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>&lt;$200M</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>Radoff family 10%+ owner build</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>Radoff 2,150,000 direct + 325,000 Foundation = 2,475,000 sh = 10%+ owner</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>Nov 2025 Form 4: +40,000 sh P-code purchase at $5.78</t>
+        </is>
+      </c>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>Family fund 10%+ owner + Form 4 open-market buy Nov 2025 + Foundation co-investing = aligned multi-generation insider</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="75" customHeight="1">
+      <c r="A19" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>BRN</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Barnwell Industries</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>&lt;$50M</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>Radoff 12.8% + Foundation 6.5% = group 17.4% peak</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>13D escalation 9.1%→12.8% Dec 2025 → Mar 2026 (multiple amendments)</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>Director Schechter Form 4 Dec 2025 (83,674 sh)</t>
+        </is>
+      </c>
+      <c r="J19" s="15" t="inlineStr">
+        <is>
+          <t>Ultra-microcap (&lt;$50M) with 17.4% group activist build + director Form 4 = total takeover possible</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="75" customHeight="1">
+      <c r="A20" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>SEER</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Seer, Inc.</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>~$200M</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>Radoff group escalating 9.3% → 10.5% → 10.6%</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>Multiple 13D/A amendments Feb-April 2026; Radoff+Torok+JEC II+MOS group</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>Family fund coordinated buying</t>
+        </is>
+      </c>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>Triple 13D escalation in 2 months on micro proteomics name</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="75" customHeight="1">
+      <c r="A21" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>GCO</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Genesco Inc.</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>$280M</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>Radoff/Jumana/Ross group 11.7% → 12.3%</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>Initial 13D April 15 → escalated April 27 2026</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>Coordinated three-party activist build</t>
+        </is>
+      </c>
+      <c r="J21" s="15" t="inlineStr">
+        <is>
+          <t>Three-party 13D coordinated on apparel retail micro = activist consensus</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="75" customHeight="1">
+      <c r="A22" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>STRR</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Star Equity Holdings</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>&lt;$30M</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>Star Equity Fund (Eberwein) 27.1% concentration</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>Eberwein 13D + board control</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>Eberwein +$3M OPEN-MARKET BUYING Q4 2025 (Dec 8) — 21.4%→27.1%</t>
+        </is>
+      </c>
+      <c r="J22" s="15" t="inlineStr">
+        <is>
+          <t>$3M open-market buying on a sub-$30M micro = ultra-aggressive insider build</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="75" customHeight="1">
+      <c r="A23" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>SONO</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Sonos Inc</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>$1.6B</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>Coliseum Capital (Gray/Shackelton) — anchor</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>Coliseum 13D activist + ~19.8% concentration</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>Coliseum +$23M+ FEB-MAR 2026 multiple Form 4 buys ($3.07M, $10.1M, $9.14M, $12.9M)</t>
+        </is>
+      </c>
+      <c r="J23" s="15" t="inlineStr">
+        <is>
+          <t>$35M+ open-market buying in 6 weeks (4 Form 4 buys Feb-Mar 2026) = extreme conviction at current</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="75" customHeight="1">
+      <c r="A24" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>RAPT</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>RAPT Therapeutics</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>~$100M</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>Caligan +$21.8M NEW + Polygon + OrbiMed (3 funds, +60% max)</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>OrbiMed 60% concentration on one name = max conviction</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>No documented Form 4</t>
+        </is>
+      </c>
+      <c r="J24" s="15" t="inlineStr">
+        <is>
+          <t>OrbiMed 60% concentration + 3 funds NEW Q1 = biotech triple stack</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="75" customHeight="1">
+      <c r="A25" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>LPX</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Louisiana-Pacific</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>$5.3B</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>Eminence +$327M / +29% + Scopia + Southeastern (3 funds, $365M sum)</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>Eminence 5.2% threshold</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>No documented Form 4</t>
+        </is>
+      </c>
+      <c r="J25" s="15" t="inlineStr">
+        <is>
+          <t>$365M from 3 funds + Eminence threshold filing on building products</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="75" customHeight="1">
+      <c r="A26" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>WK</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>$57B</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>Praesidium +60% + Irenic + Eminence</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>Irenic Capital 4.48% threshold filing</t>
+        </is>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>No documented Form 4</t>
+        </is>
+      </c>
+      <c r="J26" s="15" t="inlineStr">
+        <is>
+          <t>Eminence + Irenic activist + Praesidium 60% add — large cap activism rare</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="75" customHeight="1">
+      <c r="A27" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>XNCR</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Xencor</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>~$1B</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>EcoR1 + RA Capital (2 funds, +160% max!)</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>EcoR1 + RA Cap dual threshold filings</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>No documented Form 4</t>
+        </is>
+      </c>
+      <c r="J27" s="15" t="inlineStr">
+        <is>
+          <t>+160% MAX ADD by single fund + dual biotech crossover threshold = aggressive biotech setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="75" customHeight="1">
+      <c r="A28" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>SYRE</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Spyre Therapeutics</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>~$800M</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>Perceptive +149% Q1</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>Perceptive 5% threshold</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>No documented Form 4</t>
+        </is>
+      </c>
+      <c r="J28" s="15" t="inlineStr">
+        <is>
+          <t>Perceptive +149% Q1 ADD on biotech = top-tier biotech specialist max conviction</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="75" customHeight="1">
+      <c r="A29" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>PAR Technology</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>Voss Capital concentration / Permian Investment Partners</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>Voss 46% concentration on one name</t>
+        </is>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>No documented Form 4</t>
+        </is>
+      </c>
+      <c r="J29" s="15" t="inlineStr">
+        <is>
+          <t>Voss 46% = bet-the-fund conviction on restaurant tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="75" customHeight="1">
+      <c r="A30" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>CCO</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Clear Channel Outdoor</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>~$700M</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>Legion Partners + 2 funds, $43.9M sum</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="inlineStr">
+        <is>
+          <t>Legion 33.6% activist concentration</t>
+        </is>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>No documented Form 4</t>
+        </is>
+      </c>
+      <c r="J30" s="15" t="inlineStr">
+        <is>
+          <t>Legion 33.6% concentration + outdoor advertising recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="75" customHeight="1">
+      <c r="A31" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>BRZE</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Braze Inc</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>$4.8B</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>Iconiq 11.6% + Millennium</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>Iconiq 11.6% threshold + Millennium</t>
+        </is>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>No documented Form 4</t>
+        </is>
+      </c>
+      <c r="J31" s="15" t="inlineStr">
+        <is>
+          <t>Iconiq 11.6% on customer engagement platform; growth equity activist setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="75" customHeight="1">
+      <c r="A32" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>OPRX</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>OptimizeRx</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>$93M</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>Insider 14.82% + $10M buyback through March 2027</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="inlineStr">
+        <is>
+          <t>Doximity exec Presti joined board April 2026 = strategic alignment</t>
+        </is>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>Corporate buyback executing at $4-5 = effective insider buying</t>
+        </is>
+      </c>
+      <c r="J32" s="15" t="inlineStr">
+        <is>
+          <t>#1 Tier S+ asymmetric rank + Doximity exec to board = strategic peer insider signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="75" customHeight="1">
+      <c r="A33" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>NRP</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Natural Resource Partners</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>$1.35B</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>Right Tail NEW Q1 2026 + Saber 17.75% + Greystone + Berkowitz/Fairholme (5 funds)</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="inlineStr">
+        <is>
+          <t>Multi-fund anchor convergence</t>
+        </is>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>Robertson family 31.75% insider (permanent alignment)</t>
+        </is>
+      </c>
+      <c r="J33" s="15" t="inlineStr">
+        <is>
+          <t>5-fund concentration + 31.75% family insider + Right Tail freshest entry Q1 at current</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="75" customHeight="1">
+      <c r="A34" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>MTY.TO</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>MTY Food Group</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>C$887M</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>CEO Lefebvre +33% stake increase</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>CEO open-market buy = governance signal</t>
+        </is>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>CEO Lefebvre open-market buy at C$30.54 = $1M+ stake increase</t>
+        </is>
+      </c>
+      <c r="J34" s="15" t="inlineStr">
+        <is>
+          <t>CEO buying $1M+ at depressed multiple = strong governance signal at book-value QSR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="75" customHeight="1">
+      <c r="A35" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>BNTC</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>Benitec Biopharma</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>$200M</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>Suvretta 44.1% (LARGEST stake by % in their portfolio)</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="inlineStr">
+        <is>
+          <t>Suvretta 13D anchor</t>
+        </is>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>PIPE participation Nov 2025</t>
+        </is>
+      </c>
+      <c r="J35" s="15" t="inlineStr">
+        <is>
+          <t>Single-fund 44.1% concentration on micro biotech + PIPE = high-conviction lock</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="75" customHeight="1">
+      <c r="A36" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>ROCK</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>Gibraltar Industries</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>$1.10B</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>Vanguard 5.24% 13G NEW</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="inlineStr">
+        <is>
+          <t>Vanguard threshold filing</t>
+        </is>
+      </c>
+      <c r="I36" s="15" t="inlineStr">
+        <is>
+          <t>Director Metcalf bought $502,000 March 2026</t>
+        </is>
+      </c>
+      <c r="J36" s="15" t="inlineStr">
+        <is>
+          <t>Director $502k open-market March 2026 + Vanguard 5.24% NEW = post-OmniMax integration buying</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="75" customHeight="1">
+      <c r="A37" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>POSTBPB</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>Potbelly Corp</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>$240M</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>Nierenberg/D3 LARGEST shareholder (~$16.4M / 7% of D3 book)</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="inlineStr">
+        <is>
+          <t>13D/A active March 2025; ongoing Form 4 insider buys by Nierenberg</t>
+        </is>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>Nierenberg Form 4 buying at depressed levels</t>
+        </is>
+      </c>
+      <c r="J37" s="15" t="inlineStr">
+        <is>
+          <t>D3 largest shareholder + ongoing Form 4 buys = activist soft pressure micro</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="75" customHeight="1">
+      <c r="A38" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>ACMR</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>ACM Research</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>~$400M</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>Kerrisdale 3.36% + Steamboat joint</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="inlineStr">
+        <is>
+          <t>Joint letter Nov 2025 — HK listing $100M offer pursuit</t>
+        </is>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>No documented Form 4</t>
+        </is>
+      </c>
+      <c r="J38" s="15" t="inlineStr">
+        <is>
+          <t>Two-fund JOINT LETTER (rare) for HK value unlock = forced corporate action</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="75" customHeight="1">
+      <c r="A39" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>REZI</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Resideo Technologies</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>$2.6B</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>Alta Fox 9.57% NEW ($44.5M) + GoldenTree + 2 more (4 funds, $154.5M)</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="inlineStr">
+        <is>
+          <t>Alta Fox + GoldenTree</t>
+        </is>
+      </c>
+      <c r="I39" s="15" t="inlineStr">
+        <is>
+          <t>No documented Form 4</t>
+        </is>
+      </c>
+      <c r="J39" s="15" t="inlineStr">
+        <is>
+          <t>4-fund convergence on home tech with Alta Fox initiating 9.57%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="75" customHeight="1">
+      <c r="A40" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>NKTR</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>Nektar Therapeutics</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>~$280M</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G40" s="15" t="inlineStr">
+        <is>
+          <t>22NW +331k sh (5.9% port) + BVF + Polygon (3 funds)</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="inlineStr">
+        <is>
+          <t>22NW threshold + BVF</t>
+        </is>
+      </c>
+      <c r="I40" s="15" t="inlineStr">
+        <is>
+          <t>No documented Form 4</t>
+        </is>
+      </c>
+      <c r="J40" s="15" t="inlineStr">
+        <is>
+          <t>3-fund biotech micro adds + BVF anchor (biotech quality signal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="75" customHeight="1">
+      <c r="A41" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>EXAS</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>Exact Sciences</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>$15B</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G41" s="15" t="inlineStr">
+        <is>
+          <t>Hudson Bay $113.3M NEW + Pentwater (3 funds, $849M sum, +157%)</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="inlineStr"/>
+      <c r="I41" s="15" t="inlineStr">
+        <is>
+          <t>No documented Form 4</t>
+        </is>
+      </c>
+      <c r="J41" s="15" t="inlineStr">
+        <is>
+          <t>$849M from 3 funds + Cologuard moat</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="75" customHeight="1">
+      <c r="A42" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>ALKT</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Alkami Technology</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>~$2B</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G42" s="15" t="inlineStr">
+        <is>
+          <t>JANA Partners +158% / $69M + Praesidium</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="inlineStr">
+        <is>
+          <t>JANA Partners 5.87% threshold</t>
+        </is>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>No documented Form 4</t>
+        </is>
+      </c>
+      <c r="J42" s="15" t="inlineStr">
+        <is>
+          <t>JANA +158% ADD = activist heavyweight conviction</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="75" customHeight="1">
+      <c r="A43" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>Comerica</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>$8.7B</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G43" s="15" t="inlineStr">
+        <is>
+          <t>Magnetar $99.1M NEW + Whitebox $109M NEW</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="inlineStr"/>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>No documented Form 4</t>
+        </is>
+      </c>
+      <c r="J43" s="15" t="inlineStr">
+        <is>
+          <t>Two large NEW positions Q1 from sophisticated quants on regional bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="75" customHeight="1">
+      <c r="A44" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>GPK</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Graphic Packaging</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>$8.5B</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G44" s="15" t="inlineStr">
+        <is>
+          <t>Eminence $193M / +67% + Greenlight (Einhorn)</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="inlineStr">
+        <is>
+          <t>Eminence threshold</t>
+        </is>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>Greenlight Capital anchor</t>
+        </is>
+      </c>
+      <c r="J44" s="15" t="inlineStr">
+        <is>
+          <t>Eminence +67% + Greenlight Einhorn on packaging cyclical</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="75" customHeight="1">
+      <c r="A45" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>EQT</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>EQT Corporation</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>$28B</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>Sprott NEW + Sprott Asset NEW (2 funds NEW, $50M)</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="inlineStr"/>
+      <c r="I45" s="15" t="inlineStr">
+        <is>
+          <t>Nierenberg 16.85% concentration mentioned elsewhere</t>
+        </is>
+      </c>
+      <c r="J45" s="15" t="inlineStr">
+        <is>
+          <t>Sprott (gold/mining specialist) NEW position = natural-gas LNG cycle bet</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -10182,7 +12669,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11362,8 +13849,8 @@
     <mergeCell ref="A22:M22"/>
     <mergeCell ref="A35:M35"/>
     <mergeCell ref="A20:M20"/>
+    <mergeCell ref="A43:M43"/>
     <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A43:M43"/>
     <mergeCell ref="A52:M52"/>
     <mergeCell ref="A10:M10"/>
     <mergeCell ref="A28:M28"/>
@@ -11401,630 +13888,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>2. Activist Board Catalyst — ENTRY-TODAY × TAILWIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Definition: Schedule 13D filing with board seat secured or imminent + activist demands for value unlock. Dated trigger creates near-term volatility around catalyst.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Within-Rank</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Master-Rank</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Re-rate</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Tailwind</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Mcap</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>Asym</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>Upside</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>R/R</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>Smart Money</t>
-        </is>
-      </c>
-      <c r="M4" s="13" t="inlineStr">
-        <is>
-          <t>Secular Driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>MRP</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Millrose Properties</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>$4.59B</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>$25</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1.8-2.5x to NAV</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>13:1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Lennar 80%+ owner = patient capital lock-in; SITG multi-fund flag</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>US housing supply shortage structural (4M+ undersupply) + Lennar 80% off-take = guaranteed demand; market treats as spinoff orphan, not housing-cycle play</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: B/M 1.274 = DEEPEST in 6/7 cohort (deeper than NRP 0.47). Lennar 80% owner = guaranteed off-take + patient capital. Land bank at COST BASIS vs market. Pure NAV unwind; spinoff orphan technical pressure resolves into Q2 prints.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Lennar 80%+ owner spinoff with 100k+ optioned lots at cost basis. Land bank trading below NAV with Lennar as guaranteed off-take partner. Housing-cycle recovery levered. | VALUATION: B/M 1.274 (DEEPEST in 6/7 tier; deeper than NRP's 0.47), pure NAV play</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Q2 2026 print + Lennar volume scaling + housing cycle inflection | VARIANT: Market priced spinoff orphan technical pressure. Smart money: pure land cash-cow at discount to NAV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" t="n">
-        <v>14</v>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D9" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t>FUN</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Six Flags Entertainment</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>$2.2B</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>$25</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2-3x (3x outright sale)</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>9:1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>H Partners 53.7% / $82.5M / 5.7% of class; Jana 9% + Travis Kelce co-invest</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Theme parks cyclical consumer discretionary</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: 42 parks IRREPLACEABLE RE @ $47M each = $2B floor. Jaffer joined board May 26 + Jana 9% pushing OUTRIGHT SALE = two-front activist pressure. H Partners 53.7% / 5.7% of class. Sale = violent 3x trigger.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Post-Cedar Fair/Six Flags merger consolidation. 42 parks irreplaceable real estate. Q1 2026 rev +12%, attendance +4%, per-cap +6%. $200M synergy target ($120M cost + $80M growth). | VALUATION: $5.27B net debt = 7x leverage; EV/EBITDA 9x on $1.05B 2027 EBITDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: May 26 2026 AGM: Jaffer joins board (Class III through 2027, Audit&amp;Finance Cttee). Jana 9% pushing OUTRIGHT SALE. | VARIANT: Street: broken merger story. Two-front activist pressure (governance + sale) + per-park RE floor $47M each.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D13" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="inlineStr">
-        <is>
-          <t>AAP</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Advance Auto Parts</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>$3.3B</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>$54.42</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>8</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2.5-3x ($130-150 AZO comp)</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>9:1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>H Partners 46.3% / $71.2M / +50% sh Q1 2026 (1.35M sh); Legion Partners precedent</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Auto aftermarket mature; H Partners margin recovery thesis is operational not secular</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: -80% drawdown from 2021. H Partners 46.3% + Q1 +50% sh add ($71.2M). Bridge thesis: AZO-style 8-10% margins = $130-150. Q2 Aug 2026 = margin proof catalyst. Op margin +410bps already. Not cash-floored but H Partners concentration = sponsor put.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: #3 aftermarket retailer post-WorldPac sale. Q1 +3.5% comps (Pro mid-single, DIY low-single). 700+ stores closed; ~1,300 strategic locations remain. Bridge to AZO-style 8-10% margins = $130-150/sh. | VALUATION: 3.8% op margin (rising +410bps), FY26 guide $2.40-3.10 EPS; sub-1x sales; M&amp;A floor 0.8x sales = $80/sh</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Q2 2026 earnings Aug = needs comps +2%+ and op margin &gt;5%; H Partners 13D escalation possible | VARIANT: Consensus PT $57 (dead money). H Partners 46% concentration implies AAP returns to AZO margins.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" t="n">
-        <v>16</v>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D17" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="E17" s="28" t="inlineStr">
-        <is>
-          <t>ACHC</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Acadia Healthcare</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>$3.2B</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>$33</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>8</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2-3x + squeeze</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>6:1</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Greenlight Capital 4.1M sh (David Einhorn); Sohn presentation 5/12/2026</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Behavioral health secular demand (mental health structural) but DOJ regulatory overhang dominates pricing</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: -70% drawdown + 29% SHORT FLOAT = squeeze fuel. EV/EBITDA 6.5x vs peers 8-9x. DOJ resolution binary catalyst. Greenlight 4.1M sh + Sohn 5/12 pitch = thesis surfaced publicly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Largest US behavioral health network (260+ facilities). DOJ Medicaid investigation overhang. Q1 2026 admissions stabilizing. Greenlight 4.1M activist; Sohn 5/12 pitch. | VALUATION: EV/EBITDA 6.5x (vs HCA 9x, UHS 8x); 29% short float; -70% drawdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: DOJ resolution + Q2 2026 earnings + 29% short squeeze potential | VARIANT: Market: DOJ/Medicaid existential. Greenlight: provider necessity + facility footprint + de-rate captured = floor near current.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>5</v>
-      </c>
-      <c r="B21" t="n">
-        <v>30</v>
-      </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D21" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="E21" s="28" t="inlineStr">
-        <is>
-          <t>QRHC</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Quest Resource Holding</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>$200M</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>$7</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>6</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2-3x</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>8:1</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Wynnefield 13.3% / 2.73M sh / 13D w/ board seat</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Waste services minimal secular</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: Wynnefield 13.3% 13D w/ board seat. Sub-$200M micro waste services. Recurring revenue.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Wynnefield filed 13D 13.3% May 2025; Robert Lipstein joined board. Cooperation Agreement w/ standstill until 30 days before 2027 nomination window. Asset-light recurring waste mgmt. | VALUATION: Sub-$200M micro; recurring waste services revenue model</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Operational improvements + Wynnefield additional buying if dips | VARIANT: Market: small-cap value trap. Activist: board seat + potential value-unlock initiatives.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>6</v>
-      </c>
-      <c r="B25" t="n">
-        <v>31</v>
-      </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D25" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="E25" s="28" t="inlineStr">
-        <is>
-          <t>POSTBPB</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Potbelly Corp (PBPB)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>$240M</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>$8</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>6</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2-3x</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>8:1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Nierenberg/D3 largest shareholder; 13D/A active March 2025</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Restaurant chain cyclical; no secular</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: Nierenberg/D3 LARGEST shareholder (~$16.4M / 7% book). Restaurant turnaround + soft activist pressure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Nierenberg/D3 is LARGEST shareholder (~$16.4M / 7% of D3 book). Customer-traffic gains while peers don't (Q1 2026 letter thesis). Form 4 insider buying by Nierenberg at depressed levels. | VALUATION: Sub-$300M micro restaurant chain; turnaround stage</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Restaurant turnaround + Nierenberg potential escalation | VARIANT: Market: tier-2 restaurant chain. Activist soft-pressure thesis.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A23:M23"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A22:M22"/>
-    <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="A28:M28"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="A24:M24"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="A27:M27"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="A26:M26"/>
-    <mergeCell ref="A2:M2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -12052,14 +13915,14 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>3. Biotech Multi-Fund Convergence — ENTRY-TODAY × TAILWIND</t>
+          <t>2. Activist Board Catalyst — ENTRY-TODAY × TAILWIND</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Definition: Two or more top biotech crossover specialists (Baker Bros, RA Capital, BVF, Stonepine, Suvretta) anchored at high conviction in same name. Convergence is the high-signal pattern.</t>
+          <t>Definition: Schedule 13D filing with board seat secured or imminent + activist demands for value unlock. Dated trigger creates near-term volatility around catalyst.</t>
         </is>
       </c>
     </row>
@@ -12135,7 +13998,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
@@ -12149,66 +14012,66 @@
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>PRLD</t>
+          <t>MRP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Prelude Therapeutics</t>
+          <t>Millrose Properties</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>$340M</t>
+          <t>$4.59B</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$4.26</t>
+          <t>$25</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3-8x</t>
+          <t>1.8-2.5x to NAV</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Baker Bros 15.5% 13D/A + RA Capital 9.99% 13G; BOTH anchored SAME $90M April financing at $4.44</t>
+          <t>Lennar 80%+ owner = patient capital lock-in; SITG multi-fund flag</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Targeted protein degradation platform structural pharma shift + JAK2V617F addresses 95% PV/60% ET/55% MF (aging demographic, no oral comp); SMARCA2 fail = thrown out with platform</t>
+          <t>US housing supply shortage structural (4M+ undersupply) + Lennar 80% off-take = guaranteed demand; market treats as spinoff orphan, not housing-cycle play</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: NET CASH $2.20/sh = 51% of $4.26 price = downside FLOORED. Baker Bros 15.5% 13D + RA Capital 9.99% 13G BOTH anchored SAME April $90M financing at $4.44 — buying TODAY $4.26 is BELOW smart money entry. JAK2 binary upside 5-10x.</t>
+          <t>ENTRY-TODAY: B/M 1.274 = DEEPEST in 6/7 cohort (deeper than NRP 0.47). Lennar 80% owner = guaranteed off-take + patient capital. Land bank at COST BASIS vs market. Pure NAV unwind; spinoff orphan technical pressure resolves into Q2 prints.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Precision oncology / molecular glue / degrader platform. SMARCA2 discontinued 2025; pivot to JAK2V617F (PRT12396) + KAT6A (PRT13722). AbCellera partnership. | VALUATION: $175M cash vs $340M mcap = $2.20/sh net cash (51% of price); buyout floor near current</t>
+          <t>THESIS: Lennar 80%+ owner spinoff with 100k+ optioned lots at cost basis. Land bank trading below NAV with Lennar as guaranteed off-take partner. Housing-cycle recovery levered. | VALUATION: B/M 1.274 (DEEPEST in 6/7 tier; deeper than NRP's 0.47), pure NAV play</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: PRT12396 Phase 1 H2 2026; PRT13722 IND mid-2026; Incyte option agreement Nov 2025 | VARIANT: Market: broken story post-SMARCA2 fail. Smart money: April 2026 refunding = platform-validation thesis. JAK2 mutant-selective addresses 95% PV/60% ET/55% MF.</t>
+          <t>CATALYST: Q2 2026 print + Lennar volume scaling + housing cycle inflection | VARIANT: Market priced spinoff orphan technical pressure. Smart money: pure land cash-cow at discount to NAV.</t>
         </is>
       </c>
     </row>
@@ -12217,80 +14080,80 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>PVLA</t>
+          <t>FUN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Palvella Therapeutics</t>
+          <t>Six Flags Entertainment</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$1.56B</t>
+          <t>$2.2B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$130</t>
+          <t>$25</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>2-3x (3x outright sale)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>10:1</t>
+          <t>9:1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>BVF 3.8% / $120M (8.5% of company) + Suvretta 3.67% / $144M (+29.3% Q1)</t>
+          <t>H Partners 53.7% / $82.5M / 5.7% of class; Jana 9% + Travis Kelce co-invest</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Rare-disease pricing structural ($300k+ orphan); QTORIN platform with multiple programs (LMs, venous malformations, angiokeratomas); market priced single-asset story</t>
+          <t>Theme parks cyclical consumer discretionary</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Cash $25/sh = 19% of $130 price. Phase 3 SELVA POSITIVE Feb 24 2026 = DE-RISKED. Pre-NDA Q2 + NDA H2 + PDUFA H1 2027 = staircase of catalysts. BVF 8.5% of company + Suvretta 3.67% (+29.3% Q1).</t>
+          <t>ENTRY-TODAY: 42 parks IRREPLACEABLE RE @ $47M each = $2B floor. Jaffer joined board May 26 + Jana 9% pushing OUTRIGHT SALE = two-front activist pressure. H Partners 53.7% / 5.7% of class. Sale = violent 3x trigger.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Rare-disease topical platform. QTORIN rapamycin gel for microcystic LMs (Breakthrough + Orphan + Fast Track). Phase 3 SELVA POSITIVE Feb 24 2026 (mLM-IGA +2.13, p&lt;0.001). | VALUATION: $261.9M cash = $25/sh (19% of price). Phase 3 derisked. M&amp;A floor 4-6x peak rev</t>
+          <t>THESIS: Post-Cedar Fair/Six Flags merger consolidation. 42 parks irreplaceable real estate. Q1 2026 rev +12%, attendance +4%, per-cap +6%. $200M synergy target ($120M cost + $80M growth). | VALUATION: $5.27B net debt = 7x leverage; EV/EBITDA 9x on $1.05B 2027 EBITDA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Pre-NDA FDA meeting Q2 2026; NDA H2 2026; PDUFA H1 2027 | VARIANT: Market: single-asset rare-disease (~$1.5B). Smart money: platform with &gt;$1B peak QTORIN + venous malformations/angiokeratomas/pitavastatin programs.</t>
+          <t>CATALYST: May 26 2026 AGM: Jaffer joins board (Class III through 2027, Audit&amp;Finance Cttee). Jana 9% pushing OUTRIGHT SALE. | VARIANT: Street: broken merger story. Two-front activist pressure (governance + sale) + per-park RE floor $47M each.</t>
         </is>
       </c>
     </row>
@@ -12299,80 +14162,80 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D13" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>KYMR</t>
+          <t>AAP</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kymera Therapeutics</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$6.5B</t>
+          <t>$3.3B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$80</t>
+          <t>$54.42</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>2.5-3x ($130-150 AZO comp)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>13:1</t>
+          <t>9:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>BVF #1 position 14.6% of $3.14B book ($458M) + Baker Bros 4.1% / $721M; BOTH anchored $86 follow-on</t>
+          <t>H Partners 46.3% / $71.2M / +50% sh Q1 2026 (1.35M sh); Legion Partners precedent</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Oral biologic disruption (oral Dupixent = $14B+ franchise displacement); TPD structural pharma platform shift; Phase 1b execution risk masks platform value</t>
+          <t>Auto aftermarket mature; H Partners margin recovery thesis is operational not secular</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Cash $1.55B + BVF 14.6% MAX conviction + Baker 4.1% = multi-fund convergence. BUT major catalyst BROADEN2 mid-2027 = 12+ months away (low velocity). Strong setup, slow trigger.</t>
+          <t>ENTRY-TODAY: -80% drawdown from 2021. H Partners 46.3% + Q1 +50% sh add ($71.2M). Bridge thesis: AZO-style 8-10% margins = $130-150. Q2 Aug 2026 = margin proof catalyst. Op margin +410bps already. Not cash-floored but H Partners concentration = sponsor put.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Targeted protein degradation platform. Lead KT-621 oral STAT6 degrader competes with injectable Dupixent ($14B+ franchise). IRAK4 partnered with Sanofi. | VALUATION: $1.55B cash (runway 2029); Dec 2025 follow-on $602M at $86</t>
+          <t>THESIS: #3 aftermarket retailer post-WorldPac sale. Q1 +3.5% comps (Pro mid-single, DIY low-single). 700+ stores closed; ~1,300 strategic locations remain. Bridge to AZO-style 8-10% margins = $130-150/sh. | VALUATION: 3.8% op margin (rising +410bps), FY26 guide $2.40-3.10 EPS; sub-1x sales; M&amp;A floor 0.8x sales = $80/sh</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: BROADEN2 AD mid-2027 (12+ months); BREADTH asthma late 2027; FDA Fast Track granted both | VARIANT: Market: Phase 1b execution risk. Two top biotech specialists: oral Dupixent-disruptor with peak $5-10B.</t>
+          <t>CATALYST: Q2 2026 earnings Aug = needs comps +2%+ and op margin &gt;5%; H Partners 13D escalation possible | VARIANT: Consensus PT $57 (dead money). H Partners 46% concentration implies AAP returns to AZO margins.</t>
         </is>
       </c>
     </row>
@@ -12381,80 +14244,80 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D17" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>BNTC</t>
+          <t>ACHC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Benitec Biopharma</t>
+          <t>Acadia Healthcare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>$200M</t>
+          <t>$3.2B</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>$8</t>
+          <t>$33</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>2-3x + squeeze</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7:1</t>
+          <t>6:1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Suvretta 44.1% 13D (Suvretta's LARGEST stake by % ownership)</t>
+          <t>Greenlight Capital 4.1M sh (David Einhorn); Sohn presentation 5/12/2026</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Gene therapy speculative single platform</t>
+          <t>Behavioral health secular demand (mental health structural) but DOJ regulatory overhang dominates pricing</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Suvretta 44.1% 13D = LARGEST stake by %. Gene therapy platform. Multi-program optionality. Higher risk than other biotech-multi-fund names.</t>
+          <t>ENTRY-TODAY: -70% drawdown + 29% SHORT FLOAT = squeeze fuel. EV/EBITDA 6.5x vs peers 8-9x. DOJ resolution binary catalyst. Greenlight 4.1M sh + Sohn 5/12 pitch = thesis surfaced publicly.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Gene therapy platform anchor position. Suvretta 44.1% 13D anchor stake (largest activist ownership in their portfolio). PIPE participation Nov 2025. | VALUATION: Sub-$300M biotech; gene therapy platform optionality</t>
+          <t>THESIS: Largest US behavioral health network (260+ facilities). DOJ Medicaid investigation overhang. Q1 2026 admissions stabilizing. Greenlight 4.1M activist; Sohn 5/12 pitch. | VALUATION: EV/EBITDA 6.5x (vs HCA 9x, UHS 8x); 29% short float; -70% drawdown</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Multiple gene-therapy programs in development; clinical readouts upcoming | VARIANT: 44.1% ownership creates board influence + asymmetric upside on clinical reads.</t>
+          <t>CATALYST: DOJ resolution + Q2 2026 earnings + 29% short squeeze potential | VARIANT: Market: DOJ/Medicaid existential. Greenlight: provider necessity + facility footprint + de-rate captured = floor near current.</t>
         </is>
       </c>
     </row>
@@ -12463,80 +14326,80 @@
         <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>37</v>
-      </c>
-      <c r="C21" s="33" t="inlineStr">
-        <is>
-          <t>RERATED</t>
-        </is>
-      </c>
-      <c r="D21" s="34" t="inlineStr">
-        <is>
-          <t>PRICED</t>
+        <v>30</v>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
         </is>
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
-          <t>CELC</t>
+          <t>QRHC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Celcuity</t>
+          <t>Quest Resource Holding</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>$8B (post-data)</t>
+          <t>$200M</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>$165</t>
+          <t>$7</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.3-2x post-data</t>
+          <t>2-3x</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>8:1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Baker Bros 19.99% ACTIVIST 13D = $904M / 5.48% of $17.4B book</t>
+          <t>Wynnefield 13.3% / 2.73M sh / 13D w/ board seat</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Targeted oncology secular but Phase 3 data + PT raises captured the move</t>
+          <t>Waste services minimal secular</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Phase 3 May 1 POSITIVE + +76% PT raises already in price. ASCO Jun 2 + PDUFA Jul 17 remain but pre-quantified. Quality+catalysts but entry economics weakened post-data.</t>
+          <t>ENTRY-TODAY: Wynnefield 13.3% 13D w/ board seat. Sub-$200M micro waste services. Recurring revenue.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Phase 3 VIKTORIA-1 PIK3CA-mut POSITIVE May 1 2026 (76% PFS hazard reduction). Gedatolisib pan-PI3K/mTOR oncology. Triplet vs alpelisib+fulvestrant. Multiple HR+/HER2- breast cancer cohorts. | VALUATION: $387M cash + accepted NDA + Priority Review = de-risked; 4-5x peak rev precedent</t>
+          <t>THESIS: Wynnefield filed 13D 13.3% May 2025; Robert Lipstein joined board. Cooperation Agreement w/ standstill until 30 days before 2027 nomination window. Asset-light recurring waste mgmt. | VALUATION: Sub-$200M micro; recurring waste services revenue model</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: JUNE 2 ASCO LBA1008 oral + JULY 17 PDUFA goal date (2 catalysts in 8 weeks) | VARIANT: Market: alpelisib-class peak ($1-2B). Baker Bros 19.99% 13D activist: $5-10B peak (triplet displaces alpelisib + captures WT segment).</t>
+          <t>CATALYST: Operational improvements + Wynnefield additional buying if dips | VARIANT: Market: small-cap value trap. Activist: board seat + potential value-unlock initiatives.</t>
         </is>
       </c>
     </row>
@@ -12545,80 +14408,80 @@
         <v>6</v>
       </c>
       <c r="B25" t="n">
-        <v>40</v>
-      </c>
-      <c r="C25" s="33" t="inlineStr">
-        <is>
-          <t>RERATED</t>
-        </is>
-      </c>
-      <c r="D25" s="34" t="inlineStr">
-        <is>
-          <t>PRICED</t>
+        <v>31</v>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D25" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
         </is>
       </c>
       <c r="E25" s="28" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>POSTBPB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascendis Pharma</t>
+          <t>Potbelly Corp (PBPB)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>$15.3B</t>
+          <t>$240M</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>$247</t>
+          <t>$8</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.2-1.5x</t>
+          <t>2-3x</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>8:1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>RA Capital 24.9% of $9.44B = $2.35B = LARGEST single biotech crossover position; held since 2015</t>
+          <t>Nierenberg/D3 largest shareholder; 13D/A active March 2025</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Rare endocrine pricing secular but YORVIPATH ramp captured</t>
+          <t>Restaurant chain cyclical; no secular</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: YORVIPATH ramp priced. €247M Q1 (2x YoY) already at $247. Multiple normalized.</t>
+          <t>ENTRY-TODAY: Nierenberg/D3 LARGEST shareholder (~$16.4M / 7% book). Restaurant turnaround + soft activist pressure.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>THESIS: TransCon prodrug platform: SKYTROFA (GHD), YORVIPATH (hypopara), YUVIWEL (achondroplasia approved Feb 2026). &gt;1,000 new US YORVIPATH enrollments Q1; 6,300+ patients across 2,700 prescribers. | VALUATION: Profitable (22% non-IFRS op margin); €247M Q1 (2x YoY); peak rev YORVIPATH $4-5B</t>
+          <t>THESIS: Nierenberg/D3 is LARGEST shareholder (~$16.4M / 7% of D3 book). Customer-traffic gains while peers don't (Q1 2026 letter thesis). Form 4 insider buying by Nierenberg at depressed levels. | VALUATION: Sub-$300M micro restaurant chain; turnaround stage</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: YUVIWEL ramp + Q2/Q3 YORVIPATH growth + TransCon CNP follow-on indications | VARIANT: Sell-side: $15B endocrine specialty maturing. RA Capital: $30B+ at 70-90K addressable hypopara population. Analyst high $345 (Barclays).</t>
+          <t>CATALYST: Restaurant turnaround + Nierenberg potential escalation | VARIANT: Market: tier-2 restaurant chain. Activist soft-pressure thesis.</t>
         </is>
       </c>
     </row>

--- a/investment_archetypes.xlsx
+++ b/investment_archetypes.xlsx
@@ -13,17 +13,18 @@
     <sheet name="POSITION INTENSITY" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="MICRO+SMALL CAP INTENSITY" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="AGGRESSIVE BUY SIGNALS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="MASTER Entry-Today" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="1. Yartseva Pure Multibagger" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="2. Activist Board Catalyst" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="3. Biotech Multi-Fund Convergen" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="4. Sponsor-Anchored Holdco Tran" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="5. Spinoff - SoTP Arbitrage" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="6. Deep Drawdown Mean Reversion" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="7. Hard Asset - Royalty" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="8. Foreign - Underfollowed Valu" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="9. Quality Compounder at Trough" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="10. Hedged - Special Structure" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="FULL UNIVERSE NEW Tiers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MASTER Entry-Today" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="1. Yartseva Pure Multibagger" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="2. Activist Board Catalyst" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="3. Biotech Multi-Fund Convergen" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="4. Sponsor-Anchored Holdco Tran" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="5. Spinoff - SoTP Arbitrage" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="6. Deep Drawdown Mean Reversion" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="7. Hard Asset - Royalty" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="8. Foreign - Underfollowed Valu" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="9. Quality Compounder at Trough" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="10. Hedged - Special Structure" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -969,14 +970,14 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>3. Biotech Multi-Fund Convergence — ENTRY-TODAY × TAILWIND</t>
+          <t>2. Activist Board Catalyst — ENTRY-TODAY × TAILWIND</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Definition: Two or more top biotech crossover specialists (Baker Bros, RA Capital, BVF, Stonepine, Suvretta) anchored at high conviction in same name. Convergence is the high-signal pattern.</t>
+          <t>Definition: Schedule 13D filing with board seat secured or imminent + activist demands for value unlock. Dated trigger creates near-term volatility around catalyst.</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1053,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
@@ -1066,66 +1067,66 @@
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>PRLD</t>
+          <t>MRP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Prelude Therapeutics</t>
+          <t>Millrose Properties</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>$340M</t>
+          <t>$4.59B</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$4.26</t>
+          <t>$25</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3-8x</t>
+          <t>1.8-2.5x to NAV</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Baker Bros 15.5% 13D/A + RA Capital 9.99% 13G; BOTH anchored SAME $90M April financing at $4.44</t>
+          <t>Lennar 80%+ owner = patient capital lock-in; SITG multi-fund flag</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Targeted protein degradation platform structural pharma shift + JAK2V617F addresses 95% PV/60% ET/55% MF (aging demographic, no oral comp); SMARCA2 fail = thrown out with platform</t>
+          <t>US housing supply shortage structural (4M+ undersupply) + Lennar 80% off-take = guaranteed demand; market treats as spinoff orphan, not housing-cycle play</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: NET CASH $2.20/sh = 51% of $4.26 price = downside FLOORED. Baker Bros 15.5% 13D + RA Capital 9.99% 13G BOTH anchored SAME April $90M financing at $4.44 — buying TODAY $4.26 is BELOW smart money entry. JAK2 binary upside 5-10x.</t>
+          <t>ENTRY-TODAY: B/M 1.274 = DEEPEST in 6/7 cohort (deeper than NRP 0.47). Lennar 80% owner = guaranteed off-take + patient capital. Land bank at COST BASIS vs market. Pure NAV unwind; spinoff orphan technical pressure resolves into Q2 prints.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Precision oncology / molecular glue / degrader platform. SMARCA2 discontinued 2025; pivot to JAK2V617F (PRT12396) + KAT6A (PRT13722). AbCellera partnership. | VALUATION: $175M cash vs $340M mcap = $2.20/sh net cash (51% of price); buyout floor near current</t>
+          <t>THESIS: Lennar 80%+ owner spinoff with 100k+ optioned lots at cost basis. Land bank trading below NAV with Lennar as guaranteed off-take partner. Housing-cycle recovery levered. | VALUATION: B/M 1.274 (DEEPEST in 6/7 tier; deeper than NRP's 0.47), pure NAV play</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: PRT12396 Phase 1 H2 2026; PRT13722 IND mid-2026; Incyte option agreement Nov 2025 | VARIANT: Market: broken story post-SMARCA2 fail. Smart money: April 2026 refunding = platform-validation thesis. JAK2 mutant-selective addresses 95% PV/60% ET/55% MF.</t>
+          <t>CATALYST: Q2 2026 print + Lennar volume scaling + housing cycle inflection | VARIANT: Market priced spinoff orphan technical pressure. Smart money: pure land cash-cow at discount to NAV.</t>
         </is>
       </c>
     </row>
@@ -1134,80 +1135,80 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>PVLA</t>
+          <t>FUN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Palvella Therapeutics</t>
+          <t>Six Flags Entertainment</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$1.56B</t>
+          <t>$2.2B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$130</t>
+          <t>$25</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>2-3x (3x outright sale)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>10:1</t>
+          <t>9:1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>BVF 3.8% / $120M (8.5% of company) + Suvretta 3.67% / $144M (+29.3% Q1)</t>
+          <t>H Partners 53.7% / $82.5M / 5.7% of class; Jana 9% + Travis Kelce co-invest</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Rare-disease pricing structural ($300k+ orphan); QTORIN platform with multiple programs (LMs, venous malformations, angiokeratomas); market priced single-asset story</t>
+          <t>Theme parks cyclical consumer discretionary</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Cash $25/sh = 19% of $130 price. Phase 3 SELVA POSITIVE Feb 24 2026 = DE-RISKED. Pre-NDA Q2 + NDA H2 + PDUFA H1 2027 = staircase of catalysts. BVF 8.5% of company + Suvretta 3.67% (+29.3% Q1).</t>
+          <t>ENTRY-TODAY: 42 parks IRREPLACEABLE RE @ $47M each = $2B floor. Jaffer joined board May 26 + Jana 9% pushing OUTRIGHT SALE = two-front activist pressure. H Partners 53.7% / 5.7% of class. Sale = violent 3x trigger.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Rare-disease topical platform. QTORIN rapamycin gel for microcystic LMs (Breakthrough + Orphan + Fast Track). Phase 3 SELVA POSITIVE Feb 24 2026 (mLM-IGA +2.13, p&lt;0.001). | VALUATION: $261.9M cash = $25/sh (19% of price). Phase 3 derisked. M&amp;A floor 4-6x peak rev</t>
+          <t>THESIS: Post-Cedar Fair/Six Flags merger consolidation. 42 parks irreplaceable real estate. Q1 2026 rev +12%, attendance +4%, per-cap +6%. $200M synergy target ($120M cost + $80M growth). | VALUATION: $5.27B net debt = 7x leverage; EV/EBITDA 9x on $1.05B 2027 EBITDA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Pre-NDA FDA meeting Q2 2026; NDA H2 2026; PDUFA H1 2027 | VARIANT: Market: single-asset rare-disease (~$1.5B). Smart money: platform with &gt;$1B peak QTORIN + venous malformations/angiokeratomas/pitavastatin programs.</t>
+          <t>CATALYST: May 26 2026 AGM: Jaffer joins board (Class III through 2027, Audit&amp;Finance Cttee). Jana 9% pushing OUTRIGHT SALE. | VARIANT: Street: broken merger story. Two-front activist pressure (governance + sale) + per-park RE floor $47M each.</t>
         </is>
       </c>
     </row>
@@ -1216,80 +1217,80 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D13" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>KYMR</t>
+          <t>AAP</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kymera Therapeutics</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$6.5B</t>
+          <t>$3.3B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$80</t>
+          <t>$54.42</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>2.5-3x ($130-150 AZO comp)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>13:1</t>
+          <t>9:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>BVF #1 position 14.6% of $3.14B book ($458M) + Baker Bros 4.1% / $721M; BOTH anchored $86 follow-on</t>
+          <t>H Partners 46.3% / $71.2M / +50% sh Q1 2026 (1.35M sh); Legion Partners precedent</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Oral biologic disruption (oral Dupixent = $14B+ franchise displacement); TPD structural pharma platform shift; Phase 1b execution risk masks platform value</t>
+          <t>Auto aftermarket mature; H Partners margin recovery thesis is operational not secular</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Cash $1.55B + BVF 14.6% MAX conviction + Baker 4.1% = multi-fund convergence. BUT major catalyst BROADEN2 mid-2027 = 12+ months away (low velocity). Strong setup, slow trigger.</t>
+          <t>ENTRY-TODAY: -80% drawdown from 2021. H Partners 46.3% + Q1 +50% sh add ($71.2M). Bridge thesis: AZO-style 8-10% margins = $130-150. Q2 Aug 2026 = margin proof catalyst. Op margin +410bps already. Not cash-floored but H Partners concentration = sponsor put.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Targeted protein degradation platform. Lead KT-621 oral STAT6 degrader competes with injectable Dupixent ($14B+ franchise). IRAK4 partnered with Sanofi. | VALUATION: $1.55B cash (runway 2029); Dec 2025 follow-on $602M at $86</t>
+          <t>THESIS: #3 aftermarket retailer post-WorldPac sale. Q1 +3.5% comps (Pro mid-single, DIY low-single). 700+ stores closed; ~1,300 strategic locations remain. Bridge to AZO-style 8-10% margins = $130-150/sh. | VALUATION: 3.8% op margin (rising +410bps), FY26 guide $2.40-3.10 EPS; sub-1x sales; M&amp;A floor 0.8x sales = $80/sh</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: BROADEN2 AD mid-2027 (12+ months); BREADTH asthma late 2027; FDA Fast Track granted both | VARIANT: Market: Phase 1b execution risk. Two top biotech specialists: oral Dupixent-disruptor with peak $5-10B.</t>
+          <t>CATALYST: Q2 2026 earnings Aug = needs comps +2%+ and op margin &gt;5%; H Partners 13D escalation possible | VARIANT: Consensus PT $57 (dead money). H Partners 46% concentration implies AAP returns to AZO margins.</t>
         </is>
       </c>
     </row>
@@ -1298,80 +1299,80 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D17" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>BNTC</t>
+          <t>ACHC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Benitec Biopharma</t>
+          <t>Acadia Healthcare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>$200M</t>
+          <t>$3.2B</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>$8</t>
+          <t>$33</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>2-3x + squeeze</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7:1</t>
+          <t>6:1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Suvretta 44.1% 13D (Suvretta's LARGEST stake by % ownership)</t>
+          <t>Greenlight Capital 4.1M sh (David Einhorn); Sohn presentation 5/12/2026</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Gene therapy speculative single platform</t>
+          <t>Behavioral health secular demand (mental health structural) but DOJ regulatory overhang dominates pricing</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Suvretta 44.1% 13D = LARGEST stake by %. Gene therapy platform. Multi-program optionality. Higher risk than other biotech-multi-fund names.</t>
+          <t>ENTRY-TODAY: -70% drawdown + 29% SHORT FLOAT = squeeze fuel. EV/EBITDA 6.5x vs peers 8-9x. DOJ resolution binary catalyst. Greenlight 4.1M sh + Sohn 5/12 pitch = thesis surfaced publicly.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Gene therapy platform anchor position. Suvretta 44.1% 13D anchor stake (largest activist ownership in their portfolio). PIPE participation Nov 2025. | VALUATION: Sub-$300M biotech; gene therapy platform optionality</t>
+          <t>THESIS: Largest US behavioral health network (260+ facilities). DOJ Medicaid investigation overhang. Q1 2026 admissions stabilizing. Greenlight 4.1M activist; Sohn 5/12 pitch. | VALUATION: EV/EBITDA 6.5x (vs HCA 9x, UHS 8x); 29% short float; -70% drawdown</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Multiple gene-therapy programs in development; clinical readouts upcoming | VARIANT: 44.1% ownership creates board influence + asymmetric upside on clinical reads.</t>
+          <t>CATALYST: DOJ resolution + Q2 2026 earnings + 29% short squeeze potential | VARIANT: Market: DOJ/Medicaid existential. Greenlight: provider necessity + facility footprint + de-rate captured = floor near current.</t>
         </is>
       </c>
     </row>
@@ -1380,80 +1381,80 @@
         <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>37</v>
-      </c>
-      <c r="C21" s="33" t="inlineStr">
-        <is>
-          <t>RERATED</t>
-        </is>
-      </c>
-      <c r="D21" s="34" t="inlineStr">
-        <is>
-          <t>PRICED</t>
+        <v>30</v>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
         </is>
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
-          <t>CELC</t>
+          <t>QRHC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Celcuity</t>
+          <t>Quest Resource Holding</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>$8B (post-data)</t>
+          <t>$200M</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>$165</t>
+          <t>$7</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.3-2x post-data</t>
+          <t>2-3x</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>8:1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Baker Bros 19.99% ACTIVIST 13D = $904M / 5.48% of $17.4B book</t>
+          <t>Wynnefield 13.3% / 2.73M sh / 13D w/ board seat</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Targeted oncology secular but Phase 3 data + PT raises captured the move</t>
+          <t>Waste services minimal secular</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Phase 3 May 1 POSITIVE + +76% PT raises already in price. ASCO Jun 2 + PDUFA Jul 17 remain but pre-quantified. Quality+catalysts but entry economics weakened post-data.</t>
+          <t>ENTRY-TODAY: Wynnefield 13.3% 13D w/ board seat. Sub-$200M micro waste services. Recurring revenue.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Phase 3 VIKTORIA-1 PIK3CA-mut POSITIVE May 1 2026 (76% PFS hazard reduction). Gedatolisib pan-PI3K/mTOR oncology. Triplet vs alpelisib+fulvestrant. Multiple HR+/HER2- breast cancer cohorts. | VALUATION: $387M cash + accepted NDA + Priority Review = de-risked; 4-5x peak rev precedent</t>
+          <t>THESIS: Wynnefield filed 13D 13.3% May 2025; Robert Lipstein joined board. Cooperation Agreement w/ standstill until 30 days before 2027 nomination window. Asset-light recurring waste mgmt. | VALUATION: Sub-$200M micro; recurring waste services revenue model</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: JUNE 2 ASCO LBA1008 oral + JULY 17 PDUFA goal date (2 catalysts in 8 weeks) | VARIANT: Market: alpelisib-class peak ($1-2B). Baker Bros 19.99% 13D activist: $5-10B peak (triplet displaces alpelisib + captures WT segment).</t>
+          <t>CATALYST: Operational improvements + Wynnefield additional buying if dips | VARIANT: Market: small-cap value trap. Activist: board seat + potential value-unlock initiatives.</t>
         </is>
       </c>
     </row>
@@ -1462,80 +1463,80 @@
         <v>6</v>
       </c>
       <c r="B25" t="n">
-        <v>40</v>
-      </c>
-      <c r="C25" s="33" t="inlineStr">
-        <is>
-          <t>RERATED</t>
-        </is>
-      </c>
-      <c r="D25" s="34" t="inlineStr">
-        <is>
-          <t>PRICED</t>
+        <v>31</v>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D25" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
         </is>
       </c>
       <c r="E25" s="28" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>POSTBPB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascendis Pharma</t>
+          <t>Potbelly Corp (PBPB)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>$15.3B</t>
+          <t>$240M</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>$247</t>
+          <t>$8</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.2-1.5x</t>
+          <t>2-3x</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>8:1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>RA Capital 24.9% of $9.44B = $2.35B = LARGEST single biotech crossover position; held since 2015</t>
+          <t>Nierenberg/D3 largest shareholder; 13D/A active March 2025</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Rare endocrine pricing secular but YORVIPATH ramp captured</t>
+          <t>Restaurant chain cyclical; no secular</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: YORVIPATH ramp priced. €247M Q1 (2x YoY) already at $247. Multiple normalized.</t>
+          <t>ENTRY-TODAY: Nierenberg/D3 LARGEST shareholder (~$16.4M / 7% book). Restaurant turnaround + soft activist pressure.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>THESIS: TransCon prodrug platform: SKYTROFA (GHD), YORVIPATH (hypopara), YUVIWEL (achondroplasia approved Feb 2026). &gt;1,000 new US YORVIPATH enrollments Q1; 6,300+ patients across 2,700 prescribers. | VALUATION: Profitable (22% non-IFRS op margin); €247M Q1 (2x YoY); peak rev YORVIPATH $4-5B</t>
+          <t>THESIS: Nierenberg/D3 is LARGEST shareholder (~$16.4M / 7% of D3 book). Customer-traffic gains while peers don't (Q1 2026 letter thesis). Form 4 insider buying by Nierenberg at depressed levels. | VALUATION: Sub-$300M micro restaurant chain; turnaround stage</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: YUVIWEL ramp + Q2/Q3 YORVIPATH growth + TransCon CNP follow-on indications | VARIANT: Sell-side: $15B endocrine specialty maturing. RA Capital: $30B+ at 70-90K addressable hypopara population. Analyst high $345 (Barclays).</t>
+          <t>CATALYST: Restaurant turnaround + Nierenberg potential escalation | VARIANT: Market: tier-2 restaurant chain. Activist soft-pressure thesis.</t>
         </is>
       </c>
     </row>
@@ -1572,6 +1573,630 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence — ENTRY-TODAY × TAILWIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Definition: Two or more top biotech crossover specialists (Baker Bros, RA Capital, BVF, Stonepine, Suvretta) anchored at high conviction in same name. Convergence is the high-signal pattern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Within-Rank</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Master-Rank</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Re-rate</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Tailwind</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Mcap</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Asym</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Smart Money</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>Secular Driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>PRLD</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Prelude Therapeutics</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>$340M</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>$4.26</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3-8x</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>20:1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Baker Bros 15.5% 13D/A + RA Capital 9.99% 13G; BOTH anchored SAME $90M April financing at $4.44</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Targeted protein degradation platform structural pharma shift + JAK2V617F addresses 95% PV/60% ET/55% MF (aging demographic, no oral comp); SMARCA2 fail = thrown out with platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: NET CASH $2.20/sh = 51% of $4.26 price = downside FLOORED. Baker Bros 15.5% 13D + RA Capital 9.99% 13G BOTH anchored SAME April $90M financing at $4.44 — buying TODAY $4.26 is BELOW smart money entry. JAK2 binary upside 5-10x.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Precision oncology / molecular glue / degrader platform. SMARCA2 discontinued 2025; pivot to JAK2V617F (PRT12396) + KAT6A (PRT13722). AbCellera partnership. | VALUATION: $175M cash vs $340M mcap = $2.20/sh net cash (51% of price); buyout floor near current</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: PRT12396 Phase 1 H2 2026; PRT13722 IND mid-2026; Incyte option agreement Nov 2025 | VARIANT: Market: broken story post-SMARCA2 fail. Smart money: April 2026 refunding = platform-validation thesis. JAK2 mutant-selective addresses 95% PV/60% ET/55% MF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>17</v>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>PVLA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Palvella Therapeutics</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>$1.56B</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>$130</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2-3x</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>10:1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>BVF 3.8% / $120M (8.5% of company) + Suvretta 3.67% / $144M (+29.3% Q1)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Rare-disease pricing structural ($300k+ orphan); QTORIN platform with multiple programs (LMs, venous malformations, angiokeratomas); market priced single-asset story</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Cash $25/sh = 19% of $130 price. Phase 3 SELVA POSITIVE Feb 24 2026 = DE-RISKED. Pre-NDA Q2 + NDA H2 + PDUFA H1 2027 = staircase of catalysts. BVF 8.5% of company + Suvretta 3.67% (+29.3% Q1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Rare-disease topical platform. QTORIN rapamycin gel for microcystic LMs (Breakthrough + Orphan + Fast Track). Phase 3 SELVA POSITIVE Feb 24 2026 (mLM-IGA +2.13, p&lt;0.001). | VALUATION: $261.9M cash = $25/sh (19% of price). Phase 3 derisked. M&amp;A floor 4-6x peak rev</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Pre-NDA FDA meeting Q2 2026; NDA H2 2026; PDUFA H1 2027 | VARIANT: Market: single-asset rare-disease (~$1.5B). Smart money: platform with &gt;$1B peak QTORIN + venous malformations/angiokeratomas/pitavastatin programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>18</v>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>KYMR</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kymera Therapeutics</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>$6.5B</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>$80</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3-5x</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>13:1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>BVF #1 position 14.6% of $3.14B book ($458M) + Baker Bros 4.1% / $721M; BOTH anchored $86 follow-on</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Oral biologic disruption (oral Dupixent = $14B+ franchise displacement); TPD structural pharma platform shift; Phase 1b execution risk masks platform value</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Cash $1.55B + BVF 14.6% MAX conviction + Baker 4.1% = multi-fund convergence. BUT major catalyst BROADEN2 mid-2027 = 12+ months away (low velocity). Strong setup, slow trigger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Targeted protein degradation platform. Lead KT-621 oral STAT6 degrader competes with injectable Dupixent ($14B+ franchise). IRAK4 partnered with Sanofi. | VALUATION: $1.55B cash (runway 2029); Dec 2025 follow-on $602M at $86</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: BROADEN2 AD mid-2027 (12+ months); BREADTH asthma late 2027; FDA Fast Track granted both | VARIANT: Market: Phase 1b execution risk. Two top biotech specialists: oral Dupixent-disruptor with peak $5-10B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="n">
+        <v>28</v>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>BNTC</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Benitec Biopharma</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>$200M</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>$8</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3-5x</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7:1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Suvretta 44.1% 13D (Suvretta's LARGEST stake by % ownership)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Gene therapy speculative single platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Suvretta 44.1% 13D = LARGEST stake by %. Gene therapy platform. Multi-program optionality. Higher risk than other biotech-multi-fund names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Gene therapy platform anchor position. Suvretta 44.1% 13D anchor stake (largest activist ownership in their portfolio). PIPE participation Nov 2025. | VALUATION: Sub-$300M biotech; gene therapy platform optionality</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Multiple gene-therapy programs in development; clinical readouts upcoming | VARIANT: 44.1% ownership creates board influence + asymmetric upside on clinical reads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" t="n">
+        <v>37</v>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>RERATED</t>
+        </is>
+      </c>
+      <c r="D21" s="34" t="inlineStr">
+        <is>
+          <t>PRICED</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>CELC</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Celcuity</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>$8B (post-data)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>$165</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1.3-2x post-data</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Baker Bros 19.99% ACTIVIST 13D = $904M / 5.48% of $17.4B book</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Targeted oncology secular but Phase 3 data + PT raises captured the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Phase 3 May 1 POSITIVE + +76% PT raises already in price. ASCO Jun 2 + PDUFA Jul 17 remain but pre-quantified. Quality+catalysts but entry economics weakened post-data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Phase 3 VIKTORIA-1 PIK3CA-mut POSITIVE May 1 2026 (76% PFS hazard reduction). Gedatolisib pan-PI3K/mTOR oncology. Triplet vs alpelisib+fulvestrant. Multiple HR+/HER2- breast cancer cohorts. | VALUATION: $387M cash + accepted NDA + Priority Review = de-risked; 4-5x peak rev precedent</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: JUNE 2 ASCO LBA1008 oral + JULY 17 PDUFA goal date (2 catalysts in 8 weeks) | VARIANT: Market: alpelisib-class peak ($1-2B). Baker Bros 19.99% 13D activist: $5-10B peak (triplet displaces alpelisib + captures WT segment).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>40</v>
+      </c>
+      <c r="C25" s="33" t="inlineStr">
+        <is>
+          <t>RERATED</t>
+        </is>
+      </c>
+      <c r="D25" s="34" t="inlineStr">
+        <is>
+          <t>PRICED</t>
+        </is>
+      </c>
+      <c r="E25" s="28" t="inlineStr">
+        <is>
+          <t>ASND</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ascendis Pharma</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>$15.3B</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>$247</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1.2-1.5x</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>RA Capital 24.9% of $9.44B = $2.35B = LARGEST single biotech crossover position; held since 2015</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Rare endocrine pricing secular but YORVIPATH ramp captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: YORVIPATH ramp priced. €247M Q1 (2x YoY) already at $247. Multiple normalized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: TransCon prodrug platform: SKYTROFA (GHD), YORVIPATH (hypopara), YUVIWEL (achondroplasia approved Feb 2026). &gt;1,000 new US YORVIPATH enrollments Q1; 6,300+ patients across 2,700 prescribers. | VALUATION: Profitable (22% non-IFRS op margin); €247M Q1 (2x YoY); peak rev YORVIPATH $4-5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: YUVIWEL ramp + Q2/Q3 YORVIPATH growth + TransCon CNP follow-on indications | VARIANT: Sell-side: $15B endocrine specialty maturing. RA Capital: $30B+ at 70-90K addressable hypopara population. Analyst high $345 (Barclays).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A23:M23"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A20:M20"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A28:M28"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A24:M24"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A27:M27"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A26:M26"/>
+    <mergeCell ref="A2:M2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1765,7 +2390,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2049,7 +2674,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2494,375 +3119,6 @@
     <mergeCell ref="A15:M15"/>
     <mergeCell ref="A7:M7"/>
     <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A10:M10"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>7. Hard Asset / Royalty — ENTRY-TODAY × TAILWIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Definition: Irreplaceable asset ownership (royalty, land, minerals) with no recurring capex requirement and cash-flow distribution structure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Within-Rank</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Master-Rank</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Re-rate</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Tailwind</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Mcap</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>Asym</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>Upside</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>R/R</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>Smart Money</t>
-        </is>
-      </c>
-      <c r="M4" s="13" t="inlineStr">
-        <is>
-          <t>Secular Driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>NRP</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Natural Resource Partners</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>$1.35B</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>$105.81</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2.5-3x</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>13:1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Saber 17.75% + Greystone top + Right Tail NEW + Berkowitz</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Met coal (no green substitute for steelmaking) + Sisecam soda ash (solar glass + EV battery) = TWO structural tailwinds masked by dying-thermal-coal narrative; 6.6x vs TPL 25x is a TRUE comp gap</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: 14.5% FCF yield ALONE = pure mispricing. Royalty trust at 6.6x P/FCF vs TPL at 25x P/CF (SAME asset class) = comp gap re-rate. Distribution Nov 2026 + preferreds retire. Saber 17.75% + Right Tail NEW Q1 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: [See Archetype 1] | VALUATION: [See Archetype 1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Nov 2026 distribution + preferreds retire | VARIANT: [See Archetype 1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" t="n">
-        <v>24</v>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t>JOE</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>St. Joe Company</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>$2.8B</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>$48</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2-3x to LIFO-NAV</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>10:1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Berkowitz/Fairholme longstanding anchor</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Florida population growth secular but slow re-rate; Berkowitz anchor recognized</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: 170k Florida Panhandle acres. GAAP B/M understates LIFO land basis vs market. True NAV-based B/M likely &gt;1.0. Berkowitz anchor + Florida population growth.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Florida Panhandle landbank with 170k+ acres. GAAP B/M understates LIFO land basis vs market value. True NAV-based B/M likely &gt;1.0 even at current price. | VALUATION: Land bank: 170k acres NW Florida; GAAP B/M understates LIFO land basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Florida population growth + master plan community development + Berkowitz anchor | VARIANT: Yartseva fails on size + low GAAP B/M; correct framework is Lynch asset play.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" t="n">
-        <v>34</v>
-      </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="D13" s="34" t="inlineStr">
-        <is>
-          <t>PRICED</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="inlineStr">
-        <is>
-          <t>TPL</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Texas Pacific Land Trust</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>$30B</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>$1300</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>1.3-1.5x</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>5:1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Multi-fund quality holders; HRC anchor</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Permian premium already at 25x P/CF; secular real but no asymmetry from here</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: Already at 25x P/CF premium = ENDLESS DRILLING priced. NAV-vs-GAAP issue similar to JOE but multiple no longer cheap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Permian water + royalty optionality. Same NAV-vs-GAAP-book issue as JOE. Pricing 'endless drilling' premium. | VALUATION: Permian royalty trust at 25x P/CF (vs NRP at 6x)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Permian production growth + water revenue optionality | VARIANT: Yartseva captures FCF yield + ROA but understates B/M for land assets.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="A7:M7"/>
     <mergeCell ref="A16:M16"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A11:M11"/>
@@ -2899,14 +3155,14 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>8. Foreign / Underfollowed Value — ENTRY-TODAY × TAILWIND</t>
+          <t>7. Hard Asset / Royalty — ENTRY-TODAY × TAILWIND</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Definition: Listed outside primary US market or in segment poorly covered by US sell-side. Currency arbitrage + institutional underweight = entry edge.</t>
+          <t>Definition: Irreplaceable asset ownership (royalty, land, minerals) with no recurring capex requirement and cash-flow distribution structure.</t>
         </is>
       </c>
     </row>
@@ -2982,44 +3238,44 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>MTY.TO</t>
+          <t>NRP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MTY Food Group</t>
+          <t>Natural Resource Partners</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C$887M</t>
+          <t>$1.35B</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>C$40.41</t>
+          <t>$105.81</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2-2.5x</t>
+          <t>2.5-3x</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -3029,19 +3285,19 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CEO open-market buy</t>
+          <t>Saber 17.75% + Greystone top + Right Tail NEW + Berkowitz</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>QSR franchise consolidation secular (Inspire/RBI/Roark precedent) recognized but multiple at trough</t>
+          <t>Met coal (no green substitute for steelmaking) + Sisecam soda ash (solar glass + EV battery) = TWO structural tailwinds masked by dying-thermal-coal narrative; 6.6x vs TPL 25x is a TRUE comp gap</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: AT BOOK 1.04x + 16.7% FCF yield = pure value. M&amp;A pool at 12-14x EBITDA vs trading 7.5x = M&amp;A precedent arb. CEO Lefebvre open-market buy at C$30.54 = sponsor put. QSR consolidation trend.</t>
+          <t>ENTRY-TODAY: 14.5% FCF yield ALONE = pure mispricing. Royalty trust at 6.6x P/FCF vs TPL at 25x P/CF (SAME asset class) = comp gap re-rate. Distribution Nov 2026 + preferreds retire. Saber 17.75% + Right Tail NEW Q1 2026.</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3311,7 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Q2 2026 SSS test + NCIB | VARIANT: [See Archetype 1]</t>
+          <t>CATALYST: Nov 2026 distribution + preferreds retire | VARIANT: [See Archetype 1]</t>
         </is>
       </c>
     </row>
@@ -3064,80 +3320,80 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>BZU.IM</t>
+          <t>JOE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buzzi SpA</t>
+          <t>St. Joe Company</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>€8.9B</t>
+          <t>$2.8B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>€49</t>
+          <t>$48</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.7-2x (Kerrisdale €85 PT)</t>
+          <t>2-3x to LIFO-NAV</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>10:1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Kerrisdale Capital published long thesis Oct 2025 (€85 PT)</t>
+          <t>Berkowitz/Fairholme longstanding anchor</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>AI data-center concrete demand (US data-center capex translates to cement orders); 52% EBITDA from US; institutional underweight on Italian listing</t>
+          <t>Florida population growth secular but slow re-rate; Berkowitz anchor recognized</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: 6.8x EV/EBITDA vs peers 9-11x. AI data-center concrete demand = real (not theoretical). 52% EBITDA from US. Kerrisdale Oct 2025 €85 PT (+73%). Italian listing = institutional underweight = re-rate slow but explicit.</t>
+          <t>ENTRY-TODAY: 170k Florida Panhandle acres. GAAP B/M understates LIFO land basis vs market. True NAV-based B/M likely &gt;1.0. Berkowitz anchor + Florida population growth.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Italian cement (€8.9B mcap). 52% of EBITDA from US. AI data-center concrete demand thesis. Trading at sector-discount multiple to LafargeHolcim/CRH peers. | VALUATION: 6.8x EV/EBITDA (vs peer 9-11x); €85 PT = +73% upside</t>
+          <t>THESIS: Florida Panhandle landbank with 170k+ acres. GAAP B/M understates LIFO land basis vs market value. True NAV-based B/M likely &gt;1.0 even at current price. | VALUATION: Land bank: 170k acres NW Florida; GAAP B/M understates LIFO land basis</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: AI data-center capex translating to concrete orders; multiple re-rate to peer levels | VARIANT: Italian listing + cement = institutional underweight. Kerrisdale Oct 2025 long thesis 73% upside.</t>
+          <t>CATALYST: Florida population growth + master plan community development + Berkowitz anchor | VARIANT: Yartseva fails on size + low GAAP B/M; correct framework is Lynch asset play.</t>
         </is>
       </c>
     </row>
@@ -3146,80 +3402,80 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D13" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
+        <v>34</v>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>PRICED</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Texas Pacific Land Trust</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$1.89B</t>
+          <t>$30B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$13</t>
+          <t>$1300</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>1.3-1.5x</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>12:1</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Nine Ten Capital (Bares) 13.1% of book / 3.48M sh / $41.4M</t>
+          <t>Multi-fund quality holders; HRC anchor</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>CTV ad spend doubling 2024-2028 (eMarketer); INDEPENDENT SSP that survived ad-tech wash-out = winner-take-most; Netflix/Disney/Roku exclusive deals scaling; market priced "ad-tech roadkill"</t>
+          <t>Permian premium already at 25x P/CF; secular real but no asymmetry from here</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Independent CTV SSP = winner of ad-tech wash-out. Netflix/Disney/Roku scaling. AI integration. Nine Ten 13.1% / 3.48M sh = highest concentration.</t>
+          <t>ENTRY-TODAY: Already at 25x P/CF premium = ENDLESS DRILLING priced. NAV-vs-GAAP issue similar to JOE but multiple no longer cheap.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Independent CTV SSP. Netflix/Disney/Roku exclusive deals scaling. AI ad-buying integration. Last major non-Google scaled SSP. | VALUATION: Yartseva 6/7 (sub-$2B), B/M 0.49, FCF yield positive, ROA positive</t>
+          <t>THESIS: Permian water + royalty optionality. Same NAV-vs-GAAP-book issue as JOE. Pricing 'endless drilling' premium. | VALUATION: Permian royalty trust at 25x P/CF (vs NRP at 6x)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: CTV ad spend doubling 2024-2028 + Netflix exclusive scaling + AI integration | VARIANT: Market: ad-tech roadkill. Smart: winning independent CTV SSP that survived ad-tech wash-out.</t>
+          <t>CATALYST: Permian production growth + water revenue optionality | VARIANT: Yartseva captures FCF yield + ROA but understates B/M for land assets.</t>
         </is>
       </c>
     </row>
@@ -3268,14 +3524,14 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>9. Quality Compounder at Trough — ENTRY-TODAY × TAILWIND</t>
+          <t>8. Foreign / Underfollowed Value — ENTRY-TODAY × TAILWIND</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Definition: Defensive quality business at multi-year low multiple due to transitory headwind. Re-rate when consensus catches up to recovery.</t>
+          <t>Definition: Listed outside primary US market or in segment poorly covered by US sell-side. Currency arbitrage + institutional underweight = entry edge.</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3607,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
@@ -3365,66 +3621,66 @@
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>MTY.TO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>MTY Food Group</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>$25B</t>
+          <t>C$887M</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$52.75</t>
+          <t>C$40.41</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>2-2.5x</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>12:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Multi-fund deep-value funds Q1 2026</t>
+          <t>CEO open-market buy</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>IT services AI accelerator (vs disruptor) debate; partial market acceptance</t>
+          <t>QSR franchise consolidation secular (Inspire/RBI/Roark precedent) recognized but multiple at trough</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Yartseva 6/7 + 9.88% FCF yield + ROA 10.44% + -27% 6mo. AI accelerator-not-disruptor thesis. Defensive value vs deep-value pure play.</t>
+          <t>ENTRY-TODAY: AT BOOK 1.04x + 16.7% FCF yield = pure value. M&amp;A pool at 12-14x EBITDA vs trading 7.5x = M&amp;A precedent arb. CEO Lefebvre open-market buy at C$30.54 = sponsor put. QSR consolidation trend.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Yartseva 6/7 IT services franchise. Multi-fund consensus Q1 2026. 300k+ delivery workforce moat. AI/IT services capex super-cycle 2026-2028. | VALUATION: P/B 1.66 (B/M 0.60), 9.88% FCF yield, ROA 10.44%, -27% 6mo</t>
+          <t>THESIS: [See Archetype 1] | VALUATION: [See Archetype 1]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: AI implementation winner via enterprise partners + Q2 2026 earnings | VARIANT: Market: AI disrupts IT services. Smart: AI accelerator not disruptor.</t>
+          <t>CATALYST: Q2 2026 SSS test + NCIB | VARIANT: [See Archetype 1]</t>
         </is>
       </c>
     </row>
@@ -3433,44 +3689,44 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
-      </c>
-      <c r="C9" s="31" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+        <v>22</v>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>BZU.IM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>Buzzi SpA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$65B</t>
+          <t>€8.9B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$638</t>
+          <t>€49</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.5-2x</t>
+          <t>1.7-2x (Kerrisdale €85 PT)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3480,33 +3736,33 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Founder-led; multi-fund pharma specialist holds</t>
+          <t>Kerrisdale Capital published long thesis Oct 2025 (€85 PT)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Aging demographic + ophthalmology + immunology pipeline partially priced</t>
+          <t>AI data-center concrete demand (US data-center capex translates to cement orders); 52% EBITDA from US; institutional underweight on Italian listing</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Defensive quality. Pipeline optionality. Partial trough recovery underway.</t>
+          <t>ENTRY-TODAY: 6.8x EV/EBITDA vs peers 9-11x. AI data-center concrete demand = real (not theoretical). 52% EBITDA from US. Kerrisdale Oct 2025 €85 PT (+73%). Italian listing = institutional underweight = re-rate slow but explicit.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Founder/CEO Schleifer + Yancopoulos R&amp;D-led. $31.4B book equity + EYLEA franchise + Linvoseltamab launching. Pipeline broad. Itepekimab Phase 3 readout potential catalyst. | VALUATION: B/M 0.48, FCF yield 6.33%, P/B 2.07; Yartseva 6/7 (size only fail)</t>
+          <t>THESIS: Italian cement (€8.9B mcap). 52% of EBITDA from US. AI data-center concrete demand thesis. Trading at sector-discount multiple to LafargeHolcim/CRH peers. | VALUATION: 6.8x EV/EBITDA (vs peer 9-11x); €85 PT = +73% upside</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Itepekimab 2026-2027 data + Linvoseltamab ramp | VARIANT: Market: fianlimab miss + Eylea biosimilar. Smart: broad pipeline + buyback + founder skin.</t>
+          <t>CATALYST: AI data-center capex translating to concrete orders; multiple re-rate to peer levels | VARIANT: Italian listing + cement = institutional underweight. Kerrisdale Oct 2025 long thesis 73% upside.</t>
         </is>
       </c>
     </row>
@@ -3515,80 +3771,80 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>41</v>
-      </c>
-      <c r="C13" s="33" t="inlineStr">
-        <is>
-          <t>RERATED</t>
-        </is>
-      </c>
-      <c r="D13" s="34" t="inlineStr">
-        <is>
-          <t>PRICED</t>
+        <v>25</v>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Danaher</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$122B</t>
+          <t>$1.89B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$171</t>
+          <t>$13</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.3-1.5x</t>
+          <t>3-5x</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>12:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>D1 Capital +312% Q1 ($107M→$437M, 4th-largest position)</t>
+          <t>Nine Ten Capital (Bares) 13.1% of book / 3.48M sh / $41.4M</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Bioprocessing cycle now consensus 2H 2026</t>
+          <t>CTV ad spend doubling 2024-2028 (eMarketer); INDEPENDENT SSP that survived ad-tech wash-out = winner-take-most; Netflix/Disney/Roku exclusive deals scaling; market priced "ad-tech roadkill"</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Bouncing from trough; bioprocessing cycle now consensus; multiple expansion captured. Defensive 2H 2026 fully priced.</t>
+          <t>ENTRY-TODAY: Independent CTV SSP = winner of ad-tech wash-out. Netflix/Disney/Roku scaling. AI integration. Nine Ten 13.1% / 3.48M sh = highest concentration.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Pure-play life sciences (Cytiva bioprocessing, Beckman Dx, Cepheid). Q1 EPS $2.06 beat by 6.2%; bioprocessing inflecting positive after destock; Cepheid respiratory comp resets Q4 2026. | VALUATION: 19.7x forward P/E (trough vs 5yr avg 30x); ROA pos; B/M 0.43</t>
+          <t>THESIS: Independent CTV SSP. Netflix/Disney/Roku exclusive deals scaling. AI ad-buying integration. Last major non-Google scaled SSP. | VALUATION: Yartseva 6/7 (sub-$2B), B/M 0.49, FCF yield positive, ROA positive</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Bioprocessing book-to-bill durably &gt;1.0 + China VBP stabilization H2 2026 + Cepheid Q4 reset | VARIANT: Consensus: show-me on growth post-destock. Sundheim/D1: same stock 2019-2021 (30%/yr) at trough multiple while H2 2026 comps inflect.</t>
+          <t>CATALYST: CTV ad spend doubling 2024-2028 + Netflix exclusive scaling + AI integration | VARIANT: Market: ad-tech roadkill. Smart: winning independent CTV SSP that survived ad-tech wash-out.</t>
         </is>
       </c>
     </row>
@@ -3611,6 +3867,375 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>9. Quality Compounder at Trough — ENTRY-TODAY × TAILWIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Definition: Defensive quality business at multi-year low multiple due to transitory headwind. Re-rate when consensus catches up to recovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Within-Rank</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Master-Rank</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Re-rate</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Tailwind</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Mcap</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Asym</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Smart Money</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>Secular Driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>$25B</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>$52.75</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2-3x</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>12:1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Multi-fund deep-value funds Q1 2026</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>IT services AI accelerator (vs disruptor) debate; partial market acceptance</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Yartseva 6/7 + 9.88% FCF yield + ROA 10.44% + -27% 6mo. AI accelerator-not-disruptor thesis. Defensive value vs deep-value pure play.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Yartseva 6/7 IT services franchise. Multi-fund consensus Q1 2026. 300k+ delivery workforce moat. AI/IT services capex super-cycle 2026-2028. | VALUATION: P/B 1.66 (B/M 0.60), 9.88% FCF yield, ROA 10.44%, -27% 6mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: AI implementation winner via enterprise partners + Q2 2026 earnings | VARIANT: Market: AI disrupts IT services. Smart: AI accelerator not disruptor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>35</v>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Regeneron</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>$65B</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>$638</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1.5-2x</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>8:1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Founder-led; multi-fund pharma specialist holds</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Aging demographic + ophthalmology + immunology pipeline partially priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Defensive quality. Pipeline optionality. Partial trough recovery underway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Founder/CEO Schleifer + Yancopoulos R&amp;D-led. $31.4B book equity + EYLEA franchise + Linvoseltamab launching. Pipeline broad. Itepekimab Phase 3 readout potential catalyst. | VALUATION: B/M 0.48, FCF yield 6.33%, P/B 2.07; Yartseva 6/7 (size only fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Itepekimab 2026-2027 data + Linvoseltamab ramp | VARIANT: Market: fianlimab miss + Eylea biosimilar. Smart: broad pipeline + buyback + founder skin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>41</v>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>RERATED</t>
+        </is>
+      </c>
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>PRICED</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>DHR</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Danaher</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>$122B</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>$171</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1.3-1.5x</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>D1 Capital +312% Q1 ($107M→$437M, 4th-largest position)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Bioprocessing cycle now consensus 2H 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Bouncing from trough; bioprocessing cycle now consensus; multiple expansion captured. Defensive 2H 2026 fully priced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Pure-play life sciences (Cytiva bioprocessing, Beckman Dx, Cepheid). Q1 EPS $2.06 beat by 6.2%; bioprocessing inflecting positive after destock; Cepheid respiratory comp resets Q4 2026. | VALUATION: 19.7x forward P/E (trough vs 5yr avg 30x); ROA pos; B/M 0.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Bioprocessing book-to-bill durably &gt;1.0 + China VBP stabilization H2 2026 + Cepheid Q4 reset | VARIANT: Consensus: show-me on growth post-destock. Sundheim/D1: same stock 2019-2021 (30%/yr) at trough multiple while H2 2026 comps inflect.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A10:M10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9564,6 +10189,1577 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>FULL UNIVERSE TIER CLASSIFICATION — NEW asymmetric candidates from 455-tab scan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>Scanned all 445 fund tabs; found 288 tickers with &gt;=3 tab mentions ex mega-caps. Of these, ~50 NOT in our current 41-name asymmetric universe. Top 25 classified into TIER 1/2/3 by variant perception + entry-today asymmetry + smart money signal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TIER LEGEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>TIER 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Multi-fund consensus + clear variant perception + entry-today asymmetry intact</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>TIER 2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Strong setup with deep value OR binary catalyst OR fund concentration</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>TIER 3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Speculative / partial signal / worth tracking</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Mcap</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Fund Signal</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Variant Perception</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Catalyst</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>Asym</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>Tailwind</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>TIER 1</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Warner Bros Discovery</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>$25B</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>10 tabs / 8 material adds / +70% max ADD</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Market: linear TV death + $36B debt overhang = terminal. Variant: HBO content moat + Zaslav cost cuts $5B + debt paydown $19B-&gt;$11B = cash flow inflection priced as bankruptcy candidate.</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>HBO Max international scaling Q3 2026 + studio M&amp;A speculation + linear TV split planned</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>2.5-4x</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>-30%</t>
+        </is>
+      </c>
+      <c r="J10" s="15" t="inlineStr">
+        <is>
+          <t>8:1</t>
+        </is>
+      </c>
+      <c r="K10" s="15" t="inlineStr">
+        <is>
+          <t>PARTIAL (streaming consolidation; pricing power inflection)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>TIER 1</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>CRH</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>CRH plc (Irish building materials)</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>$70B</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>7 tabs / 5 HC / 3 material adds</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Market: legacy materials cyclical. Variant: US data-center concrete demand = AI capex tailwind (SAME thesis as BZU.IM but US-listed = lower friction for institutional adds).</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>AI data-center cement orders + US infrastructure cycle + buyback expansion</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>1.7-2.2x</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="J11" s="15" t="inlineStr">
+        <is>
+          <t>8:1</t>
+        </is>
+      </c>
+      <c r="K11" s="15" t="inlineStr">
+        <is>
+          <t>NOT (AI data-center concrete unpriced — same as BZU.IM but US-friction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>TIER 1</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>PCG</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>PG&amp;E</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>$40B</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>8 tabs / 8 HC / 2 material adds / +83% max ADD</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>Market: California wildfire risk + bankruptcy stigma. Variant: AB 1054 wildfire fund passed + Diablo Canyon extension + AI data-center load growth in NorCal = utility re-rate to peer multiple.</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>AI/EV electricity demand growth + rate case approvals + dividend restoration H2 2026</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>1.8-2.5x</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>-25%</t>
+        </is>
+      </c>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>7:1</t>
+        </is>
+      </c>
+      <c r="K12" s="15" t="inlineStr">
+        <is>
+          <t>NOT (AI data-center electricity demand unpriced for CA utility)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>TIER 1</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>MDGL</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Madrigal Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>$7.5B</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>5 HC / 1 new init / +149% max ADD</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Market: single-asset post-approval (resmetirom for NASH/MASH). Variant: First-mover advantage on $5-10B MASH TAM with addressable 2-3M patients; current penetration &lt;5% = early innings.</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>Rezdiffra commercial ramp Q2-Q3 2026 + Phase 3 cirrhotic readout 2027 + EU launch</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>2-3x</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>-30%</t>
+        </is>
+      </c>
+      <c r="J13" s="15" t="inlineStr">
+        <is>
+          <t>8:1</t>
+        </is>
+      </c>
+      <c r="K13" s="15" t="inlineStr">
+        <is>
+          <t>NOT (MASH treatment paradigm shift)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>TIER 1</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>SHC</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Sotera Health</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>$3.5B</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>4 HC / 3 material adds / +9% max ADD (also held by Kerrisdale +9% Q1)</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>Market: ethylene oxide litigation + COTY-style asbestos overhang. Variant: Critical sterilization MOAT for medical devices ($4B addressable, no green substitute) + lawsuits settled = pure compounder.</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>Litigation overhang resolution + medical device sterilization volume growth</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>2-3x</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>-25%</t>
+        </is>
+      </c>
+      <c r="J14" s="15" t="inlineStr">
+        <is>
+          <t>9:1</t>
+        </is>
+      </c>
+      <c r="K14" s="15" t="inlineStr">
+        <is>
+          <t>NOT (medical device sterilization moat unpriced post-litigation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>TIER 2</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>$110B</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>5 HC / 4 material adds / +200% max ADD</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>Market: HBM oversupply by 2027. Variant: AI memory demand structural; Micron HBM3E qualified for NVDA Blackwell = supply-constrained pricing power through 2027.</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>HBM3E ramp + DDR5 pricing + AI memory share gains</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>1.5-2x</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>-25%</t>
+        </is>
+      </c>
+      <c r="J15" s="15" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="K15" s="15" t="inlineStr">
+        <is>
+          <t>PARTIAL (AI memory partly priced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>TIER 2</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>CLBT</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Cellebrite DI</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>$3.5B</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>4 HC / 3 material adds / +340% max ADD (massive)</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>Market: niche digital forensics. Variant: AI-enabled law enforcement evidence platform; mission-critical software with 90%+ gross margin = SaaS quality at unrecognized multiple.</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>Federal AI procurement budget + UFED Cloud growth</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>2-3x</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>-30%</t>
+        </is>
+      </c>
+      <c r="J16" s="15" t="inlineStr">
+        <is>
+          <t>7:1</t>
+        </is>
+      </c>
+      <c r="K16" s="15" t="inlineStr">
+        <is>
+          <t>NOT (AI law enforcement spend secular)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>TIER 2</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>KVUE</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Kenvue (J&amp;J consumer spinoff)</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>$45B</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>3 HC / 3 new init / +169% max ADD</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Market: spinoff orphan + Tylenol/autism litigation noise. Variant: Tylenol/Listerine/Band-Aid brand portfolio at sub-12x P/E with category leadership; lawsuits dismissed.</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>Q2 2026 brand growth proof + litigation closure + dividend hike</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>1.6-2x</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="J17" s="15" t="inlineStr">
+        <is>
+          <t>6:1</t>
+        </is>
+      </c>
+      <c r="K17" s="15" t="inlineStr">
+        <is>
+          <t>PARTIAL (consumer staples re-rate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>TIER 2</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>CPNG</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Coupang (Korean e-commerce)</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>$50B</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>6 HC / 5 material adds / +66% max ADD</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Market: Korean consumer weakness + Eats losses. Variant: Korean Prime monopoly + Eats break-even + AI logistics moat = post-MaaS profitability inflection.</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>Q2 2026 op margin proof + Taiwan expansion + Eats break-even</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>1.8-2.2x</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>-25%</t>
+        </is>
+      </c>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>7:1</t>
+        </is>
+      </c>
+      <c r="K18" s="15" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="80" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>TIER 2</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>BLDR</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Builders FirstSource</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>$14B</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>5 HC / 3 material adds / +597% MAX ADD</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>Market: housing slowdown cyclical. Variant: structural undersupply 4M+ homes + scale advantages over fragmented competitors + buyback math.</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>Mortgage rate cuts + housing starts inflection + buyback compounding</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>2-3x</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>-30%</t>
+        </is>
+      </c>
+      <c r="J19" s="15" t="inlineStr">
+        <is>
+          <t>7:1</t>
+        </is>
+      </c>
+      <c r="K19" s="15" t="inlineStr">
+        <is>
+          <t>NOT (US housing supply shortage unpriced — peer to MRP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>TIER 2</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>SDRL</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Seadrill</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>$2.5B</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>1 13D / 3 material adds / +597% MAX ADD</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Market: declining oil demand peak. Variant: offshore drilling rig shortage post-bankruptcies; day rates +60% off-cycle; 7th-gen drillships scarce.</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>Day rate spike + tender awards + Petrobras contracts H2 2026</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>2-3x</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>-40%</t>
+        </is>
+      </c>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>6:1</t>
+        </is>
+      </c>
+      <c r="K20" s="15" t="inlineStr">
+        <is>
+          <t>PARTIAL (deepwater supply gap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>TIER 2</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>MNKTQ</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Mallinckrodt (post-bankruptcy)</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>&lt;$200M</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>3 13D / 3 material adds (post-BK emergence)</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>Market: opioid bankruptcy stigma + specialty pharma decline. Variant: post-BK clean balance sheet + Acthar gel + 3 distressed-debt funds anchored.</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>Post-BK equity rerate + specialty pharma growth + Acthar Medicare path</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>2-4x</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>-40%</t>
+        </is>
+      </c>
+      <c r="J21" s="15" t="inlineStr">
+        <is>
+          <t>6:1</t>
+        </is>
+      </c>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>TIER 2</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>AERO</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Grupo Aeromexico (post-BK)</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>~$2B</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>1 13D / 2 material adds / 4 new positions</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>Market: post-BK Mexican carrier discount. Variant: Silver Point + SVPGlobal + Baupost all NEW = distressed value experts confirming thesis post-emergence.</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>Mexican aviation cycle + tourism rebound + JV with Delta</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>1.7-2.5x</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>-30%</t>
+        </is>
+      </c>
+      <c r="J22" s="15" t="inlineStr">
+        <is>
+          <t>6:1</t>
+        </is>
+      </c>
+      <c r="K22" s="15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>TIER 2</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>APG</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>API Group</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>$11B</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>7 HC / 2 material adds / +48% max</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>Market: industrial services low-growth. Variant: Chubb Fire &amp; Security acquisition synergy + recurring service revenue 70% + cross-sell.</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>Chubb integration + M&amp;A platform growth</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>1.8-2.2x</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="J23" s="15" t="inlineStr">
+        <is>
+          <t>7:1</t>
+        </is>
+      </c>
+      <c r="K23" s="15" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>TIER 2</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>AppLovin</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>$110B (mega cap-ish)</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>5 HC / 4 material adds</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>Market: ad-tech roadkill peer (CRTO/DV). Variant: AXON AI ad targeting platform inflection + gaming installs = winner of post-ATT mobile ad recovery.</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>AXON expansion + AI ad targeting moat</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>1.4-1.8x (high mcap dilutes asymmetry)</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>-25%</t>
+        </is>
+      </c>
+      <c r="J24" s="15" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="K24" s="15" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>TIER 3</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>$25B</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>4 HC / 2 material adds / 1 13D / +40% max</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>AI infra GPU-as-a-service; bubble valuation but moat real</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>Hyperscaler contracts + NVDA capacity allocation</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>1.5-2x</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>-50%</t>
+        </is>
+      </c>
+      <c r="J25" s="15" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="K25" s="15" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="80" customHeight="1">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>TIER 3</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>SATS</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>EchoStar (Ergen)</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>$3B</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>6 HC / 2 material adds / 2 new positions</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>Ergen-controlled spectrum + DISH merger optionality</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>DISH transaction + spectrum monetization</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>2-4x</t>
+        </is>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>-50%</t>
+        </is>
+      </c>
+      <c r="J26" s="15" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="K26" s="15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="80" customHeight="1">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>TIER 3</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>RVMD</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Revolution Medicines</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>$8B</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>5 HC / 1 new init</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>KRAS-mutant oncology multi-asset platform</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>RMC-6236 Phase 3 readouts 2027</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>2-3x</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>-40%</t>
+        </is>
+      </c>
+      <c r="J27" s="15" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="K27" s="15" t="inlineStr">
+        <is>
+          <t>NOT (KRAS unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="80" customHeight="1">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>TIER 3</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>MicroStrategy</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>$60B</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>5 HC / 3 material adds</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>Bitcoin treasury proxy; convertible structure</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>Bitcoin price + dilution mechanics</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>1.5-3x</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>-50%</t>
+        </is>
+      </c>
+      <c r="J28" s="15" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="K28" s="15" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="80" customHeight="1">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>TIER 3</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>UNF</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>UniFirst</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>$3B</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>1 HC / 1 13D / 2 material adds / +640% MAX ADD</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>Uniform rental cyclical; Cintas precedent at 25x; activist setup</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>PE bid or activist board pressure</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>1.5-2.5x</t>
+        </is>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>-25%</t>
+        </is>
+      </c>
+      <c r="J29" s="15" t="inlineStr">
+        <is>
+          <t>6:1</t>
+        </is>
+      </c>
+      <c r="K29" s="15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="80" customHeight="1">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>TIER 3</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>DoorDash</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>$70B</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>3 HC / 3 material adds / 2 new / +236% max ADD</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>Cycle through cohort math; profitable inflection</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>Operating leverage Q2-Q3 + grocery expansion</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="inlineStr">
+        <is>
+          <t>1.5-2x</t>
+        </is>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>-25%</t>
+        </is>
+      </c>
+      <c r="J30" s="15" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="K30" s="15" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="80" customHeight="1">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>TIER 3</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>CNC</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Centene</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>$30B</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>3 HC / 3 material adds / 2 new / +69% max</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>Medicare Advantage rate cuts overhang; Medicaid redeterminations</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>2026 bid cycle clarity + state Medicaid wins</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>1.7-2.2x</t>
+        </is>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>-30%</t>
+        </is>
+      </c>
+      <c r="J31" s="15" t="inlineStr">
+        <is>
+          <t>6:1</t>
+        </is>
+      </c>
+      <c r="K31" s="15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="80" customHeight="1">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>TIER 3</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>$60B</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>3 HC / 2 new init / +112% max</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>Crypto trading rebound + regulatory clarity</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>Spot ETF growth + Base L2 + staking yield</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="inlineStr">
+        <is>
+          <t>1.5-2.5x</t>
+        </is>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>-40%</t>
+        </is>
+      </c>
+      <c r="J32" s="15" t="inlineStr">
+        <is>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="K32" s="15" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="80" customHeight="1">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>TIER 3</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>EXAS</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Exact Sciences</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>$15B</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>Already mentioned earlier — 3 funds +157% max ADD</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>Cologuard moat + MCED expansion</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>CMS coverage + MCED launch</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="inlineStr">
+        <is>
+          <t>1.7-2.2x</t>
+        </is>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>-30%</t>
+        </is>
+      </c>
+      <c r="J33" s="15" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="K33" s="15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="80" customHeight="1">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>TIER 3</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>CHYM</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Chime Financial</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>~$15B (post-IPO)</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>3 HC / 4 new positions</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>Post-IPO neobank consolidation; growth thesis</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>Profitability inflection + customer add growth</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>1.5-2.5x</t>
+        </is>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>-40%</t>
+        </is>
+      </c>
+      <c r="J34" s="15" t="inlineStr">
+        <is>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="K34" s="15" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12669,7 +14865,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13848,8 +16044,8 @@
     <mergeCell ref="A8:M8"/>
     <mergeCell ref="A22:M22"/>
     <mergeCell ref="A35:M35"/>
+    <mergeCell ref="A43:M43"/>
     <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A43:M43"/>
     <mergeCell ref="A38:M38"/>
     <mergeCell ref="A52:M52"/>
     <mergeCell ref="A10:M10"/>
@@ -13886,628 +16082,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>2. Activist Board Catalyst — ENTRY-TODAY × TAILWIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Definition: Schedule 13D filing with board seat secured or imminent + activist demands for value unlock. Dated trigger creates near-term volatility around catalyst.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Within-Rank</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Master-Rank</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Re-rate</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Tailwind</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Mcap</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>Asym</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>Upside</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>R/R</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>Smart Money</t>
-        </is>
-      </c>
-      <c r="M4" s="13" t="inlineStr">
-        <is>
-          <t>Secular Driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>MRP</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Millrose Properties</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>$4.59B</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>$25</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1.8-2.5x to NAV</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>13:1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Lennar 80%+ owner = patient capital lock-in; SITG multi-fund flag</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>US housing supply shortage structural (4M+ undersupply) + Lennar 80% off-take = guaranteed demand; market treats as spinoff orphan, not housing-cycle play</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: B/M 1.274 = DEEPEST in 6/7 cohort (deeper than NRP 0.47). Lennar 80% owner = guaranteed off-take + patient capital. Land bank at COST BASIS vs market. Pure NAV unwind; spinoff orphan technical pressure resolves into Q2 prints.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Lennar 80%+ owner spinoff with 100k+ optioned lots at cost basis. Land bank trading below NAV with Lennar as guaranteed off-take partner. Housing-cycle recovery levered. | VALUATION: B/M 1.274 (DEEPEST in 6/7 tier; deeper than NRP's 0.47), pure NAV play</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Q2 2026 print + Lennar volume scaling + housing cycle inflection | VARIANT: Market priced spinoff orphan technical pressure. Smart money: pure land cash-cow at discount to NAV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" t="n">
-        <v>14</v>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D9" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t>FUN</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Six Flags Entertainment</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>$2.2B</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>$25</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2-3x (3x outright sale)</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>9:1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>H Partners 53.7% / $82.5M / 5.7% of class; Jana 9% + Travis Kelce co-invest</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Theme parks cyclical consumer discretionary</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: 42 parks IRREPLACEABLE RE @ $47M each = $2B floor. Jaffer joined board May 26 + Jana 9% pushing OUTRIGHT SALE = two-front activist pressure. H Partners 53.7% / 5.7% of class. Sale = violent 3x trigger.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Post-Cedar Fair/Six Flags merger consolidation. 42 parks irreplaceable real estate. Q1 2026 rev +12%, attendance +4%, per-cap +6%. $200M synergy target ($120M cost + $80M growth). | VALUATION: $5.27B net debt = 7x leverage; EV/EBITDA 9x on $1.05B 2027 EBITDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: May 26 2026 AGM: Jaffer joins board (Class III through 2027, Audit&amp;Finance Cttee). Jana 9% pushing OUTRIGHT SALE. | VARIANT: Street: broken merger story. Two-front activist pressure (governance + sale) + per-park RE floor $47M each.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D13" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="inlineStr">
-        <is>
-          <t>AAP</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Advance Auto Parts</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>$3.3B</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>$54.42</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>8</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2.5-3x ($130-150 AZO comp)</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>9:1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>H Partners 46.3% / $71.2M / +50% sh Q1 2026 (1.35M sh); Legion Partners precedent</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Auto aftermarket mature; H Partners margin recovery thesis is operational not secular</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: -80% drawdown from 2021. H Partners 46.3% + Q1 +50% sh add ($71.2M). Bridge thesis: AZO-style 8-10% margins = $130-150. Q2 Aug 2026 = margin proof catalyst. Op margin +410bps already. Not cash-floored but H Partners concentration = sponsor put.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: #3 aftermarket retailer post-WorldPac sale. Q1 +3.5% comps (Pro mid-single, DIY low-single). 700+ stores closed; ~1,300 strategic locations remain. Bridge to AZO-style 8-10% margins = $130-150/sh. | VALUATION: 3.8% op margin (rising +410bps), FY26 guide $2.40-3.10 EPS; sub-1x sales; M&amp;A floor 0.8x sales = $80/sh</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Q2 2026 earnings Aug = needs comps +2%+ and op margin &gt;5%; H Partners 13D escalation possible | VARIANT: Consensus PT $57 (dead money). H Partners 46% concentration implies AAP returns to AZO margins.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" t="n">
-        <v>16</v>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D17" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="E17" s="28" t="inlineStr">
-        <is>
-          <t>ACHC</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Acadia Healthcare</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>$3.2B</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>$33</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>8</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2-3x + squeeze</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>6:1</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Greenlight Capital 4.1M sh (David Einhorn); Sohn presentation 5/12/2026</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Behavioral health secular demand (mental health structural) but DOJ regulatory overhang dominates pricing</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: -70% drawdown + 29% SHORT FLOAT = squeeze fuel. EV/EBITDA 6.5x vs peers 8-9x. DOJ resolution binary catalyst. Greenlight 4.1M sh + Sohn 5/12 pitch = thesis surfaced publicly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Largest US behavioral health network (260+ facilities). DOJ Medicaid investigation overhang. Q1 2026 admissions stabilizing. Greenlight 4.1M activist; Sohn 5/12 pitch. | VALUATION: EV/EBITDA 6.5x (vs HCA 9x, UHS 8x); 29% short float; -70% drawdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: DOJ resolution + Q2 2026 earnings + 29% short squeeze potential | VARIANT: Market: DOJ/Medicaid existential. Greenlight: provider necessity + facility footprint + de-rate captured = floor near current.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>5</v>
-      </c>
-      <c r="B21" t="n">
-        <v>30</v>
-      </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D21" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="E21" s="28" t="inlineStr">
-        <is>
-          <t>QRHC</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Quest Resource Holding</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>$200M</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>$7</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>6</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2-3x</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>8:1</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Wynnefield 13.3% / 2.73M sh / 13D w/ board seat</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Waste services minimal secular</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: Wynnefield 13.3% 13D w/ board seat. Sub-$200M micro waste services. Recurring revenue.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Wynnefield filed 13D 13.3% May 2025; Robert Lipstein joined board. Cooperation Agreement w/ standstill until 30 days before 2027 nomination window. Asset-light recurring waste mgmt. | VALUATION: Sub-$200M micro; recurring waste services revenue model</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Operational improvements + Wynnefield additional buying if dips | VARIANT: Market: small-cap value trap. Activist: board seat + potential value-unlock initiatives.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>6</v>
-      </c>
-      <c r="B25" t="n">
-        <v>31</v>
-      </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D25" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="E25" s="28" t="inlineStr">
-        <is>
-          <t>POSTBPB</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Potbelly Corp (PBPB)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>$240M</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>$8</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>6</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2-3x</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>8:1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Nierenberg/D3 largest shareholder; 13D/A active March 2025</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Restaurant chain cyclical; no secular</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: Nierenberg/D3 LARGEST shareholder (~$16.4M / 7% book). Restaurant turnaround + soft activist pressure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Nierenberg/D3 is LARGEST shareholder (~$16.4M / 7% of D3 book). Customer-traffic gains while peers don't (Q1 2026 letter thesis). Form 4 insider buying by Nierenberg at depressed levels. | VALUATION: Sub-$300M micro restaurant chain; turnaround stage</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Restaurant turnaround + Nierenberg potential escalation | VARIANT: Market: tier-2 restaurant chain. Activist soft-pressure thesis.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A23:M23"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A22:M22"/>
-    <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="A28:M28"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="A24:M24"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="A27:M27"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="A26:M26"/>
-    <mergeCell ref="A2:M2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/investment_archetypes.xlsx
+++ b/investment_archetypes.xlsx
@@ -8,23 +8,24 @@
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="TIER S+ Secular×Asymmetric" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MAX Skin + Recent Entry" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="POSITION INTENSITY" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="MICRO+SMALL CAP INTENSITY" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="AGGRESSIVE BUY SIGNALS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="FULL UNIVERSE NEW Tiers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="MASTER Entry-Today" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="1. Yartseva Pure Multibagger" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="2. Activist Board Catalyst" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="3. Biotech Multi-Fund Convergen" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="4. Sponsor-Anchored Holdco Tran" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="5. Spinoff - SoTP Arbitrage" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="6. Deep Drawdown Mean Reversion" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="7. Hard Asset - Royalty" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="8. Foreign - Underfollowed Valu" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="9. Quality Compounder at Trough" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="10. Hedged - Special Structure" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="FORENSIC ENTRY-TODAY TIER 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TIER S+ Secular×Asymmetric" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MAX Skin + Recent Entry" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="POSITION INTENSITY" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="MICRO+SMALL CAP INTENSITY" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="AGGRESSIVE BUY SIGNALS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="FULL UNIVERSE NEW Tiers" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="MASTER Entry-Today" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="1. Yartseva Pure Multibagger" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="2. Activist Board Catalyst" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="3. Biotech Multi-Fund Convergen" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="4. Sponsor-Anchored Holdco Tran" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="5. Spinoff - SoTP Arbitrage" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="6. Deep Drawdown Mean Reversion" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="7. Hard Asset - Royalty" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="8. Foreign - Underfollowed Valu" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="9. Quality Compounder at Trough" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="10. Hedged - Special Structure" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -154,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -229,6 +230,9 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -949,7 +953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -970,14 +974,14 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>2. Activist Board Catalyst — ENTRY-TODAY × TAILWIND</t>
+          <t>1. Yartseva Pure Multibagger — ENTRY-TODAY × TAILWIND</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Definition: Schedule 13D filing with board seat secured or imminent + activist demands for value unlock. Dated trigger creates near-term volatility around catalyst.</t>
+          <t>Definition: Sub-$2B mcap; B/M &gt;0.40; FCF yield &gt;5%; ROA &gt;0; near 52w low; 6mo negative. Pure quantitative multibagger setup per CAFE WP 33 (Feb 2025).</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
@@ -1067,66 +1071,66 @@
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>MRP</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Millrose Properties</t>
+          <t>OptimizeRx</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>$4.59B</t>
+          <t>$93M</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$25</t>
+          <t>$4.82</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.8-2.5x to NAV</t>
+          <t>2-4x ($11.50 PT)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>13:1</t>
+          <t>12:1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Lennar 80%+ owner = patient capital lock-in; SITG multi-fund flag</t>
+          <t>Insider 14.82%; $10M buyback through March 2027; Doximity exec Presti to board April 2026</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>US housing supply shortage structural (4M+ undersupply) + Lennar 80% off-take = guaranteed demand; market treats as spinoff orphan, not housing-cycle play</t>
+          <t>Digital pharma messaging shift to EHR-native channels (Doximity-style TAM); pharma DTC compliance with MFN actually accelerates digital share; market focused on near-term MFN overhang</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: B/M 1.274 = DEEPEST in 6/7 cohort (deeper than NRP 0.47). Lennar 80% owner = guaranteed off-take + patient capital. Land bank at COST BASIS vs market. Pure NAV unwind; spinoff orphan technical pressure resolves into Q2 prints.</t>
+          <t>ENTRY-TODAY: SUB-BOOK 0.70x + $19M FCF profitable + insider 14.82% + analyst $11.50 (138%) + sub-$100M float = ANY DSP Q4 print violently re-rates. Smart money still building (not exiting). True intrinsic value &gt; 2x current.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Lennar 80%+ owner spinoff with 100k+ optioned lots at cost basis. Land bank trading below NAV with Lennar as guaranteed off-take partner. Housing-cycle recovery levered. | VALUATION: B/M 1.274 (DEEPEST in 6/7 tier; deeper than NRP's 0.47), pure NAV play</t>
+          <t>THESIS: Digital health POC pharma messaging to 60%+ US prescribers. May 21 2026 DeepIntent integration = first DSP accessing OPRX EHR network (Q3 2026 launch) opens &gt;80% of digital pharma budgets. | VALUATION: P/B 0.70 (sub-book), P/FCF 4.89, 15.7% FCF yield, EV/Sales 0.88, Adj EBITDA 4.4x EV</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Q2 2026 print + Lennar volume scaling + housing cycle inflection | VARIANT: Market priced spinoff orphan technical pressure. Smart money: pure land cash-cow at discount to NAV.</t>
+          <t>CATALYST: Q4 2026 DSP integration revenue start + Q2 2026 earnings Aug 14 | VARIANT: Market: MFN victim; Smart money: profitable ($19M FCF) at 0.7x book, target $11.50 (138% upside).</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1139,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
@@ -1149,66 +1153,66 @@
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>FUN</t>
+          <t>INMD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Six Flags Entertainment</t>
+          <t>InMode Ltd</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$2.2B</t>
+          <t>$869M</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$25</t>
+          <t>$13.71</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2-3x (3x outright sale)</t>
+          <t>2-3x ($25-30)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>9:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>H Partners 53.7% / $82.5M / 5.7% of class; Jana 9% + Travis Kelce co-invest</t>
+          <t>Steel Partners 25.5% of book; Mizrahy +800k sh ($10.7M)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Theme parks cyclical consumer discretionary</t>
+          <t>Aesthetic devices = cyclical consumer, not secular structural</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: 42 parks IRREPLACEABLE RE @ $47M each = $2B floor. Jaffer joined board May 26 + Jana 9% pushing OUTRIGHT SALE = two-front activist pressure. H Partners 53.7% / 5.7% of class. Sale = violent 3x trigger.</t>
+          <t>ENTRY-TODAY: CASH FLOOR: $8.47/sh = 62% of $13.71. Steel Partners 25.5% book + implied $18-20 takeout. Founder Mizrahy +800k sh ($10.7M Feb 2026) at current = sponsor put. Cash + M&amp;A double-floor; upside on Steel re-bid.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Post-Cedar Fair/Six Flags merger consolidation. 42 parks irreplaceable real estate. Q1 2026 rev +12%, attendance +4%, per-cap +6%. $200M synergy target ($120M cost + $80M growth). | VALUATION: $5.27B net debt = 7x leverage; EV/EBITDA 9x on $1.05B 2027 EBITDA</t>
+          <t>THESIS: Israeli aesthetic device leader (Morpheus8, BodyTite). 85% recurring consumables. Steel Partners +155% Q1 2026 = 25.5% of their book; founder Mizrahy bought 800k sh ($10.7M) Feb 2026. | VALUATION: P/B 1.32, FCF $537M cash = $8.47/sh (62% of price), 77.8% gross margin</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: May 26 2026 AGM: Jaffer joins board (Class III through 2027, Audit&amp;Finance Cttee). Jana 9% pushing OUTRIGHT SALE. | VARIANT: Street: broken merger story. Two-front activist pressure (governance + sale) + per-park RE floor $47M each.</t>
+          <t>CATALYST: Q2 2026 earnings ~Aug 5 + potential Steel renewed bid ($18 prior) | VARIANT: Market: Israeli geopolitical + aesthetic cycle. Smart money: $11-12 floor on cash alone; Steel implied $20+ takeout.</t>
         </is>
       </c>
     </row>
@@ -1217,80 +1221,80 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D13" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
+        <v>8</v>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>AAP</t>
+          <t>GLOB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Globant SA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$3.3B</t>
+          <t>$1.68B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$54.42</t>
+          <t>$43.50</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.5-3x ($130-150 AZO comp)</t>
+          <t>3-5x if class action clears</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>9:1</t>
+          <t>10:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>H Partners 46.3% / $71.2M / +50% sh Q1 2026 (1.35M sh); Legion Partners precedent</t>
+          <t>Cartica historical 6.5% Q4 2022; sentiment bottom 16% short float</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Auto aftermarket mature; H Partners margin recovery thesis is operational not secular</t>
+          <t>LatAm IT services + AI services adoption (Globant AI Pods); class action overhang masks secular validation</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: -80% drawdown from 2021. H Partners 46.3% + Q1 +50% sh add ($71.2M). Bridge thesis: AZO-style 8-10% margins = $130-150. Q2 Aug 2026 = margin proof catalyst. Op margin +410bps already. Not cash-floored but H Partners concentration = sponsor put.</t>
+          <t>ENTRY-TODAY: P/E 5.91 SECTOR LOW + P/FCF 5.56 + EV/EBITDA 4.95x + 17% FCF yield = DEEPLY undervalued by every metric. Class action JUN 23 IS the catalyst that creates the discount (clears = violent rerate). AI Pods $32.8M ARR from $0 in 12mo + $352M pipeline.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>THESIS: #3 aftermarket retailer post-WorldPac sale. Q1 +3.5% comps (Pro mid-single, DIY low-single). 700+ stores closed; ~1,300 strategic locations remain. Bridge to AZO-style 8-10% margins = $130-150/sh. | VALUATION: 3.8% op margin (rising +410bps), FY26 guide $2.40-3.10 EPS; sub-1x sales; M&amp;A floor 0.8x sales = $80/sh</t>
+          <t>THESIS: LatAm IT services with AI Pods inflection ($32.8M ARR from $0 in 12 months; $352M pipeline; 40% top-20 client penetration). Founder Migoya 23-year tenure + ~3% via Founders Trust. | VALUATION: P/E 5.91 (sector low), P/B 0.78, P/FCF 5.56, 17% FCF yield, EV/EBITDA 4.95</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Q2 2026 earnings Aug = needs comps +2%+ and op margin &gt;5%; H Partners 13D escalation possible | VARIANT: Consensus PT $57 (dead money). H Partners 46% concentration implies AAP returns to AZO margins.</t>
+          <t>CATALYST: Q3 2026 AI Pods print + Argentina FX tailwind + ENRGI platform launch H2 | VARIANT: Market: melting India-IT comp. Smart money: AI mix shift to higher-margin work + LatAm cost arb. CAVEAT: securities class action (lead plaintiff June 23, 2026); COO resigned July 2025 not replaced.</t>
         </is>
       </c>
     </row>
@@ -1299,80 +1303,80 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D17" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
         </is>
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>ACHC</t>
+          <t>CRTO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Acadia Healthcare</t>
+          <t>Criteo SA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>$3.2B</t>
+          <t>$866M</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>$33</t>
+          <t>$13.50</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2-3x + squeeze</t>
+          <t>2.5-4x</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>6:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Greenlight Capital 4.1M sh (David Einhorn); Sohn presentation 5/12/2026</t>
+          <t>Nierenberg D3 9.37% / +19% Q1 2026; Petrus Advisers activist</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Behavioral health secular demand (mental health structural) but DOJ regulatory overhang dominates pricing</t>
+          <t>Retail media TAM $200B by 2028 (Insider Intelligence); 235-retailer scale incl Lowes/Costco; OpenAI partnership live; market priced terminal decline, missed shift to Commerce Yield retail media</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: -70% drawdown + 29% SHORT FLOAT = squeeze fuel. EV/EBITDA 6.5x vs peers 8-9x. DOJ resolution binary catalyst. Greenlight 4.1M sh + Sohn 5/12 pitch = thesis surfaced publicly.</t>
+          <t>ENTRY-TODAY: P/E 3.73 fwd + P/FCF 4.98 + EV/EBITDA 2.28x + 20.7% FCF yield = DEEP. Q3 2026 anniversary of scope losses REMOVES the headwind printed in Q1. Petrus Advisers activist + $200M buyback (22% cap) + Nierenberg D3 +19% Q1.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Largest US behavioral health network (260+ facilities). DOJ Medicaid investigation overhang. Q1 2026 admissions stabilizing. Greenlight 4.1M activist; Sohn 5/12 pitch. | VALUATION: EV/EBITDA 6.5x (vs HCA 9x, UHS 8x); 29% short float; -70% drawdown</t>
+          <t>THESIS: Performance ad-tech pivoting to Commerce Yield retail media (235 retailers incl Lowes/Costco). $1B+ media spend Q1 2026 (+8% cc). OpenAI partnership live with 1,000+ brands. Q1 retail media -31% ex-scope -- actual underlying +24%. | VALUATION: P/E 3.73 (fwd), P/B 0.79, P/FCF 4.98, EV/EBITDA 2.28, 20.7% FCF yield</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: DOJ resolution + Q2 2026 earnings + 29% short squeeze potential | VARIANT: Market: DOJ/Medicaid existential. Greenlight: provider necessity + facility footprint + de-rate captured = floor near current.</t>
+          <t>CATALYST: Q3 2026 anniversary of scope losses + Luxembourg redomiciliation + $200M buyback (22% cap) | VARIANT: Market prices terminal decline; Petrus Advisers activist + 33% FCF yield + retail media TAM $200B by 2028.</t>
         </is>
       </c>
     </row>
@@ -1381,80 +1385,80 @@
         <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D21" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
         </is>
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
-          <t>QRHC</t>
+          <t>NRP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Quest Resource Holding</t>
+          <t>Natural Resource Partners</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>$200M</t>
+          <t>$1.35B</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>$7</t>
+          <t>$105.81</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>2.5-3x</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Wynnefield 13.3% / 2.73M sh / 13D w/ board seat</t>
+          <t>Saber/Huber 17.75%, Greystone top, Right Tail NEW Q1 2026, Berkowitz/Fairholme</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Waste services minimal secular</t>
+          <t>Met coal (no green substitute for steelmaking) + Sisecam soda ash (solar glass + EV battery) = TWO structural tailwinds masked by dying-thermal-coal narrative; 6.6x vs TPL 25x is a TRUE comp gap</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Wynnefield 13.3% 13D w/ board seat. Sub-$200M micro waste services. Recurring revenue.</t>
+          <t>ENTRY-TODAY: 14.5% FCF yield ALONE = pure mispricing. Royalty trust at 6.6x P/FCF vs TPL at 25x P/CF (SAME asset class) = comp gap re-rate. Distribution Nov 2026 + preferreds retire. Saber 17.75% + Right Tail NEW Q1 2026.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Wynnefield filed 13D 13.3% May 2025; Robert Lipstein joined board. Cooperation Agreement w/ standstill until 30 days before 2027 nomination window. Asset-light recurring waste mgmt. | VALUATION: Sub-$200M micro; recurring waste services revenue model</t>
+          <t>THESIS: Royalty trust on 13M mineral acres + 49% Sisecam soda ash JV. Near-zero debt by mid-2026 after $109M paydown + preferred retirement. Distribution increase guided for November 2026 (delayed from prior guide due to Sisecam capital call). | VALUATION: P/B 2.26 (B/M 0.47), 14.5% FCF yield, ROA 10.5%, 6.6x P/FCF</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Operational improvements + Wynnefield additional buying if dips | VARIANT: Market: small-cap value trap. Activist: board seat + potential value-unlock initiatives.</t>
+          <t>CATALYST: Nov 2026 distribution step-up + preferreds retire; Q3 2026 Sisecam recovery sig | VARIANT: Market: dying coal MLP. Smart money: debt-free royalty with 12% FCF yield, comparable to TPL at 25x P/CF (NRP at 6x).</t>
         </is>
       </c>
     </row>
@@ -1463,40 +1467,40 @@
         <v>6</v>
       </c>
       <c r="B25" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D25" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
+      <c r="D25" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E25" s="28" t="inlineStr">
         <is>
-          <t>POSTBPB</t>
+          <t>CARS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Potbelly Corp (PBPB)</t>
+          <t>Cars.com</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>$240M</t>
+          <t>$560M</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>$8</t>
+          <t>$10</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1505,63 +1509,658 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>11:1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Nierenberg/D3 largest shareholder; 13D/A active March 2025</t>
+          <t>Yartseva 7/7 - smart money still building</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Restaurant chain cyclical; no secular</t>
+          <t>Auto digitization secular but dealer SaaS partially priced via subscription metrics</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Nierenberg/D3 LARGEST shareholder (~$16.4M / 7% book). Restaurant turnaround + soft activist pressure.</t>
+          <t>ENTRY-TODAY: P/B 0.83 + P/FCF 3.5 + 28% TTM FCF yield + EV/EBITDA 2.7x = DEEP. Q1 EPS $0.45 vs $0.13 est (+246% BEAT). $90M buyback (16% cap raised from $60M) = buyback math compounds violently with cheap multiple.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Nierenberg/D3 is LARGEST shareholder (~$16.4M / 7% of D3 book). Customer-traffic gains while peers don't (Q1 2026 letter thesis). Form 4 insider buying by Nierenberg at depressed levels. | VALUATION: Sub-$300M micro restaurant chain; turnaround stage</t>
+          <t>THESIS: Digital dealer SaaS (19,390 dealers x $2,473 ARPD/mo, 90% recurring). Q1 EPS $0.45 vs $0.13 est (+246%). Subscription +2%; OEM/National -12% (cyclical bottom). | VALUATION: P/B 0.83, P/FCF 3.5, 28% TTM FCF yield, EV/EBITDA 2.7x</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Restaurant turnaround + Nierenberg potential escalation | VARIANT: Market: tier-2 restaurant chain. Activist soft-pressure thesis.</t>
+          <t>CATALYST: $25-30M annualized cost program 2027 + $90M buyback (16% cap raised from $60M) | VARIANT: Street: declining auto Yellow Pages at 4x P/FCF. Variant: 90% SaaS dealer recurring + buyback math.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" t="n">
+        <v>19</v>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="E29" s="28" t="inlineStr">
+        <is>
+          <t>VITL</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vital Farms</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>$13</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2-3x ($30-40)</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>10:1</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>No major fund concentrated yet = entry preserved; Yartseva 6/7</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Pasture-raised premium category creation real but partially recognized</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Deepest drawdown -68.76% + 11% ROA sustained = exceptional. BUT B/M 0.74 = not deeply undervalued vs book; M&amp;A precedent 4x sales = $50 = +260%. Brand-led re-rate is SLOW not violent. No defined binary catalyst.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Pasture-raised egg category creator with brand moat. Walmart/Target/Whole Foods distribution. 11% ROA sustained THROUGH the avian flu crash = exceptional earnings power. | VALUATION: B/M 0.74, ROA 11% (BEST in 6/7 tier), -68.76% from peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Avian flu egg-supply normalization + summer pricing + M&amp;A speculation | VARIANT: Market lumped premium VITL with commodity egg crash. Reality: brand pricing power retained. Strategic buyers: Kraft Heinz, Hain, General Mills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>8</v>
+      </c>
+      <c r="B33" t="n">
+        <v>20</v>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D33" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E33" s="28" t="inlineStr">
+        <is>
+          <t>FTLF</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>FitLife Brands</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>$93M</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>$10</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>3-5x</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>13:1</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Smoak Capital residual position; previously a Smoak top-5</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Microcap nutraceutical reversion; no secular driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Microcap $93M = sub-institutional minimum = any flow violently moves. Yartseva 7/7 cleanest setup. -43.9% 6mo. B/M 0.49. Pure micro-mean-reversion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Microcap nutraceutical at $93M cap. Sub-institutional minimum. Classic Yartseva discarded-microcap profile with positive FCF + ROA + extreme drawdown. | VALUATION: P/B 2.05, B/M 0.49, FCF yield 8.2%, ROA 7.2%, near 52w low, -43.9% 6mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Q2 2026 earnings; M&amp;A speculation; recovery in supplement category | VARIANT: Market: forgotten micro. Smart money: pure Yartseva mean-reversion target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>9</v>
+      </c>
+      <c r="B37" t="n">
+        <v>21</v>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D37" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="E37" s="28" t="inlineStr">
+        <is>
+          <t>MTY.TO</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>MTY Food Group</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>C$887M</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>C$40.41</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2-2.5x</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>13:1</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>CEO Lefebvre open-market buy at C$30.54 (+33% stake)</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>QSR franchise consolidation secular (Inspire/RBI/Roark precedent) recognized but multiple at trough</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: AT BOOK 1.04x + 16.7% FCF yield = pure value. M&amp;A pool at 12-14x EBITDA vs trading 7.5x = M&amp;A precedent arb. CEO Lefebvre open-market buy at C$30.54 = sponsor put. QSR consolidation trend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Multi-brand Canadian QSR franchisor (90 banners incl Cold Stone, Mucho Burrito, Papa Murphy's). 7,000+ locations, 98%+ franchised. Q1 EPS C$0.98 BEAT vs C$0.80 cons. | VALUATION: P/B 1.04 (trading at book!), EV/EBITDA 7.5x (vs QSR peer 14-18x), 16.7% FCF yield</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Q2 2026 earnings test SSS stabilization + NCIB 5% of float through July | VARIANT: Market: melting ice cube. Variant: SSS troughing + debt paying down + M&amp;A pool (RBI, Inspire at 12-14x EBITDA).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>10</v>
+      </c>
+      <c r="B41" t="n">
+        <v>32</v>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D41" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E41" s="28" t="inlineStr">
+        <is>
+          <t>ROCK</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Gibraltar Industries</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>$1.10B</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>$39.69</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1.8-2.2x</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>7:1</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Director Metcalf bought $502k March 2026; Vanguard 5.24% 13G</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Industrial roofing cyclical post-OmniMax integration</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: OmniMax integration year. FY27 EPS $5+ at 15x = $75-90. Director Form 4 buy March 2026. Cyclical, not deep value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: 3-segment industrial (Residential 80%, Renewables, Agtech). OmniMax acquisition closed Feb 2026 ($1.335B) = #1 in residential roofing accessories. FY26 guide $1.76-1.83B rev, $3.65-4.05 EPS. | VALUATION: P/B 1.34, FCF yield 6.5%, ROA 2.95%, EV/Sales 1.0x vs peer 1.5x</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Q2 2026 earnings = first clean OmniMax quarter; aluminum normalization; Q3 reroofing season | VARIANT: Market: busted SPAC with 1.56 D/E. Variant: one-time integration year; FY27 EPS $5+ at 15x = $75-90.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>11</v>
+      </c>
+      <c r="B45" t="n">
+        <v>36</v>
+      </c>
+      <c r="C45" s="31" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="D45" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E45" s="28" t="inlineStr">
+        <is>
+          <t>DV</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>DoubleVerify</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>$1.50B</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>$9</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1.5-2x (was 3x)</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>6:1</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Insider 12.69% (high for ad-tech); Yartseva 7/7</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>CTV verification rally already underway, partial capture</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: CTV verification rally underway = partial upside captured. Q1 +10% rev printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Pure-play ad verification (68% market share in fraud detection vs IAS 2.7%). 4,300+ customers vs IAS 169. Q1 2026 rev +10%, EBITDA 31% margin. CTV +28%, social activation +92%. | VALUATION: P/FCF 11x (trough), EV/EBITDA 9.6x, EV/Sales 1.9x, 9% FCF yield</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: ABS streaming Do Not Air list rollout Q2/Q3 + Meta activation $12M ARR to $50M+ path | VARIANT: Market: Google MRC self-measurement threat. Variant: CTV verification underpenetrated (10%) vs display (70%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>12</v>
+      </c>
+      <c r="B49" t="n">
+        <v>38</v>
+      </c>
+      <c r="C49" s="33" t="inlineStr">
+        <is>
+          <t>RERATED</t>
+        </is>
+      </c>
+      <c r="D49" s="34" t="inlineStr">
+        <is>
+          <t>PRICED</t>
+        </is>
+      </c>
+      <c r="E49" s="28" t="inlineStr">
+        <is>
+          <t>HRMY</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Harmony Biosciences</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>$1.77B</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>$31</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1.5-2x</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>6:1</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>M&amp;A buyers: Jazz Pharma, Lundbeck, Otsuka; Catalyst Pharma precedent</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Orexin/sleep disorders secular validated by Lilly $6.3B Centessa; comp already priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Q1 +17% WAKIX printed; pediatric FDA Feb priced; Lilly orexin validated = thesis worked. Buy-pre-catalyst opportunity passed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: $1B+ WAKIX franchise (pitolisant for narcolepsy). Q1 2026 rev +17% to $215M; pediatric FDA approval Feb 13 2026 extends IP to 2030 (pediatric exclusivity to 2040s). 5 Phase 3 trials in pipeline. | VALUATION: P/B 1.91, P/Sales 2.05, FCF yield 19.36%, 26% net cash position</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Pitolisant GR NDA Q2 2026 (PDUFA Q1 2027); BP-205 Phase 1 PK mid-2026 | VARIANT: Market: single-product cliff. Smart money: Lilly's $6.3B Centessa (Q3 2026 close) validated orexin space + IP estate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>13</v>
+      </c>
+      <c r="B53" t="n">
+        <v>39</v>
+      </c>
+      <c r="C53" s="33" t="inlineStr">
+        <is>
+          <t>RERATED</t>
+        </is>
+      </c>
+      <c r="D53" s="34" t="inlineStr">
+        <is>
+          <t>PRICED</t>
+        </is>
+      </c>
+      <c r="E53" s="28" t="inlineStr">
+        <is>
+          <t>TREE</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>LendingTree</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>$525M</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>$37.50</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>4</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1.3-1.7x</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Yartseva 7/7 + post-Q1 inflection demonstrated</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Insurance up-cycle secular now consensus post-Q1 inflection</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Q1 +37% rev / +71% EBITDA already PRINTED. S&amp;P upgraded. Insurance cycle now consensus. Inflection over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Three-segment marketplace (Insurance 68%, Consumer 20%, Home 12%) at Q1 2026 inflection: rev +37%, VMM +28%, EBITDA +71%, Insurance +51%. Net leverage falling 3.4x→2.1x; S&amp;P upgraded. | VALUATION: P/E 2.92, P/FCF 7.2, ROE 88.6%, B/M 0.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Q2 2026 print + $575M July 2025 converts retired + Fed rate cuts unlock Home/Consumer | VARIANT: Street disbelieves Insurance durability. Variant: insurance carriers in year-2 of 5-7yr up-cycle = $200M+ EBITDA into 2027.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="41">
     <mergeCell ref="A14:M14"/>
     <mergeCell ref="A23:M23"/>
+    <mergeCell ref="A32:M32"/>
     <mergeCell ref="A8:M8"/>
     <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A35:M35"/>
     <mergeCell ref="A20:M20"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A43:M43"/>
+    <mergeCell ref="A52:M52"/>
     <mergeCell ref="A10:M10"/>
     <mergeCell ref="A28:M28"/>
     <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A44:M44"/>
+    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="A34:M34"/>
+    <mergeCell ref="A40:M40"/>
+    <mergeCell ref="A48:M48"/>
+    <mergeCell ref="A30:M30"/>
+    <mergeCell ref="A39:M39"/>
     <mergeCell ref="A15:M15"/>
     <mergeCell ref="A24:M24"/>
     <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A51:M51"/>
+    <mergeCell ref="A36:M36"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A6:M6"/>
     <mergeCell ref="A7:M7"/>
     <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A54:M54"/>
+    <mergeCell ref="A46:M46"/>
     <mergeCell ref="A27:M27"/>
     <mergeCell ref="A12:M12"/>
     <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A50:M50"/>
     <mergeCell ref="A26:M26"/>
+    <mergeCell ref="A56:M56"/>
+    <mergeCell ref="A55:M55"/>
     <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A47:M47"/>
+    <mergeCell ref="A42:M42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1594,14 +2193,14 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>3. Biotech Multi-Fund Convergence — ENTRY-TODAY × TAILWIND</t>
+          <t>2. Activist Board Catalyst — ENTRY-TODAY × TAILWIND</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Definition: Two or more top biotech crossover specialists (Baker Bros, RA Capital, BVF, Stonepine, Suvretta) anchored at high conviction in same name. Convergence is the high-signal pattern.</t>
+          <t>Definition: Schedule 13D filing with board seat secured or imminent + activist demands for value unlock. Dated trigger creates near-term volatility around catalyst.</t>
         </is>
       </c>
     </row>
@@ -1677,7 +2276,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
@@ -1691,66 +2290,66 @@
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>PRLD</t>
+          <t>MRP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Prelude Therapeutics</t>
+          <t>Millrose Properties</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>$340M</t>
+          <t>$4.59B</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$4.26</t>
+          <t>$25</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3-8x</t>
+          <t>1.8-2.5x to NAV</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Baker Bros 15.5% 13D/A + RA Capital 9.99% 13G; BOTH anchored SAME $90M April financing at $4.44</t>
+          <t>Lennar 80%+ owner = patient capital lock-in; SITG multi-fund flag</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Targeted protein degradation platform structural pharma shift + JAK2V617F addresses 95% PV/60% ET/55% MF (aging demographic, no oral comp); SMARCA2 fail = thrown out with platform</t>
+          <t>US housing supply shortage structural (4M+ undersupply) + Lennar 80% off-take = guaranteed demand; market treats as spinoff orphan, not housing-cycle play</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: NET CASH $2.20/sh = 51% of $4.26 price = downside FLOORED. Baker Bros 15.5% 13D + RA Capital 9.99% 13G BOTH anchored SAME April $90M financing at $4.44 — buying TODAY $4.26 is BELOW smart money entry. JAK2 binary upside 5-10x.</t>
+          <t>ENTRY-TODAY: B/M 1.274 = DEEPEST in 6/7 cohort (deeper than NRP 0.47). Lennar 80% owner = guaranteed off-take + patient capital. Land bank at COST BASIS vs market. Pure NAV unwind; spinoff orphan technical pressure resolves into Q2 prints.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Precision oncology / molecular glue / degrader platform. SMARCA2 discontinued 2025; pivot to JAK2V617F (PRT12396) + KAT6A (PRT13722). AbCellera partnership. | VALUATION: $175M cash vs $340M mcap = $2.20/sh net cash (51% of price); buyout floor near current</t>
+          <t>THESIS: Lennar 80%+ owner spinoff with 100k+ optioned lots at cost basis. Land bank trading below NAV with Lennar as guaranteed off-take partner. Housing-cycle recovery levered. | VALUATION: B/M 1.274 (DEEPEST in 6/7 tier; deeper than NRP's 0.47), pure NAV play</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: PRT12396 Phase 1 H2 2026; PRT13722 IND mid-2026; Incyte option agreement Nov 2025 | VARIANT: Market: broken story post-SMARCA2 fail. Smart money: April 2026 refunding = platform-validation thesis. JAK2 mutant-selective addresses 95% PV/60% ET/55% MF.</t>
+          <t>CATALYST: Q2 2026 print + Lennar volume scaling + housing cycle inflection | VARIANT: Market priced spinoff orphan technical pressure. Smart money: pure land cash-cow at discount to NAV.</t>
         </is>
       </c>
     </row>
@@ -1759,80 +2358,80 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>PVLA</t>
+          <t>FUN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Palvella Therapeutics</t>
+          <t>Six Flags Entertainment</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$1.56B</t>
+          <t>$2.2B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$130</t>
+          <t>$25</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>2-3x (3x outright sale)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>10:1</t>
+          <t>9:1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>BVF 3.8% / $120M (8.5% of company) + Suvretta 3.67% / $144M (+29.3% Q1)</t>
+          <t>H Partners 53.7% / $82.5M / 5.7% of class; Jana 9% + Travis Kelce co-invest</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Rare-disease pricing structural ($300k+ orphan); QTORIN platform with multiple programs (LMs, venous malformations, angiokeratomas); market priced single-asset story</t>
+          <t>Theme parks cyclical consumer discretionary</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Cash $25/sh = 19% of $130 price. Phase 3 SELVA POSITIVE Feb 24 2026 = DE-RISKED. Pre-NDA Q2 + NDA H2 + PDUFA H1 2027 = staircase of catalysts. BVF 8.5% of company + Suvretta 3.67% (+29.3% Q1).</t>
+          <t>ENTRY-TODAY: 42 parks IRREPLACEABLE RE @ $47M each = $2B floor. Jaffer joined board May 26 + Jana 9% pushing OUTRIGHT SALE = two-front activist pressure. H Partners 53.7% / 5.7% of class. Sale = violent 3x trigger.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Rare-disease topical platform. QTORIN rapamycin gel for microcystic LMs (Breakthrough + Orphan + Fast Track). Phase 3 SELVA POSITIVE Feb 24 2026 (mLM-IGA +2.13, p&lt;0.001). | VALUATION: $261.9M cash = $25/sh (19% of price). Phase 3 derisked. M&amp;A floor 4-6x peak rev</t>
+          <t>THESIS: Post-Cedar Fair/Six Flags merger consolidation. 42 parks irreplaceable real estate. Q1 2026 rev +12%, attendance +4%, per-cap +6%. $200M synergy target ($120M cost + $80M growth). | VALUATION: $5.27B net debt = 7x leverage; EV/EBITDA 9x on $1.05B 2027 EBITDA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Pre-NDA FDA meeting Q2 2026; NDA H2 2026; PDUFA H1 2027 | VARIANT: Market: single-asset rare-disease (~$1.5B). Smart money: platform with &gt;$1B peak QTORIN + venous malformations/angiokeratomas/pitavastatin programs.</t>
+          <t>CATALYST: May 26 2026 AGM: Jaffer joins board (Class III through 2027, Audit&amp;Finance Cttee). Jana 9% pushing OUTRIGHT SALE. | VARIANT: Street: broken merger story. Two-front activist pressure (governance + sale) + per-park RE floor $47M each.</t>
         </is>
       </c>
     </row>
@@ -1841,80 +2440,80 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D13" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>KYMR</t>
+          <t>AAP</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kymera Therapeutics</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$6.5B</t>
+          <t>$3.3B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$80</t>
+          <t>$54.42</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>2.5-3x ($130-150 AZO comp)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>13:1</t>
+          <t>9:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>BVF #1 position 14.6% of $3.14B book ($458M) + Baker Bros 4.1% / $721M; BOTH anchored $86 follow-on</t>
+          <t>H Partners 46.3% / $71.2M / +50% sh Q1 2026 (1.35M sh); Legion Partners precedent</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Oral biologic disruption (oral Dupixent = $14B+ franchise displacement); TPD structural pharma platform shift; Phase 1b execution risk masks platform value</t>
+          <t>Auto aftermarket mature; H Partners margin recovery thesis is operational not secular</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Cash $1.55B + BVF 14.6% MAX conviction + Baker 4.1% = multi-fund convergence. BUT major catalyst BROADEN2 mid-2027 = 12+ months away (low velocity). Strong setup, slow trigger.</t>
+          <t>ENTRY-TODAY: -80% drawdown from 2021. H Partners 46.3% + Q1 +50% sh add ($71.2M). Bridge thesis: AZO-style 8-10% margins = $130-150. Q2 Aug 2026 = margin proof catalyst. Op margin +410bps already. Not cash-floored but H Partners concentration = sponsor put.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Targeted protein degradation platform. Lead KT-621 oral STAT6 degrader competes with injectable Dupixent ($14B+ franchise). IRAK4 partnered with Sanofi. | VALUATION: $1.55B cash (runway 2029); Dec 2025 follow-on $602M at $86</t>
+          <t>THESIS: #3 aftermarket retailer post-WorldPac sale. Q1 +3.5% comps (Pro mid-single, DIY low-single). 700+ stores closed; ~1,300 strategic locations remain. Bridge to AZO-style 8-10% margins = $130-150/sh. | VALUATION: 3.8% op margin (rising +410bps), FY26 guide $2.40-3.10 EPS; sub-1x sales; M&amp;A floor 0.8x sales = $80/sh</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: BROADEN2 AD mid-2027 (12+ months); BREADTH asthma late 2027; FDA Fast Track granted both | VARIANT: Market: Phase 1b execution risk. Two top biotech specialists: oral Dupixent-disruptor with peak $5-10B.</t>
+          <t>CATALYST: Q2 2026 earnings Aug = needs comps +2%+ and op margin &gt;5%; H Partners 13D escalation possible | VARIANT: Consensus PT $57 (dead money). H Partners 46% concentration implies AAP returns to AZO margins.</t>
         </is>
       </c>
     </row>
@@ -1923,80 +2522,80 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D17" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>BNTC</t>
+          <t>ACHC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Benitec Biopharma</t>
+          <t>Acadia Healthcare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>$200M</t>
+          <t>$3.2B</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>$8</t>
+          <t>$33</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>2-3x + squeeze</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7:1</t>
+          <t>6:1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Suvretta 44.1% 13D (Suvretta's LARGEST stake by % ownership)</t>
+          <t>Greenlight Capital 4.1M sh (David Einhorn); Sohn presentation 5/12/2026</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Gene therapy speculative single platform</t>
+          <t>Behavioral health secular demand (mental health structural) but DOJ regulatory overhang dominates pricing</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Suvretta 44.1% 13D = LARGEST stake by %. Gene therapy platform. Multi-program optionality. Higher risk than other biotech-multi-fund names.</t>
+          <t>ENTRY-TODAY: -70% drawdown + 29% SHORT FLOAT = squeeze fuel. EV/EBITDA 6.5x vs peers 8-9x. DOJ resolution binary catalyst. Greenlight 4.1M sh + Sohn 5/12 pitch = thesis surfaced publicly.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Gene therapy platform anchor position. Suvretta 44.1% 13D anchor stake (largest activist ownership in their portfolio). PIPE participation Nov 2025. | VALUATION: Sub-$300M biotech; gene therapy platform optionality</t>
+          <t>THESIS: Largest US behavioral health network (260+ facilities). DOJ Medicaid investigation overhang. Q1 2026 admissions stabilizing. Greenlight 4.1M activist; Sohn 5/12 pitch. | VALUATION: EV/EBITDA 6.5x (vs HCA 9x, UHS 8x); 29% short float; -70% drawdown</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Multiple gene-therapy programs in development; clinical readouts upcoming | VARIANT: 44.1% ownership creates board influence + asymmetric upside on clinical reads.</t>
+          <t>CATALYST: DOJ resolution + Q2 2026 earnings + 29% short squeeze potential | VARIANT: Market: DOJ/Medicaid existential. Greenlight: provider necessity + facility footprint + de-rate captured = floor near current.</t>
         </is>
       </c>
     </row>
@@ -2005,80 +2604,80 @@
         <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>37</v>
-      </c>
-      <c r="C21" s="33" t="inlineStr">
-        <is>
-          <t>RERATED</t>
-        </is>
-      </c>
-      <c r="D21" s="34" t="inlineStr">
-        <is>
-          <t>PRICED</t>
+        <v>30</v>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
         </is>
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
-          <t>CELC</t>
+          <t>QRHC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Celcuity</t>
+          <t>Quest Resource Holding</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>$8B (post-data)</t>
+          <t>$200M</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>$165</t>
+          <t>$7</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.3-2x post-data</t>
+          <t>2-3x</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>8:1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Baker Bros 19.99% ACTIVIST 13D = $904M / 5.48% of $17.4B book</t>
+          <t>Wynnefield 13.3% / 2.73M sh / 13D w/ board seat</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Targeted oncology secular but Phase 3 data + PT raises captured the move</t>
+          <t>Waste services minimal secular</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Phase 3 May 1 POSITIVE + +76% PT raises already in price. ASCO Jun 2 + PDUFA Jul 17 remain but pre-quantified. Quality+catalysts but entry economics weakened post-data.</t>
+          <t>ENTRY-TODAY: Wynnefield 13.3% 13D w/ board seat. Sub-$200M micro waste services. Recurring revenue.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Phase 3 VIKTORIA-1 PIK3CA-mut POSITIVE May 1 2026 (76% PFS hazard reduction). Gedatolisib pan-PI3K/mTOR oncology. Triplet vs alpelisib+fulvestrant. Multiple HR+/HER2- breast cancer cohorts. | VALUATION: $387M cash + accepted NDA + Priority Review = de-risked; 4-5x peak rev precedent</t>
+          <t>THESIS: Wynnefield filed 13D 13.3% May 2025; Robert Lipstein joined board. Cooperation Agreement w/ standstill until 30 days before 2027 nomination window. Asset-light recurring waste mgmt. | VALUATION: Sub-$200M micro; recurring waste services revenue model</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: JUNE 2 ASCO LBA1008 oral + JULY 17 PDUFA goal date (2 catalysts in 8 weeks) | VARIANT: Market: alpelisib-class peak ($1-2B). Baker Bros 19.99% 13D activist: $5-10B peak (triplet displaces alpelisib + captures WT segment).</t>
+          <t>CATALYST: Operational improvements + Wynnefield additional buying if dips | VARIANT: Market: small-cap value trap. Activist: board seat + potential value-unlock initiatives.</t>
         </is>
       </c>
     </row>
@@ -2087,80 +2686,80 @@
         <v>6</v>
       </c>
       <c r="B25" t="n">
-        <v>40</v>
-      </c>
-      <c r="C25" s="33" t="inlineStr">
-        <is>
-          <t>RERATED</t>
-        </is>
-      </c>
-      <c r="D25" s="34" t="inlineStr">
-        <is>
-          <t>PRICED</t>
+        <v>31</v>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D25" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
         </is>
       </c>
       <c r="E25" s="28" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>POSTBPB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascendis Pharma</t>
+          <t>Potbelly Corp (PBPB)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>$15.3B</t>
+          <t>$240M</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>$247</t>
+          <t>$8</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.2-1.5x</t>
+          <t>2-3x</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>8:1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>RA Capital 24.9% of $9.44B = $2.35B = LARGEST single biotech crossover position; held since 2015</t>
+          <t>Nierenberg/D3 largest shareholder; 13D/A active March 2025</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Rare endocrine pricing secular but YORVIPATH ramp captured</t>
+          <t>Restaurant chain cyclical; no secular</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: YORVIPATH ramp priced. €247M Q1 (2x YoY) already at $247. Multiple normalized.</t>
+          <t>ENTRY-TODAY: Nierenberg/D3 LARGEST shareholder (~$16.4M / 7% book). Restaurant turnaround + soft activist pressure.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>THESIS: TransCon prodrug platform: SKYTROFA (GHD), YORVIPATH (hypopara), YUVIWEL (achondroplasia approved Feb 2026). &gt;1,000 new US YORVIPATH enrollments Q1; 6,300+ patients across 2,700 prescribers. | VALUATION: Profitable (22% non-IFRS op margin); €247M Q1 (2x YoY); peak rev YORVIPATH $4-5B</t>
+          <t>THESIS: Nierenberg/D3 is LARGEST shareholder (~$16.4M / 7% of D3 book). Customer-traffic gains while peers don't (Q1 2026 letter thesis). Form 4 insider buying by Nierenberg at depressed levels. | VALUATION: Sub-$300M micro restaurant chain; turnaround stage</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: YUVIWEL ramp + Q2/Q3 YORVIPATH growth + TransCon CNP follow-on indications | VARIANT: Sell-side: $15B endocrine specialty maturing. RA Capital: $30B+ at 70-90K addressable hypopara population. Analyst high $345 (Barclays).</t>
+          <t>CATALYST: Restaurant turnaround + Nierenberg potential escalation | VARIANT: Market: tier-2 restaurant chain. Activist soft-pressure thesis.</t>
         </is>
       </c>
     </row>
@@ -2197,6 +2796,630 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence — ENTRY-TODAY × TAILWIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Definition: Two or more top biotech crossover specialists (Baker Bros, RA Capital, BVF, Stonepine, Suvretta) anchored at high conviction in same name. Convergence is the high-signal pattern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Within-Rank</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Master-Rank</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Re-rate</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Tailwind</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Mcap</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Asym</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Smart Money</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>Secular Driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>PRLD</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Prelude Therapeutics</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>$340M</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>$4.26</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3-8x</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>20:1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Baker Bros 15.5% 13D/A + RA Capital 9.99% 13G; BOTH anchored SAME $90M April financing at $4.44</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Targeted protein degradation platform structural pharma shift + JAK2V617F addresses 95% PV/60% ET/55% MF (aging demographic, no oral comp); SMARCA2 fail = thrown out with platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: NET CASH $2.20/sh = 51% of $4.26 price = downside FLOORED. Baker Bros 15.5% 13D + RA Capital 9.99% 13G BOTH anchored SAME April $90M financing at $4.44 — buying TODAY $4.26 is BELOW smart money entry. JAK2 binary upside 5-10x.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Precision oncology / molecular glue / degrader platform. SMARCA2 discontinued 2025; pivot to JAK2V617F (PRT12396) + KAT6A (PRT13722). AbCellera partnership. | VALUATION: $175M cash vs $340M mcap = $2.20/sh net cash (51% of price); buyout floor near current</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: PRT12396 Phase 1 H2 2026; PRT13722 IND mid-2026; Incyte option agreement Nov 2025 | VARIANT: Market: broken story post-SMARCA2 fail. Smart money: April 2026 refunding = platform-validation thesis. JAK2 mutant-selective addresses 95% PV/60% ET/55% MF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>17</v>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>PVLA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Palvella Therapeutics</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>$1.56B</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>$130</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2-3x</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>10:1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>BVF 3.8% / $120M (8.5% of company) + Suvretta 3.67% / $144M (+29.3% Q1)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Rare-disease pricing structural ($300k+ orphan); QTORIN platform with multiple programs (LMs, venous malformations, angiokeratomas); market priced single-asset story</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Cash $25/sh = 19% of $130 price. Phase 3 SELVA POSITIVE Feb 24 2026 = DE-RISKED. Pre-NDA Q2 + NDA H2 + PDUFA H1 2027 = staircase of catalysts. BVF 8.5% of company + Suvretta 3.67% (+29.3% Q1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Rare-disease topical platform. QTORIN rapamycin gel for microcystic LMs (Breakthrough + Orphan + Fast Track). Phase 3 SELVA POSITIVE Feb 24 2026 (mLM-IGA +2.13, p&lt;0.001). | VALUATION: $261.9M cash = $25/sh (19% of price). Phase 3 derisked. M&amp;A floor 4-6x peak rev</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Pre-NDA FDA meeting Q2 2026; NDA H2 2026; PDUFA H1 2027 | VARIANT: Market: single-asset rare-disease (~$1.5B). Smart money: platform with &gt;$1B peak QTORIN + venous malformations/angiokeratomas/pitavastatin programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>18</v>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>KYMR</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kymera Therapeutics</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>$6.5B</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>$80</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3-5x</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>13:1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>BVF #1 position 14.6% of $3.14B book ($458M) + Baker Bros 4.1% / $721M; BOTH anchored $86 follow-on</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Oral biologic disruption (oral Dupixent = $14B+ franchise displacement); TPD structural pharma platform shift; Phase 1b execution risk masks platform value</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Cash $1.55B + BVF 14.6% MAX conviction + Baker 4.1% = multi-fund convergence. BUT major catalyst BROADEN2 mid-2027 = 12+ months away (low velocity). Strong setup, slow trigger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Targeted protein degradation platform. Lead KT-621 oral STAT6 degrader competes with injectable Dupixent ($14B+ franchise). IRAK4 partnered with Sanofi. | VALUATION: $1.55B cash (runway 2029); Dec 2025 follow-on $602M at $86</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: BROADEN2 AD mid-2027 (12+ months); BREADTH asthma late 2027; FDA Fast Track granted both | VARIANT: Market: Phase 1b execution risk. Two top biotech specialists: oral Dupixent-disruptor with peak $5-10B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="n">
+        <v>28</v>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>BNTC</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Benitec Biopharma</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>$200M</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>$8</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3-5x</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7:1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Suvretta 44.1% 13D (Suvretta's LARGEST stake by % ownership)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Gene therapy speculative single platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Suvretta 44.1% 13D = LARGEST stake by %. Gene therapy platform. Multi-program optionality. Higher risk than other biotech-multi-fund names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Gene therapy platform anchor position. Suvretta 44.1% 13D anchor stake (largest activist ownership in their portfolio). PIPE participation Nov 2025. | VALUATION: Sub-$300M biotech; gene therapy platform optionality</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Multiple gene-therapy programs in development; clinical readouts upcoming | VARIANT: 44.1% ownership creates board influence + asymmetric upside on clinical reads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" t="n">
+        <v>37</v>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>RERATED</t>
+        </is>
+      </c>
+      <c r="D21" s="34" t="inlineStr">
+        <is>
+          <t>PRICED</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>CELC</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Celcuity</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>$8B (post-data)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>$165</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1.3-2x post-data</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Baker Bros 19.99% ACTIVIST 13D = $904M / 5.48% of $17.4B book</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Targeted oncology secular but Phase 3 data + PT raises captured the move</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Phase 3 May 1 POSITIVE + +76% PT raises already in price. ASCO Jun 2 + PDUFA Jul 17 remain but pre-quantified. Quality+catalysts but entry economics weakened post-data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Phase 3 VIKTORIA-1 PIK3CA-mut POSITIVE May 1 2026 (76% PFS hazard reduction). Gedatolisib pan-PI3K/mTOR oncology. Triplet vs alpelisib+fulvestrant. Multiple HR+/HER2- breast cancer cohorts. | VALUATION: $387M cash + accepted NDA + Priority Review = de-risked; 4-5x peak rev precedent</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: JUNE 2 ASCO LBA1008 oral + JULY 17 PDUFA goal date (2 catalysts in 8 weeks) | VARIANT: Market: alpelisib-class peak ($1-2B). Baker Bros 19.99% 13D activist: $5-10B peak (triplet displaces alpelisib + captures WT segment).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>40</v>
+      </c>
+      <c r="C25" s="33" t="inlineStr">
+        <is>
+          <t>RERATED</t>
+        </is>
+      </c>
+      <c r="D25" s="34" t="inlineStr">
+        <is>
+          <t>PRICED</t>
+        </is>
+      </c>
+      <c r="E25" s="28" t="inlineStr">
+        <is>
+          <t>ASND</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ascendis Pharma</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>$15.3B</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>$247</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1.2-1.5x</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>RA Capital 24.9% of $9.44B = $2.35B = LARGEST single biotech crossover position; held since 2015</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Rare endocrine pricing secular but YORVIPATH ramp captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: YORVIPATH ramp priced. €247M Q1 (2x YoY) already at $247. Multiple normalized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: TransCon prodrug platform: SKYTROFA (GHD), YORVIPATH (hypopara), YUVIWEL (achondroplasia approved Feb 2026). &gt;1,000 new US YORVIPATH enrollments Q1; 6,300+ patients across 2,700 prescribers. | VALUATION: Profitable (22% non-IFRS op margin); €247M Q1 (2x YoY); peak rev YORVIPATH $4-5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: YUVIWEL ramp + Q2/Q3 YORVIPATH growth + TransCon CNP follow-on indications | VARIANT: Sell-side: $15B endocrine specialty maturing. RA Capital: $30B+ at 70-90K addressable hypopara population. Analyst high $345 (Barclays).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A23:M23"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A20:M20"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A28:M28"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A24:M24"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A27:M27"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A26:M26"/>
+    <mergeCell ref="A2:M2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2390,7 +3613,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2674,7 +3897,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3119,375 +4342,6 @@
     <mergeCell ref="A15:M15"/>
     <mergeCell ref="A7:M7"/>
     <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A10:M10"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>7. Hard Asset / Royalty — ENTRY-TODAY × TAILWIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Definition: Irreplaceable asset ownership (royalty, land, minerals) with no recurring capex requirement and cash-flow distribution structure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Within-Rank</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Master-Rank</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Re-rate</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Tailwind</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Mcap</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>Asym</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>Upside</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>R/R</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>Smart Money</t>
-        </is>
-      </c>
-      <c r="M4" s="13" t="inlineStr">
-        <is>
-          <t>Secular Driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>NRP</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Natural Resource Partners</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>$1.35B</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>$105.81</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2.5-3x</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>13:1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Saber 17.75% + Greystone top + Right Tail NEW + Berkowitz</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Met coal (no green substitute for steelmaking) + Sisecam soda ash (solar glass + EV battery) = TWO structural tailwinds masked by dying-thermal-coal narrative; 6.6x vs TPL 25x is a TRUE comp gap</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: 14.5% FCF yield ALONE = pure mispricing. Royalty trust at 6.6x P/FCF vs TPL at 25x P/CF (SAME asset class) = comp gap re-rate. Distribution Nov 2026 + preferreds retire. Saber 17.75% + Right Tail NEW Q1 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: [See Archetype 1] | VALUATION: [See Archetype 1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Nov 2026 distribution + preferreds retire | VARIANT: [See Archetype 1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" t="n">
-        <v>24</v>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t>JOE</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>St. Joe Company</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>$2.8B</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>$48</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2-3x to LIFO-NAV</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>10:1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Berkowitz/Fairholme longstanding anchor</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Florida population growth secular but slow re-rate; Berkowitz anchor recognized</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: 170k Florida Panhandle acres. GAAP B/M understates LIFO land basis vs market. True NAV-based B/M likely &gt;1.0. Berkowitz anchor + Florida population growth.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Florida Panhandle landbank with 170k+ acres. GAAP B/M understates LIFO land basis vs market value. True NAV-based B/M likely &gt;1.0 even at current price. | VALUATION: Land bank: 170k acres NW Florida; GAAP B/M understates LIFO land basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Florida population growth + master plan community development + Berkowitz anchor | VARIANT: Yartseva fails on size + low GAAP B/M; correct framework is Lynch asset play.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" t="n">
-        <v>34</v>
-      </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="D13" s="34" t="inlineStr">
-        <is>
-          <t>PRICED</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="inlineStr">
-        <is>
-          <t>TPL</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Texas Pacific Land Trust</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>$30B</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>$1300</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>1.3-1.5x</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>5:1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Multi-fund quality holders; HRC anchor</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Permian premium already at 25x P/CF; secular real but no asymmetry from here</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: Already at 25x P/CF premium = ENDLESS DRILLING priced. NAV-vs-GAAP issue similar to JOE but multiple no longer cheap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Permian water + royalty optionality. Same NAV-vs-GAAP-book issue as JOE. Pricing 'endless drilling' premium. | VALUATION: Permian royalty trust at 25x P/CF (vs NRP at 6x)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Permian production growth + water revenue optionality | VARIANT: Yartseva captures FCF yield + ROA but understates B/M for land assets.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="A7:M7"/>
     <mergeCell ref="A16:M16"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A11:M11"/>
@@ -3524,14 +4378,14 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>8. Foreign / Underfollowed Value — ENTRY-TODAY × TAILWIND</t>
+          <t>7. Hard Asset / Royalty — ENTRY-TODAY × TAILWIND</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Definition: Listed outside primary US market or in segment poorly covered by US sell-side. Currency arbitrage + institutional underweight = entry edge.</t>
+          <t>Definition: Irreplaceable asset ownership (royalty, land, minerals) with no recurring capex requirement and cash-flow distribution structure.</t>
         </is>
       </c>
     </row>
@@ -3607,44 +4461,44 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>MTY.TO</t>
+          <t>NRP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MTY Food Group</t>
+          <t>Natural Resource Partners</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C$887M</t>
+          <t>$1.35B</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>C$40.41</t>
+          <t>$105.81</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2-2.5x</t>
+          <t>2.5-3x</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -3654,19 +4508,19 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CEO open-market buy</t>
+          <t>Saber 17.75% + Greystone top + Right Tail NEW + Berkowitz</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>QSR franchise consolidation secular (Inspire/RBI/Roark precedent) recognized but multiple at trough</t>
+          <t>Met coal (no green substitute for steelmaking) + Sisecam soda ash (solar glass + EV battery) = TWO structural tailwinds masked by dying-thermal-coal narrative; 6.6x vs TPL 25x is a TRUE comp gap</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: AT BOOK 1.04x + 16.7% FCF yield = pure value. M&amp;A pool at 12-14x EBITDA vs trading 7.5x = M&amp;A precedent arb. CEO Lefebvre open-market buy at C$30.54 = sponsor put. QSR consolidation trend.</t>
+          <t>ENTRY-TODAY: 14.5% FCF yield ALONE = pure mispricing. Royalty trust at 6.6x P/FCF vs TPL at 25x P/CF (SAME asset class) = comp gap re-rate. Distribution Nov 2026 + preferreds retire. Saber 17.75% + Right Tail NEW Q1 2026.</t>
         </is>
       </c>
     </row>
@@ -3680,7 +4534,7 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Q2 2026 SSS test + NCIB | VARIANT: [See Archetype 1]</t>
+          <t>CATALYST: Nov 2026 distribution + preferreds retire | VARIANT: [See Archetype 1]</t>
         </is>
       </c>
     </row>
@@ -3689,80 +4543,80 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>BZU.IM</t>
+          <t>JOE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buzzi SpA</t>
+          <t>St. Joe Company</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>€8.9B</t>
+          <t>$2.8B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>€49</t>
+          <t>$48</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.7-2x (Kerrisdale €85 PT)</t>
+          <t>2-3x to LIFO-NAV</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8:1</t>
+          <t>10:1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Kerrisdale Capital published long thesis Oct 2025 (€85 PT)</t>
+          <t>Berkowitz/Fairholme longstanding anchor</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>AI data-center concrete demand (US data-center capex translates to cement orders); 52% EBITDA from US; institutional underweight on Italian listing</t>
+          <t>Florida population growth secular but slow re-rate; Berkowitz anchor recognized</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: 6.8x EV/EBITDA vs peers 9-11x. AI data-center concrete demand = real (not theoretical). 52% EBITDA from US. Kerrisdale Oct 2025 €85 PT (+73%). Italian listing = institutional underweight = re-rate slow but explicit.</t>
+          <t>ENTRY-TODAY: 170k Florida Panhandle acres. GAAP B/M understates LIFO land basis vs market. True NAV-based B/M likely &gt;1.0. Berkowitz anchor + Florida population growth.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Italian cement (€8.9B mcap). 52% of EBITDA from US. AI data-center concrete demand thesis. Trading at sector-discount multiple to LafargeHolcim/CRH peers. | VALUATION: 6.8x EV/EBITDA (vs peer 9-11x); €85 PT = +73% upside</t>
+          <t>THESIS: Florida Panhandle landbank with 170k+ acres. GAAP B/M understates LIFO land basis vs market value. True NAV-based B/M likely &gt;1.0 even at current price. | VALUATION: Land bank: 170k acres NW Florida; GAAP B/M understates LIFO land basis</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: AI data-center capex translating to concrete orders; multiple re-rate to peer levels | VARIANT: Italian listing + cement = institutional underweight. Kerrisdale Oct 2025 long thesis 73% upside.</t>
+          <t>CATALYST: Florida population growth + master plan community development + Berkowitz anchor | VARIANT: Yartseva fails on size + low GAAP B/M; correct framework is Lynch asset play.</t>
         </is>
       </c>
     </row>
@@ -3771,80 +4625,80 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D13" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
+        <v>34</v>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>PRICED</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Texas Pacific Land Trust</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$1.89B</t>
+          <t>$30B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$13</t>
+          <t>$1300</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3-5x</t>
+          <t>1.3-1.5x</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>12:1</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Nine Ten Capital (Bares) 13.1% of book / 3.48M sh / $41.4M</t>
+          <t>Multi-fund quality holders; HRC anchor</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>CTV ad spend doubling 2024-2028 (eMarketer); INDEPENDENT SSP that survived ad-tech wash-out = winner-take-most; Netflix/Disney/Roku exclusive deals scaling; market priced "ad-tech roadkill"</t>
+          <t>Permian premium already at 25x P/CF; secular real but no asymmetry from here</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Independent CTV SSP = winner of ad-tech wash-out. Netflix/Disney/Roku scaling. AI integration. Nine Ten 13.1% / 3.48M sh = highest concentration.</t>
+          <t>ENTRY-TODAY: Already at 25x P/CF premium = ENDLESS DRILLING priced. NAV-vs-GAAP issue similar to JOE but multiple no longer cheap.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Independent CTV SSP. Netflix/Disney/Roku exclusive deals scaling. AI ad-buying integration. Last major non-Google scaled SSP. | VALUATION: Yartseva 6/7 (sub-$2B), B/M 0.49, FCF yield positive, ROA positive</t>
+          <t>THESIS: Permian water + royalty optionality. Same NAV-vs-GAAP-book issue as JOE. Pricing 'endless drilling' premium. | VALUATION: Permian royalty trust at 25x P/CF (vs NRP at 6x)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: CTV ad spend doubling 2024-2028 + Netflix exclusive scaling + AI integration | VARIANT: Market: ad-tech roadkill. Smart: winning independent CTV SSP that survived ad-tech wash-out.</t>
+          <t>CATALYST: Permian production growth + water revenue optionality | VARIANT: Yartseva captures FCF yield + ROA but understates B/M for land assets.</t>
         </is>
       </c>
     </row>
@@ -3893,14 +4747,14 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>9. Quality Compounder at Trough — ENTRY-TODAY × TAILWIND</t>
+          <t>8. Foreign / Underfollowed Value — ENTRY-TODAY × TAILWIND</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Definition: Defensive quality business at multi-year low multiple due to transitory headwind. Re-rate when consensus catches up to recovery.</t>
+          <t>Definition: Listed outside primary US market or in segment poorly covered by US sell-side. Currency arbitrage + institutional underweight = entry edge.</t>
         </is>
       </c>
     </row>
@@ -3976,7 +4830,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
@@ -3990,66 +4844,66 @@
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>MTY.TO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>MTY Food Group</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>$25B</t>
+          <t>C$887M</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$52.75</t>
+          <t>C$40.41</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2-3x</t>
+          <t>2-2.5x</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>12:1</t>
+          <t>13:1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Multi-fund deep-value funds Q1 2026</t>
+          <t>CEO open-market buy</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>IT services AI accelerator (vs disruptor) debate; partial market acceptance</t>
+          <t>QSR franchise consolidation secular (Inspire/RBI/Roark precedent) recognized but multiple at trough</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Yartseva 6/7 + 9.88% FCF yield + ROA 10.44% + -27% 6mo. AI accelerator-not-disruptor thesis. Defensive value vs deep-value pure play.</t>
+          <t>ENTRY-TODAY: AT BOOK 1.04x + 16.7% FCF yield = pure value. M&amp;A pool at 12-14x EBITDA vs trading 7.5x = M&amp;A precedent arb. CEO Lefebvre open-market buy at C$30.54 = sponsor put. QSR consolidation trend.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Yartseva 6/7 IT services franchise. Multi-fund consensus Q1 2026. 300k+ delivery workforce moat. AI/IT services capex super-cycle 2026-2028. | VALUATION: P/B 1.66 (B/M 0.60), 9.88% FCF yield, ROA 10.44%, -27% 6mo</t>
+          <t>THESIS: [See Archetype 1] | VALUATION: [See Archetype 1]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: AI implementation winner via enterprise partners + Q2 2026 earnings | VARIANT: Market: AI disrupts IT services. Smart: AI accelerator not disruptor.</t>
+          <t>CATALYST: Q2 2026 SSS test + NCIB | VARIANT: [See Archetype 1]</t>
         </is>
       </c>
     </row>
@@ -4058,44 +4912,44 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
-      </c>
-      <c r="C9" s="31" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+        <v>22</v>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>BZU.IM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>Buzzi SpA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$65B</t>
+          <t>€8.9B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$638</t>
+          <t>€49</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.5-2x</t>
+          <t>1.7-2x (Kerrisdale €85 PT)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4105,33 +4959,33 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Founder-led; multi-fund pharma specialist holds</t>
+          <t>Kerrisdale Capital published long thesis Oct 2025 (€85 PT)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Aging demographic + ophthalmology + immunology pipeline partially priced</t>
+          <t>AI data-center concrete demand (US data-center capex translates to cement orders); 52% EBITDA from US; institutional underweight on Italian listing</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Defensive quality. Pipeline optionality. Partial trough recovery underway.</t>
+          <t>ENTRY-TODAY: 6.8x EV/EBITDA vs peers 9-11x. AI data-center concrete demand = real (not theoretical). 52% EBITDA from US. Kerrisdale Oct 2025 €85 PT (+73%). Italian listing = institutional underweight = re-rate slow but explicit.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Founder/CEO Schleifer + Yancopoulos R&amp;D-led. $31.4B book equity + EYLEA franchise + Linvoseltamab launching. Pipeline broad. Itepekimab Phase 3 readout potential catalyst. | VALUATION: B/M 0.48, FCF yield 6.33%, P/B 2.07; Yartseva 6/7 (size only fail)</t>
+          <t>THESIS: Italian cement (€8.9B mcap). 52% of EBITDA from US. AI data-center concrete demand thesis. Trading at sector-discount multiple to LafargeHolcim/CRH peers. | VALUATION: 6.8x EV/EBITDA (vs peer 9-11x); €85 PT = +73% upside</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Itepekimab 2026-2027 data + Linvoseltamab ramp | VARIANT: Market: fianlimab miss + Eylea biosimilar. Smart: broad pipeline + buyback + founder skin.</t>
+          <t>CATALYST: AI data-center capex translating to concrete orders; multiple re-rate to peer levels | VARIANT: Italian listing + cement = institutional underweight. Kerrisdale Oct 2025 long thesis 73% upside.</t>
         </is>
       </c>
     </row>
@@ -4140,80 +4994,80 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>41</v>
-      </c>
-      <c r="C13" s="33" t="inlineStr">
-        <is>
-          <t>RERATED</t>
-        </is>
-      </c>
-      <c r="D13" s="34" t="inlineStr">
-        <is>
-          <t>PRICED</t>
+        <v>25</v>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>NOT</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Danaher</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$122B</t>
+          <t>$1.89B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$171</t>
+          <t>$13</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.3-1.5x</t>
+          <t>3-5x</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>12:1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>D1 Capital +312% Q1 ($107M→$437M, 4th-largest position)</t>
+          <t>Nine Ten Capital (Bares) 13.1% of book / 3.48M sh / $41.4M</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Bioprocessing cycle now consensus 2H 2026</t>
+          <t>CTV ad spend doubling 2024-2028 (eMarketer); INDEPENDENT SSP that survived ad-tech wash-out = winner-take-most; Netflix/Disney/Roku exclusive deals scaling; market priced "ad-tech roadkill"</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>ENTRY-TODAY: Bouncing from trough; bioprocessing cycle now consensus; multiple expansion captured. Defensive 2H 2026 fully priced.</t>
+          <t>ENTRY-TODAY: Independent CTV SSP = winner of ad-tech wash-out. Netflix/Disney/Roku scaling. AI integration. Nine Ten 13.1% / 3.48M sh = highest concentration.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>THESIS: Pure-play life sciences (Cytiva bioprocessing, Beckman Dx, Cepheid). Q1 EPS $2.06 beat by 6.2%; bioprocessing inflecting positive after destock; Cepheid respiratory comp resets Q4 2026. | VALUATION: 19.7x forward P/E (trough vs 5yr avg 30x); ROA pos; B/M 0.43</t>
+          <t>THESIS: Independent CTV SSP. Netflix/Disney/Roku exclusive deals scaling. AI ad-buying integration. Last major non-Google scaled SSP. | VALUATION: Yartseva 6/7 (sub-$2B), B/M 0.49, FCF yield positive, ROA positive</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>CATALYST: Bioprocessing book-to-bill durably &gt;1.0 + China VBP stabilization H2 2026 + Cepheid Q4 reset | VARIANT: Consensus: show-me on growth post-destock. Sundheim/D1: same stock 2019-2021 (30%/yr) at trough multiple while H2 2026 comps inflect.</t>
+          <t>CATALYST: CTV ad spend doubling 2024-2028 + Netflix exclusive scaling + AI integration | VARIANT: Market: ad-tech roadkill. Smart: winning independent CTV SSP that survived ad-tech wash-out.</t>
         </is>
       </c>
     </row>
@@ -4236,6 +5090,375 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>9. Quality Compounder at Trough — ENTRY-TODAY × TAILWIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Definition: Defensive quality business at multi-year low multiple due to transitory headwind. Re-rate when consensus catches up to recovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Within-Rank</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Master-Rank</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Re-rate</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Tailwind</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Mcap</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Asym</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Smart Money</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>Secular Driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>$25B</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>$52.75</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2-3x</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>12:1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Multi-fund deep-value funds Q1 2026</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>IT services AI accelerator (vs disruptor) debate; partial market acceptance</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Yartseva 6/7 + 9.88% FCF yield + ROA 10.44% + -27% 6mo. AI accelerator-not-disruptor thesis. Defensive value vs deep-value pure play.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Yartseva 6/7 IT services franchise. Multi-fund consensus Q1 2026. 300k+ delivery workforce moat. AI/IT services capex super-cycle 2026-2028. | VALUATION: P/B 1.66 (B/M 0.60), 9.88% FCF yield, ROA 10.44%, -27% 6mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: AI implementation winner via enterprise partners + Q2 2026 earnings | VARIANT: Market: AI disrupts IT services. Smart: AI accelerator not disruptor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>35</v>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Regeneron</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>$65B</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>$638</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1.5-2x</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>8:1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Founder-led; multi-fund pharma specialist holds</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Aging demographic + ophthalmology + immunology pipeline partially priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Defensive quality. Pipeline optionality. Partial trough recovery underway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Founder/CEO Schleifer + Yancopoulos R&amp;D-led. $31.4B book equity + EYLEA franchise + Linvoseltamab launching. Pipeline broad. Itepekimab Phase 3 readout potential catalyst. | VALUATION: B/M 0.48, FCF yield 6.33%, P/B 2.07; Yartseva 6/7 (size only fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Itepekimab 2026-2027 data + Linvoseltamab ramp | VARIANT: Market: fianlimab miss + Eylea biosimilar. Smart: broad pipeline + buyback + founder skin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>41</v>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>RERATED</t>
+        </is>
+      </c>
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>PRICED</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>DHR</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Danaher</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>$122B</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>$171</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1.3-1.5x</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>D1 Capital +312% Q1 ($107M→$437M, 4th-largest position)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Bioprocessing cycle now consensus 2H 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>ENTRY-TODAY: Bouncing from trough; bioprocessing cycle now consensus; multiple expansion captured. Defensive 2H 2026 fully priced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>THESIS: Pure-play life sciences (Cytiva bioprocessing, Beckman Dx, Cepheid). Q1 EPS $2.06 beat by 6.2%; bioprocessing inflecting positive after destock; Cepheid respiratory comp resets Q4 2026. | VALUATION: 19.7x forward P/E (trough vs 5yr avg 30x); ROA pos; B/M 0.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>CATALYST: Bioprocessing book-to-bill durably &gt;1.0 + China VBP stabilization H2 2026 + Cepheid Q4 reset | VARIANT: Consensus: show-me on growth post-destock. Sundheim/D1: same stock 2019-2021 (30%/yr) at trough multiple while H2 2026 comps inflect.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A10:M10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4695,6 +5918,1638 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>FORENSIC ENTRY-TODAY TIER 1 — Brutal Buy-Today Filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>Every TIER 1 name must pass ALL 5 forensic checks: (1) Current price BELOW or AT smart money cost basis  (2) Catalyst measurable in DAYS/WEEKS (not vague H2)  (3) Variant perception STILL INTACT  (4) Bounded downside (cash/NAV/13D)  (5) Not deeply in money</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="38" t="inlineStr">
+        <is>
+          <t>TIER 1 — Passes ALL 5 forensic checks (15 names)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Mcap</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Price Today</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Smart Money Entry / vs Current</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Catalyst (Days Out)</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>Downside Floor</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>Variant Perception Intact</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>Forensic Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="95" customHeight="1">
+      <c r="A6" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>PRLD</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>$340M</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>$4.26</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Baker 15.5% + RA Cap 9.99% BOTH at $4.44 (April 2026 $90M financing)
+→ -4% UNDERWATER vs DUAL anchor entry</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>PRT12396 Phase 1 readout H2 2026 (3-6 months); Incyte option agreement Nov 2025 monetizable
+(≈ 90-180 days (H2 2026 readout))</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>$2.20 net cash/sh = 51% of price = HARD FLOOR</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>YES — SMARCA2 fail narrative dominates; market missing platform validation by Baker+RA</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>PASS — underwater dual anchor + cash floor + binary 3-6mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="95" customHeight="1">
+      <c r="A7" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>HHH</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>$3.5B</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>$63.77</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Ackman 47% via $900M common @ $100/sh + $1B preferred
+→ -36% UNDERWATER vs Ackman cost basis</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Vantage Specialty Insurance close Q2 2026 = 30-45 DAYS
+(≈ 30-45 days (Vantage close))</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>NAV $95-105/sh (RE + insurance float); -34% to NAV bottom</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>YES — RE conglomerate discount; insurance float not yet integrated in multiple</t>
+        </is>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>PASS — Ackman put floor + imminent dated catalyst + NAV discount</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="95" customHeight="1">
+      <c r="A8" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>INMD</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>$869M</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>$13.71</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Steel +155% Q1 (25.5% of $338M book) + Founder Mizrahy 800k sh @ $13.50 Feb 2026
+→ FLAT vs both Steel build and founder Feb 2026 buy</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Q2 2026 earnings ~Aug 5 (60-70 days) + Steel re-bid potential ($18 prior)
+(≈ 60-90 days (Q2 earnings))</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>$8.47/sh cash = 62% of price = HARD FLOOR</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>YES — aesthetics-cycle narrative; Steel + founder both built at current = market missing M&amp;A value</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>PASS — activist + founder dual signal AT current + cash floor + M&amp;A optionality</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="95" customHeight="1">
+      <c r="A9" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>OPRX</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>$93M</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>$4.82</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>Corporate $10M buyback executing at $4-5 + Doximity exec Presti to board April 2026 at $4.82
+→ FLAT — buyback at current; insider 14.82% aligned</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Q2 2026 earnings Aug 14 (75 days) + Q4 DSP integration revenue start (180 days)
+(≈ 75 days (Q2 earnings) / 180 days (DSP))</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>P/B 0.70 sub-book + $19M FCF; analyst PT $11.50 (+138%)</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>YES — MFN overhang masks digital pharma EHR-native shift</t>
+        </is>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>PASS — sub-book + insider 14.82% + Doximity peer exec to board + buyback at current</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="95" customHeight="1">
+      <c r="A10" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>$3.9B</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>$30</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>D3/Nierenberg +425% Q1 (LARGEST single add in 442-tab universe) built at $30
+→ FLAT vs D3 Q1 build; Director Form 4 buys May 2026 at $30-31</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>MTS spin January 4, 2027 (board-approved Sept 2025) = ~215 days
+(≈ 215 days (MTS spin Jan 4 2027))</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>SoTP: MTS $5.2B + STS $5.3B EV = $55-65/sh combined vs $30 today</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>YES — HomeSafe distraction + class action overhang masks defense+nuclear secular</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>PASS — largest single fund add in universe + insider buying May + defined spin date</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="95" customHeight="1">
+      <c r="A11" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>LQDA</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>$5.3B</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>$60</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Buckley Capital 32% LONG + PUT structure ($44.7M notional)
+→ Sophisticated hedge structure = expects violent move EITHER WAY</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>"327 patent ruling PENDING = BINARY (could be days to weeks)
+(≈ 0-90 days (patent ruling could be any time))</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>PUT-hedged structure = bounded downside; $200M cash; UTHR M&amp;A floor</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>YES — patent binary unresolved; Buckley positioning signals violent move expected</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>PASS — binary catalyst pending + sophisticated put-hedged structure + M&amp;A floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="95" customHeight="1">
+      <c r="A12" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>CTMX-WT</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>varies</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>BVF Partners 13G/A Tranche 2 warrants
+→ Warrants compress to zero at expiration</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>WARRANTS EXPIRE 7/3/2026 = ~33 DAYS
+(≈ 33 days (binary timer))</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>Warrant = -100% if expires worthless; bounded loss</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>YES — BVF biotech book quality signal; pure binary structure</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>PASS — purest dated binary in universe; BVF anchor signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="95" customHeight="1">
+      <c r="A13" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>NRP</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>$1.35B</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>$105.81</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>Right Tail Capital NEW Q1 2026 at ~$105; Saber 17.75% + Robertson family 31.75%
+→ FLAT vs Right Tail freshest entry; family aligned permanently</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Q3 2026 Sisecam recovery signal + Nov 2026 distribution step-up (90-180 days)
+(≈ 90-180 days (Q3 + Nov distribution))</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>14.5% FCF yield ALONE caps downside; debt-free by mid-2026</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>YES — dying-coal narrative masks royalty trust mechanics; 6.6x vs TPL 25x P/CF</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>PASS — 5-fund concentration + family 31.75% + Right Tail Q1 at current</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="95" customHeight="1">
+      <c r="A14" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>MRP</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>$4.59B</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>$25</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>Lennar 80%+ owner = patient capital LOCK + Brave Warrior (Greenberg) +60% Q1
+→ FLAT vs Lennar spin cost + Brave Warrior current band entry</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>Q2 2026 earnings (60-90 days) + housing-cycle inflection ongoing
+(≈ 60-90 days (Q2 print))</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>B/M 1.274 DEEPEST in cohort; land bank at cost basis</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>YES — spinoff orphan technical pressure; market treats as not housing-cycle play</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>PASS — deepest B/M + Lennar sponsor lock + Brave Warrior recent ADD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="95" customHeight="1">
+      <c r="A15" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>$25B</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>~$11</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>Multi-fund Q1 2026 adds (8 tabs) at $9-11 = AT or BELOW current; max ADD +70%
+→ FLAT to MODESTLY ABOVE smart money Q1 entry band</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>Streaming spin announcement Dec 2025 → execution timeline + Q3 2026 cash flow inflection (~120 days)
+(≈ 120 days (Q3 cash flow proof) / spin transaction 2026)</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>HBO Max content library replacement cost $30B+ vs $25B EV; spin unlocks SoTP value</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>YES — linear TV death narrative; market missing HBO Max international + cost cuts + debt paydown $36B→$11B</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>PASS — 8-fund Q1 accumulation at current band + defined spin catalyst + SoTP value</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="95" customHeight="1">
+      <c r="A16" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>SHC</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>$3.5B</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>~$14</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>Kerrisdale +9% Q1 at ~$13.50 + 4 HC + 3 ADDs across funds in Q1
+→ FLAT vs Kerrisdale recent add + multi-fund Q1 band</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>Ethylene oxide litigation resolution + Q2 2026 sterilization volume + Q3 ECO production normalization
+(≈ 60-90 days (Q2 earnings + litigation milestones))</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>Sterilization MOAT ($4B addressable, no green substitute); peer multiple 15-20x EBITDA vs 9x</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>YES — EO litigation overhang persists; market missing medical device sterilization criticality</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>PASS — Kerrisdale Q1 add at current + medical device moat + bounded litigation downside</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="95" customHeight="1">
+      <c r="A17" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>MNKTQ</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>&lt;$200M</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>post-BK trough</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>Hudson Bay 5.19% Feb 2026 + Marathon + 1 more = 3 distressed-debt fund 13D filers
+→ FLAT vs distressed fund Q1 13D entries</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Post-BK equity rerate as Acthar revenue grows + opioid liability discharged
+(≈ 90-180 days (Q2/Q3 earnings + Acthar Medicare path))</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>Acthar gel franchise + specialty pharma cash flow; distressed-debt funds reorganization mechanics</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>YES — opioid BK stigma masks clean post-BK balance sheet + specialty pharma</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>PASS — 3 distressed funds Q1 13D + post-BK trough valuation + bounded by Acthar</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="95" customHeight="1">
+      <c r="A18" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>CPNG</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>$50B</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>~$24</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>Duquesne Family +45% Q4 + Eminence + Tiger Global = 6 HC at current band
+→ FLAT to modestly above Q4-Q1 multi-fund adds</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Q2 2026 op margin proof + Eats break-even + Taiwan expansion (~60-90 days)
+(≈ 60-90 days (Q2 print))</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>Korean Prime monopoly + $5B+ cash; 3% TAM penetration</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>YES — Korean consumer weakness + Eats losses narrative; market missing logistics moat + AI logistics</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>PASS — 6-fund consensus + recent Q4 adds at current + Q2 catalyst defined</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="95" customHeight="1">
+      <c r="A19" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>PCG</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>$40B</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>~$18</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>8 HC consensus across 8 tabs + 2 material adds +83% max
+→ AT or near multi-fund deep-value entry band</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>H2 2026 dividend restoration target + Diablo Canyon decision + rate case approvals
+(≈ 120-180 days (H2 dividend + rate case))</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>AB 1054 wildfire fund passed = liability cap; AI data-center NorCal demand floor</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>YES — wildfire BK stigma persists; market missing AI/EV electricity demand growth + dividend return</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>PASS — 8 HC consensus + defined dividend catalyst + AI electricity tailwind</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="95" customHeight="1">
+      <c r="A20" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>AERO</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>~$2B</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>post-BK trough</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>Silver Point 9.0% 13G Feb 2026 + SVPGlobal NEW + Baupost ~2% = 3 distressed-value funds Q1
+→ FLAT vs three distressed fund Q1 entries</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Mexican aviation cycle + tourism rebound + Delta JV optimization (90-180 days)
+(≈ 90-180 days (Q2 traffic + Delta JV))</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>Post-BK clean balance sheet + Mexican Prime aviation slot value</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>YES — post-BK Mexican carrier discount; market missing Delta JV optimization + Mexican GDP recovery</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>PASS — Silver Point 13G + SVPGlobal + Baupost three-fund convergence at current</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="39" t="inlineStr">
+        <is>
+          <t>TIER 2 — Strong but partial signal or longer-dated catalyst (12 names)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Mcap</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Price Today</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Smart Money Entry / vs Current</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Forensic Concern (why not Tier 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="50" customHeight="1">
+      <c r="A24" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>KYMR</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>$6.5B</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>$80</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>BVF 14.6% MAX + Baker 4.1% both at $86 follow-on Dec 2025
+→ -7% UNDERWATER vs dual top biotech anchor</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>Catalyst BROADEN2 mid-2027 = 12+ months out (low velocity)</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="n"/>
+      <c r="H24" s="15" t="n"/>
+      <c r="I24" s="15" t="n"/>
+    </row>
+    <row r="25" ht="50" customHeight="1">
+      <c r="A25" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>AAP</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>$3.3B</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>$54</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>H Partners 46.3% + Q1 +50% sh add (1.35M new)
+→ MODESTLY in money (~5-15%)</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>Operational margin recovery thesis dependent on Q2 print; no cash floor</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="n"/>
+      <c r="H25" s="15" t="n"/>
+      <c r="I25" s="15" t="n"/>
+    </row>
+    <row r="26" ht="50" customHeight="1">
+      <c r="A26" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>FUN</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>$2.2B</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>$25</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>H Partners 53.7% + Jana 9% + Cove Street +1,711%
+→ FLAT to modest</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>Weather risk Q2-Q3 + synergy execution dependent; activist horizon 6-12mo</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="n"/>
+      <c r="H26" s="15" t="n"/>
+      <c r="I26" s="15" t="n"/>
+    </row>
+    <row r="27" ht="50" customHeight="1">
+      <c r="A27" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>CRTO</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>$866M</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>$13.50</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>D3 9.37% +19% Q1 + Petrus activist + $200M buyback
+→ FLAT vs D3 Q1 add band</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>Anniversary scope lap Q3 2026 = ~4 months; partial rerate already</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="n"/>
+      <c r="H27" s="15" t="n"/>
+      <c r="I27" s="15" t="n"/>
+    </row>
+    <row r="28" ht="50" customHeight="1">
+      <c r="A28" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>CLBT</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>$3.5B</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>~$21</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>4 HC + +340% max ADD
+→ PARTIAL — some adds at lower prices</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>Volatile recent run; AI procurement timing uncertain</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="15" t="n"/>
+      <c r="I28" s="15" t="n"/>
+    </row>
+    <row r="29" ht="50" customHeight="1">
+      <c r="A29" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>KVUE</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>$45B</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>~$21</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>3 NEW positions Q1 + 169% max ADD
+→ FLAT vs Q1 NEW position band</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>Litigation tail risk + slower brand growth re-rate</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="n"/>
+      <c r="H29" s="15" t="n"/>
+      <c r="I29" s="15" t="n"/>
+    </row>
+    <row r="30" ht="50" customHeight="1">
+      <c r="A30" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>BNTC</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>$200M</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr"/>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suvretta 44.1% activist (LARGEST stake by %)
+→ </t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>Single-fund concentration risk; biotech speculation</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="15" t="n"/>
+      <c r="I30" s="15" t="n"/>
+    </row>
+    <row r="31" ht="50" customHeight="1">
+      <c r="A31" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>ACHC</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>$3.2B</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>$33</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Greenlight 4.1M sh + Sohn 5/12 pitch
+→ </t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>DOJ resolution timing unknown; behavioral health regulatory tail</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="n"/>
+      <c r="H31" s="15" t="n"/>
+      <c r="I31" s="15" t="n"/>
+    </row>
+    <row r="32" ht="50" customHeight="1">
+      <c r="A32" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>PVLA</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>$1.56B</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>$130</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BVF + Suvretta +29.3% Q1
+→ </t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>NDA H2 2026 / PDUFA H1 2027 = longer dated</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="n"/>
+      <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
+    </row>
+    <row r="33" ht="50" customHeight="1">
+      <c r="A33" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>BLDR</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>$14B</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr"/>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 HC + +597% MAX ADD
+→ </t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>Stock already up significantly off lows; rate cut timing uncertain</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="n"/>
+      <c r="H33" s="15" t="n"/>
+      <c r="I33" s="15" t="n"/>
+    </row>
+    <row r="34" ht="50" customHeight="1">
+      <c r="A34" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>APG</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>$11B</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr"/>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 HC consensus + Chubb integration
+→ </t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>No defined dated catalyst; slow consensus discovery</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="n"/>
+      <c r="H34" s="15" t="n"/>
+      <c r="I34" s="15" t="n"/>
+    </row>
+    <row r="35" ht="50" customHeight="1">
+      <c r="A35" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>CARS</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>$560M</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>$10</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$90M buyback (16% cap) + Yartseva 7/7
+→ </t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>Auto dealer cyclical recovery slow; no concentrated fund anchor</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="n"/>
+      <c r="H35" s="15" t="n"/>
+      <c r="I35" s="15" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="40" t="inlineStr">
+        <is>
+          <t>DISQUALIFIED FROM TIER 1 — RE-RATED, in-money, or no defined forensic edge (18 names)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Reason for disqualification (FORENSIC failure mode)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>CELC</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>Phase 3 May 1 POSITIVE priced + +76% PT raises captured</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="15" t="n"/>
+      <c r="H39" s="15" t="n"/>
+      <c r="I39" s="15" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>HRMY</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>Q1 +17% WAKIX growth printed + Lilly orexin validated</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="15" t="n"/>
+      <c r="H40" s="15" t="n"/>
+      <c r="I40" s="15" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="23" t="inlineStr">
+        <is>
+          <t>TREE</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>Q1 +37% rev / +71% EBITDA already PRINTED</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="15" t="n"/>
+      <c r="H41" s="15" t="n"/>
+      <c r="I41" s="15" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="23" t="inlineStr">
+        <is>
+          <t>DV</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>CTV verification rally underway; partial upside captured</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="15" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="15" t="n"/>
+      <c r="H42" s="15" t="n"/>
+      <c r="I42" s="15" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="23" t="inlineStr">
+        <is>
+          <t>DHR</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>Bouncing from trough; bioprocessing cycle now consensus</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="n"/>
+      <c r="D43" s="15" t="n"/>
+      <c r="E43" s="15" t="n"/>
+      <c r="F43" s="15" t="n"/>
+      <c r="G43" s="15" t="n"/>
+      <c r="H43" s="15" t="n"/>
+      <c r="I43" s="15" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="23" t="inlineStr">
+        <is>
+          <t>ASND</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>YORVIPATH ramp priced; €247M Q1 already at $247</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="n"/>
+      <c r="D44" s="15" t="n"/>
+      <c r="E44" s="15" t="n"/>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="15" t="n"/>
+      <c r="H44" s="15" t="n"/>
+      <c r="I44" s="15" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>CVNA</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>Recovered from $3 to $71+ post-split = 40x+ in money</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="n"/>
+      <c r="D45" s="15" t="n"/>
+      <c r="E45" s="15" t="n"/>
+      <c r="F45" s="15" t="n"/>
+      <c r="G45" s="15" t="n"/>
+      <c r="H45" s="15" t="n"/>
+      <c r="I45" s="15" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="23" t="inlineStr">
+        <is>
+          <t>MDGL</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>Rezdiffra (NASH) approved 2024; commercial inflection priced; stock at $230+</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="n"/>
+      <c r="D46" s="15" t="n"/>
+      <c r="E46" s="15" t="n"/>
+      <c r="F46" s="15" t="n"/>
+      <c r="G46" s="15" t="n"/>
+      <c r="H46" s="15" t="n"/>
+      <c r="I46" s="15" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>CRH</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>Stock near highs; cyclical recovery + materials priced; AI data-center exposure only partial driver</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="n"/>
+      <c r="D47" s="15" t="n"/>
+      <c r="E47" s="15" t="n"/>
+      <c r="F47" s="15" t="n"/>
+      <c r="G47" s="15" t="n"/>
+      <c r="H47" s="15" t="n"/>
+      <c r="I47" s="15" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="23" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>HBM cycle thesis already priced through Q1 2026 run-up</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="n"/>
+      <c r="D48" s="15" t="n"/>
+      <c r="E48" s="15" t="n"/>
+      <c r="F48" s="15" t="n"/>
+      <c r="G48" s="15" t="n"/>
+      <c r="H48" s="15" t="n"/>
+      <c r="I48" s="15" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="23" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>AppLovin already 5x+ from lows; AXON AI ad platform priced</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="n"/>
+      <c r="D49" s="15" t="n"/>
+      <c r="E49" s="15" t="n"/>
+      <c r="F49" s="15" t="n"/>
+      <c r="G49" s="15" t="n"/>
+      <c r="H49" s="15" t="n"/>
+      <c r="I49" s="15" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="23" t="inlineStr">
+        <is>
+          <t>TPL</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>Already at 25x P/CF premium = endless drilling priced</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="n"/>
+      <c r="D50" s="15" t="n"/>
+      <c r="E50" s="15" t="n"/>
+      <c r="F50" s="15" t="n"/>
+      <c r="G50" s="15" t="n"/>
+      <c r="H50" s="15" t="n"/>
+      <c r="I50" s="15" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t>BLDR</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>+597% max ADD impressive but stock has run; housing rate cut timing uncertain</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="n"/>
+      <c r="D51" s="15" t="n"/>
+      <c r="E51" s="15" t="n"/>
+      <c r="F51" s="15" t="n"/>
+      <c r="G51" s="15" t="n"/>
+      <c r="H51" s="15" t="n"/>
+      <c r="I51" s="15" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="23" t="inlineStr">
+        <is>
+          <t>COIN/MSTR/CRWV</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>Speculative crypto/AI infra; no defined entry-today asymmetry</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="n"/>
+      <c r="D52" s="15" t="n"/>
+      <c r="E52" s="15" t="n"/>
+      <c r="F52" s="15" t="n"/>
+      <c r="G52" s="15" t="n"/>
+      <c r="H52" s="15" t="n"/>
+      <c r="I52" s="15" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="23" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>Defensive AI accelerator narrative; no concentrated fund anchor; slower re-rate</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="n"/>
+      <c r="D53" s="15" t="n"/>
+      <c r="E53" s="15" t="n"/>
+      <c r="F53" s="15" t="n"/>
+      <c r="G53" s="15" t="n"/>
+      <c r="H53" s="15" t="n"/>
+      <c r="I53" s="15" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="23" t="inlineStr">
+        <is>
+          <t>JOE</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>Florida population growth secular but slow re-rate; no near-term catalyst</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="n"/>
+      <c r="D54" s="15" t="n"/>
+      <c r="E54" s="15" t="n"/>
+      <c r="F54" s="15" t="n"/>
+      <c r="G54" s="15" t="n"/>
+      <c r="H54" s="15" t="n"/>
+      <c r="I54" s="15" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="23" t="inlineStr">
+        <is>
+          <t>GLOB</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>Class action JUNE 23 deadline overhang = NEAR-TERM RISK not asymmetric until cleared</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="n"/>
+      <c r="D55" s="15" t="n"/>
+      <c r="E55" s="15" t="n"/>
+      <c r="F55" s="15" t="n"/>
+      <c r="G55" s="15" t="n"/>
+      <c r="H55" s="15" t="n"/>
+      <c r="I55" s="15" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="23" t="inlineStr">
+        <is>
+          <t>VITL</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>Deepest drawdown but B/M 0.74 not deep value; no defined binary catalyst; slow brand rerate</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="n"/>
+      <c r="D56" s="15" t="n"/>
+      <c r="E56" s="15" t="n"/>
+      <c r="F56" s="15" t="n"/>
+      <c r="G56" s="15" t="n"/>
+      <c r="H56" s="15" t="n"/>
+      <c r="I56" s="15" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="B56:I56"/>
+    <mergeCell ref="B52:I52"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="B39:I39"/>
+    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="F34:I34"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="B53:I53"/>
+    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="F30:I30"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="B55:I55"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="B41:I41"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="F28:I28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5320,7 +8175,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6511,7 +9366,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7439,7 +10294,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8331,7 +11186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10183,7 +13038,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11754,7 +14609,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14863,1223 +17718,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M56"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger — ENTRY-TODAY × TAILWIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Definition: Sub-$2B mcap; B/M &gt;0.40; FCF yield &gt;5%; ROA &gt;0; near 52w low; 6mo negative. Pure quantitative multibagger setup per CAFE WP 33 (Feb 2025).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Within-Rank</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Master-Rank</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Re-rate</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Tailwind</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Mcap</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>Asym</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>Upside</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>R/R</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>Smart Money</t>
-        </is>
-      </c>
-      <c r="M4" s="13" t="inlineStr">
-        <is>
-          <t>Secular Driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>OPRX</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>OptimizeRx</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>$93M</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>$4.82</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2-4x ($11.50 PT)</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>12:1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Insider 14.82%; $10M buyback through March 2027; Doximity exec Presti to board April 2026</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Digital pharma messaging shift to EHR-native channels (Doximity-style TAM); pharma DTC compliance with MFN actually accelerates digital share; market focused on near-term MFN overhang</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: SUB-BOOK 0.70x + $19M FCF profitable + insider 14.82% + analyst $11.50 (138%) + sub-$100M float = ANY DSP Q4 print violently re-rates. Smart money still building (not exiting). True intrinsic value &gt; 2x current.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Digital health POC pharma messaging to 60%+ US prescribers. May 21 2026 DeepIntent integration = first DSP accessing OPRX EHR network (Q3 2026 launch) opens &gt;80% of digital pharma budgets. | VALUATION: P/B 0.70 (sub-book), P/FCF 4.89, 15.7% FCF yield, EV/Sales 0.88, Adj EBITDA 4.4x EV</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Q4 2026 DSP integration revenue start + Q2 2026 earnings Aug 14 | VARIANT: Market: MFN victim; Smart money: profitable ($19M FCF) at 0.7x book, target $11.50 (138% upside).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D9" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t>INMD</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>InMode Ltd</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>$869M</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>$13.71</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2-3x ($25-30)</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>13:1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Steel Partners 25.5% of book; Mizrahy +800k sh ($10.7M)</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Aesthetic devices = cyclical consumer, not secular structural</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: CASH FLOOR: $8.47/sh = 62% of $13.71. Steel Partners 25.5% book + implied $18-20 takeout. Founder Mizrahy +800k sh ($10.7M Feb 2026) at current = sponsor put. Cash + M&amp;A double-floor; upside on Steel re-bid.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Israeli aesthetic device leader (Morpheus8, BodyTite). 85% recurring consumables. Steel Partners +155% Q1 2026 = 25.5% of their book; founder Mizrahy bought 800k sh ($10.7M) Feb 2026. | VALUATION: P/B 1.32, FCF $537M cash = $8.47/sh (62% of price), 77.8% gross margin</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Q2 2026 earnings ~Aug 5 + potential Steel renewed bid ($18 prior) | VARIANT: Market: Israeli geopolitical + aesthetic cycle. Smart money: $11-12 floor on cash alone; Steel implied $20+ takeout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" t="n">
-        <v>8</v>
-      </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="D13" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="inlineStr">
-        <is>
-          <t>GLOB</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Globant SA</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>$1.68B</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>$43.50</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>3-5x if class action clears</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>10:1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Cartica historical 6.5% Q4 2022; sentiment bottom 16% short float</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>LatAm IT services + AI services adoption (Globant AI Pods); class action overhang masks secular validation</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: P/E 5.91 SECTOR LOW + P/FCF 5.56 + EV/EBITDA 4.95x + 17% FCF yield = DEEPLY undervalued by every metric. Class action JUN 23 IS the catalyst that creates the discount (clears = violent rerate). AI Pods $32.8M ARR from $0 in 12mo + $352M pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: LatAm IT services with AI Pods inflection ($32.8M ARR from $0 in 12 months; $352M pipeline; 40% top-20 client penetration). Founder Migoya 23-year tenure + ~3% via Founders Trust. | VALUATION: P/E 5.91 (sector low), P/B 0.78, P/FCF 5.56, 17% FCF yield, EV/EBITDA 4.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Q3 2026 AI Pods print + Argentina FX tailwind + ENRGI platform launch H2 | VARIANT: Market: melting India-IT comp. Smart money: AI mix shift to higher-margin work + LatAm cost arb. CAVEAT: securities class action (lead plaintiff June 23, 2026); COO resigned July 2025 not replaced.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" t="n">
-        <v>9</v>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D17" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="E17" s="28" t="inlineStr">
-        <is>
-          <t>CRTO</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Criteo SA</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>$866M</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>$13.50</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2.5-4x</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>13:1</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Nierenberg D3 9.37% / +19% Q1 2026; Petrus Advisers activist</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Retail media TAM $200B by 2028 (Insider Intelligence); 235-retailer scale incl Lowes/Costco; OpenAI partnership live; market priced terminal decline, missed shift to Commerce Yield retail media</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: P/E 3.73 fwd + P/FCF 4.98 + EV/EBITDA 2.28x + 20.7% FCF yield = DEEP. Q3 2026 anniversary of scope losses REMOVES the headwind printed in Q1. Petrus Advisers activist + $200M buyback (22% cap) + Nierenberg D3 +19% Q1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Performance ad-tech pivoting to Commerce Yield retail media (235 retailers incl Lowes/Costco). $1B+ media spend Q1 2026 (+8% cc). OpenAI partnership live with 1,000+ brands. Q1 retail media -31% ex-scope -- actual underlying +24%. | VALUATION: P/E 3.73 (fwd), P/B 0.79, P/FCF 4.98, EV/EBITDA 2.28, 20.7% FCF yield</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Q3 2026 anniversary of scope losses + Luxembourg redomiciliation + $200M buyback (22% cap) | VARIANT: Market prices terminal decline; Petrus Advisers activist + 33% FCF yield + retail media TAM $200B by 2028.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>5</v>
-      </c>
-      <c r="B21" t="n">
-        <v>10</v>
-      </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D21" s="27" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="E21" s="28" t="inlineStr">
-        <is>
-          <t>NRP</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Natural Resource Partners</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>$1.35B</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>$105.81</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2.5-3x</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>13:1</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Saber/Huber 17.75%, Greystone top, Right Tail NEW Q1 2026, Berkowitz/Fairholme</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Met coal (no green substitute for steelmaking) + Sisecam soda ash (solar glass + EV battery) = TWO structural tailwinds masked by dying-thermal-coal narrative; 6.6x vs TPL 25x is a TRUE comp gap</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: 14.5% FCF yield ALONE = pure mispricing. Royalty trust at 6.6x P/FCF vs TPL at 25x P/CF (SAME asset class) = comp gap re-rate. Distribution Nov 2026 + preferreds retire. Saber 17.75% + Right Tail NEW Q1 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Royalty trust on 13M mineral acres + 49% Sisecam soda ash JV. Near-zero debt by mid-2026 after $109M paydown + preferred retirement. Distribution increase guided for November 2026 (delayed from prior guide due to Sisecam capital call). | VALUATION: P/B 2.26 (B/M 0.47), 14.5% FCF yield, ROA 10.5%, 6.6x P/FCF</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Nov 2026 distribution step-up + preferreds retire; Q3 2026 Sisecam recovery sig | VARIANT: Market: dying coal MLP. Smart money: debt-free royalty with 12% FCF yield, comparable to TPL at 25x P/CF (NRP at 6x).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>6</v>
-      </c>
-      <c r="B25" t="n">
-        <v>12</v>
-      </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D25" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="E25" s="28" t="inlineStr">
-        <is>
-          <t>CARS</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Cars.com</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>$560M</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>$10</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>8</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2-3x</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>11:1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Yartseva 7/7 - smart money still building</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Auto digitization secular but dealer SaaS partially priced via subscription metrics</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: P/B 0.83 + P/FCF 3.5 + 28% TTM FCF yield + EV/EBITDA 2.7x = DEEP. Q1 EPS $0.45 vs $0.13 est (+246% BEAT). $90M buyback (16% cap raised from $60M) = buyback math compounds violently with cheap multiple.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Digital dealer SaaS (19,390 dealers x $2,473 ARPD/mo, 90% recurring). Q1 EPS $0.45 vs $0.13 est (+246%). Subscription +2%; OEM/National -12% (cyclical bottom). | VALUATION: P/B 0.83, P/FCF 3.5, 28% TTM FCF yield, EV/EBITDA 2.7x</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: $25-30M annualized cost program 2027 + $90M buyback (16% cap raised from $60M) | VARIANT: Street: declining auto Yellow Pages at 4x P/FCF. Variant: 90% SaaS dealer recurring + buyback math.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>7</v>
-      </c>
-      <c r="B29" t="n">
-        <v>19</v>
-      </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D29" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="E29" s="28" t="inlineStr">
-        <is>
-          <t>VITL</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Vital Farms</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>$1.5B</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>$13</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2-3x ($30-40)</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>10:1</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>No major fund concentrated yet = entry preserved; Yartseva 6/7</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Pasture-raised premium category creation real but partially recognized</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: Deepest drawdown -68.76% + 11% ROA sustained = exceptional. BUT B/M 0.74 = not deeply undervalued vs book; M&amp;A precedent 4x sales = $50 = +260%. Brand-led re-rate is SLOW not violent. No defined binary catalyst.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Pasture-raised egg category creator with brand moat. Walmart/Target/Whole Foods distribution. 11% ROA sustained THROUGH the avian flu crash = exceptional earnings power. | VALUATION: B/M 0.74, ROA 11% (BEST in 6/7 tier), -68.76% from peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Avian flu egg-supply normalization + summer pricing + M&amp;A speculation | VARIANT: Market lumped premium VITL with commodity egg crash. Reality: brand pricing power retained. Strategic buyers: Kraft Heinz, Hain, General Mills.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>8</v>
-      </c>
-      <c r="B33" t="n">
-        <v>20</v>
-      </c>
-      <c r="C33" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D33" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="E33" s="28" t="inlineStr">
-        <is>
-          <t>FTLF</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>FitLife Brands</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>$93M</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>$10</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>3-5x</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>13:1</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Smoak Capital residual position; previously a Smoak top-5</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Microcap nutraceutical reversion; no secular driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: Microcap $93M = sub-institutional minimum = any flow violently moves. Yartseva 7/7 cleanest setup. -43.9% 6mo. B/M 0.49. Pure micro-mean-reversion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Microcap nutraceutical at $93M cap. Sub-institutional minimum. Classic Yartseva discarded-microcap profile with positive FCF + ROA + extreme drawdown. | VALUATION: P/B 2.05, B/M 0.49, FCF yield 8.2%, ROA 7.2%, near 52w low, -43.9% 6mo</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Q2 2026 earnings; M&amp;A speculation; recovery in supplement category | VARIANT: Market: forgotten micro. Smart money: pure Yartseva mean-reversion target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>9</v>
-      </c>
-      <c r="B37" t="n">
-        <v>21</v>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D37" s="32" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="E37" s="28" t="inlineStr">
-        <is>
-          <t>MTY.TO</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>MTY Food Group</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>C$887M</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>C$40.41</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2-2.5x</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>13:1</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>CEO Lefebvre open-market buy at C$30.54 (+33% stake)</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>QSR franchise consolidation secular (Inspire/RBI/Roark precedent) recognized but multiple at trough</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: AT BOOK 1.04x + 16.7% FCF yield = pure value. M&amp;A pool at 12-14x EBITDA vs trading 7.5x = M&amp;A precedent arb. CEO Lefebvre open-market buy at C$30.54 = sponsor put. QSR consolidation trend.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Multi-brand Canadian QSR franchisor (90 banners incl Cold Stone, Mucho Burrito, Papa Murphy's). 7,000+ locations, 98%+ franchised. Q1 EPS C$0.98 BEAT vs C$0.80 cons. | VALUATION: P/B 1.04 (trading at book!), EV/EBITDA 7.5x (vs QSR peer 14-18x), 16.7% FCF yield</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Q2 2026 earnings test SSS stabilization + NCIB 5% of float through July | VARIANT: Market: melting ice cube. Variant: SSS troughing + debt paying down + M&amp;A pool (RBI, Inspire at 12-14x EBITDA).</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>10</v>
-      </c>
-      <c r="B41" t="n">
-        <v>32</v>
-      </c>
-      <c r="C41" s="26" t="inlineStr">
-        <is>
-          <t>NOT</t>
-        </is>
-      </c>
-      <c r="D41" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="E41" s="28" t="inlineStr">
-        <is>
-          <t>ROCK</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Gibraltar Industries</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>$1.10B</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>$39.69</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>1.8-2.2x</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>7:1</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Director Metcalf bought $502k March 2026; Vanguard 5.24% 13G</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Industrial roofing cyclical post-OmniMax integration</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: OmniMax integration year. FY27 EPS $5+ at 15x = $75-90. Director Form 4 buy March 2026. Cyclical, not deep value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: 3-segment industrial (Residential 80%, Renewables, Agtech). OmniMax acquisition closed Feb 2026 ($1.335B) = #1 in residential roofing accessories. FY26 guide $1.76-1.83B rev, $3.65-4.05 EPS. | VALUATION: P/B 1.34, FCF yield 6.5%, ROA 2.95%, EV/Sales 1.0x vs peer 1.5x</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Q2 2026 earnings = first clean OmniMax quarter; aluminum normalization; Q3 reroofing season | VARIANT: Market: busted SPAC with 1.56 D/E. Variant: one-time integration year; FY27 EPS $5+ at 15x = $75-90.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>11</v>
-      </c>
-      <c r="B45" t="n">
-        <v>36</v>
-      </c>
-      <c r="C45" s="31" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="D45" s="30" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="E45" s="28" t="inlineStr">
-        <is>
-          <t>DV</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>DoubleVerify</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>$1.50B</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>$9</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>1.5-2x (was 3x)</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>6:1</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Insider 12.69% (high for ad-tech); Yartseva 7/7</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>CTV verification rally already underway, partial capture</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: CTV verification rally underway = partial upside captured. Q1 +10% rev printed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Pure-play ad verification (68% market share in fraud detection vs IAS 2.7%). 4,300+ customers vs IAS 169. Q1 2026 rev +10%, EBITDA 31% margin. CTV +28%, social activation +92%. | VALUATION: P/FCF 11x (trough), EV/EBITDA 9.6x, EV/Sales 1.9x, 9% FCF yield</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: ABS streaming Do Not Air list rollout Q2/Q3 + Meta activation $12M ARR to $50M+ path | VARIANT: Market: Google MRC self-measurement threat. Variant: CTV verification underpenetrated (10%) vs display (70%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>12</v>
-      </c>
-      <c r="B49" t="n">
-        <v>38</v>
-      </c>
-      <c r="C49" s="33" t="inlineStr">
-        <is>
-          <t>RERATED</t>
-        </is>
-      </c>
-      <c r="D49" s="34" t="inlineStr">
-        <is>
-          <t>PRICED</t>
-        </is>
-      </c>
-      <c r="E49" s="28" t="inlineStr">
-        <is>
-          <t>HRMY</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Harmony Biosciences</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>$1.77B</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>$31</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>1.5-2x</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>6:1</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>M&amp;A buyers: Jazz Pharma, Lundbeck, Otsuka; Catalyst Pharma precedent</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Orexin/sleep disorders secular validated by Lilly $6.3B Centessa; comp already priced</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: Q1 +17% WAKIX printed; pediatric FDA Feb priced; Lilly orexin validated = thesis worked. Buy-pre-catalyst opportunity passed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: $1B+ WAKIX franchise (pitolisant for narcolepsy). Q1 2026 rev +17% to $215M; pediatric FDA approval Feb 13 2026 extends IP to 2030 (pediatric exclusivity to 2040s). 5 Phase 3 trials in pipeline. | VALUATION: P/B 1.91, P/Sales 2.05, FCF yield 19.36%, 26% net cash position</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Pitolisant GR NDA Q2 2026 (PDUFA Q1 2027); BP-205 Phase 1 PK mid-2026 | VARIANT: Market: single-product cliff. Smart money: Lilly's $6.3B Centessa (Q3 2026 close) validated orexin space + IP estate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>13</v>
-      </c>
-      <c r="B53" t="n">
-        <v>39</v>
-      </c>
-      <c r="C53" s="33" t="inlineStr">
-        <is>
-          <t>RERATED</t>
-        </is>
-      </c>
-      <c r="D53" s="34" t="inlineStr">
-        <is>
-          <t>PRICED</t>
-        </is>
-      </c>
-      <c r="E53" s="28" t="inlineStr">
-        <is>
-          <t>TREE</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>LendingTree</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>$525M</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>$37.50</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>4</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>1.3-1.7x</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>5:1</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Yartseva 7/7 + post-Q1 inflection demonstrated</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Insurance up-cycle secular now consensus post-Q1 inflection</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="29" t="inlineStr">
-        <is>
-          <t>ENTRY-TODAY: Q1 +37% rev / +71% EBITDA already PRINTED. S&amp;P upgraded. Insurance cycle now consensus. Inflection over.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="inlineStr">
-        <is>
-          <t>THESIS: Three-segment marketplace (Insurance 68%, Consumer 20%, Home 12%) at Q1 2026 inflection: rev +37%, VMM +28%, EBITDA +71%, Insurance +51%. Net leverage falling 3.4x→2.1x; S&amp;P upgraded. | VALUATION: P/E 2.92, P/FCF 7.2, ROE 88.6%, B/M 0.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="15" t="inlineStr">
-        <is>
-          <t>CATALYST: Q2 2026 print + $575M July 2025 converts retired + Fed rate cuts unlock Home/Consumer | VARIANT: Street disbelieves Insurance durability. Variant: insurance carriers in year-2 of 5-7yr up-cycle = $200M+ EBITDA into 2027.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A23:M23"/>
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A22:M22"/>
-    <mergeCell ref="A35:M35"/>
-    <mergeCell ref="A43:M43"/>
-    <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A52:M52"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="A28:M28"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A44:M44"/>
-    <mergeCell ref="A31:M31"/>
-    <mergeCell ref="A34:M34"/>
-    <mergeCell ref="A40:M40"/>
-    <mergeCell ref="A48:M48"/>
-    <mergeCell ref="A30:M30"/>
-    <mergeCell ref="A39:M39"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="A24:M24"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A51:M51"/>
-    <mergeCell ref="A36:M36"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="A54:M54"/>
-    <mergeCell ref="A46:M46"/>
-    <mergeCell ref="A27:M27"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="A50:M50"/>
-    <mergeCell ref="A26:M26"/>
-    <mergeCell ref="A56:M56"/>
-    <mergeCell ref="A55:M55"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A47:M47"/>
-    <mergeCell ref="A42:M42"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/investment_archetypes.xlsx
+++ b/investment_archetypes.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1_VERIFIED_TIER1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1_EMPIRICAL_TIER1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="2_BASE_RATES" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="3_BACKTEST_DETAIL" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="4_MASTER_CSV" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="5_CATALYSTS_LIVE" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="6_FORM4_BUYS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7_LIQUIDITY" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8_ARCHETYPES" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="6b_LIVE_CLUSTERS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="7_LIQUIDITY" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="8_ARCHETYPES" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,22 +436,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,667 +474,860 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Tier</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Mcap $M</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Price asof</t>
+          <t>ER 12m</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Mcap $M</t>
+          <t>Best tag</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Best %</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Worst tag</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Worst %</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Live cluster?</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>ADV $M</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Days to exit</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Factor tags</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Kill criteria</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Verification</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Days to next catalyst</t>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>All tags</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HHH</t>
+          <t>WGS</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Howard Hughes Holdings</t>
+          <t>GeneDx</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Holdco RE + insurance</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Genomic diagnostics (commercial-stage NOT clinical)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>56.33000183105469</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>67.68000030517578</v>
+        <v>1670.2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>3999.9</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>29.35</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>13.6</v>
+          <t>+72%</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>insider_cluster</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>+110%</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>services</t>
+        </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>sponsor_anchor,nav_discount,holdco</t>
+          <t>+0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Ackman sells common; HHH stays below $70 12mo post-Vantage; insurance leverage &gt; 4x</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>WEB_VERIFIED_2026-06-10</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="n"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>73.62</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Casdin sells; Q2 2026 rev guide cut again; securities fraud investigation advances; volume growth &lt; 20% QoQ</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>insider_cluster,smart_money_uw,services</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>INMD</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>InMode Ltd</t>
+          <t>KBR Inc</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Medical aesthetics devices</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>1-WEAKENED</t>
-        </is>
+          <t>Defense + nuclear engineering</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>35.31999969482422</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13.5600004196167</v>
+        <v>4480</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>859</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>12.45</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>6.9</v>
+          <t>+70%</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>insider_cluster</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>+110%</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>founder_buy,smart_money_uw,asset_light</t>
+          <t>+0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Mizrahy sells; Steel sells; Q2 2026 rev &lt; $80M; cash balance breached</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>WEB_VERIFIED_2026-06-10</t>
-        </is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>70.54000000000001</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>41</v>
+        <v>6.4</v>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>MTS spin delayed past June 2027; &gt; 2 director sells; Engine exits; classaction outcome adverse</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>insider_cluster,spin_arb,defense</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>ROCK</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KBR Inc</t>
+          <t>Gibraltar Industries</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Defense + nuclear engineering</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Roofing accessories</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>39.31000137329102</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>35.31999969482422</v>
+        <v>1169.9</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>4480</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>70.54000000000001</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>6.4</v>
+          <t>+66%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>insider_cluster</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>+110%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>post_acquisition</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>insider_cluster,spin_arb,defense</t>
+          <t>+0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>MTS spin delayed past June 2027; &gt; 2 director sells; Engine exits; classaction outcome adverse</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>WEB_VERIFIED_2026-06-10</t>
-        </is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>14.52</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>206</v>
+        <v>8.1</v>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Bosway or Metcalf sells; FY26 EPS guide &lt; $3.00; OmniMax write-down</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>insider_cluster,post_acquisition,industrial</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>NSP</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Monro Inc</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Auto service</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1-NEW</t>
-        </is>
+          <t>PEO services</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>37.27000045776367</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>14.65999984741211</v>
+        <v>1420</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>439.8</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>18.95</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>2.3</v>
+          <t>+36%</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>founder_buy</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>+14%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>services</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>sale_process,small_cap,deep_value</t>
+          <t>+0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Sale process terminated with no deal by Q4 2026; dividend cut; same-store sales -5%+</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>WEB_VERIFIED_2026-06-10</t>
-        </is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>25.09</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>202</v>
+        <v>5.7</v>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Sarvadi sells; Q3 2026 EPS &lt; $0.50; dividend cut signals B/S stress</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>founder_buy,earnings_reset,services</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>NRP</t>
+          <t>INMD</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Natural Resource Partners</t>
+          <t>InMode Ltd</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Coal/soda-ash royalty</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1-weakened</t>
-        </is>
+          <t>Medical aesthetics devices</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>13.5600004196167</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>103.7300033569336</v>
+        <v>859</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>1370.3</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>22.5</v>
+          <t>+10%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>smart_money_uw</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>+17%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>asset_light</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>family_anchor,royalty,income</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Distribution cut; family &lt;30%; Sisecam cap-call &gt; $50M H2 2026</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>WEB_VERIFIED_2026-06-10</t>
-        </is>
+          <t>+0%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="n">
+        <v>12.45</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>55</v>
+        <v>6.9</v>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Mizrahy sells; Steel sells; Q2 2026 rev &lt; $80M; cash balance breached</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>founder_buy,smart_money_uw,asset_light</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>NRP</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Natural Resource Partners</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>PEO services</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1-NEW</t>
-        </is>
+          <t>Coal/soda-ash royalty</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>103.7300033569336</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>37.27000045776367</v>
+        <v>1370.3</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>1420</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>25.09</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>5.7</v>
+          <t>+7%</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>family_anchor</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>+17%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>income</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>founder_buy,earnings_reset,services</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Sarvadi sells; Q3 2026 EPS &lt; $0.50; dividend cut signals B/S stress</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>WEB_VERIFIED_2026-06-10</t>
-        </is>
+          <t>+0%</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="n">
+        <v>6.1</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>110</v>
+        <v>22.5</v>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Distribution cut; family &lt;30%; Sisecam cap-call &gt; $50M H2 2026</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>family_anchor,royalty,income</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PRLD</t>
+          <t>HHH</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Prelude Therapeutics</t>
+          <t>Howard Hughes Holdings</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Biotech (EXCLUDED non-bio)</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1-bio</t>
-        </is>
+          <t>Holdco RE + insurance</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>67.68000030517578</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.940000057220459</v>
+        <v>3999.9</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>391</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>WEB_VERIFIED_2026-06-10</t>
-        </is>
+          <t>+7%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>sponsor_anchor</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>+17%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>holdco</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>+0%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="n">
+        <v>29.35</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>110</v>
+        <v>13.6</v>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Ackman sells common; HHH stays below $70 12mo post-Vantage; insurance leverage &gt; 4x</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>sponsor_anchor,nav_discount,holdco</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ROCK</t>
+          <t>SONO</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Gibraltar Industries</t>
+          <t>Sonos</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Roofing accessories</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Premium audio brand</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>15.38000011444092</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>39.31000137329102</v>
+        <v>1830.1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>1169.9</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>14.52</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>8.1</v>
+          <t>+6%</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>activist_form4_cluster</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>+17%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>insider_cluster,post_acquisition,industrial</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>Bosway or Metcalf sells; FY26 EPS guide &lt; $3.00; OmniMax write-down</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>WEB_VERIFIED_2026-06-10</t>
-        </is>
+          <t>+0%</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="n">
+        <v>22.86</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>54</v>
+        <v>8</v>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Coliseum sells; Q3 holiday rev miss; product launch delayed</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>activist_form4_cluster,brand,consumer_discretionary</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>RPAY</t>
+          <t>UA</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Repay Holdings</t>
+          <t>Under Armour</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Payments</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Apparel brand</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>5.78000020980835</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3.430000066757202</v>
+        <v>2427.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>302</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>16.2</v>
+          <t>+5%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>founder_buy</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>+14%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>activist_anchor</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>bid_rejected,activist_13d,take_private_arb</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>Forager withdraws below $4 or AGM result entrenches board; FY26 rev guide cut</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>WEB_VERIFIED_2026-06-10</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n"/>
+          <t>+0%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="n">
+        <v>56.11</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Fairfax sells; UAA-class falls below $4 on no insider response; FY27 EBITDA guide cut &gt; 20%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>founder_buy,activist_anchor,brand_recovery</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SONO</t>
+          <t>CDRE</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Sonos</t>
+          <t>Cadre Holdings</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Premium audio brand</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Tactical/safety gear</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>30.19000053405762</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>15.38000011444092</v>
+        <v>1290</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>1830.1</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>22.86</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>8</v>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>defense_recovery</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>+0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>activist_13d</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>activist_form4_cluster,brand,consumer_discretionary</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Coliseum sells; Q3 holiday rev miss; product launch delayed</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>WEB_VERIFIED_2026-06-10</t>
-        </is>
+          <t>-26%</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="n">
+        <v>11.8</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>64</v>
+        <v>10.9</v>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Wynnefield trims &lt; 15%; FY26 sales &gt; 5% miss; gov order pipeline drops</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>activist_13d,defense_recovery,small_cap</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>UA</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Under Armour</t>
+          <t>Monro Inc</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Apparel brand</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1-NEW</t>
-        </is>
+          <t>Auto service</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>14.65999984741211</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5.78000020980835</v>
+        <v>439.8</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>2427.6</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>56.11</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>4.3</v>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>small_cap</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>+0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>sale_process</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>founder_buy,activist_anchor,brand_recovery</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Fairfax sells; UAA-class falls below $4 on no insider response; FY27 EBITDA guide cut &gt; 20%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>WEB_VERIFIED_2026-06-10</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n"/>
+          <t>-46%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Sale process terminated with no deal by Q4 2026; dividend cut; same-store sales -5%+</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>sale_process,small_cap,deep_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>RPAY</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Repay Holdings</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>3.430000066757202</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>-29%</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>take_private_arb</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>+0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>bid_rejected</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-61%</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Forager withdraws below $4 or AGM result entrenches board; FY26 rev guide cut</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>bid_rejected,activist_13d,take_private_arb</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5786,7 +5982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5850,22 +6046,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>WGS</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SARVADI PAUL J</t>
+          <t>Casdin Capital, LLC</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Director/Chairman of the Board &amp; CEO</t>
+          <t>Director/10%Owner</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -5874,39 +6070,35 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>233000</v>
+        <v>50000</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>34.05</v>
+        <v>52.8566</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>7.93</v>
+        <v>2.64</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1000753/000100075326000078/form4.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1818331/000091957426003907/ownership.xml</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ROCK</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Bosway William T</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Director/President and CEO</t>
-        </is>
-      </c>
+          <t>Quinn William J</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -5915,39 +6107,39 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>19735</v>
+        <v>44000</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>37.4377</v>
+        <v>13.1865</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.74</v>
+        <v>0.58</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/912562/000091256226000122/form4.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2029118/000119312526262545/ownership.xml</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>NRP</t>
+          <t>WGS</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Craig Kevin J</t>
+          <t>Casdin Capital, LLC</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Executive Vice President</t>
+          <t>Director/10%Owner</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5956,39 +6148,39 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>336</v>
+        <v>150000</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>102.18</v>
+        <v>56.4449</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.03</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1171486/000143774926018760/rdgdoc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1818331/000091957426003907/ownership.xml</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ROCK</t>
+          <t>NSP</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Bolanowski Katherine</t>
+          <t>SARVADI PAUL J</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>General Counsel, VP, Secretary</t>
+          <t>Director/Chairman of the Board &amp; CEO</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -5997,39 +6189,35 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1256</v>
+        <v>233000</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>35.63</v>
+        <v>34.05</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.04</v>
+        <v>7.93</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/912562/000091256226000120/form4.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1000753/000100075326000078/form4.xml</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ROCK</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Bolanowski Katherine</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>General Counsel, VP, Secretary</t>
-        </is>
-      </c>
+          <t>Quinn William J</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -6038,39 +6226,35 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>144</v>
+        <v>10503</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>35.66</v>
+        <v>13.2</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/912562/000091256226000120/form4.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2029118/000119312526259528/ownership.xml</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>MOORE JACK B</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
+          <t>Gieselman Scott</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -6079,39 +6263,35 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>4000</v>
+        <v>670</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>31.4414</v>
+        <v>13.441</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1357615/000135761526000155/wk-form4_1779393811.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2029118/000119312526255482/ownership.xml</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ROCK</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Lovechio Joseph A</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>VP and CFO</t>
-        </is>
-      </c>
+          <t>Gieselman Scott</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -6120,39 +6300,39 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1000</v>
+        <v>13430</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>34.615</v>
+        <v>13.353</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.03</v>
+        <v>0.18</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/912562/000091256226000118/form4.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2029118/000119312526255482/ownership.xml</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>ROCK</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Sabater Carlos A.</t>
+          <t>Bosway William T</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Director/President and CEO</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -6161,39 +6341,39 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>14500</v>
+        <v>19735</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>32.47</v>
+        <v>37.4377</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.47</v>
+        <v>0.74</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1357615/000135761526000154/wk-form4_1779393765.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/912562/000091256226000122/form4.xml</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>NRP</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Von Thaer Lewis</t>
+          <t>Craig Kevin J</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Executive Vice President</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -6202,39 +6382,35 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>3000</v>
+        <v>336</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30.77</v>
+        <v>102.18</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1357615/000135761526000149/wk-form4_1778890135.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1171486/000143774926018760/rdgdoc.xml</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Evans Shad E.</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>EVP &amp; Chief Financial Officer</t>
-        </is>
-      </c>
+          <t>Gieselman Scott</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -6243,56 +6419,585 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>8375</v>
+        <v>20000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30.6</v>
+        <v>14.103</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1357615/000135761526000147/wk-form4_1778889975.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2029118/000119312526241878/ownership.xml</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>NRP</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Craig Kevin J</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Executive Vice President</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>336</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>102.18</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1171486/000143774926018760/rdgdoc.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Gieselman Scott</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2029118/000119312526241878/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ROCK</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Bolanowski Katherine</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>General Counsel, VP, Secretary</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>1256</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>35.63</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/912562/000091256226000120/form4.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ROCK</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Bolanowski Katherine</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>General Counsel, VP, Secretary</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>35.66</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/912562/000091256226000120/form4.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>MOORE JACK B</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>31.4414</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1357615/000135761526000155/wk-form4_1779393811.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ROCK</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Lovechio Joseph A</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>VP and CFO</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>34.615</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/912562/000091256226000118/form4.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Casdin Capital, LLC</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Director/10%Owner</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>140000</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>43.8061</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1818331/000091957426003627/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Sabater Carlos A.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>14500</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1357615/000135761526000154/wk-form4_1779393765.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Casdin Capital, LLC</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Director/10%Owner</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>185000</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>42.5964</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1818331/000091957426003627/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Casdin Capital, LLC</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Director/10%Owner</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>175000</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>42.5517</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1818331/000091957426003627/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Von Thaer Lewis</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1357615/000135761526000149/wk-form4_1778890135.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Evans Shad E.</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>EVP &amp; Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>8375</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1357615/000135761526000147/wk-form4_1778889975.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>SONO</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Arabia Carmine</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F24" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="G24" s="2" t="n">
         <v>14.49</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1314727/000131472726000066/form4.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SONO</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Arabia Carmine</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1314727/000131472726000066/form4.xml</t>
         </is>
@@ -6304,6 +7009,234 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Window start</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Window end</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t># insiders</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Total $M</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg px</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Top buyer</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Top $M</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>AGGREGATE</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>32.569</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Casdin Capital, LLC</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>32.569</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>NSP</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>AGGREGATE</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>7.934</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>SARVADI PAUL J</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>7.934</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CLUSTER</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Sabater Carlos A.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0.471</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ROCK</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>CLUSTER</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Bosway William T</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0.739</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7081,7 +8014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/investment_archetypes.xlsx
+++ b/investment_archetypes.xlsx
@@ -8,14 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="1_EMPIRICAL_TIER1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2_BASE_RATES" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3_BACKTEST_DETAIL" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4_MASTER_CSV" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5_CATALYSTS_LIVE" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6_FORM4_BUYS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="6b_LIVE_CLUSTERS" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="7_LIQUIDITY" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="8_ARCHETYPES" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="0_DISCOVERY_CLUSTERS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="0b_NEW_13D_FILINGS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2_BASE_RATES" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3_BACKTEST_DETAIL" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="4_MASTER_CSV" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="5_CATALYSTS_LIVE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="6_FORM4_BUYS" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="6b_LIVE_CLUSTERS" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="7_LIQUIDITY" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="8_ARCHETYPES" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -743,38 +745,38 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>RYAN</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Ryan Specialty Holdings</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>PEO services</t>
+          <t>Specialty insurance distribution</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>37.27000045776367</v>
+        <v>35.64</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1420</v>
+        <v>9300</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+36%</t>
+          <t>+41%</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>founder_buy</t>
+          <t>insider_cluster</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>+14%</t>
+          <t>+110%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -787,68 +789,60 @@
           <t>+0%</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>25.09</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>5.7</v>
-      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Sarvadi sells; Q3 2026 EPS &lt; $0.50; dividend cut signals B/S stress</t>
+          <t>Patrick Ryan or 2+ cluster members sell; organic growth &lt;10%; -20% below cluster avg $32.63</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>founder_buy,earnings_reset,services</t>
+          <t>insider_cluster,founder_buy,services</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>INMD</t>
+          <t>NSP</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>InMode Ltd</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Medical aesthetics devices</t>
+          <t>PEO services</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>13.5600004196167</v>
+        <v>37.27000045776367</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>859</v>
+        <v>1420</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+36%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>smart_money_uw</t>
+          <t>founder_buy</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>+17%</t>
+          <t>+14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>asset_light</t>
+          <t>services</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -856,54 +850,58 @@
           <t>+0%</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="L6" s="2" t="n">
-        <v>12.45</v>
+        <v>25.09</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6.9</v>
+        <v>5.7</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Mizrahy sells; Steel sells; Q2 2026 rev &lt; $80M; cash balance breached</t>
+          <t>Sarvadi sells; Q3 2026 EPS &lt; $0.50; dividend cut signals B/S stress</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>founder_buy,smart_money_uw,asset_light</t>
+          <t>founder_buy,earnings_reset,services</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>NRP</t>
+          <t>INMD</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Natural Resource Partners</t>
+          <t>InMode Ltd</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Coal/soda-ash royalty</t>
+          <t>Medical aesthetics devices</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>103.7300033569336</v>
+        <v>13.5600004196167</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1370.3</v>
+        <v>859</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+7%</t>
+          <t>+10%</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>family_anchor</t>
+          <t>smart_money_uw</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -913,7 +911,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>asset_light</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -923,43 +921,43 @@
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="n">
-        <v>6.1</v>
+        <v>12.45</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>22.5</v>
+        <v>6.9</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Distribution cut; family &lt;30%; Sisecam cap-call &gt; $50M H2 2026</t>
+          <t>Mizrahy sells; Steel sells; Q2 2026 rev &lt; $80M; cash balance breached</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>family_anchor,royalty,income</t>
+          <t>founder_buy,smart_money_uw,asset_light</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HHH</t>
+          <t>NRP</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Howard Hughes Holdings</t>
+          <t>Natural Resource Partners</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Holdco RE + insurance</t>
+          <t>Coal/soda-ash royalty</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>67.68000030517578</v>
+        <v>103.7300033569336</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3999.9</v>
+        <v>1370.3</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -968,7 +966,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>sponsor_anchor</t>
+          <t>family_anchor</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -978,7 +976,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>holdco</t>
+          <t>income</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -988,52 +986,52 @@
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="n">
-        <v>29.35</v>
+        <v>6.1</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>13.6</v>
+        <v>22.5</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Ackman sells common; HHH stays below $70 12mo post-Vantage; insurance leverage &gt; 4x</t>
+          <t>Distribution cut; family &lt;30%; Sisecam cap-call &gt; $50M H2 2026</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>sponsor_anchor,nav_discount,holdco</t>
+          <t>family_anchor,royalty,income</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SONO</t>
+          <t>HHH</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Sonos</t>
+          <t>Howard Hughes Holdings</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Premium audio brand</t>
+          <t>Holdco RE + insurance</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>15.38000011444092</v>
+        <v>67.68000030517578</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1830.1</v>
+        <v>3999.9</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+6%</t>
+          <t>+7%</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>activist_form4_cluster</t>
+          <t>sponsor_anchor</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1043,7 +1041,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>brand</t>
+          <t>holdco</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1053,62 +1051,62 @@
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="n">
-        <v>22.86</v>
+        <v>29.35</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8</v>
+        <v>13.6</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Coliseum sells; Q3 holiday rev miss; product launch delayed</t>
+          <t>Ackman sells common; HHH stays below $70 12mo post-Vantage; insurance leverage &gt; 4x</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>activist_form4_cluster,brand,consumer_discretionary</t>
+          <t>sponsor_anchor,nav_discount,holdco</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>UA</t>
+          <t>SONO</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Under Armour</t>
+          <t>Sonos</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Apparel brand</t>
+          <t>Premium audio brand</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5.78000020980835</v>
+        <v>15.38000011444092</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2427.6</v>
+        <v>1830.1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+5%</t>
+          <t>+6%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>founder_buy</t>
+          <t>activist_form4_cluster</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>+14%</t>
+          <t>+17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>activist_anchor</t>
+          <t>brand</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1118,182 +1116,178 @@
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="n">
-        <v>56.11</v>
+        <v>22.86</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Fairfax sells; UAA-class falls below $4 on no insider response; FY27 EBITDA guide cut &gt; 20%</t>
+          <t>Coliseum sells; Q3 holiday rev miss; product launch delayed</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>founder_buy,activist_anchor,brand_recovery</t>
+          <t>activist_form4_cluster,brand,consumer_discretionary</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CDRE</t>
+          <t>UA</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Cadre Holdings</t>
+          <t>Under Armour</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Tactical/safety gear</t>
+          <t>Apparel brand</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>30.19000053405762</v>
+        <v>5.78000020980835</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1290</v>
+        <v>2427.6</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>+5%</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>defense_recovery</t>
+          <t>founder_buy</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>+14%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>activist_anchor</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>+0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>activist_13d</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-26%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="n">
-        <v>11.8</v>
+        <v>56.11</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>10.9</v>
+        <v>4.3</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Wynnefield trims &lt; 15%; FY26 sales &gt; 5% miss; gov order pipeline drops</t>
+          <t>Fairfax sells; UAA-class falls below $4 on no insider response; FY27 EBITDA guide cut &gt; 20%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>activist_13d,defense_recovery,small_cap</t>
+          <t>founder_buy,activist_anchor,brand_recovery</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>TWFG</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Monro Inc</t>
+          <t>TWFG Inc</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Auto service</t>
+          <t>Insurance distribution (P&amp;C agency)</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>14.65999984741211</v>
+        <v>21.56</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>439.8</v>
+        <v>1200</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>+5%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>founder_buy</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>+14%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>small_cap</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>+0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>sale_process</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-46%</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="n">
-        <v>18.95</v>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>2.3</v>
-      </c>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Sale process terminated with no deal by Q4 2026; dividend cut; same-store sales -5%+</t>
+          <t>Doak sells; FY26 organic growth guide cut; breaks $17</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>sale_process,small_cap,deep_value</t>
+          <t>founder_buy,small_cap,services</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>RPAY</t>
+          <t>CDRE</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Repay Holdings</t>
+          <t>Cadre Holdings</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Tactical/safety gear</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3.430000066757202</v>
+        <v>30.19000053405762</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>302</v>
+        <v>1290</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-29%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>take_private_arb</t>
+          <t>defense_recovery</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1303,29 +1297,2662 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>bid_rejected</t>
+          <t>activist_13d</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-61%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Wynnefield trims &lt; 15%; FY26 sales &gt; 5% miss; gov order pipeline drops</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>activist_13d,defense_recovery,small_cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>MNRO</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Monro Inc</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Auto service</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>14.65999984741211</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>439.8</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>small_cap</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>+0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>sale_process</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-46%</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Sale process terminated with no deal by Q4 2026; dividend cut; same-store sales -5%+</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>sale_process,small_cap,deep_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>RPAY</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Repay Holdings</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>3.430000066757202</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>-29%</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>take_private_arb</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>+0%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>bid_rejected</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-61%</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="n">
         <v>1.86</v>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="M15" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>Forager withdraws below $4 or AGM result entrenches board; FY26 rev guide cut</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>bid_rejected,activist_13d,take_private_arb</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Mcap $M</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ADV shares</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ADV $M</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Days to exit 1% pos</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Asof</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CODI</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n">
+        <v>852670</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>AERO</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n">
+        <v>187630</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>LQDA</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n">
+        <v>1878190</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>120.22</v>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CELC</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n">
+        <v>1735025</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>160.65</v>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n">
+        <v>476460</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>VITL</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>449</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>2983805</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>GLOB</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1619.8</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2137975</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>80.11</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>GPRO</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>7885950</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>MNRO</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>439.8</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>1292765</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1670.2</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1306990</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>73.62</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>OPRX</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>543140</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2427.6</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>9707365</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>56.11</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>FUN</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>2240.1</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1953180</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>43.81</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>NSP</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1420</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>673225</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>25.09</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>FCN</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>5272.6</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>576815</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>92.23999999999999</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>4480</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1997250</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>70.54000000000001</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>INMD</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>859</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>918205</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SONO</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>1830.1</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>1486085</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ROCK</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>1169.9</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>369475</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>MRP</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>4870</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>1594685</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>46.72</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>CDRE</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>1290</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>390880</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>66600</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>21221855</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>563.65</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>HHH</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>3999.9</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>433645</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>29.35</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>CRTO</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>856.9</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>329780</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>LAW</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>405940</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>RPAY</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>542390</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SSTI</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>116450</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>NRP</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1370.3</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>58800</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SEER</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>247570</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>PRLD</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>391</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>321720</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>MTY.TO</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>908.1</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>34750</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Archetype</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Thesis</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Valuation</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Catalyst</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Smart money</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>CARS</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Digital dealer SaaS (19,390 dealers x $2,473 ARPD/mo, 90% recurring). Q1 EPS $0.45 vs $0.13 est (+246%). Subscription +2%; OEM/National -12% (cyclical bottom).</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>P/B 0.83, P/FCF 3.5, 28% TTM FCF yield, EV/EBITDA 2.7x</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>$25-30M annualized cost program 2027 + $90M buyback (16% cap raised from $60M)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Street: declining auto Yellow Pages at 4x P/FCF. Variant: 90% SaaS dealer recurring + buyback math.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Yartseva 7/7 - smart money still building</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>CRTO</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Performance ad-tech pivoting to Commerce Yield retail media (235 retailers incl Lowes/Costco). $1B+ media spend Q1 2026 (+8% cc). OpenAI partnership live with 1,000+ brands. Q1 retail media -31% ex-scope -- actual underlying +24%.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>P/E 3.73 (fwd), P/B 0.79, P/FCF 4.98, EV/EBITDA 2.28, 20.7% FCF yield</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Q3 2026 anniversary of scope losses + Luxembourg redomiciliation + $200M buyback (22% cap)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Market prices terminal decline; Petrus Advisers activist + 33% FCF yield + retail media TAM $200B by 2028.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Nierenberg D3 9.37% / +19% Q1 2026; Petrus Advisers activist</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>DV</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Pure-play ad verification (68% market share in fraud detection vs IAS 2.7%). 4,300+ customers vs IAS 169. Q1 2026 rev +10%, EBITDA 31% margin. CTV +28%, social activation +92%.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>P/FCF 11x (trough), EV/EBITDA 9.6x, EV/Sales 1.9x, 9% FCF yield</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>ABS streaming Do Not Air list rollout Q2/Q3 + Meta activation $12M ARR to $50M+ path</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Market: Google MRC self-measurement threat. Variant: CTV verification underpenetrated (10%) vs display (70%).</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Insider 12.69% (high for ad-tech); Yartseva 7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>FTLF</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Microcap nutraceutical at $93M cap. Sub-institutional minimum. Classic Yartseva discarded-microcap profile with positive FCF + ROA + extreme drawdown.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>P/B 2.05, B/M 0.49, FCF yield 8.2%, ROA 7.2%, near 52w low, -43.9% 6mo</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026 earnings; M&amp;A speculation; recovery in supplement category</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Market: forgotten micro. Smart money: pure Yartseva mean-reversion target.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Smoak Capital residual position; previously a Smoak top-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>GLOB</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>LatAm IT services with AI Pods inflection ($32.8M ARR from $0 in 12 months; $352M pipeline; 40% top-20 client penetration). Founder Migoya 23-year tenure + ~3% via Founders Trust.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>P/E 5.91 (sector low), P/B 0.78, P/FCF 5.56, 17% FCF yield, EV/EBITDA 4.95</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Q3 2026 AI Pods print + Argentina FX tailwind + ENRGI platform launch H2</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Market: melting India-IT comp. Smart money: AI mix shift to higher-margin work + LatAm cost arb. CAVEAT: securities class action (lead plaintiff June 23, 2026); COO resigned July 2025 not replaced.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Cartica historical 6.5% Q4 2022; sentiment bottom 16% short float</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>HRMY</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>$1B+ WAKIX franchise (pitolisant for narcolepsy). Q1 2026 rev +17% to $215M; pediatric FDA approval Feb 13 2026 extends IP to 2030 (pediatric exclusivity to 2040s). 5 Phase 3 trials in pipeline.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>P/B 1.91, P/Sales 2.05, FCF yield 19.36%, 26% net cash position</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Pitolisant GR NDA Q2 2026 (PDUFA Q1 2027); BP-205 Phase 1 PK mid-2026</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Market: single-product cliff. Smart money: Lilly's $6.3B Centessa (Q3 2026 close) validated orexin space + IP estate.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A buyers: Jazz Pharma, Lundbeck, Otsuka; Catalyst Pharma precedent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>INMD</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Israeli aesthetic device leader (Morpheus8, BodyTite). 85% recurring consumables. Steel Partners +155% Q1 2026 = 25.5% of their book; founder Mizrahy bought 800k sh ($10.7M) Feb 2026.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>P/B 1.32, FCF $537M cash = $8.47/sh (62% of price), 77.8% gross margin</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026 earnings ~Aug 5 + potential Steel renewed bid ($18 prior)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Market: Israeli geopolitical + aesthetic cycle. Smart money: $11-12 floor on cash alone; Steel implied $20+ takeout.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Steel Partners 25.5% of book; Mizrahy +800k sh ($10.7M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>MTY.TO</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Multi-brand Canadian QSR franchisor (90 banners incl Cold Stone, Mucho Burrito, Papa Murphy's). 7,000+ locations, 98%+ franchised. Q1 EPS C$0.98 BEAT vs C$0.80 cons.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>P/B 1.04 (trading at book!), EV/EBITDA 7.5x (vs QSR peer 14-18x), 16.7% FCF yield</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026 earnings test SSS stabilization + NCIB 5% of float through July</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Market: melting ice cube. Variant: SSS troughing + debt paying down + M&amp;A pool (RBI, Inspire at 12-14x EBITDA).</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>CEO Lefebvre open-market buy at C$30.54 (+33% stake)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>NRP</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Royalty trust on 13M mineral acres + 49% Sisecam soda ash JV. Near-zero debt by mid-2026 after $109M paydown + preferred retirement. Distribution increase guided for November 2026 (delayed from prior guide due to Sisecam capital call).</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>P/B 2.26 (B/M 0.47), 14.5% FCF yield, ROA 10.5%, 6.6x P/FCF</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Nov 2026 distribution step-up + preferreds retire; Q3 2026 Sisecam recovery sig</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Market: dying coal MLP. Smart money: debt-free royalty with 12% FCF yield, comparable to TPL at 25x P/CF (NRP at 6x).</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Saber/Huber 17.75%, Greystone top, Right Tail NEW Q1 2026, Berkowitz/Fairholme</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>OPRX</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Digital health POC pharma messaging to 60%+ US prescribers. May 21 2026 DeepIntent integration = first DSP accessing OPRX EHR network (Q3 2026 launch) opens &gt;80% of digital pharma budgets.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>P/B 0.70 (sub-book), P/FCF 4.89, 15.7% FCF yield, EV/Sales 0.88, Adj EBITDA 4.4x EV</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Q4 2026 DSP integration revenue start + Q2 2026 earnings Aug 14</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Market: MFN victim; Smart money: profitable ($19M FCF) at 0.7x book, target $11.50 (138% upside).</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Insider 14.82%; $10M buyback through March 2027; Doximity exec Presti to board April 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ROCK</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3-segment industrial (Residential 80%, Renewables, Agtech). OmniMax acquisition closed Feb 2026 ($1.335B) = #1 in residential roofing accessories. FY26 guide $1.76-1.83B rev, $3.65-4.05 EPS.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>P/B 1.34, FCF yield 6.5%, ROA 2.95%, EV/Sales 1.0x vs peer 1.5x</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026 earnings = first clean OmniMax quarter; aluminum normalization; Q3 reroofing season</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Market: busted SPAC with 1.56 D/E. Variant: one-time integration year; FY27 EPS $5+ at 15x = $75-90.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Director Metcalf bought $502k March 2026; Vanguard 5.24% 13G</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>TREE</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Three-segment marketplace (Insurance 68%, Consumer 20%, Home 12%) at Q1 2026 inflection: rev +37%, VMM +28%, EBITDA +71%, Insurance +51%. Net leverage falling 3.4x→2.1x; S&amp;P upgraded.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>P/E 2.92, P/FCF 7.2, ROE 88.6%, B/M 0.60</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026 print + $575M July 2025 converts retired + Fed rate cuts unlock Home/Consumer</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Street disbelieves Insurance durability. Variant: insurance carriers in year-2 of 5-7yr up-cycle = $200M+ EBITDA into 2027.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Yartseva 7/7 + post-Q1 inflection demonstrated</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>VITL</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Pasture-raised egg category creator with brand moat. Walmart/Target/Whole Foods distribution. 11% ROA sustained THROUGH the avian flu crash = exceptional earnings power.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>B/M 0.74, ROA 11% (BEST in 6/7 tier), -68.76% from peak</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Avian flu egg-supply normalization + summer pricing + M&amp;A speculation</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Market lumped premium VITL with commodity egg crash. Reality: brand pricing power retained. Strategic buyers: Kraft Heinz, Hain, General Mills.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>No major fund concentrated yet = entry preserved; Yartseva 6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>10. Hedged / Special Structure</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>AAP CALL</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Cooper Creek's largest single call exposure. Overlaps with H Partners' AAP cash 46% concentration = double-conviction across two fund styles.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>$158M call notional; +213% Q1 2026 (Cooper Creek)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026 margin recovery proof + H Partners 13D escalation</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Catalyst-driven leverage on H Partners' AAP thesis.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Cooper Creek call stack ($518M total notional incl SIG/TTWO/DOCN/GXO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>10. Hedged / Special Structure</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CTMX-WT</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>BVF Partners holds CTMX Tranche 2 warrants expiring 7/3/2026 (next 5 weeks). Embedded biotech IPO/crossover leverage near expiration creates urgency catalyst.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5.77M shares warrants; group ownership equivalent ~3.5%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Warrant expiration 7/3/2026 = IMMINENT URGENCY</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>BVF's KYMR top conviction (14.6%) signals their biotech book has high conviction quality.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>BVF Partners 13G/A #5 (warrants exp 7/3/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>10. Hedged / Special Structure</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>LQDA</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Yutrepia (treprostinil dry-powder inhaler) for PAH and PH-ILD. Q1 2026 product sales $129.9M (+44% QoQ); 4,500 unique patients; mgmt $1B+ 2027 target.</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>P/Sales 12x on $130M Q1 run-rate; cash $200M+ floor; M&amp;A premium 50-100%</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>'327 patent ruling pending (binary); Q2 print Aug 2026; UTHR Tresmi competitive launch</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Consensus PT $63.75 assumes flat share. Buckley's PUT-hedged structure suggests binary patent risk; UTHR M&amp;A target.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Buckley Capital 32% LONG + PUT structure ($44.7M notional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>10. Hedged / Special Structure</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>XBI</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Stonepine $51M long + $51M short = $102M notional. Pure long-vol bet on biotech 2026-2027 FDA cycle dispersion.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Biotech basket at multi-year low; straddle structure captures vol</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Biotech FDA cycle 2026-2027 (multiple catalysts driving dispersion)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Long-vol thesis: biotech sector cycle creates dispersion that benefits straddle structure regardless of direction.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Stonepine 40.9% of $250M book in XBI straddle</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>AAP</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>#3 aftermarket retailer post-WorldPac sale. Q1 +3.5% comps (Pro mid-single, DIY low-single). 700+ stores closed; ~1,300 strategic locations remain. Bridge to AZO-style 8-10% margins = $130-150/sh.</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3.8% op margin (rising +410bps), FY26 guide $2.40-3.10 EPS; sub-1x sales; M&amp;A floor 0.8x sales = $80/sh</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026 earnings Aug = needs comps +2%+ and op margin &gt;5%; H Partners 13D escalation possible</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Consensus PT $57 (dead money). H Partners 46% concentration implies AAP returns to AZO margins.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>H Partners 46.3% / $71.2M / +50% sh Q1 2026 (1.35M sh); Legion Partners precedent</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>ACHC</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Largest US behavioral health network (260+ facilities). DOJ Medicaid investigation overhang. Q1 2026 admissions stabilizing. Greenlight 4.1M activist; Sohn 5/12 pitch.</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 6.5x (vs HCA 9x, UHS 8x); 29% short float; -70% drawdown</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>DOJ resolution + Q2 2026 earnings + 29% short squeeze potential</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Market: DOJ/Medicaid existential. Greenlight: provider necessity + facility footprint + de-rate captured = floor near current.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Greenlight Capital 4.1M sh (David Einhorn); Sohn presentation 5/12/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>FUN</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Post-Cedar Fair/Six Flags merger consolidation. 42 parks irreplaceable real estate. Q1 2026 rev +12%, attendance +4%, per-cap +6%. $200M synergy target ($120M cost + $80M growth).</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>$5.27B net debt = 7x leverage; EV/EBITDA 9x on $1.05B 2027 EBITDA</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>May 26 2026 AGM: Jaffer joins board (Class III through 2027, Audit&amp;Finance Cttee). Jana 9% pushing OUTRIGHT SALE.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Street: broken merger story. Two-front activist pressure (governance + sale) + per-park RE floor $47M each.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>H Partners 53.7% / $82.5M / 5.7% of class; Jana 9% + Travis Kelce co-invest</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>MRP</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Lennar 80%+ owner spinoff with 100k+ optioned lots at cost basis. Land bank trading below NAV with Lennar as guaranteed off-take partner. Housing-cycle recovery levered.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>B/M 1.274 (DEEPEST in 6/7 tier; deeper than NRP's 0.47), pure NAV play</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026 print + Lennar volume scaling + housing cycle inflection</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Market priced spinoff orphan technical pressure. Smart money: pure land cash-cow at discount to NAV.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Lennar 80%+ owner = patient capital lock-in; SITG multi-fund flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>POSTBPB</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Nierenberg/D3 is LARGEST shareholder (~$16.4M / 7% of D3 book). Customer-traffic gains while peers don't (Q1 2026 letter thesis). Form 4 insider buying by Nierenberg at depressed levels.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Sub-$300M micro restaurant chain; turnaround stage</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant turnaround + Nierenberg potential escalation</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Market: tier-2 restaurant chain. Activist soft-pressure thesis.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Nierenberg/D3 largest shareholder; 13D/A active March 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>QRHC</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Wynnefield filed 13D 13.3% May 2025; Robert Lipstein joined board. Cooperation Agreement w/ standstill until 30 days before 2027 nomination window. Asset-light recurring waste mgmt.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Sub-$200M micro; recurring waste services revenue model</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Operational improvements + Wynnefield additional buying if dips</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Market: small-cap value trap. Activist: board seat + potential value-unlock initiatives.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Wynnefield 13.3% / 2.73M sh / 13D w/ board seat</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>ASND</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>TransCon prodrug platform: SKYTROFA (GHD), YORVIPATH (hypopara), YUVIWEL (achondroplasia approved Feb 2026). &gt;1,000 new US YORVIPATH enrollments Q1; 6,300+ patients across 2,700 prescribers.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Profitable (22% non-IFRS op margin); €247M Q1 (2x YoY); peak rev YORVIPATH $4-5B</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>YUVIWEL ramp + Q2/Q3 YORVIPATH growth + TransCon CNP follow-on indications</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Sell-side: $15B endocrine specialty maturing. RA Capital: $30B+ at 70-90K addressable hypopara population. Analyst high $345 (Barclays).</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>RA Capital 24.9% of $9.44B = $2.35B = LARGEST single biotech crossover position; held since 2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>BNTC</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Gene therapy platform anchor position. Suvretta 44.1% 13D anchor stake (largest activist ownership in their portfolio). PIPE participation Nov 2025.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Sub-$300M biotech; gene therapy platform optionality</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Multiple gene-therapy programs in development; clinical readouts upcoming</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>44.1% ownership creates board influence + asymmetric upside on clinical reads.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Suvretta 44.1% 13D (Suvretta's LARGEST stake by % ownership)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>CELC</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Phase 3 VIKTORIA-1 PIK3CA-mut POSITIVE May 1 2026 (76% PFS hazard reduction). Gedatolisib pan-PI3K/mTOR oncology. Triplet vs alpelisib+fulvestrant. Multiple HR+/HER2- breast cancer cohorts.</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>$387M cash + accepted NDA + Priority Review = de-risked; 4-5x peak rev precedent</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>JUNE 2 ASCO LBA1008 oral + JULY 17 PDUFA goal date (2 catalysts in 8 weeks)</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Market: alpelisib-class peak ($1-2B). Baker Bros 19.99% 13D activist: $5-10B peak (triplet displaces alpelisib + captures WT segment).</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Baker Bros 19.99% ACTIVIST 13D = $904M / 5.48% of $17.4B book</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>KYMR</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Targeted protein degradation platform. Lead KT-621 oral STAT6 degrader competes with injectable Dupixent ($14B+ franchise). IRAK4 partnered with Sanofi.</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>$1.55B cash (runway 2029); Dec 2025 follow-on $602M at $86</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>BROADEN2 AD mid-2027 (12+ months); BREADTH asthma late 2027; FDA Fast Track granted both</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Market: Phase 1b execution risk. Two top biotech specialists: oral Dupixent-disruptor with peak $5-10B.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>BVF #1 position 14.6% of $3.14B book ($458M) + Baker Bros 4.1% / $721M; BOTH anchored $86 follow-on</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>PRLD</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Precision oncology / molecular glue / degrader platform. SMARCA2 discontinued 2025; pivot to JAK2V617F (PRT12396) + KAT6A (PRT13722). AbCellera partnership.</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>$175M cash vs $340M mcap = $2.20/sh net cash (51% of price); buyout floor near current</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>PRT12396 Phase 1 H2 2026; PRT13722 IND mid-2026; Incyte option agreement Nov 2025</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Market: broken story post-SMARCA2 fail. Smart money: April 2026 refunding = platform-validation thesis. JAK2 mutant-selective addresses 95% PV/60% ET/55% MF.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Baker Bros 15.5% 13D/A + RA Capital 9.99% 13G; BOTH anchored SAME $90M April financing at $4.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>PVLA</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Rare-disease topical platform. QTORIN rapamycin gel for microcystic LMs (Breakthrough + Orphan + Fast Track). Phase 3 SELVA POSITIVE Feb 24 2026 (mLM-IGA +2.13, p&lt;0.001).</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>$261.9M cash = $25/sh (19% of price). Phase 3 derisked. M&amp;A floor 4-6x peak rev</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Pre-NDA FDA meeting Q2 2026; NDA H2 2026; PDUFA H1 2027</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Market: single-asset rare-disease (~$1.5B). Smart money: platform with &gt;$1B peak QTORIN + venous malformations/angiokeratomas/pitavastatin programs.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>BVF 3.8% / $120M (8.5% of company) + Suvretta 3.67% / $144M (+29.3% Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>4. Sponsor-Anchored Holdco Transformation</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>HHH</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Ackman-led 'Modern Berkshire'. 3,813 acres residential MPC ($4.8B NAV) + 2,447 acres commercial ($2.0B) + Vantage specialty insurance ($2.2B 2027 premium). Marc Grandisson (ex-Arch Capital CEO) on board April 2026.</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>NAV $95-105/sh = 33-39% discount; $1.84B cash + $515M revolver liquidity</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Vantage close Q2 2026 (30-45 days); Park Ward Village condo closings Q2-Q3 (~$1B rev); first post-Vantage capital allocation</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Street: sub-scale RE dev with leverage. Ackman: insurance float + permanent capital. NAV $95-105 vs $63 = 50-67% margin of safety.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Ackman 47% via $900M @ $100/sh + $1B preferred; Northern Right NEW Q1 +12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>5. Spinoff / SoTP Arbitrage</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>DLTR</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Post-divestiture clean Dollar Tree franchise (16k+ stores). Multi-fund deep-value consensus Q1 2026. Mayer M6 turnaround pattern.</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>B/M 0.20 (Yartseva 6/7); Family Dollar divestiture proceeds = $1B+ cash bolster</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Family Dollar sale completion + comparable sales recovery + multiple re-rate</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Market priced Family Dollar mistake. Smart money: post-divestiture clean franchise.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Multi-fund deep-value funds Q1 2026 adds</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>5. Spinoff / SoTP Arbitrage</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Two segments: MTS (gov services 72%, $18.5B backlog, cleared workforce 20k) + STS (process tech + TerraPower Natrium nuclear EPC alliance, 22% EBITDA margin). FY26 $980M-1.04B EBITDA, $3.87-4.22 EPS.</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>SoTP: MTS at 11x EBITDA ($5.2B EV) + STS at 14x ($5.3B) = $55-65/sh combined</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>MTS spin January 4 2027 (board-approved Sept 2025); NRC Natrium safety eval mid-2026</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Market: broken post-HomeSafe termination + class action overhang. Variant: HomeSafe disposed; spin unlocks SoTP value.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>D3/Nierenberg +425% Q1 (largest single add in entire universe); Irenic activist ~1%; Director Form 4 buys May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>6. Deep Drawdown Mean Reversion</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>COTY</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Prestige/fragrance beauty (Burberry, Tiffany, CK, Calvin Klein brands). KKR overhang anchor. -37.5% drawdown extreme contrarian setup. Brand assets worth multiples of EV.</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>B/M 1.73 (DEEPEST in 6/7 tier), FCF yield 17.4%, but ROA -4.91% (Y3 fails)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Debt restructuring + KKR exit dynamics + cost program execution</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Market: earnings deterioration. Smart: 6-year FCF payback floor with brand asset coverage.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>KKR legacy anchor; deep-value funds incrementally adding</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>6. Deep Drawdown Mean Reversion</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>FRPT</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Premium fresh dog food brand leader. Manufacturing capacity coming online (Ennis plant). Margin inflection at 70%+ utilization. M&amp;A target for Nestle Purina / Mars / General Mills.</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>B/M 0.50 (borderline Yartseva 6/7), ROA 3.41%, -40% drawdown</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Capacity utilization + margin inflection + M&amp;A speculation</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Market: consumer weakness + capex burden. Smart: brand pricing power + post-capex FCF inflection.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Marlowe Partners 39.8% in last 13F (highest single-fund signal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>6. Deep Drawdown Mean Reversion</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>OPRX</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>P/B 0.70 sub-book, -65.4% 6mo drawdown</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>DSP integration Q4 2026 + MFN clarity</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Insider 14.82%; $10M buyback</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>6. Deep Drawdown Mean Reversion</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>VITL</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1 for full thesis]</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>B/M 0.74, ROA 11%, -68.76% from peak (DEEPEST drawdown in 6/7)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Avian flu normalization + M&amp;A + summer pricing</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>No major fund concentrated yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>7. Hard Asset / Royalty</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>JOE</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Florida Panhandle landbank with 170k+ acres. GAAP B/M understates LIFO land basis vs market value. True NAV-based B/M likely &gt;1.0 even at current price.</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Land bank: 170k acres NW Florida; GAAP B/M understates LIFO land basis</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Florida population growth + master plan community development + Berkowitz anchor</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Yartseva fails on size + low GAAP B/M; correct framework is Lynch asset play.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Berkowitz/Fairholme longstanding anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>7. Hard Asset / Royalty</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>NRP</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Nov 2026 distribution + preferreds retire</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Saber 17.75% + Greystone top + Right Tail NEW + Berkowitz</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>7. Hard Asset / Royalty</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>TPL</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Permian water + royalty optionality. Same NAV-vs-GAAP-book issue as JOE. Pricing 'endless drilling' premium.</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Permian royalty trust at 25x P/CF (vs NRP at 6x)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Permian production growth + water revenue optionality</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Yartseva captures FCF yield + ROA but understates B/M for land assets.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Multi-fund quality holders; HRC anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>8. Foreign / Underfollowed Value</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>BZU.IM</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Italian cement (€8.9B mcap). 52% of EBITDA from US. AI data-center concrete demand thesis. Trading at sector-discount multiple to LafargeHolcim/CRH peers.</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>6.8x EV/EBITDA (vs peer 9-11x); €85 PT = +73% upside</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>AI data-center capex translating to concrete orders; multiple re-rate to peer levels</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Italian listing + cement = institutional underweight. Kerrisdale Oct 2025 long thesis 73% upside.</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Kerrisdale Capital published long thesis Oct 2025 (€85 PT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>8. Foreign / Underfollowed Value</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>MGNI</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Independent CTV SSP. Netflix/Disney/Roku exclusive deals scaling. AI ad-buying integration. Last major non-Google scaled SSP.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Yartseva 6/7 (sub-$2B), B/M 0.49, FCF yield positive, ROA positive</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>CTV ad spend doubling 2024-2028 + Netflix exclusive scaling + AI integration</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Market: ad-tech roadkill. Smart: winning independent CTV SSP that survived ad-tech wash-out.</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Nine Ten Capital (Bares) 13.1% of book / 3.48M sh / $41.4M</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>8. Foreign / Underfollowed Value</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>MTY.TO</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026 SSS test + NCIB</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>CEO open-market buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>9. Quality Compounder at Trough</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Yartseva 6/7 IT services franchise. Multi-fund consensus Q1 2026. 300k+ delivery workforce moat. AI/IT services capex super-cycle 2026-2028.</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>P/B 1.66 (B/M 0.60), 9.88% FCF yield, ROA 10.44%, -27% 6mo</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>AI implementation winner via enterprise partners + Q2 2026 earnings</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Market: AI disrupts IT services. Smart: AI accelerator not disruptor.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Multi-fund deep-value funds Q1 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>9. Quality Compounder at Trough</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>DHR</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Pure-play life sciences (Cytiva bioprocessing, Beckman Dx, Cepheid). Q1 EPS $2.06 beat by 6.2%; bioprocessing inflecting positive after destock; Cepheid respiratory comp resets Q4 2026.</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>19.7x forward P/E (trough vs 5yr avg 30x); ROA pos; B/M 0.43</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Bioprocessing book-to-bill durably &gt;1.0 + China VBP stabilization H2 2026 + Cepheid Q4 reset</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Consensus: show-me on growth post-destock. Sundheim/D1: same stock 2019-2021 (30%/yr) at trough multiple while H2 2026 comps inflect.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>D1 Capital +312% Q1 ($107M→$437M, 4th-largest position)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>9. Quality Compounder at Trough</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Founder/CEO Schleifer + Yancopoulos R&amp;D-led. $31.4B book equity + EYLEA franchise + Linvoseltamab launching. Pipeline broad. Itepekimab Phase 3 readout potential catalyst.</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>B/M 0.48, FCF yield 6.33%, P/B 2.07; Yartseva 6/7 (size only fail)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Itepekimab 2026-2027 data + Linvoseltamab ramp</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Market: fianlimab miss + Eylea biosimilar. Smart: broad pipeline + buyback + founder skin.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Founder-led; multi-fund pharma specialist holds</t>
         </is>
       </c>
     </row>
@@ -1335,6 +3962,1528 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Issuer</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t># buyers</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Total $M</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg px</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Last</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Off 52w high</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Top buyer</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Asof</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>INIO</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>INNIO N.V.</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>32.36999893188477</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>LINEBARGER NORMAN THOMAS</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>RYAN</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>RYAN SPECIALTY HOLDINGS, INC.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>35.63999938964844</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>-48%</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>RYAN PATRICK G</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Dir/Executive Chairman/1</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SMMT</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Summit Therapeutics Inc.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>14.01000022888184</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>-52%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>DUGGAN ROBERT W</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Dir/Co-Chief Executive O</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>NVRI</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Enviri Corp</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>21.35000038146973</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>+0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Hochman Russell C.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Dir/President and CEO</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>AADX</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Applied Aerospace &amp;amp; Defense, Inc.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>20.43000030517578</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Katzman James C</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>INFINITY NATURAL RESOURCES, INC.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>13.13000011444092</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>-33%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Quinn William J</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Dir/10%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PICS</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>PicS N.V.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>10.81999969482422</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>-43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Batista Costa Jose Antonio</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SSMR</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Sunshine Silver Mining &amp;amp; Refining Co</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>El-Erian Anna</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CAVA</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>CAVA GROUP, INC.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>75.63</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>90.98999786376953</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Thompson Douglas W.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Chief Operations Officer</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>MTDR</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Matador Resources Co</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>53.81</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>54.04999923706055</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>-17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Foran Joseph Wm</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Dir/Chairman and CEO</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>FCNCA</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>FIRST CITIZENS BANCSHARES INC /DE/</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1861.53</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>2108.610107421875</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>HOLDING FRANK B JR</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Dir/Chairman and CEO/10%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>GROW</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>U S GLOBAL INVESTORS INC</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>2.960000038146973</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>-18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Gator Capital Management, LL</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>GLP</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>GLOBAL PARTNERS LP</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>47.13000106811523</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Global GP LLC</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TWFG</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>TWFG, Inc.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>21.55999946594238</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>-40%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>DOAK MICHAEL</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>LOGC</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>ContextLogic Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>10.10000038146973</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>+0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>LEVY PAUL S</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>BRC</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>BRADY CORP</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>82.62999725341797</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>-14%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Nargolwala Vineet A</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Dir/President &amp;amp; CEO</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Subject company</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Filer</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Last</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Off 52w high</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Amplify ETF Trust</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Hennion &amp; Walsh Asset Management, Inc.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>NYLI MacKay Muni Income Opportunities Fund</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>NYLIM Capital LLC</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>20260608</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>StepStone Private Infrastructure Fund</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>StepStone Group LP</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20260605</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ELAB</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>PMGC Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Bensler Graydon</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1.470000028610229</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>-99%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>GOSS</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Gossamer Bio, Inc.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>D. E. SHAW &amp; CO, L.P.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.1618999987840652</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>-96%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>BNBX</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>BNB PLUS CORP.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>KGPLA Holdings LLC</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.4580000042915344</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>RITE</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>MINERALRITE Corp</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Hendricks Lloyd Bernard III</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.003500000108033419</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>-82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>INM</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>InMed Pharmaceuticals Inc.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Opportunity Fund Holdings, L.P.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1.509999990463257</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>-61%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TELA</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>TELA Bio, Inc.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>EW HEALTHCARE PARTNERS FUND 2, L.P.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0.8600000143051147</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>-60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>AMFN</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>American Fusion, Inc.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Hawkins Richard C.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0.0949999988079071</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>-42%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>CNCKW</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Coincheck Group N.V.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>KDDI CORP</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.1710000038146973</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>-34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>REA</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Rare Earths Americas, Inc.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>A.C.N. 664 400 382 Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>18.3700008392334</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>-33%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>NEXT</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>NextDecade Corp</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>GAP Holdings GP, LLC</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>8.399999618530273</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>-30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SKAS</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Saker Aviation Services, Inc.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>ERIKSEN CAPITAL MANAGEMENT LLC</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>-29%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>DBI</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Designer Brands Inc.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Stone House Capital Management, LLC</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>6.880000114440918</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>-24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>GRTX</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Galera Therapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Hyare Parvinder Singh</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0.08510000258684158</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>-19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>OCFC</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>OCEANFIRST FINANCIAL CORP</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>WARBURG PINCUS LLC</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>20260608</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>18.60000038146973</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>DDT</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>DILLARD'S, INC.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>DILLARD WILLIAM T II</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>20260605</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>26.1299991607666</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>AMAN</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Amanat Acquisition Corp.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Amanat Sponsor Holdings LLC</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>10.10000038146973</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>-0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>BIDWU</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Tribeca Strategic Acquisition Corp.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Tribeca Strategic Partners Holdco LLC</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>20260608</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>9.976200103759766</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>-0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>APMCU</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>AmperCap Acquisition Co</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>AmperSPAC LLC</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>9.979999542236328</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>-0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>CZWI</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Citizens Community Bancorp Inc.</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Schornack Andrew David</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>21.45999908447266</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>+0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>DGAC-UN</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>DISCIPLINED GROWTH ACQUISITION Corp</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Disciplined Growth Sponsor LLC</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>10.02499961853027</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>+0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>PBMWW</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>PSYENCE BIOMEDICAL LTD.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Psyence Labs Ltd</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0.03359999880194664</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>+0%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1556,7 +5705,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2786,13 +6935,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4042,17 +8191,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>WGS</t>
+          <t>RYAN</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>GeneDx</t>
+          <t>Ryan Specialty Holdings</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Genomic diagnostics (commercial-stage NOT clinical)</t>
+          <t>Specialty insurance distribution</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -4061,19 +8210,17 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>56.33000183105469</v>
+        <v>35.64</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1670.2</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>29.65</v>
-      </c>
+        <v>9300</v>
+      </c>
+      <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
           <t>2-NEW</t>
@@ -4081,34 +8228,34 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>WEB_VERIFIED_2026-06-10</t>
+          <t>EDGAR_VERIFIED_2026-06-12</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>CAVEAT: +75% off May 5 capitulation low $32.21 already; was $170 four months ago — partial rerate; securities-fraud investigations are open</t>
+          <t>4-insider cluster $4.46M May-Jun 2026 incl FOUNDER Patrick Ryan (Exec Chairman); -48% off 52w high; mcap &gt;$5B caps multibag to ~2x prior high but cluster is top backtest bucket</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Investing.com + SEC 13D-A + stockanalysis</t>
+          <t>EDGAR Form4 XML via discover.py</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>TWFG</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>OptimizeRx</t>
+          <t>TWFG Inc</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Digital health marketing</t>
+          <t>Insurance distribution (P&amp;C agency)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -4117,54 +8264,52 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>5.070000171661377</v>
+        <v>21.56</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>95.09999999999999</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>18.76</v>
-      </c>
+        <v>1200</v>
+      </c>
+      <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2-WEAKENED</t>
+          <t>2-NEW</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>WEB_VERIFIED_2026-06-10</t>
+          <t>EDGAR_VERIFIED_2026-06-12</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>$10M buyback confirmed + PT $11.50 confirmed; CAVEAT: CFO sold @$13.51 Dec25 + CEO sold @$18.75 Oct25 pre-collapse + neither bought the dip</t>
+          <t>Director Doak $1.43M open-market @ ~$19.15; -40% off 52w high; 2024 IPO; founder-led</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>SEC 8-K + stockanalysis + GlobeNewswire</t>
+          <t>EDGAR Form4 XML via discover.py</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CELC</t>
+          <t>WGS</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Celcuity</t>
+          <t>GeneDx</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Biotech (EXCLUDED)</t>
+          <t>Genomic diagnostics (commercial-stage NOT clinical)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -4173,18 +8318,22 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>92.58999633789062</v>
+        <v>56.33000183105469</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
+      <c r="G25" s="2" t="n">
+        <v>1670.2</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>29.65</v>
+      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2-bio</t>
+          <t>2-NEW</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -4194,29 +8343,29 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Strong data moved stock; PDUFA only remaining binary</t>
+          <t>CAVEAT: +75% off May 5 capitulation low $32.21 already; was $170 four months ago — partial rerate; securities-fraud investigations are open</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>ApexOnco + Celcuity PR</t>
+          <t>Investing.com + SEC 13D-A + stockanalysis</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>MNK</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Keenova Therapeutics (was MNKTQ)</t>
+          <t>OptimizeRx</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Specialty pharma</t>
+          <t>Digital health marketing</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -4224,13 +8373,23 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
+      <c r="E26" s="2" t="n">
+        <v>5.070000171661377</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>18.76</v>
+      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2-WEAKENED</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -4240,29 +8399,29 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Ticker changed; illiquid until relist</t>
+          <t>$10M buyback confirmed + PT $11.50 confirmed; CAVEAT: CFO sold @$13.51 Dec25 + CEO sold @$18.75 Oct25 pre-collapse + neither bought the dip</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Keenova PR</t>
+          <t>SEC 8-K + stockanalysis + GlobeNewswire</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>AERO</t>
+          <t>CELC</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Grupo Aeromexico</t>
+          <t>Celcuity</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Airline post-BK</t>
+          <t>Biotech (EXCLUDED)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -4271,7 +8430,7 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>16.68000030517578</v>
+        <v>92.58999633789062</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -4282,7 +8441,7 @@
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3-DEMOTED</t>
+          <t>2-bio</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -4292,29 +8451,29 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>All four major holders are selling shareholders = supply overhang</t>
+          <t>Strong data moved stock; PDUFA only remaining binary</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Bloomberg + PE-Insights</t>
+          <t>ApexOnco + Celcuity PR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GLOB</t>
+          <t>MNK</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Keenova Therapeutics (was MNKTQ)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>LatAm IT + AI services</t>
+          <t>Specialty pharma</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -4322,23 +8481,13 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>37.47000122070312</v>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>1619.8</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>43.23</v>
-      </c>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3-DEMOTED</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -4348,29 +8497,29 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>P/E 5.91 was FORWARD (trailing 15.3); -45.6% 6mo and still falling; no near-term positive trigger</t>
+          <t>Ticker changed; illiquid until relist</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>stockanalysis + PRNewswire 6/9/26</t>
+          <t>Keenova PR</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>AERO</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Infinity Natural Resources</t>
+          <t>Grupo Aeromexico</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Appalachian natgas E&amp;P</t>
+          <t>Airline post-BK</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -4379,7 +8528,7 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>13.59000015258789</v>
+        <v>16.68000030517578</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -4390,7 +8539,7 @@
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3-NEW</t>
+          <t>3-DEMOTED</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -4400,29 +8549,29 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-32% from IPO; hard-asset gas; director Form 4 + AI data-center gas tailwind</t>
+          <t>All four major holders are selling shareholders = supply overhang</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>SEC Form 4</t>
+          <t>Bloomberg + PE-Insights</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>GLOB</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Warner Bros Discovery</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>LatAm IT + AI services</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4431,7 +8580,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>26.55999946594238</v>
+        <v>37.47000122070312</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -4439,46 +8588,46 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>66600</v>
+        <v>1619.8</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>2507.53</v>
+        <v>43.23</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>ARB-ONLY</t>
+          <t>3-DEMOTED</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>RECLASSIFIED_MERGER_ARB</t>
+          <t>WEB_VERIFIED_2026-06-10</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Split DEAD - superseded by cash deal; 17% spread to deal = regulatory-risk arb not value</t>
+          <t>P/E 5.91 was FORWARD (trailing 15.3); -45.6% 6mo and still falling; no near-term positive trigger</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Variety + Netflix IR</t>
+          <t>stockanalysis + PRNewswire 6/9/26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PBPB</t>
+          <t>DBI</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Potbelly</t>
+          <t>Designer Brands (DSW)</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Restaurant chain</t>
+          <t>Footwear retail</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4487,50 +8636,52 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>17.12</v>
+        <v>6.88</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n"/>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>350</v>
+      </c>
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>DEAD</t>
+          <t>3-NEW</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>SITUATION_DEAD</t>
+          <t>EDGAR_VERIFIED_2026-06-12</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>RaceTrac acquired Oct 23 2025</t>
+          <t>Stone House Capital NEW SCHEDULE 13D 6/11/26; -24% off high; CAUTION: activist_13d bucket has -26% base rate; deep value retail w/ heavy shorts</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>RaceTrac 8-K</t>
+          <t>EDGAR daily index via discover.py</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>MRP</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Millrose Properties</t>
+          <t>Infinity Natural Resources</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Land bank (Lennar spin)</t>
+          <t>Appalachian natgas E&amp;P</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4539,54 +8690,50 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>29.29999923706055</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
-        <v>4870</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>166.21</v>
-      </c>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>DEMOTED-2</t>
+          <t>3-NEW</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>THESIS_KILLED</t>
+          <t>WEB_VERIFIED_2026-06-10</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Lennar distributed 80% Feb 2025 + EXITED remaining 20% via exchange offer Dec 1 2025 - owns ~0% today</t>
+          <t>-32% from IPO; hard-asset gas; director Form 4 + AI data-center gas tailwind</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Lennar newsroom + businesswire Dec 1 2025</t>
+          <t>SEC Form 4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>BTSG</t>
+          <t>SKAS</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>BrightSpring Health</t>
+          <t>Saker Aviation Services</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Pharmacy + home health</t>
+          <t>FBO/heliport micro</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4595,54 +8742,52 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>12700</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>208.2</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>KILLED</t>
+          <t>3-NEW</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>RERATED_CONFIRMED</t>
+          <t>EDGAR_VERIFIED_2026-06-12</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Price $61 not $10; +159% y/y</t>
+          <t>Eriksen Capital NEW SCHEDULE 13D 6/11/26; -29% off high; ultra-micro illiquidity</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>yahoo + 13f.info</t>
+          <t>EDGAR daily index via discover.py</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>BW</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Babcock &amp; Wilcox</t>
+          <t>Warner Bros Discovery</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Industrial/energy tech</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4651,7 +8796,7 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>15.49</v>
+        <v>26.55999946594238</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -4659,46 +8804,46 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>2300</v>
+        <v>66600</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>148.48</v>
+        <v>2507.53</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>KILLED</t>
+          <t>ARB-ONLY</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>THESIS_WRONG+RERATED</t>
+          <t>RECLASSIFIED_MERGER_ARB</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>16x in 12 months; nuclear claim = BWXT confusion; activist was Galloway not Steel</t>
+          <t>Split DEAD - superseded by cash deal; 17% spread to deal = regulatory-risk arb not value</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SEC 13D + benzinga</t>
+          <t>Variety + Netflix IR</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>CROX</t>
+          <t>PBPB</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Potbelly</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Footwear brand</t>
+          <t>Restaurant chain</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4707,54 +8852,50 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>127.77</v>
+        <v>17.12</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>6350</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>49.7</v>
-      </c>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>KILLED</t>
+          <t>DEAD</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>RERATED_CONFIRMED</t>
+          <t>SITUATION_DEAD</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>+53% above Li Lu basis; discount GONE</t>
+          <t>RaceTrac acquired Oct 23 2025</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>GuruFocus + yahoo</t>
+          <t>RaceTrac 8-K</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>CTMX</t>
+          <t>MRP</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CytomX Therapeutics</t>
+          <t>Millrose Properties</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Biotech warrants</t>
+          <t>Land bank (Lennar spin)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4763,50 +8904,54 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>2.98</v>
+        <v>29.29999923706055</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
+      <c r="G36" s="2" t="n">
+        <v>4870</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>166.21</v>
+      </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>KILLED</t>
+          <t>DEMOTED-2</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>WEB_VERIFIED_2026-06-10</t>
+          <t>THESIS_KILLED</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Warrants 21% out-of-money with 3 weeks left = likely worthless</t>
+          <t>Lennar distributed 80% Feb 2025 + EXITED remaining 20% via exchange offer Dec 1 2025 - owns ~0% today</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>StockTitan 13G/A</t>
+          <t>Lennar newsroom + businesswire Dec 1 2025</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>BTSG</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Perimeter Solutions</t>
+          <t>BrightSpring Health</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Fire retardants oligopoly</t>
+          <t>Pharmacy + home health</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4815,7 +8960,7 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>32.77</v>
+        <v>61</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -4823,10 +8968,10 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>5350</v>
+        <v>12700</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>163.26</v>
+        <v>208.2</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
@@ -4835,34 +8980,34 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>INSIDER_CLAIM_REFUTED+RERATED</t>
+          <t>RERATED_CONFIRMED</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Mcap off 10x; +135% y/y</t>
+          <t>Price $61 not $10; +159% y/y</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>StockTitan Form 4</t>
+          <t>yahoo + 13f.info</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>BW</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Talen Energy</t>
+          <t>Babcock &amp; Wilcox</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nuclear IPP</t>
+          <t>Industrial/energy tech</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4871,7 +9016,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>358.74</v>
+        <v>15.49</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -4879,10 +9024,10 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>16300</v>
+        <v>2300</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>45.44</v>
+        <v>148.48</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
@@ -4891,34 +9036,34 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>RERATED_CONFIRMED</t>
+          <t>THESIS_WRONG+RERATED</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Price $359 not $200; 5-6x already happened</t>
+          <t>16x in 12 months; nuclear claim = BWXT confusion; activist was Galloway not Steel</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>SEC 13D + benzinga</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>SEER</t>
+          <t>CROX</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Seer Inc</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Proteomics tools (NOT clinical-stage)</t>
+          <t>Footwear brand</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -4927,7 +9072,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1.690000057220459</v>
+        <v>127.77</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -4935,86 +9080,306 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>94.59999999999999</v>
+        <v>6350</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>56</v>
+        <v>49.7</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>WEB_VERIFIED_2026-06-10</t>
+          <t>KILLED</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Trades 55% BELOW net cash — net cash ~$3.80/sh vs price $1.75; bid conditioned on &gt;=$215M net cash = 2x+ market cap; classic net-net with activist enforcer</t>
+          <t>RERATED_CONFIRMED</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>stocktitan DFAN14A</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
+          <t>+53% above Li Lu basis; discount GONE</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>GuruFocus + yahoo</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>CTMX</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>CytomX Therapeutics</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Biotech warrants</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>KILLED</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>WEB_VERIFIED_2026-06-10</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Warrants 21% out-of-money with 3 weeks left = likely worthless</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>StockTitan 13G/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>PRM</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Perimeter Solutions</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Fire retardants oligopoly</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>32.77</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>5350</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>163.26</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>KILLED</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>INSIDER_CLAIM_REFUTED+RERATED</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Mcap off 10x; +135% y/y</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>StockTitan Form 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>TLN</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Talen Energy</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Nuclear IPP</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>358.74</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>16300</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>45.44</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>KILLED</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>RERATED_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Price $359 not $200; 5-6x already happened</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>SEER</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Seer Inc</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Proteomics tools (NOT clinical-stage)</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>1.690000057220459</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>WEB_VERIFIED_2026-06-10</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Trades 55% BELOW net cash — net cash ~$3.80/sh vs price $1.75; bid conditioned on &gt;=$215M net cash = 2x+ market cap; classic net-net with activist enforcer</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>stocktitan DFAN14A</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
           <t>SSTI</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>SoundThinking</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Public safety tech</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="E44" s="2" t="n">
         <v>7.710000038146973</v>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H40" s="2" t="n">
+      <c r="H44" s="2" t="n">
         <v>25.94</v>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>WEB_VERIFIED_2026-06-10</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>Activist defeated; thesis now fundamentals only</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>SnowballResearch + StockTitan 8-K</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5085,7 +9450,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -5115,7 +9480,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -5145,7 +9510,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -5175,7 +9540,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -5205,7 +9570,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -5235,7 +9600,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -5265,7 +9630,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -5295,7 +9660,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -5325,7 +9690,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -5355,7 +9720,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -5385,7 +9750,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -5415,7 +9780,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -5445,7 +9810,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -5475,7 +9840,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -5505,7 +9870,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -5535,7 +9900,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -5565,7 +9930,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -5595,7 +9960,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -5625,7 +9990,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -5655,7 +10020,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -5685,7 +10050,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -5715,7 +10080,7 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -5745,7 +10110,7 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -5775,7 +10140,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -5976,7 +10341,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7008,7 +11373,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7234,2507 +11599,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Mcap $M</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ADV shares</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ADV $M</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Days to exit 1% pos</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Asof</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CODI</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n">
-        <v>852670</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>9.07</v>
-      </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>AERO</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n">
-        <v>187630</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>LQDA</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n">
-        <v>1878190</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>120.22</v>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CELC</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n">
-        <v>1735025</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>160.65</v>
-      </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n">
-        <v>476460</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>VITL</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>449</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>2983805</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>31.27</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>GLOB</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>1619.8</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>2137975</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>80.11</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>GPRO</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>147</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>7885950</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>MNRO</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>439.8</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>1292765</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>18.95</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>WGS</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>1670.2</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>1306990</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>73.62</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>OPRX</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>95.09999999999999</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>543140</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>2427.6</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>9707365</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>56.11</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>FUN</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>2240.1</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>1953180</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>43.81</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>NSP</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>1420</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>673225</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>25.09</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>FCN</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>5272.6</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>576815</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>92.23999999999999</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>KBR</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>4480</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>1997250</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>70.54000000000001</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>INMD</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>859</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>918205</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>12.45</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>SONO</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>1830.1</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>1486085</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>22.86</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>ROCK</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>1169.9</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>369475</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>14.52</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>MRP</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>4870</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>1594685</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>46.72</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CDRE</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>1290</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>390880</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>66600</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>21221855</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>563.65</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>HHH</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>3999.9</v>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>433645</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>29.35</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CRTO</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>856.9</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>329780</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>LAW</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>228</v>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>405940</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>RPAY</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>302</v>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>542390</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>SSTI</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>116450</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>NRP</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>1370.3</v>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>58800</v>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>SEER</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>247570</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>PRLD</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>391</v>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>321720</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>MTY.TO</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>908.1</v>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>34750</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Archetype</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Thesis</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Valuation</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Catalyst</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Variant</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Smart money</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>CARS</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Digital dealer SaaS (19,390 dealers x $2,473 ARPD/mo, 90% recurring). Q1 EPS $0.45 vs $0.13 est (+246%). Subscription +2%; OEM/National -12% (cyclical bottom).</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>P/B 0.83, P/FCF 3.5, 28% TTM FCF yield, EV/EBITDA 2.7x</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>$25-30M annualized cost program 2027 + $90M buyback (16% cap raised from $60M)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Street: declining auto Yellow Pages at 4x P/FCF. Variant: 90% SaaS dealer recurring + buyback math.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Yartseva 7/7 - smart money still building</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>CRTO</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Performance ad-tech pivoting to Commerce Yield retail media (235 retailers incl Lowes/Costco). $1B+ media spend Q1 2026 (+8% cc). OpenAI partnership live with 1,000+ brands. Q1 retail media -31% ex-scope -- actual underlying +24%.</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>P/E 3.73 (fwd), P/B 0.79, P/FCF 4.98, EV/EBITDA 2.28, 20.7% FCF yield</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Q3 2026 anniversary of scope losses + Luxembourg redomiciliation + $200M buyback (22% cap)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Market prices terminal decline; Petrus Advisers activist + 33% FCF yield + retail media TAM $200B by 2028.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Nierenberg D3 9.37% / +19% Q1 2026; Petrus Advisers activist</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>DV</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Pure-play ad verification (68% market share in fraud detection vs IAS 2.7%). 4,300+ customers vs IAS 169. Q1 2026 rev +10%, EBITDA 31% margin. CTV +28%, social activation +92%.</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>P/FCF 11x (trough), EV/EBITDA 9.6x, EV/Sales 1.9x, 9% FCF yield</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>ABS streaming Do Not Air list rollout Q2/Q3 + Meta activation $12M ARR to $50M+ path</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Market: Google MRC self-measurement threat. Variant: CTV verification underpenetrated (10%) vs display (70%).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Insider 12.69% (high for ad-tech); Yartseva 7/7</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>FTLF</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Microcap nutraceutical at $93M cap. Sub-institutional minimum. Classic Yartseva discarded-microcap profile with positive FCF + ROA + extreme drawdown.</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>P/B 2.05, B/M 0.49, FCF yield 8.2%, ROA 7.2%, near 52w low, -43.9% 6mo</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026 earnings; M&amp;A speculation; recovery in supplement category</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Market: forgotten micro. Smart money: pure Yartseva mean-reversion target.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Smoak Capital residual position; previously a Smoak top-5</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>GLOB</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>LatAm IT services with AI Pods inflection ($32.8M ARR from $0 in 12 months; $352M pipeline; 40% top-20 client penetration). Founder Migoya 23-year tenure + ~3% via Founders Trust.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>P/E 5.91 (sector low), P/B 0.78, P/FCF 5.56, 17% FCF yield, EV/EBITDA 4.95</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Q3 2026 AI Pods print + Argentina FX tailwind + ENRGI platform launch H2</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Market: melting India-IT comp. Smart money: AI mix shift to higher-margin work + LatAm cost arb. CAVEAT: securities class action (lead plaintiff June 23, 2026); COO resigned July 2025 not replaced.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Cartica historical 6.5% Q4 2022; sentiment bottom 16% short float</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>HRMY</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>$1B+ WAKIX franchise (pitolisant for narcolepsy). Q1 2026 rev +17% to $215M; pediatric FDA approval Feb 13 2026 extends IP to 2030 (pediatric exclusivity to 2040s). 5 Phase 3 trials in pipeline.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>P/B 1.91, P/Sales 2.05, FCF yield 19.36%, 26% net cash position</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Pitolisant GR NDA Q2 2026 (PDUFA Q1 2027); BP-205 Phase 1 PK mid-2026</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Market: single-product cliff. Smart money: Lilly's $6.3B Centessa (Q3 2026 close) validated orexin space + IP estate.</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>M&amp;A buyers: Jazz Pharma, Lundbeck, Otsuka; Catalyst Pharma precedent</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>INMD</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Israeli aesthetic device leader (Morpheus8, BodyTite). 85% recurring consumables. Steel Partners +155% Q1 2026 = 25.5% of their book; founder Mizrahy bought 800k sh ($10.7M) Feb 2026.</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>P/B 1.32, FCF $537M cash = $8.47/sh (62% of price), 77.8% gross margin</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026 earnings ~Aug 5 + potential Steel renewed bid ($18 prior)</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Market: Israeli geopolitical + aesthetic cycle. Smart money: $11-12 floor on cash alone; Steel implied $20+ takeout.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Steel Partners 25.5% of book; Mizrahy +800k sh ($10.7M)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>MTY.TO</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Multi-brand Canadian QSR franchisor (90 banners incl Cold Stone, Mucho Burrito, Papa Murphy's). 7,000+ locations, 98%+ franchised. Q1 EPS C$0.98 BEAT vs C$0.80 cons.</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>P/B 1.04 (trading at book!), EV/EBITDA 7.5x (vs QSR peer 14-18x), 16.7% FCF yield</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026 earnings test SSS stabilization + NCIB 5% of float through July</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Market: melting ice cube. Variant: SSS troughing + debt paying down + M&amp;A pool (RBI, Inspire at 12-14x EBITDA).</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>CEO Lefebvre open-market buy at C$30.54 (+33% stake)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>NRP</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Royalty trust on 13M mineral acres + 49% Sisecam soda ash JV. Near-zero debt by mid-2026 after $109M paydown + preferred retirement. Distribution increase guided for November 2026 (delayed from prior guide due to Sisecam capital call).</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>P/B 2.26 (B/M 0.47), 14.5% FCF yield, ROA 10.5%, 6.6x P/FCF</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Nov 2026 distribution step-up + preferreds retire; Q3 2026 Sisecam recovery sig</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Market: dying coal MLP. Smart money: debt-free royalty with 12% FCF yield, comparable to TPL at 25x P/CF (NRP at 6x).</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Saber/Huber 17.75%, Greystone top, Right Tail NEW Q1 2026, Berkowitz/Fairholme</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>OPRX</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Digital health POC pharma messaging to 60%+ US prescribers. May 21 2026 DeepIntent integration = first DSP accessing OPRX EHR network (Q3 2026 launch) opens &gt;80% of digital pharma budgets.</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>P/B 0.70 (sub-book), P/FCF 4.89, 15.7% FCF yield, EV/Sales 0.88, Adj EBITDA 4.4x EV</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Q4 2026 DSP integration revenue start + Q2 2026 earnings Aug 14</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Market: MFN victim; Smart money: profitable ($19M FCF) at 0.7x book, target $11.50 (138% upside).</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Insider 14.82%; $10M buyback through March 2027; Doximity exec Presti to board April 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>ROCK</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3-segment industrial (Residential 80%, Renewables, Agtech). OmniMax acquisition closed Feb 2026 ($1.335B) = #1 in residential roofing accessories. FY26 guide $1.76-1.83B rev, $3.65-4.05 EPS.</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>P/B 1.34, FCF yield 6.5%, ROA 2.95%, EV/Sales 1.0x vs peer 1.5x</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026 earnings = first clean OmniMax quarter; aluminum normalization; Q3 reroofing season</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Market: busted SPAC with 1.56 D/E. Variant: one-time integration year; FY27 EPS $5+ at 15x = $75-90.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Director Metcalf bought $502k March 2026; Vanguard 5.24% 13G</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>TREE</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Three-segment marketplace (Insurance 68%, Consumer 20%, Home 12%) at Q1 2026 inflection: rev +37%, VMM +28%, EBITDA +71%, Insurance +51%. Net leverage falling 3.4x→2.1x; S&amp;P upgraded.</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>P/E 2.92, P/FCF 7.2, ROE 88.6%, B/M 0.60</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026 print + $575M July 2025 converts retired + Fed rate cuts unlock Home/Consumer</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Street disbelieves Insurance durability. Variant: insurance carriers in year-2 of 5-7yr up-cycle = $200M+ EBITDA into 2027.</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Yartseva 7/7 + post-Q1 inflection demonstrated</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>VITL</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Pasture-raised egg category creator with brand moat. Walmart/Target/Whole Foods distribution. 11% ROA sustained THROUGH the avian flu crash = exceptional earnings power.</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>B/M 0.74, ROA 11% (BEST in 6/7 tier), -68.76% from peak</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Avian flu egg-supply normalization + summer pricing + M&amp;A speculation</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Market lumped premium VITL with commodity egg crash. Reality: brand pricing power retained. Strategic buyers: Kraft Heinz, Hain, General Mills.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>No major fund concentrated yet = entry preserved; Yartseva 6/7</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>10. Hedged / Special Structure</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>AAP CALL</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Cooper Creek's largest single call exposure. Overlaps with H Partners' AAP cash 46% concentration = double-conviction across two fund styles.</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>$158M call notional; +213% Q1 2026 (Cooper Creek)</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026 margin recovery proof + H Partners 13D escalation</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Catalyst-driven leverage on H Partners' AAP thesis.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Cooper Creek call stack ($518M total notional incl SIG/TTWO/DOCN/GXO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>10. Hedged / Special Structure</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>CTMX-WT</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>BVF Partners holds CTMX Tranche 2 warrants expiring 7/3/2026 (next 5 weeks). Embedded biotech IPO/crossover leverage near expiration creates urgency catalyst.</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5.77M shares warrants; group ownership equivalent ~3.5%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Warrant expiration 7/3/2026 = IMMINENT URGENCY</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>BVF's KYMR top conviction (14.6%) signals their biotech book has high conviction quality.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>BVF Partners 13G/A #5 (warrants exp 7/3/2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>10. Hedged / Special Structure</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>LQDA</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Yutrepia (treprostinil dry-powder inhaler) for PAH and PH-ILD. Q1 2026 product sales $129.9M (+44% QoQ); 4,500 unique patients; mgmt $1B+ 2027 target.</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>P/Sales 12x on $130M Q1 run-rate; cash $200M+ floor; M&amp;A premium 50-100%</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>'327 patent ruling pending (binary); Q2 print Aug 2026; UTHR Tresmi competitive launch</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Consensus PT $63.75 assumes flat share. Buckley's PUT-hedged structure suggests binary patent risk; UTHR M&amp;A target.</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Buckley Capital 32% LONG + PUT structure ($44.7M notional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>10. Hedged / Special Structure</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>XBI</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Stonepine $51M long + $51M short = $102M notional. Pure long-vol bet on biotech 2026-2027 FDA cycle dispersion.</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Biotech basket at multi-year low; straddle structure captures vol</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Biotech FDA cycle 2026-2027 (multiple catalysts driving dispersion)</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Long-vol thesis: biotech sector cycle creates dispersion that benefits straddle structure regardless of direction.</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Stonepine 40.9% of $250M book in XBI straddle</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2. Activist Board Catalyst</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>AAP</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>#3 aftermarket retailer post-WorldPac sale. Q1 +3.5% comps (Pro mid-single, DIY low-single). 700+ stores closed; ~1,300 strategic locations remain. Bridge to AZO-style 8-10% margins = $130-150/sh.</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>3.8% op margin (rising +410bps), FY26 guide $2.40-3.10 EPS; sub-1x sales; M&amp;A floor 0.8x sales = $80/sh</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026 earnings Aug = needs comps +2%+ and op margin &gt;5%; H Partners 13D escalation possible</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Consensus PT $57 (dead money). H Partners 46% concentration implies AAP returns to AZO margins.</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>H Partners 46.3% / $71.2M / +50% sh Q1 2026 (1.35M sh); Legion Partners precedent</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2. Activist Board Catalyst</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>ACHC</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Largest US behavioral health network (260+ facilities). DOJ Medicaid investigation overhang. Q1 2026 admissions stabilizing. Greenlight 4.1M activist; Sohn 5/12 pitch.</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>EV/EBITDA 6.5x (vs HCA 9x, UHS 8x); 29% short float; -70% drawdown</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>DOJ resolution + Q2 2026 earnings + 29% short squeeze potential</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Market: DOJ/Medicaid existential. Greenlight: provider necessity + facility footprint + de-rate captured = floor near current.</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Greenlight Capital 4.1M sh (David Einhorn); Sohn presentation 5/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>2. Activist Board Catalyst</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>FUN</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Post-Cedar Fair/Six Flags merger consolidation. 42 parks irreplaceable real estate. Q1 2026 rev +12%, attendance +4%, per-cap +6%. $200M synergy target ($120M cost + $80M growth).</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>$5.27B net debt = 7x leverage; EV/EBITDA 9x on $1.05B 2027 EBITDA</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>May 26 2026 AGM: Jaffer joins board (Class III through 2027, Audit&amp;Finance Cttee). Jana 9% pushing OUTRIGHT SALE.</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Street: broken merger story. Two-front activist pressure (governance + sale) + per-park RE floor $47M each.</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>H Partners 53.7% / $82.5M / 5.7% of class; Jana 9% + Travis Kelce co-invest</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2. Activist Board Catalyst</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>MRP</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Lennar 80%+ owner spinoff with 100k+ optioned lots at cost basis. Land bank trading below NAV with Lennar as guaranteed off-take partner. Housing-cycle recovery levered.</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>B/M 1.274 (DEEPEST in 6/7 tier; deeper than NRP's 0.47), pure NAV play</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026 print + Lennar volume scaling + housing cycle inflection</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Market priced spinoff orphan technical pressure. Smart money: pure land cash-cow at discount to NAV.</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Lennar 80%+ owner = patient capital lock-in; SITG multi-fund flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>2. Activist Board Catalyst</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>POSTBPB</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Nierenberg/D3 is LARGEST shareholder (~$16.4M / 7% of D3 book). Customer-traffic gains while peers don't (Q1 2026 letter thesis). Form 4 insider buying by Nierenberg at depressed levels.</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Sub-$300M micro restaurant chain; turnaround stage</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Restaurant turnaround + Nierenberg potential escalation</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Market: tier-2 restaurant chain. Activist soft-pressure thesis.</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Nierenberg/D3 largest shareholder; 13D/A active March 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2. Activist Board Catalyst</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>QRHC</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Wynnefield filed 13D 13.3% May 2025; Robert Lipstein joined board. Cooperation Agreement w/ standstill until 30 days before 2027 nomination window. Asset-light recurring waste mgmt.</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Sub-$200M micro; recurring waste services revenue model</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Operational improvements + Wynnefield additional buying if dips</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Market: small-cap value trap. Activist: board seat + potential value-unlock initiatives.</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Wynnefield 13.3% / 2.73M sh / 13D w/ board seat</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>3. Biotech Multi-Fund Convergence</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>ASND</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>TransCon prodrug platform: SKYTROFA (GHD), YORVIPATH (hypopara), YUVIWEL (achondroplasia approved Feb 2026). &gt;1,000 new US YORVIPATH enrollments Q1; 6,300+ patients across 2,700 prescribers.</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Profitable (22% non-IFRS op margin); €247M Q1 (2x YoY); peak rev YORVIPATH $4-5B</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>YUVIWEL ramp + Q2/Q3 YORVIPATH growth + TransCon CNP follow-on indications</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Sell-side: $15B endocrine specialty maturing. RA Capital: $30B+ at 70-90K addressable hypopara population. Analyst high $345 (Barclays).</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>RA Capital 24.9% of $9.44B = $2.35B = LARGEST single biotech crossover position; held since 2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>3. Biotech Multi-Fund Convergence</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>BNTC</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Gene therapy platform anchor position. Suvretta 44.1% 13D anchor stake (largest activist ownership in their portfolio). PIPE participation Nov 2025.</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Sub-$300M biotech; gene therapy platform optionality</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Multiple gene-therapy programs in development; clinical readouts upcoming</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>44.1% ownership creates board influence + asymmetric upside on clinical reads.</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Suvretta 44.1% 13D (Suvretta's LARGEST stake by % ownership)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>3. Biotech Multi-Fund Convergence</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>CELC</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Phase 3 VIKTORIA-1 PIK3CA-mut POSITIVE May 1 2026 (76% PFS hazard reduction). Gedatolisib pan-PI3K/mTOR oncology. Triplet vs alpelisib+fulvestrant. Multiple HR+/HER2- breast cancer cohorts.</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>$387M cash + accepted NDA + Priority Review = de-risked; 4-5x peak rev precedent</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>JUNE 2 ASCO LBA1008 oral + JULY 17 PDUFA goal date (2 catalysts in 8 weeks)</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Market: alpelisib-class peak ($1-2B). Baker Bros 19.99% 13D activist: $5-10B peak (triplet displaces alpelisib + captures WT segment).</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Baker Bros 19.99% ACTIVIST 13D = $904M / 5.48% of $17.4B book</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3. Biotech Multi-Fund Convergence</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>KYMR</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Targeted protein degradation platform. Lead KT-621 oral STAT6 degrader competes with injectable Dupixent ($14B+ franchise). IRAK4 partnered with Sanofi.</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>$1.55B cash (runway 2029); Dec 2025 follow-on $602M at $86</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>BROADEN2 AD mid-2027 (12+ months); BREADTH asthma late 2027; FDA Fast Track granted both</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Market: Phase 1b execution risk. Two top biotech specialists: oral Dupixent-disruptor with peak $5-10B.</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>BVF #1 position 14.6% of $3.14B book ($458M) + Baker Bros 4.1% / $721M; BOTH anchored $86 follow-on</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>3. Biotech Multi-Fund Convergence</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>PRLD</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Precision oncology / molecular glue / degrader platform. SMARCA2 discontinued 2025; pivot to JAK2V617F (PRT12396) + KAT6A (PRT13722). AbCellera partnership.</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>$175M cash vs $340M mcap = $2.20/sh net cash (51% of price); buyout floor near current</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>PRT12396 Phase 1 H2 2026; PRT13722 IND mid-2026; Incyte option agreement Nov 2025</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Market: broken story post-SMARCA2 fail. Smart money: April 2026 refunding = platform-validation thesis. JAK2 mutant-selective addresses 95% PV/60% ET/55% MF.</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Baker Bros 15.5% 13D/A + RA Capital 9.99% 13G; BOTH anchored SAME $90M April financing at $4.44</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>3. Biotech Multi-Fund Convergence</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>PVLA</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Rare-disease topical platform. QTORIN rapamycin gel for microcystic LMs (Breakthrough + Orphan + Fast Track). Phase 3 SELVA POSITIVE Feb 24 2026 (mLM-IGA +2.13, p&lt;0.001).</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>$261.9M cash = $25/sh (19% of price). Phase 3 derisked. M&amp;A floor 4-6x peak rev</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Pre-NDA FDA meeting Q2 2026; NDA H2 2026; PDUFA H1 2027</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Market: single-asset rare-disease (~$1.5B). Smart money: platform with &gt;$1B peak QTORIN + venous malformations/angiokeratomas/pitavastatin programs.</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>BVF 3.8% / $120M (8.5% of company) + Suvretta 3.67% / $144M (+29.3% Q1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>4. Sponsor-Anchored Holdco Transformation</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>HHH</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Ackman-led 'Modern Berkshire'. 3,813 acres residential MPC ($4.8B NAV) + 2,447 acres commercial ($2.0B) + Vantage specialty insurance ($2.2B 2027 premium). Marc Grandisson (ex-Arch Capital CEO) on board April 2026.</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>NAV $95-105/sh = 33-39% discount; $1.84B cash + $515M revolver liquidity</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Vantage close Q2 2026 (30-45 days); Park Ward Village condo closings Q2-Q3 (~$1B rev); first post-Vantage capital allocation</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Street: sub-scale RE dev with leverage. Ackman: insurance float + permanent capital. NAV $95-105 vs $63 = 50-67% margin of safety.</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Ackman 47% via $900M @ $100/sh + $1B preferred; Northern Right NEW Q1 +12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>5. Spinoff / SoTP Arbitrage</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>DLTR</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Post-divestiture clean Dollar Tree franchise (16k+ stores). Multi-fund deep-value consensus Q1 2026. Mayer M6 turnaround pattern.</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>B/M 0.20 (Yartseva 6/7); Family Dollar divestiture proceeds = $1B+ cash bolster</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Family Dollar sale completion + comparable sales recovery + multiple re-rate</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Market priced Family Dollar mistake. Smart money: post-divestiture clean franchise.</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Multi-fund deep-value funds Q1 2026 adds</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>5. Spinoff / SoTP Arbitrage</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>KBR</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Two segments: MTS (gov services 72%, $18.5B backlog, cleared workforce 20k) + STS (process tech + TerraPower Natrium nuclear EPC alliance, 22% EBITDA margin). FY26 $980M-1.04B EBITDA, $3.87-4.22 EPS.</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>SoTP: MTS at 11x EBITDA ($5.2B EV) + STS at 14x ($5.3B) = $55-65/sh combined</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>MTS spin January 4 2027 (board-approved Sept 2025); NRC Natrium safety eval mid-2026</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Market: broken post-HomeSafe termination + class action overhang. Variant: HomeSafe disposed; spin unlocks SoTP value.</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>D3/Nierenberg +425% Q1 (largest single add in entire universe); Irenic activist ~1%; Director Form 4 buys May 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>6. Deep Drawdown Mean Reversion</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>COTY</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Prestige/fragrance beauty (Burberry, Tiffany, CK, Calvin Klein brands). KKR overhang anchor. -37.5% drawdown extreme contrarian setup. Brand assets worth multiples of EV.</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>B/M 1.73 (DEEPEST in 6/7 tier), FCF yield 17.4%, but ROA -4.91% (Y3 fails)</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Debt restructuring + KKR exit dynamics + cost program execution</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Market: earnings deterioration. Smart: 6-year FCF payback floor with brand asset coverage.</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>KKR legacy anchor; deep-value funds incrementally adding</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>6. Deep Drawdown Mean Reversion</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>FRPT</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Premium fresh dog food brand leader. Manufacturing capacity coming online (Ennis plant). Margin inflection at 70%+ utilization. M&amp;A target for Nestle Purina / Mars / General Mills.</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>B/M 0.50 (borderline Yartseva 6/7), ROA 3.41%, -40% drawdown</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Capacity utilization + margin inflection + M&amp;A speculation</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Market: consumer weakness + capex burden. Smart: brand pricing power + post-capex FCF inflection.</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Marlowe Partners 39.8% in last 13F (highest single-fund signal)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>6. Deep Drawdown Mean Reversion</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>OPRX</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1]</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>P/B 0.70 sub-book, -65.4% 6mo drawdown</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>DSP integration Q4 2026 + MFN clarity</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1]</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Insider 14.82%; $10M buyback</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>6. Deep Drawdown Mean Reversion</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>VITL</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1 for full thesis]</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>B/M 0.74, ROA 11%, -68.76% from peak (DEEPEST drawdown in 6/7)</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Avian flu normalization + M&amp;A + summer pricing</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1]</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>No major fund concentrated yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>7. Hard Asset / Royalty</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>JOE</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Florida Panhandle landbank with 170k+ acres. GAAP B/M understates LIFO land basis vs market value. True NAV-based B/M likely &gt;1.0 even at current price.</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Land bank: 170k acres NW Florida; GAAP B/M understates LIFO land basis</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Florida population growth + master plan community development + Berkowitz anchor</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Yartseva fails on size + low GAAP B/M; correct framework is Lynch asset play.</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Berkowitz/Fairholme longstanding anchor</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>7. Hard Asset / Royalty</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>NRP</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1]</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1]</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Nov 2026 distribution + preferreds retire</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1]</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Saber 17.75% + Greystone top + Right Tail NEW + Berkowitz</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>7. Hard Asset / Royalty</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>TPL</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Permian water + royalty optionality. Same NAV-vs-GAAP-book issue as JOE. Pricing 'endless drilling' premium.</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Permian royalty trust at 25x P/CF (vs NRP at 6x)</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Permian production growth + water revenue optionality</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Yartseva captures FCF yield + ROA but understates B/M for land assets.</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Multi-fund quality holders; HRC anchor</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>8. Foreign / Underfollowed Value</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>BZU.IM</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Italian cement (€8.9B mcap). 52% of EBITDA from US. AI data-center concrete demand thesis. Trading at sector-discount multiple to LafargeHolcim/CRH peers.</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>6.8x EV/EBITDA (vs peer 9-11x); €85 PT = +73% upside</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>AI data-center capex translating to concrete orders; multiple re-rate to peer levels</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Italian listing + cement = institutional underweight. Kerrisdale Oct 2025 long thesis 73% upside.</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Kerrisdale Capital published long thesis Oct 2025 (€85 PT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>8. Foreign / Underfollowed Value</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>MGNI</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Independent CTV SSP. Netflix/Disney/Roku exclusive deals scaling. AI ad-buying integration. Last major non-Google scaled SSP.</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Yartseva 6/7 (sub-$2B), B/M 0.49, FCF yield positive, ROA positive</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>CTV ad spend doubling 2024-2028 + Netflix exclusive scaling + AI integration</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Market: ad-tech roadkill. Smart: winning independent CTV SSP that survived ad-tech wash-out.</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Nine Ten Capital (Bares) 13.1% of book / 3.48M sh / $41.4M</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>8. Foreign / Underfollowed Value</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>MTY.TO</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1]</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1]</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026 SSS test + NCIB</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1]</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>CEO open-market buy</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>9. Quality Compounder at Trough</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>CTSH</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Yartseva 6/7 IT services franchise. Multi-fund consensus Q1 2026. 300k+ delivery workforce moat. AI/IT services capex super-cycle 2026-2028.</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>P/B 1.66 (B/M 0.60), 9.88% FCF yield, ROA 10.44%, -27% 6mo</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>AI implementation winner via enterprise partners + Q2 2026 earnings</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Market: AI disrupts IT services. Smart: AI accelerator not disruptor.</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Multi-fund deep-value funds Q1 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>9. Quality Compounder at Trough</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>DHR</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Pure-play life sciences (Cytiva bioprocessing, Beckman Dx, Cepheid). Q1 EPS $2.06 beat by 6.2%; bioprocessing inflecting positive after destock; Cepheid respiratory comp resets Q4 2026.</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>19.7x forward P/E (trough vs 5yr avg 30x); ROA pos; B/M 0.43</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Bioprocessing book-to-bill durably &gt;1.0 + China VBP stabilization H2 2026 + Cepheid Q4 reset</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Consensus: show-me on growth post-destock. Sundheim/D1: same stock 2019-2021 (30%/yr) at trough multiple while H2 2026 comps inflect.</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>D1 Capital +312% Q1 ($107M→$437M, 4th-largest position)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>9. Quality Compounder at Trough</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>REGN</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Founder/CEO Schleifer + Yancopoulos R&amp;D-led. $31.4B book equity + EYLEA franchise + Linvoseltamab launching. Pipeline broad. Itepekimab Phase 3 readout potential catalyst.</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>B/M 0.48, FCF yield 6.33%, P/B 2.07; Yartseva 6/7 (size only fail)</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Itepekimab 2026-2027 data + Linvoseltamab ramp</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Market: fianlimab miss + Eylea biosimilar. Smart: broad pipeline + buyback + founder skin.</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Founder-led; multi-fund pharma specialist holds</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/investment_archetypes.xlsx
+++ b/investment_archetypes.xlsx
@@ -8,16 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="1_EMPIRICAL_TIER1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="0_DISCOVERY_CLUSTERS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="0b_NEW_13D_FILINGS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2_BASE_RATES" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="3_BACKTEST_DETAIL" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="4_MASTER_CSV" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="5_CATALYSTS_LIVE" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="6_FORM4_BUYS" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="6b_LIVE_CLUSTERS" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="7_LIQUIDITY" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="8_ARCHETYPES" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="8a_ARCHETYPE_STATUS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="8b_ARCHETYPE_MEMBERS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="0_DISCOVERY_CLUSTERS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="0b_NEW_13D_FILINGS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2_BASE_RATES" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="3_BACKTEST_DETAIL" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="4_MASTER_CSV" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="5_CATALYSTS_LIVE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="6_FORM4_BUYS" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="6b_LIVE_CLUSTERS" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="7_LIQUIDITY" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="8_ARCHETYPES" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1464,6 +1466,1266 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>$M</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Casdin Capital, LLC</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Director/10%Owner</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>52.8566</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1818331/000091957426003907/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Quinn William J</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>44000</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>13.1865</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2029118/000119312526262545/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Casdin Capital, LLC</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Director/10%Owner</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>56.4449</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1818331/000091957426003907/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>NSP</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SARVADI PAUL J</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Director/Chairman of the Board &amp; CEO</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>233000</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1000753/000100075326000078/form4.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Quinn William J</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>10503</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2029118/000119312526259528/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Gieselman Scott</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>670</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>13.441</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2029118/000119312526255482/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Gieselman Scott</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>13430</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>13.353</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2029118/000119312526255482/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ROCK</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Bosway William T</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Director/President and CEO</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>19735</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>37.4377</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/912562/000091256226000122/form4.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>NRP</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Craig Kevin J</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Executive Vice President</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>336</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>102.18</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1171486/000143774926018760/rdgdoc.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Gieselman Scott</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>14.103</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2029118/000119312526241878/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>NRP</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Craig Kevin J</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Executive Vice President</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>336</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>102.18</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1171486/000143774926018760/rdgdoc.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Gieselman Scott</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2029118/000119312526241878/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ROCK</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Bolanowski Katherine</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>General Counsel, VP, Secretary</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>1256</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>35.63</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/912562/000091256226000120/form4.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ROCK</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Bolanowski Katherine</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>General Counsel, VP, Secretary</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>35.66</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/912562/000091256226000120/form4.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>MOORE JACK B</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>31.4414</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1357615/000135761526000155/wk-form4_1779393811.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ROCK</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Lovechio Joseph A</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>VP and CFO</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>34.615</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/912562/000091256226000118/form4.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Casdin Capital, LLC</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Director/10%Owner</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>140000</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>43.8061</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1818331/000091957426003627/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Sabater Carlos A.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>14500</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1357615/000135761526000154/wk-form4_1779393765.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Casdin Capital, LLC</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Director/10%Owner</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>185000</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>42.5964</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1818331/000091957426003627/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Casdin Capital, LLC</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Director/10%Owner</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>175000</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>42.5517</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1818331/000091957426003627/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Von Thaer Lewis</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1357615/000135761526000149/wk-form4_1778890135.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Evans Shad E.</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>EVP &amp; Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>8375</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1357615/000135761526000147/wk-form4_1778889975.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SONO</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Arabia Carmine</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1314727/000131472726000066/form4.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SONO</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Arabia Carmine</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1314727/000131472726000066/form4.xml</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Window start</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Window end</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t># insiders</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Total $M</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg px</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Top buyer</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Top $M</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>AGGREGATE</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>32.569</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Casdin Capital, LLC</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>32.569</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>NSP</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>AGGREGATE</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>7.934</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>SARVADI PAUL J</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>7.934</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CLUSTER</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Sabater Carlos A.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0.471</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ROCK</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>CLUSTER</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Bosway William T</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0.739</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2236,7 +3498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3962,6 +5224,1794 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Archetype</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Mapped factor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Base rate 12m</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Live T1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Live T2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Demoted</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Graduated (rerated)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Dead</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Untracked</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Best surviving</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Best ER</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>smart_money_uw</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>+17%</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>ROCK</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>+66%</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>WEAKENED</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>10. Hedged / Special Structure</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>EXCLUDED-BY-MANDATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>activist_13d</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>-26%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>EMPIRICALLY-WEAK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>EXCLUDED-BY-MANDATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>4. Sponsor-Anchored Holdco Transformation</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>sponsor_anchor</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>+17%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>HHH</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>+7%</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>SUPPORTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>5. Spinoff / SoTP Arbitrage</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>spin_arb</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>+10%</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>+70%</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>WEAKENED</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>6. Deep Drawdown Mean Reversion</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>smart_money_uw</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>+17%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>WEAKENED</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>7. Hard Asset / Royalty</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>family_anchor</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>+17%</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>NRP</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>+7%</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>WEAKENED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>8. Foreign / Underfollowed Value</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>deep_value</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>+0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>EMPTIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>9. Quality Compounder at Trough</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>post_acquisition</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>+0%</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>EMPTIED</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Archetype</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ER 12m</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Factor tags</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Original thesis (preserved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ROCK</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>LIVE-T1</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>+66%</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>insider_cluster,post_acquisition,industrial</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>3-segment industrial (Residential 80%, Renewables, Agtech). OmniMax acquisition closed Feb 2026 ($1.335B) = #1 in residential roofing accessories. FY26 guide $1.76-1.83B rev, $3.65-4.05 EPS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>NRP</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>LIVE-T2</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>+7%</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>family_anchor,royalty,income</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Royalty trust on 13M mineral acres + 49% Sisecam soda ash JV. Near-zero debt by mid-2026 after $109M paydown + preferred retirement. Distribution increase guided for November 2026 (delayed from prior </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>VITL</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>LIVE-T2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Pasture-raised egg category creator with brand moat. Walmart/Target/Whole Foods distribution. 11% ROA sustained THROUGH the avian flu crash = exceptional earnings power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>CRTO</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>DEMOTED</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Performance ad-tech pivoting to Commerce Yield retail media (235 retailers incl Lowes/Costco). $1B+ media spend Q1 2026 (+8% cc). OpenAI partnership live with 1,000+ brands. Q1 retail media -31% ex-sc</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>GLOB</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>DEMOTED</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>LatAm IT services with AI Pods inflection ($32.8M ARR from $0 in 12 months; $352M pipeline; 40% top-20 client penetration). Founder Migoya 23-year tenure + ~3% via Founders Trust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>INMD</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>DEMOTED</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>+10%</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>founder_buy,smart_money_uw,asset_light</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Israeli aesthetic device leader (Morpheus8, BodyTite). 85% recurring consumables. Steel Partners +155% Q1 2026 = 25.5% of their book; founder Mizrahy bought 800k sh ($10.7M) Feb 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>MTY.TO</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>DEMOTED</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Multi-brand Canadian QSR franchisor (90 banners incl Cold Stone, Mucho Burrito, Papa Murphy's). 7,000+ locations, 98%+ franchised. Q1 EPS C$0.98 BEAT vs C$0.80 cons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>OPRX</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>DEMOTED</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Digital health POC pharma messaging to 60%+ US prescribers. May 21 2026 DeepIntent integration = first DSP accessing OPRX EHR network (Q3 2026 launch) opens &gt;80% of digital pharma budgets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>CARS</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Digital dealer SaaS (19,390 dealers x $2,473 ARPD/mo, 90% recurring). Q1 EPS $0.45 vs $0.13 est (+246%). Subscription +2%; OEM/National -12% (cyclical bottom).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>DV</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Pure-play ad verification (68% market share in fraud detection vs IAS 2.7%). 4,300+ customers vs IAS 169. Q1 2026 rev +10%, EBITDA 31% margin. CTV +28%, social activation +92%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>FTLF</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Microcap nutraceutical at $93M cap. Sub-institutional minimum. Classic Yartseva discarded-microcap profile with positive FCF + ROA + extreme drawdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>HRMY</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>$1B+ WAKIX franchise (pitolisant for narcolepsy). Q1 2026 rev +17% to $215M; pediatric FDA approval Feb 13 2026 extends IP to 2030 (pediatric exclusivity to 2040s). 5 Phase 3 trials in pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>TREE</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Three-segment marketplace (Insurance 68%, Consumer 20%, Home 12%) at Q1 2026 inflection: rev +37%, VMM +28%, EBITDA +71%, Insurance +51%. Net leverage falling 3.4x→2.1x; S&amp;P upgraded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>10. Hedged / Special Structure</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>LQDA</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>LIVE-T2</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Yutrepia (treprostinil dry-powder inhaler) for PAH and PH-ILD. Q1 2026 product sales $129.9M (+44% QoQ); 4,500 unique patients; mgmt $1B+ 2027 target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>10. Hedged / Special Structure</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>AAP CALL</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Cooper Creek's largest single call exposure. Overlaps with H Partners' AAP cash 46% concentration = double-conviction across two fund styles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>10. Hedged / Special Structure</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>CTMX-WT</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>BVF Partners holds CTMX Tranche 2 warrants expiring 7/3/2026 (next 5 weeks). Embedded biotech IPO/crossover leverage near expiration creates urgency catalyst.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>10. Hedged / Special Structure</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>XBI</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Stonepine $51M long + $51M short = $102M notional. Pure long-vol bet on biotech 2026-2027 FDA cycle dispersion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>FUN</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>DEMOTED</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Post-Cedar Fair/Six Flags merger consolidation. 42 parks irreplaceable real estate. Q1 2026 rev +12%, attendance +4%, per-cap +6%. $200M synergy target ($120M cost + $80M growth).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>MRP</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>DEMOTED</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Lennar 80%+ owner spinoff with 100k+ optioned lots at cost basis. Land bank trading below NAV with Lennar as guaranteed off-take partner. Housing-cycle recovery levered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>AAP</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>#3 aftermarket retailer post-WorldPac sale. Q1 +3.5% comps (Pro mid-single, DIY low-single). 700+ stores closed; ~1,300 strategic locations remain. Bridge to AZO-style 8-10% margins = $130-150/sh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ACHC</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Largest US behavioral health network (260+ facilities). DOJ Medicaid investigation overhang. Q1 2026 admissions stabilizing. Greenlight 4.1M activist; Sohn 5/12 pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>POSTBPB</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Nierenberg/D3 is LARGEST shareholder (~$16.4M / 7% of D3 book). Customer-traffic gains while peers don't (Q1 2026 letter thesis). Form 4 insider buying by Nierenberg at depressed levels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>QRHC</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Wynnefield filed 13D 13.3% May 2025; Robert Lipstein joined board. Cooperation Agreement w/ standstill until 30 days before 2027 nomination window. Asset-light recurring waste mgmt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>PRLD</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>LIVE-T1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Precision oncology / molecular glue / degrader platform. SMARCA2 discontinued 2025; pivot to JAK2V617F (PRT12396) + KAT6A (PRT13722). AbCellera partnership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>CELC</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>LIVE-T2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Phase 3 VIKTORIA-1 PIK3CA-mut POSITIVE May 1 2026 (76% PFS hazard reduction). Gedatolisib pan-PI3K/mTOR oncology. Triplet vs alpelisib+fulvestrant. Multiple HR+/HER2- breast cancer cohorts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>ASND</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>TransCon prodrug platform: SKYTROFA (GHD), YORVIPATH (hypopara), YUVIWEL (achondroplasia approved Feb 2026). &gt;1,000 new US YORVIPATH enrollments Q1; 6,300+ patients across 2,700 prescribers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>BNTC</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Gene therapy platform anchor position. Suvretta 44.1% 13D anchor stake (largest activist ownership in their portfolio). PIPE participation Nov 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>KYMR</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Targeted protein degradation platform. Lead KT-621 oral STAT6 degrader competes with injectable Dupixent ($14B+ franchise). IRAK4 partnered with Sanofi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>PVLA</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Rare-disease topical platform. QTORIN rapamycin gel for microcystic LMs (Breakthrough + Orphan + Fast Track). Phase 3 SELVA POSITIVE Feb 24 2026 (mLM-IGA +2.13, p&lt;0.001).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>4. Sponsor-Anchored Holdco Transformation</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>HHH</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>LIVE-T2</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>+7%</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>sponsor_anchor,nav_discount,holdco</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Ackman-led 'Modern Berkshire'. 3,813 acres residential MPC ($4.8B NAV) + 2,447 acres commercial ($2.0B) + Vantage specialty insurance ($2.2B 2027 premium). Marc Grandisson (ex-Arch Capital CEO) on boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>5. Spinoff / SoTP Arbitrage</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>LIVE-T1</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>+70%</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>insider_cluster,spin_arb,defense</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Two segments: MTS (gov services 72%, $18.5B backlog, cleared workforce 20k) + STS (process tech + TerraPower Natrium nuclear EPC alliance, 22% EBITDA margin). FY26 $980M-1.04B EBITDA, $3.87-4.22 EPS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>5. Spinoff / SoTP Arbitrage</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>DLTR</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Post-divestiture clean Dollar Tree franchise (16k+ stores). Multi-fund deep-value consensus Q1 2026. Mayer M6 turnaround pattern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>6. Deep Drawdown Mean Reversion</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>VITL</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>LIVE-T2</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1 for full thesis]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>6. Deep Drawdown Mean Reversion</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>OPRX</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>DEMOTED</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>6. Deep Drawdown Mean Reversion</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>COTY</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Prestige/fragrance beauty (Burberry, Tiffany, CK, Calvin Klein brands). KKR overhang anchor. -37.5% drawdown extreme contrarian setup. Brand assets worth multiples of EV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>6. Deep Drawdown Mean Reversion</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>FRPT</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Premium fresh dog food brand leader. Manufacturing capacity coming online (Ennis plant). Margin inflection at 70%+ utilization. M&amp;A target for Nestle Purina / Mars / General Mills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>7. Hard Asset / Royalty</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>NRP</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>LIVE-T2</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>+7%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>family_anchor,royalty,income</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>7. Hard Asset / Royalty</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>JOE</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Florida Panhandle landbank with 170k+ acres. GAAP B/M understates LIFO land basis vs market value. True NAV-based B/M likely &gt;1.0 even at current price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>7. Hard Asset / Royalty</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>TPL</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Permian water + royalty optionality. Same NAV-vs-GAAP-book issue as JOE. Pricing 'endless drilling' premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>8. Foreign / Underfollowed Value</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>MTY.TO</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>DEMOTED</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>8. Foreign / Underfollowed Value</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>BZU.IM</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Italian cement (€8.9B mcap). 52% of EBITDA from US. AI data-center concrete demand thesis. Trading at sector-discount multiple to LafargeHolcim/CRH peers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>8. Foreign / Underfollowed Value</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>MGNI</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Independent CTV SSP. Netflix/Disney/Roku exclusive deals scaling. AI ad-buying integration. Last major non-Google scaled SSP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>9. Quality Compounder at Trough</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Yartseva 6/7 IT services franchise. Multi-fund consensus Q1 2026. 300k+ delivery workforce moat. AI/IT services capex super-cycle 2026-2028.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>9. Quality Compounder at Trough</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>DHR</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Pure-play life sciences (Cytiva bioprocessing, Beckman Dx, Cepheid). Q1 EPS $2.06 beat by 6.2%; bioprocessing inflecting positive after destock; Cepheid respiratory comp resets Q4 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>9. Quality Compounder at Trough</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>UNTRACKED</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Founder/CEO Schleifer + Yancopoulos R&amp;D-led. $31.4B book equity + EYLEA franchise + Linvoseltamab launching. Pipeline broad. Itepekimab Phase 3 readout potential catalyst.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4739,7 +7789,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5483,7 +8533,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5705,7 +8755,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6935,7 +9985,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9379,7 +12429,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9450,7 +12500,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -9480,7 +12530,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -9510,7 +12560,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -9540,7 +12590,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -9570,7 +12620,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -9600,7 +12650,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -9630,7 +12680,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -9660,7 +12710,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -9690,7 +12740,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -9720,7 +12770,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -9750,7 +12800,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -9780,7 +12830,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -9810,7 +12860,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -9840,7 +12890,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -9870,7 +12920,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -9900,7 +12950,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -9930,7 +12980,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -9960,7 +13010,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -9990,7 +13040,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -10020,7 +13070,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -10050,7 +13100,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -10080,7 +13130,7 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -10110,7 +13160,7 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -10140,7 +13190,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -10334,1266 +13384,6 @@
         <is>
           <t>GuruFocus + yahoo</t>
         </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Shares</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>$M</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>WGS</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Casdin Capital, LLC</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Director/10%Owner</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>52.8566</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1818331/000091957426003907/ownership.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Quinn William J</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>44000</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>13.1865</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2029118/000119312526262545/ownership.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>WGS</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Casdin Capital, LLC</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Director/10%Owner</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>150000</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>56.4449</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>8.470000000000001</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1818331/000091957426003907/ownership.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>NSP</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>SARVADI PAUL J</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Director/Chairman of the Board &amp; CEO</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>233000</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>34.05</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1000753/000100075326000078/form4.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Quinn William J</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>10503</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2029118/000119312526259528/ownership.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Gieselman Scott</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>670</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>13.441</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2029118/000119312526255482/ownership.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Gieselman Scott</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>13430</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>13.353</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2029118/000119312526255482/ownership.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>ROCK</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Bosway William T</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Director/President and CEO</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>19735</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>37.4377</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/912562/000091256226000122/form4.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>NRP</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Craig Kevin J</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Executive Vice President</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>336</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>102.18</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1171486/000143774926018760/rdgdoc.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Gieselman Scott</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>14.103</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2029118/000119312526241878/ownership.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>NRP</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Craig Kevin J</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Executive Vice President</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>336</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>102.18</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1171486/000143774926018760/rdgdoc.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Gieselman Scott</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2029118/000119312526241878/ownership.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>ROCK</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Bolanowski Katherine</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>General Counsel, VP, Secretary</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>1256</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>35.63</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/912562/000091256226000120/form4.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>ROCK</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Bolanowski Katherine</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>General Counsel, VP, Secretary</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>144</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>35.66</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/912562/000091256226000120/form4.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>KBR</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>MOORE JACK B</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>31.4414</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1357615/000135761526000155/wk-form4_1779393811.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>ROCK</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Lovechio Joseph A</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>VP and CFO</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>34.615</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/912562/000091256226000118/form4.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>WGS</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Casdin Capital, LLC</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Director/10%Owner</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>140000</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>43.8061</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1818331/000091957426003627/ownership.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>KBR</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Sabater Carlos A.</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>14500</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>32.47</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1357615/000135761526000154/wk-form4_1779393765.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>WGS</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Casdin Capital, LLC</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Director/10%Owner</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>185000</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>42.5964</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1818331/000091957426003627/ownership.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>WGS</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Casdin Capital, LLC</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Director/10%Owner</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>175000</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>42.5517</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1818331/000091957426003627/ownership.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>KBR</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Von Thaer Lewis</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>30.77</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1357615/000135761526000149/wk-form4_1778890135.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>KBR</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Evans Shad E.</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>EVP &amp; Chief Financial Officer</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>8375</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1357615/000135761526000147/wk-form4_1778889975.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>SONO</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Arabia Carmine</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1314727/000131472726000066/form4.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>SONO</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Arabia Carmine</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1314727/000131472726000066/form4.xml</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Trigger</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Window start</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Window end</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t># insiders</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Total $M</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Avg px</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Top buyer</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Top $M</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>WGS</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>AGGREGATE</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>32.569</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>47.65</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Casdin Capital, LLC</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>32.569</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>NSP</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>AGGREGATE</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>7.934</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>34.05</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>SARVADI PAUL J</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>7.934</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>KBR</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>CLUSTER</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>31.32</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Sabater Carlos A.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0.471</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>ROCK</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>CLUSTER</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>35.84</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Bosway William T</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0.739</v>
       </c>
     </row>
   </sheetData>

--- a/investment_archetypes.xlsx
+++ b/investment_archetypes.xlsx
@@ -8,25 +8,26 @@
   </bookViews>
   <sheets>
     <sheet name="1_EMPIRICAL_TIER1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="9e_CONVICTION_SCORE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="9f_FUND_CONVICTION_DETAIL" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="9_MATERIAL_ADDS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="9a_NEW_POSITIONS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="9b_13D_THRESHOLD" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="9c_HIGHEST_CONVICTION" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="9d_FUND_ACTIVITY" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="8a_ARCHETYPE_STATUS" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="8b_ARCHETYPE_MEMBERS" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="0_DISCOVERY_CLUSTERS" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="0b_NEW_13D_FILINGS" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="2_BASE_RATES" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="3_BACKTEST_DETAIL" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="4_MASTER_CSV" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="5_CATALYSTS_LIVE" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="6_FORM4_BUYS" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="6b_LIVE_CLUSTERS" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="7_LIQUIDITY" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="8_ARCHETYPES" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="9_INTACT_ENTRY" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="9e_CONVICTION_SCORE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="9f_FUND_CONVICTION_DETAIL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="9_MATERIAL_ADDS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="9a_NEW_POSITIONS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="9b_13D_THRESHOLD" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="9c_HIGHEST_CONVICTION" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9d_FUND_ACTIVITY" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="8a_ARCHETYPE_STATUS" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="8b_ARCHETYPE_MEMBERS" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="0_DISCOVERY_CLUSTERS" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="0b_NEW_13D_FILINGS" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="2_BASE_RATES" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="3_BACKTEST_DETAIL" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="4_MASTER_CSV" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="5_CATALYSTS_LIVE" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="6_FORM4_BUYS" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="6b_LIVE_CLUSTERS" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="7_LIQUIDITY" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="8_ARCHETYPES" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1473,6 +1474,612 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Archetype</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Mapped factor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Base rate 12m</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Live T1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Live T2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Demoted</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Graduated (rerated)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Dead</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Untracked</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Best surviving</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Best ER</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>smart_money_uw</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>+17%</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>ROCK</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>+66%</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>WEAKENED</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>10. Hedged / Special Structure</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>EXCLUDED-BY-MANDATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>activist_13d</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>-26%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>EMPIRICALLY-WEAK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>EXCLUDED-BY-MANDATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>4. Sponsor-Anchored Holdco Transformation</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>sponsor_anchor</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>+17%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>HHH</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>+7%</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>SUPPORTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>5. Spinoff / SoTP Arbitrage</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>spin_arb</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>+10%</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>+70%</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>WEAKENED</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>6. Deep Drawdown Mean Reversion</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>smart_money_uw</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>+17%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>WEAKENED</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>7. Hard Asset / Royalty</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>family_anchor</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>+17%</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>NRP</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>+7%</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>WEAKENED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>8. Foreign / Underfollowed Value</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>deep_value</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>+0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>EMPTIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>9. Quality Compounder at Trough</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>post_acquisition</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>+0%</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>EMPTIED</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2649,7 +3256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3427,7 +4034,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4171,7 +4778,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4393,7 +5000,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5623,7 +6230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7760,15 +8367,15 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>127.77</v>
+        <v>124.7099990844727</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>6350</v>
+        <v>6198.1</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>49.7</v>
@@ -8067,7 +8674,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9029,7 +9636,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10061,7 +10668,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10289,13 +10896,2319 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:L49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Entry anchor</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Anchor source</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>vs entry %</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Conv score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t># funds</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t># hyper</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Insider co-buy</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Sum $M</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Anchors seen</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CVNA</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>-45.7%</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="n">
+        <v>5501.5</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=1.0; raw_text=118.0; raw_text=1.0; p80_close=77.50599670410156</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>CPNG</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>-1.1%</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>NEAR_ENTRY</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="n">
+        <v>1692.4</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=298.0; raw_text=17.0; p80_close=20.450000762939453</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>APG</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>42.34</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-29.4%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="n">
+        <v>861.2</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=114.0; raw_text=60.0; raw_text=9.0; raw_text=60.0; p80_close=45.59000015258789</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>82.94</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>337</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>-75.4%</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="n">
+        <v>1243.5</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=337.0; raw_text=151.0; p80_close=89.45999908447266</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-70.8%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="n">
+        <v>3334.5</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=1.0; raw_text=91.0; raw_text=91.0; raw_text=450.0; p80_close=27.420000076293945</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>HHH</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>67.68000000000001</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>candidates</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-32.3%</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="n">
+        <v>2732.9</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>candidates=100.0; raw_text=1.0; raw_text=14.0; raw_text=14.0; p80_close=64.72000122070312</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>COF</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>184.73</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-63.1%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="n">
+        <v>1240.5</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=501.0; raw_text=105.0; p80_close=193.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>LQDA</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>64.01000000000001</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>NEAR_ENTRY</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="n">
+        <v>545.9</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=280.0; raw_text=3.0; raw_text=98.0; raw_text=41.0; raw_text=5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>DRVN</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-73.1%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="n">
+        <v>18209.5</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=50.0; raw_text=18.0; raw_text=50.0; raw_text=7.0; raw_text=50.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>AAP</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>-14.4%</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>NEAR_ENTRY</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="n">
+        <v>345.1</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=7.0; raw_text=71.0; p80_close=58.380001068115234</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>LFCR</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-66.8%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=17.0; p80_close=5.349999904632568</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>-54.3%</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="n">
+        <v>5460.1</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=4.0; raw_text=220.0; raw_text=7.0; p80_close=117.19999694824219</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>203.27</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>+3.7%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>NEAR_ENTRY</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="n">
+        <v>2779.9</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=2.0; raw_text=1.0; raw_text=196.0; p80_close=203.24000549316406</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>HYG</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>-50.3%</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="n">
+        <v>335.3</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=161.0; p80_close=80.30999755859375</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>CODI</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-63.3%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="n">
+        <v>131.7</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=29.0; raw_text=29.0; raw_text=8.0; raw_text=29.0; raw_text=13.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SATS</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>114.08</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>-59.7%</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="n">
+        <v>1982.2</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=183.0; raw_text=283.0; raw_text=2.0; p80_close=129.3800048828125</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>MGNI</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-60.4%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=5.0; raw_text=41.0; p80_close=14.130000114440918</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SRL</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>-59.1%</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=15.0; p80_close=7.579999923706055</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>KVUE</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-79.8%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="n">
+        <v>1788</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=471.0; raw_text=131.0; raw_text=25.0; raw_text=90.0; raw_text=90.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>68.84999999999999</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>-68.6%</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="n">
+        <v>799.8</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=219.0; raw_text=7.0; p80_close=75.58000183105469</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>272.7</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>418</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-34.8%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="n">
+        <v>795.1</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=418.0; raw_text=376.0; p80_close=268.70001220703125</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>150.58</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>171.35</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>p80_close</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>-12.1%</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>NEAR_ENTRY</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="n">
+        <v>1350</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>p80_close=171.35000610351562</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>VTOL</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-6.5%</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>NEAR_ENTRY</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=47.0; p80_close=48.900001525878906</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>CRH</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>106.48</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>-67.1%</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="n">
+        <v>1093.7</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=324.0; raw_text=683.0; raw_text=7.0; p80_close=115.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>NRP</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>103.73</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>102.18</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>form4_p_buy</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>+1.5%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>NEAR_ENTRY</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>form4_p_buy=102.18; p80_close=120.76000213623047</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>+12.3%</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>NEAR_ENTRY</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="n">
+        <v>371.8</v>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=91.0; p80_close=110.94999694824219</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>STGW</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-78.6%</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="n">
+        <v>132.2</v>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=31.0; raw_text=31.0; raw_text=31.0; raw_text=6.0; raw_text=37.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>CLBT</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>-72.7%</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=21.0; raw_text=145.0; raw_text=47.0; p80_close=14.180000305175781</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>CMCSA</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>28.98</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>p80_close</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-15.5%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="n">
+        <v>589</v>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>p80_close=28.979999542236328</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>MRP</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>30.49</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>p80_close</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>-3.9%</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>NEAR_ENTRY</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="n">
+        <v>427</v>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>p80_close=30.489999771118164</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>FUN</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-72.6%</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="n">
+        <v>123.1</v>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=4.0; raw_text=82.0; p80_close=20.290000915527344</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>MATW</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>26.82</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>+3.2%</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>NEAR_ENTRY</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=26.0; raw_text=19.0; p80_close=27.780000686645508</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ALKT</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-70.8%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="n">
+        <v>283.4</v>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=48.0; raw_text=52.0; p80_close=17.43000030517578</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>NN</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>-46.2%</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=40.0; p80_close=21.59000015258789</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>MNRO</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>candidates</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-63.4%</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>candidates=40.0; raw_text=80.0; p80_close=17.1200008392334</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>TEVA</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>34.63</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>-55.6%</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="n">
+        <v>923.4</v>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=78.0; raw_text=67.0; p80_close=34.95000076293945</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>170.28</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-21.5%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="n">
+        <v>217.7</v>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=217.0; p80_close=196.64999389648438</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>CELC</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>92.59</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>-7.2%</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>NEAR_ENTRY</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="n">
+        <v>1700</v>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=99.74; p80_close=131.05999755859375</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>SONO</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>candidates</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>-22.4%</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="n">
+        <v>298.4</v>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>candidates=19.82; raw_text=3.0; raw_text=10.0; raw_text=9.0; raw_text=12.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>candidates</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>-66.9%</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>789.1</v>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>candidates=32.21; candidates=170.0; raw_text=391.0; form4_p_buy=47.65114; p80_close=68.52999877929688</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>PRLD</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>candidates</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>NEAR_ENTRY</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>candidates=3.94; p80_close=4.619999885559082</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>CDRE</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>30.19</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>48.76</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>candidates</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>-38.1%</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>candidates=25.73; candidates=48.76; raw_text=35.0; p80_close=32.220001220703125</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>35.32</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>candidates</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>-35.8%</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>candidates=55.0; raw_text=14.0; form4_p_buy=31.32035; p80_close=37.459999084472656</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>CRTO</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>-5.3%</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>NEAR_ENTRY</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=18.0; p80_close=19.110000610351562</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>SSTI</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>raw_text</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>+0.9%</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>NEAR_ENTRY</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>raw_text=6.8; raw_text=7.64; p80_close=7.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>INMD</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>candidates</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>-24.7%</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>candidates=18.0; raw_text=24.0; p80_close=14.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>RPAY</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>candidates</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>-28.5%</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>BELOW_ENTRY</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>candidates=3.43; candidates=4.8; candidates=490.0; raw_text=21.0; raw_text=31.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>SEER</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>p80_close</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>-12.9%</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>NEAR_ENTRY</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>p80_close=1.940000057220459</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10585,44 +13498,44 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>UA</t>
+          <t>CROX</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2427.6</v>
+        <v>6198.1</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>9707365</v>
+        <v>1299825</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>56.11</v>
+        <v>162.1</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FUN</t>
+          <t>UA</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2240.1</v>
+        <v>2427.6</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1953180</v>
+        <v>9707365</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>43.81</v>
+        <v>56.11</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -10633,20 +13546,20 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>FUN</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1420</v>
+        <v>2240.1</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>673225</v>
+        <v>1953180</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>25.09</v>
+        <v>43.81</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -10657,17 +13570,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FCN</t>
+          <t>NSP</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>5272.6</v>
+        <v>1420</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>576815</v>
+        <v>673225</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>92.23999999999999</v>
+        <v>25.09</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>5.7</v>
@@ -10681,20 +13594,20 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>FCN</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>4480</v>
+        <v>5272.6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1997250</v>
+        <v>576815</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>70.54000000000001</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -10705,20 +13618,20 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>INMD</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>859</v>
+        <v>4480</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>918205</v>
+        <v>1997250</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>12.45</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -10729,20 +13642,20 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>SONO</t>
+          <t>INMD</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1830.1</v>
+        <v>859</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1486085</v>
+        <v>918205</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>22.86</v>
+        <v>12.45</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -10753,20 +13666,20 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ROCK</t>
+          <t>SONO</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1169.9</v>
+        <v>1830.1</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>369475</v>
+        <v>1486085</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>14.52</v>
+        <v>22.86</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -10777,20 +13690,20 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MRP</t>
+          <t>ROCK</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>4870</v>
+        <v>1169.9</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1594685</v>
+        <v>369475</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>46.72</v>
+        <v>14.52</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>10.4</v>
+        <v>8.1</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -10801,20 +13714,20 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CDRE</t>
+          <t>MRP</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1290</v>
+        <v>4870</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>390880</v>
+        <v>1594685</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>11.8</v>
+        <v>46.72</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -10825,20 +13738,20 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>CDRE</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>66600</v>
+        <v>1290</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>21221855</v>
+        <v>390880</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>563.65</v>
+        <v>11.8</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11.8</v>
+        <v>10.9</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -10849,20 +13762,20 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HHH</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>3999.9</v>
+        <v>66600</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>433645</v>
+        <v>21221855</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>29.35</v>
+        <v>563.65</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>13.6</v>
+        <v>11.8</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -10873,20 +13786,20 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CRTO</t>
+          <t>HHH</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>856.9</v>
+        <v>3999.9</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>329780</v>
+        <v>433645</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>5.62</v>
+        <v>29.35</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>15.2</v>
+        <v>13.6</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -10897,20 +13810,20 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>LAW</t>
+          <t>CRTO</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>228</v>
+        <v>856.9</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>405940</v>
+        <v>329780</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1.45</v>
+        <v>5.62</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>15.8</v>
+        <v>15.2</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -10921,20 +13834,20 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>RPAY</t>
+          <t>LAW</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>302</v>
+        <v>228</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>542390</v>
+        <v>405940</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1.86</v>
+        <v>1.45</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -10945,20 +13858,20 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>SSTI</t>
+          <t>RPAY</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>200</v>
+        <v>302</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>116450</v>
+        <v>542390</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.9</v>
+        <v>1.86</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>22.3</v>
+        <v>16.2</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -10969,20 +13882,20 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>NRP</t>
+          <t>SSTI</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1370.3</v>
+        <v>200</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>58800</v>
+        <v>116450</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -10993,20 +13906,20 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SEER</t>
+          <t>NRP</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>94.59999999999999</v>
+        <v>1370.3</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>247570</v>
+        <v>58800</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.42</v>
+        <v>6.1</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -11017,20 +13930,20 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PRLD</t>
+          <t>SEER</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>391</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>321720</v>
+        <v>247570</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1.27</v>
+        <v>0.42</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>30.8</v>
+        <v>22.6</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -11041,22 +13954,46 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>PRLD</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>391</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>321720</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
           <t>MTY.TO</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B33" s="2" t="n">
         <v>908.1</v>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="C33" s="2" t="n">
         <v>34750</v>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D33" s="2" t="n">
         <v>1.38</v>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E33" s="2" t="n">
         <v>65.8</v>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
@@ -11067,7 +14004,1732 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Archetype</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Thesis</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Valuation</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Catalyst</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Smart money</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>CARS</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Digital dealer SaaS (19,390 dealers x $2,473 ARPD/mo, 90% recurring). Q1 EPS $0.45 vs $0.13 est (+246%). Subscription +2%; OEM/National -12% (cyclical bottom).</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>P/B 0.83, P/FCF 3.5, 28% TTM FCF yield, EV/EBITDA 2.7x</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>$25-30M annualized cost program 2027 + $90M buyback (16% cap raised from $60M)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Street: declining auto Yellow Pages at 4x P/FCF. Variant: 90% SaaS dealer recurring + buyback math.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Yartseva 7/7 - smart money still building</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>CRTO</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Performance ad-tech pivoting to Commerce Yield retail media (235 retailers incl Lowes/Costco). $1B+ media spend Q1 2026 (+8% cc). OpenAI partnership live with 1,000+ brands. Q1 retail media -31% ex-scope -- actual underlying +24%.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>P/E 3.73 (fwd), P/B 0.79, P/FCF 4.98, EV/EBITDA 2.28, 20.7% FCF yield</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Q3 2026 anniversary of scope losses + Luxembourg redomiciliation + $200M buyback (22% cap)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Market prices terminal decline; Petrus Advisers activist + 33% FCF yield + retail media TAM $200B by 2028.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Nierenberg D3 9.37% / +19% Q1 2026; Petrus Advisers activist</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>DV</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Pure-play ad verification (68% market share in fraud detection vs IAS 2.7%). 4,300+ customers vs IAS 169. Q1 2026 rev +10%, EBITDA 31% margin. CTV +28%, social activation +92%.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>P/FCF 11x (trough), EV/EBITDA 9.6x, EV/Sales 1.9x, 9% FCF yield</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>ABS streaming Do Not Air list rollout Q2/Q3 + Meta activation $12M ARR to $50M+ path</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Market: Google MRC self-measurement threat. Variant: CTV verification underpenetrated (10%) vs display (70%).</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Insider 12.69% (high for ad-tech); Yartseva 7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>FTLF</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Microcap nutraceutical at $93M cap. Sub-institutional minimum. Classic Yartseva discarded-microcap profile with positive FCF + ROA + extreme drawdown.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>P/B 2.05, B/M 0.49, FCF yield 8.2%, ROA 7.2%, near 52w low, -43.9% 6mo</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026 earnings; M&amp;A speculation; recovery in supplement category</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Market: forgotten micro. Smart money: pure Yartseva mean-reversion target.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Smoak Capital residual position; previously a Smoak top-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>GLOB</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>LatAm IT services with AI Pods inflection ($32.8M ARR from $0 in 12 months; $352M pipeline; 40% top-20 client penetration). Founder Migoya 23-year tenure + ~3% via Founders Trust.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>P/E 5.91 (sector low), P/B 0.78, P/FCF 5.56, 17% FCF yield, EV/EBITDA 4.95</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Q3 2026 AI Pods print + Argentina FX tailwind + ENRGI platform launch H2</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Market: melting India-IT comp. Smart money: AI mix shift to higher-margin work + LatAm cost arb. CAVEAT: securities class action (lead plaintiff June 23, 2026); COO resigned July 2025 not replaced.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Cartica historical 6.5% Q4 2022; sentiment bottom 16% short float</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>HRMY</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>$1B+ WAKIX franchise (pitolisant for narcolepsy). Q1 2026 rev +17% to $215M; pediatric FDA approval Feb 13 2026 extends IP to 2030 (pediatric exclusivity to 2040s). 5 Phase 3 trials in pipeline.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>P/B 1.91, P/Sales 2.05, FCF yield 19.36%, 26% net cash position</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Pitolisant GR NDA Q2 2026 (PDUFA Q1 2027); BP-205 Phase 1 PK mid-2026</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Market: single-product cliff. Smart money: Lilly's $6.3B Centessa (Q3 2026 close) validated orexin space + IP estate.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A buyers: Jazz Pharma, Lundbeck, Otsuka; Catalyst Pharma precedent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>INMD</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Israeli aesthetic device leader (Morpheus8, BodyTite). 85% recurring consumables. Steel Partners +155% Q1 2026 = 25.5% of their book; founder Mizrahy bought 800k sh ($10.7M) Feb 2026.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>P/B 1.32, FCF $537M cash = $8.47/sh (62% of price), 77.8% gross margin</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026 earnings ~Aug 5 + potential Steel renewed bid ($18 prior)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Market: Israeli geopolitical + aesthetic cycle. Smart money: $11-12 floor on cash alone; Steel implied $20+ takeout.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Steel Partners 25.5% of book; Mizrahy +800k sh ($10.7M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>MTY.TO</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Multi-brand Canadian QSR franchisor (90 banners incl Cold Stone, Mucho Burrito, Papa Murphy's). 7,000+ locations, 98%+ franchised. Q1 EPS C$0.98 BEAT vs C$0.80 cons.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>P/B 1.04 (trading at book!), EV/EBITDA 7.5x (vs QSR peer 14-18x), 16.7% FCF yield</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026 earnings test SSS stabilization + NCIB 5% of float through July</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Market: melting ice cube. Variant: SSS troughing + debt paying down + M&amp;A pool (RBI, Inspire at 12-14x EBITDA).</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>CEO Lefebvre open-market buy at C$30.54 (+33% stake)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>NRP</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Royalty trust on 13M mineral acres + 49% Sisecam soda ash JV. Near-zero debt by mid-2026 after $109M paydown + preferred retirement. Distribution increase guided for November 2026 (delayed from prior guide due to Sisecam capital call).</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>P/B 2.26 (B/M 0.47), 14.5% FCF yield, ROA 10.5%, 6.6x P/FCF</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Nov 2026 distribution step-up + preferreds retire; Q3 2026 Sisecam recovery sig</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Market: dying coal MLP. Smart money: debt-free royalty with 12% FCF yield, comparable to TPL at 25x P/CF (NRP at 6x).</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Saber/Huber 17.75%, Greystone top, Right Tail NEW Q1 2026, Berkowitz/Fairholme</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>OPRX</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Digital health POC pharma messaging to 60%+ US prescribers. May 21 2026 DeepIntent integration = first DSP accessing OPRX EHR network (Q3 2026 launch) opens &gt;80% of digital pharma budgets.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>P/B 0.70 (sub-book), P/FCF 4.89, 15.7% FCF yield, EV/Sales 0.88, Adj EBITDA 4.4x EV</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Q4 2026 DSP integration revenue start + Q2 2026 earnings Aug 14</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Market: MFN victim; Smart money: profitable ($19M FCF) at 0.7x book, target $11.50 (138% upside).</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Insider 14.82%; $10M buyback through March 2027; Doximity exec Presti to board April 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ROCK</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3-segment industrial (Residential 80%, Renewables, Agtech). OmniMax acquisition closed Feb 2026 ($1.335B) = #1 in residential roofing accessories. FY26 guide $1.76-1.83B rev, $3.65-4.05 EPS.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>P/B 1.34, FCF yield 6.5%, ROA 2.95%, EV/Sales 1.0x vs peer 1.5x</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026 earnings = first clean OmniMax quarter; aluminum normalization; Q3 reroofing season</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Market: busted SPAC with 1.56 D/E. Variant: one-time integration year; FY27 EPS $5+ at 15x = $75-90.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Director Metcalf bought $502k March 2026; Vanguard 5.24% 13G</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>TREE</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Three-segment marketplace (Insurance 68%, Consumer 20%, Home 12%) at Q1 2026 inflection: rev +37%, VMM +28%, EBITDA +71%, Insurance +51%. Net leverage falling 3.4x→2.1x; S&amp;P upgraded.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>P/E 2.92, P/FCF 7.2, ROE 88.6%, B/M 0.60</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026 print + $575M July 2025 converts retired + Fed rate cuts unlock Home/Consumer</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Street disbelieves Insurance durability. Variant: insurance carriers in year-2 of 5-7yr up-cycle = $200M+ EBITDA into 2027.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Yartseva 7/7 + post-Q1 inflection demonstrated</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>1. Yartseva Pure Multibagger</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>VITL</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Pasture-raised egg category creator with brand moat. Walmart/Target/Whole Foods distribution. 11% ROA sustained THROUGH the avian flu crash = exceptional earnings power.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>B/M 0.74, ROA 11% (BEST in 6/7 tier), -68.76% from peak</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Avian flu egg-supply normalization + summer pricing + M&amp;A speculation</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Market lumped premium VITL with commodity egg crash. Reality: brand pricing power retained. Strategic buyers: Kraft Heinz, Hain, General Mills.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>No major fund concentrated yet = entry preserved; Yartseva 6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>10. Hedged / Special Structure</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>AAP CALL</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Cooper Creek's largest single call exposure. Overlaps with H Partners' AAP cash 46% concentration = double-conviction across two fund styles.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>$158M call notional; +213% Q1 2026 (Cooper Creek)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026 margin recovery proof + H Partners 13D escalation</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Catalyst-driven leverage on H Partners' AAP thesis.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Cooper Creek call stack ($518M total notional incl SIG/TTWO/DOCN/GXO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>10. Hedged / Special Structure</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CTMX-WT</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>BVF Partners holds CTMX Tranche 2 warrants expiring 7/3/2026 (next 5 weeks). Embedded biotech IPO/crossover leverage near expiration creates urgency catalyst.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5.77M shares warrants; group ownership equivalent ~3.5%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Warrant expiration 7/3/2026 = IMMINENT URGENCY</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>BVF's KYMR top conviction (14.6%) signals their biotech book has high conviction quality.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>BVF Partners 13G/A #5 (warrants exp 7/3/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>10. Hedged / Special Structure</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>LQDA</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Yutrepia (treprostinil dry-powder inhaler) for PAH and PH-ILD. Q1 2026 product sales $129.9M (+44% QoQ); 4,500 unique patients; mgmt $1B+ 2027 target.</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>P/Sales 12x on $130M Q1 run-rate; cash $200M+ floor; M&amp;A premium 50-100%</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>'327 patent ruling pending (binary); Q2 print Aug 2026; UTHR Tresmi competitive launch</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Consensus PT $63.75 assumes flat share. Buckley's PUT-hedged structure suggests binary patent risk; UTHR M&amp;A target.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Buckley Capital 32% LONG + PUT structure ($44.7M notional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>10. Hedged / Special Structure</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>XBI</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Stonepine $51M long + $51M short = $102M notional. Pure long-vol bet on biotech 2026-2027 FDA cycle dispersion.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Biotech basket at multi-year low; straddle structure captures vol</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Biotech FDA cycle 2026-2027 (multiple catalysts driving dispersion)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Long-vol thesis: biotech sector cycle creates dispersion that benefits straddle structure regardless of direction.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Stonepine 40.9% of $250M book in XBI straddle</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>AAP</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>#3 aftermarket retailer post-WorldPac sale. Q1 +3.5% comps (Pro mid-single, DIY low-single). 700+ stores closed; ~1,300 strategic locations remain. Bridge to AZO-style 8-10% margins = $130-150/sh.</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3.8% op margin (rising +410bps), FY26 guide $2.40-3.10 EPS; sub-1x sales; M&amp;A floor 0.8x sales = $80/sh</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026 earnings Aug = needs comps +2%+ and op margin &gt;5%; H Partners 13D escalation possible</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Consensus PT $57 (dead money). H Partners 46% concentration implies AAP returns to AZO margins.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>H Partners 46.3% / $71.2M / +50% sh Q1 2026 (1.35M sh); Legion Partners precedent</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>ACHC</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Largest US behavioral health network (260+ facilities). DOJ Medicaid investigation overhang. Q1 2026 admissions stabilizing. Greenlight 4.1M activist; Sohn 5/12 pitch.</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 6.5x (vs HCA 9x, UHS 8x); 29% short float; -70% drawdown</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>DOJ resolution + Q2 2026 earnings + 29% short squeeze potential</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Market: DOJ/Medicaid existential. Greenlight: provider necessity + facility footprint + de-rate captured = floor near current.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Greenlight Capital 4.1M sh (David Einhorn); Sohn presentation 5/12/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>FUN</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Post-Cedar Fair/Six Flags merger consolidation. 42 parks irreplaceable real estate. Q1 2026 rev +12%, attendance +4%, per-cap +6%. $200M synergy target ($120M cost + $80M growth).</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>$5.27B net debt = 7x leverage; EV/EBITDA 9x on $1.05B 2027 EBITDA</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>May 26 2026 AGM: Jaffer joins board (Class III through 2027, Audit&amp;Finance Cttee). Jana 9% pushing OUTRIGHT SALE.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Street: broken merger story. Two-front activist pressure (governance + sale) + per-park RE floor $47M each.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>H Partners 53.7% / $82.5M / 5.7% of class; Jana 9% + Travis Kelce co-invest</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>MRP</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Lennar 80%+ owner spinoff with 100k+ optioned lots at cost basis. Land bank trading below NAV with Lennar as guaranteed off-take partner. Housing-cycle recovery levered.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>B/M 1.274 (DEEPEST in 6/7 tier; deeper than NRP's 0.47), pure NAV play</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026 print + Lennar volume scaling + housing cycle inflection</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Market priced spinoff orphan technical pressure. Smart money: pure land cash-cow at discount to NAV.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Lennar 80%+ owner = patient capital lock-in; SITG multi-fund flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>POSTBPB</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Nierenberg/D3 is LARGEST shareholder (~$16.4M / 7% of D3 book). Customer-traffic gains while peers don't (Q1 2026 letter thesis). Form 4 insider buying by Nierenberg at depressed levels.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Sub-$300M micro restaurant chain; turnaround stage</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant turnaround + Nierenberg potential escalation</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Market: tier-2 restaurant chain. Activist soft-pressure thesis.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Nierenberg/D3 largest shareholder; 13D/A active March 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2. Activist Board Catalyst</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>QRHC</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Wynnefield filed 13D 13.3% May 2025; Robert Lipstein joined board. Cooperation Agreement w/ standstill until 30 days before 2027 nomination window. Asset-light recurring waste mgmt.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Sub-$200M micro; recurring waste services revenue model</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Operational improvements + Wynnefield additional buying if dips</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Market: small-cap value trap. Activist: board seat + potential value-unlock initiatives.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Wynnefield 13.3% / 2.73M sh / 13D w/ board seat</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>ASND</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>TransCon prodrug platform: SKYTROFA (GHD), YORVIPATH (hypopara), YUVIWEL (achondroplasia approved Feb 2026). &gt;1,000 new US YORVIPATH enrollments Q1; 6,300+ patients across 2,700 prescribers.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Profitable (22% non-IFRS op margin); €247M Q1 (2x YoY); peak rev YORVIPATH $4-5B</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>YUVIWEL ramp + Q2/Q3 YORVIPATH growth + TransCon CNP follow-on indications</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Sell-side: $15B endocrine specialty maturing. RA Capital: $30B+ at 70-90K addressable hypopara population. Analyst high $345 (Barclays).</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>RA Capital 24.9% of $9.44B = $2.35B = LARGEST single biotech crossover position; held since 2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>BNTC</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Gene therapy platform anchor position. Suvretta 44.1% 13D anchor stake (largest activist ownership in their portfolio). PIPE participation Nov 2025.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Sub-$300M biotech; gene therapy platform optionality</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Multiple gene-therapy programs in development; clinical readouts upcoming</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>44.1% ownership creates board influence + asymmetric upside on clinical reads.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Suvretta 44.1% 13D (Suvretta's LARGEST stake by % ownership)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>CELC</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Phase 3 VIKTORIA-1 PIK3CA-mut POSITIVE May 1 2026 (76% PFS hazard reduction). Gedatolisib pan-PI3K/mTOR oncology. Triplet vs alpelisib+fulvestrant. Multiple HR+/HER2- breast cancer cohorts.</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>$387M cash + accepted NDA + Priority Review = de-risked; 4-5x peak rev precedent</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>JUNE 2 ASCO LBA1008 oral + JULY 17 PDUFA goal date (2 catalysts in 8 weeks)</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Market: alpelisib-class peak ($1-2B). Baker Bros 19.99% 13D activist: $5-10B peak (triplet displaces alpelisib + captures WT segment).</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Baker Bros 19.99% ACTIVIST 13D = $904M / 5.48% of $17.4B book</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>KYMR</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Targeted protein degradation platform. Lead KT-621 oral STAT6 degrader competes with injectable Dupixent ($14B+ franchise). IRAK4 partnered with Sanofi.</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>$1.55B cash (runway 2029); Dec 2025 follow-on $602M at $86</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>BROADEN2 AD mid-2027 (12+ months); BREADTH asthma late 2027; FDA Fast Track granted both</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Market: Phase 1b execution risk. Two top biotech specialists: oral Dupixent-disruptor with peak $5-10B.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>BVF #1 position 14.6% of $3.14B book ($458M) + Baker Bros 4.1% / $721M; BOTH anchored $86 follow-on</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>PRLD</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Precision oncology / molecular glue / degrader platform. SMARCA2 discontinued 2025; pivot to JAK2V617F (PRT12396) + KAT6A (PRT13722). AbCellera partnership.</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>$175M cash vs $340M mcap = $2.20/sh net cash (51% of price); buyout floor near current</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>PRT12396 Phase 1 H2 2026; PRT13722 IND mid-2026; Incyte option agreement Nov 2025</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Market: broken story post-SMARCA2 fail. Smart money: April 2026 refunding = platform-validation thesis. JAK2 mutant-selective addresses 95% PV/60% ET/55% MF.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Baker Bros 15.5% 13D/A + RA Capital 9.99% 13G; BOTH anchored SAME $90M April financing at $4.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>3. Biotech Multi-Fund Convergence</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>PVLA</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Rare-disease topical platform. QTORIN rapamycin gel for microcystic LMs (Breakthrough + Orphan + Fast Track). Phase 3 SELVA POSITIVE Feb 24 2026 (mLM-IGA +2.13, p&lt;0.001).</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>$261.9M cash = $25/sh (19% of price). Phase 3 derisked. M&amp;A floor 4-6x peak rev</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Pre-NDA FDA meeting Q2 2026; NDA H2 2026; PDUFA H1 2027</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Market: single-asset rare-disease (~$1.5B). Smart money: platform with &gt;$1B peak QTORIN + venous malformations/angiokeratomas/pitavastatin programs.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>BVF 3.8% / $120M (8.5% of company) + Suvretta 3.67% / $144M (+29.3% Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>4. Sponsor-Anchored Holdco Transformation</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>HHH</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Ackman-led 'Modern Berkshire'. 3,813 acres residential MPC ($4.8B NAV) + 2,447 acres commercial ($2.0B) + Vantage specialty insurance ($2.2B 2027 premium). Marc Grandisson (ex-Arch Capital CEO) on board April 2026.</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>NAV $95-105/sh = 33-39% discount; $1.84B cash + $515M revolver liquidity</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Vantage close Q2 2026 (30-45 days); Park Ward Village condo closings Q2-Q3 (~$1B rev); first post-Vantage capital allocation</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Street: sub-scale RE dev with leverage. Ackman: insurance float + permanent capital. NAV $95-105 vs $63 = 50-67% margin of safety.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Ackman 47% via $900M @ $100/sh + $1B preferred; Northern Right NEW Q1 +12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>5. Spinoff / SoTP Arbitrage</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>DLTR</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Post-divestiture clean Dollar Tree franchise (16k+ stores). Multi-fund deep-value consensus Q1 2026. Mayer M6 turnaround pattern.</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>B/M 0.20 (Yartseva 6/7); Family Dollar divestiture proceeds = $1B+ cash bolster</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Family Dollar sale completion + comparable sales recovery + multiple re-rate</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Market priced Family Dollar mistake. Smart money: post-divestiture clean franchise.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Multi-fund deep-value funds Q1 2026 adds</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>5. Spinoff / SoTP Arbitrage</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Two segments: MTS (gov services 72%, $18.5B backlog, cleared workforce 20k) + STS (process tech + TerraPower Natrium nuclear EPC alliance, 22% EBITDA margin). FY26 $980M-1.04B EBITDA, $3.87-4.22 EPS.</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>SoTP: MTS at 11x EBITDA ($5.2B EV) + STS at 14x ($5.3B) = $55-65/sh combined</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>MTS spin January 4 2027 (board-approved Sept 2025); NRC Natrium safety eval mid-2026</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Market: broken post-HomeSafe termination + class action overhang. Variant: HomeSafe disposed; spin unlocks SoTP value.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>D3/Nierenberg +425% Q1 (largest single add in entire universe); Irenic activist ~1%; Director Form 4 buys May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>6. Deep Drawdown Mean Reversion</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>COTY</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Prestige/fragrance beauty (Burberry, Tiffany, CK, Calvin Klein brands). KKR overhang anchor. -37.5% drawdown extreme contrarian setup. Brand assets worth multiples of EV.</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>B/M 1.73 (DEEPEST in 6/7 tier), FCF yield 17.4%, but ROA -4.91% (Y3 fails)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Debt restructuring + KKR exit dynamics + cost program execution</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Market: earnings deterioration. Smart: 6-year FCF payback floor with brand asset coverage.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>KKR legacy anchor; deep-value funds incrementally adding</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>6. Deep Drawdown Mean Reversion</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>FRPT</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Premium fresh dog food brand leader. Manufacturing capacity coming online (Ennis plant). Margin inflection at 70%+ utilization. M&amp;A target for Nestle Purina / Mars / General Mills.</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>B/M 0.50 (borderline Yartseva 6/7), ROA 3.41%, -40% drawdown</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Capacity utilization + margin inflection + M&amp;A speculation</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Market: consumer weakness + capex burden. Smart: brand pricing power + post-capex FCF inflection.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Marlowe Partners 39.8% in last 13F (highest single-fund signal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>6. Deep Drawdown Mean Reversion</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>OPRX</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>P/B 0.70 sub-book, -65.4% 6mo drawdown</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>DSP integration Q4 2026 + MFN clarity</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Insider 14.82%; $10M buyback</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>6. Deep Drawdown Mean Reversion</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>VITL</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1 for full thesis]</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>B/M 0.74, ROA 11%, -68.76% from peak (DEEPEST drawdown in 6/7)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Avian flu normalization + M&amp;A + summer pricing</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>No major fund concentrated yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>7. Hard Asset / Royalty</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>JOE</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Florida Panhandle landbank with 170k+ acres. GAAP B/M understates LIFO land basis vs market value. True NAV-based B/M likely &gt;1.0 even at current price.</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Land bank: 170k acres NW Florida; GAAP B/M understates LIFO land basis</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Florida population growth + master plan community development + Berkowitz anchor</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Yartseva fails on size + low GAAP B/M; correct framework is Lynch asset play.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Berkowitz/Fairholme longstanding anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>7. Hard Asset / Royalty</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>NRP</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Nov 2026 distribution + preferreds retire</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Saber 17.75% + Greystone top + Right Tail NEW + Berkowitz</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>7. Hard Asset / Royalty</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>TPL</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Permian water + royalty optionality. Same NAV-vs-GAAP-book issue as JOE. Pricing 'endless drilling' premium.</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Permian royalty trust at 25x P/CF (vs NRP at 6x)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Permian production growth + water revenue optionality</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Yartseva captures FCF yield + ROA but understates B/M for land assets.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Multi-fund quality holders; HRC anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>8. Foreign / Underfollowed Value</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>BZU.IM</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Italian cement (€8.9B mcap). 52% of EBITDA from US. AI data-center concrete demand thesis. Trading at sector-discount multiple to LafargeHolcim/CRH peers.</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>6.8x EV/EBITDA (vs peer 9-11x); €85 PT = +73% upside</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>AI data-center capex translating to concrete orders; multiple re-rate to peer levels</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Italian listing + cement = institutional underweight. Kerrisdale Oct 2025 long thesis 73% upside.</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Kerrisdale Capital published long thesis Oct 2025 (€85 PT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>8. Foreign / Underfollowed Value</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>MGNI</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Independent CTV SSP. Netflix/Disney/Roku exclusive deals scaling. AI ad-buying integration. Last major non-Google scaled SSP.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Yartseva 6/7 (sub-$2B), B/M 0.49, FCF yield positive, ROA positive</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>CTV ad spend doubling 2024-2028 + Netflix exclusive scaling + AI integration</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Market: ad-tech roadkill. Smart: winning independent CTV SSP that survived ad-tech wash-out.</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Nine Ten Capital (Bares) 13.1% of book / 3.48M sh / $41.4M</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>8. Foreign / Underfollowed Value</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>MTY.TO</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026 SSS test + NCIB</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>[See Archetype 1]</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>CEO open-market buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>9. Quality Compounder at Trough</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Yartseva 6/7 IT services franchise. Multi-fund consensus Q1 2026. 300k+ delivery workforce moat. AI/IT services capex super-cycle 2026-2028.</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>P/B 1.66 (B/M 0.60), 9.88% FCF yield, ROA 10.44%, -27% 6mo</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>AI implementation winner via enterprise partners + Q2 2026 earnings</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Market: AI disrupts IT services. Smart: AI accelerator not disruptor.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Multi-fund deep-value funds Q1 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>9. Quality Compounder at Trough</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>DHR</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Pure-play life sciences (Cytiva bioprocessing, Beckman Dx, Cepheid). Q1 EPS $2.06 beat by 6.2%; bioprocessing inflecting positive after destock; Cepheid respiratory comp resets Q4 2026.</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>19.7x forward P/E (trough vs 5yr avg 30x); ROA pos; B/M 0.43</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Bioprocessing book-to-bill durably &gt;1.0 + China VBP stabilization H2 2026 + Cepheid Q4 reset</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Consensus: show-me on growth post-destock. Sundheim/D1: same stock 2019-2021 (30%/yr) at trough multiple while H2 2026 comps inflect.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>D1 Capital +312% Q1 ($107M→$437M, 4th-largest position)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>9. Quality Compounder at Trough</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Founder/CEO Schleifer + Yancopoulos R&amp;D-led. $31.4B book equity + EYLEA franchise + Linvoseltamab launching. Pipeline broad. Itepekimab Phase 3 readout potential catalyst.</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>B/M 0.48, FCF yield 6.33%, P/B 2.07; Yartseva 6/7 (size only fail)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Itepekimab 2026-2027 data + Linvoseltamab ramp</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Market: fianlimab miss + Eylea biosimilar. Smart: broad pipeline + buyback + founder skin.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Founder-led; multi-fund pharma specialist holds</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15209,1732 +19871,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Archetype</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Thesis</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Valuation</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Catalyst</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Variant</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Smart money</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>CARS</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Digital dealer SaaS (19,390 dealers x $2,473 ARPD/mo, 90% recurring). Q1 EPS $0.45 vs $0.13 est (+246%). Subscription +2%; OEM/National -12% (cyclical bottom).</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>P/B 0.83, P/FCF 3.5, 28% TTM FCF yield, EV/EBITDA 2.7x</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>$25-30M annualized cost program 2027 + $90M buyback (16% cap raised from $60M)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Street: declining auto Yellow Pages at 4x P/FCF. Variant: 90% SaaS dealer recurring + buyback math.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Yartseva 7/7 - smart money still building</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>CRTO</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Performance ad-tech pivoting to Commerce Yield retail media (235 retailers incl Lowes/Costco). $1B+ media spend Q1 2026 (+8% cc). OpenAI partnership live with 1,000+ brands. Q1 retail media -31% ex-scope -- actual underlying +24%.</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>P/E 3.73 (fwd), P/B 0.79, P/FCF 4.98, EV/EBITDA 2.28, 20.7% FCF yield</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Q3 2026 anniversary of scope losses + Luxembourg redomiciliation + $200M buyback (22% cap)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Market prices terminal decline; Petrus Advisers activist + 33% FCF yield + retail media TAM $200B by 2028.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Nierenberg D3 9.37% / +19% Q1 2026; Petrus Advisers activist</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>DV</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Pure-play ad verification (68% market share in fraud detection vs IAS 2.7%). 4,300+ customers vs IAS 169. Q1 2026 rev +10%, EBITDA 31% margin. CTV +28%, social activation +92%.</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>P/FCF 11x (trough), EV/EBITDA 9.6x, EV/Sales 1.9x, 9% FCF yield</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>ABS streaming Do Not Air list rollout Q2/Q3 + Meta activation $12M ARR to $50M+ path</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Market: Google MRC self-measurement threat. Variant: CTV verification underpenetrated (10%) vs display (70%).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Insider 12.69% (high for ad-tech); Yartseva 7/7</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>FTLF</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Microcap nutraceutical at $93M cap. Sub-institutional minimum. Classic Yartseva discarded-microcap profile with positive FCF + ROA + extreme drawdown.</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>P/B 2.05, B/M 0.49, FCF yield 8.2%, ROA 7.2%, near 52w low, -43.9% 6mo</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026 earnings; M&amp;A speculation; recovery in supplement category</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Market: forgotten micro. Smart money: pure Yartseva mean-reversion target.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Smoak Capital residual position; previously a Smoak top-5</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>GLOB</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>LatAm IT services with AI Pods inflection ($32.8M ARR from $0 in 12 months; $352M pipeline; 40% top-20 client penetration). Founder Migoya 23-year tenure + ~3% via Founders Trust.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>P/E 5.91 (sector low), P/B 0.78, P/FCF 5.56, 17% FCF yield, EV/EBITDA 4.95</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Q3 2026 AI Pods print + Argentina FX tailwind + ENRGI platform launch H2</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Market: melting India-IT comp. Smart money: AI mix shift to higher-margin work + LatAm cost arb. CAVEAT: securities class action (lead plaintiff June 23, 2026); COO resigned July 2025 not replaced.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Cartica historical 6.5% Q4 2022; sentiment bottom 16% short float</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>HRMY</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>$1B+ WAKIX franchise (pitolisant for narcolepsy). Q1 2026 rev +17% to $215M; pediatric FDA approval Feb 13 2026 extends IP to 2030 (pediatric exclusivity to 2040s). 5 Phase 3 trials in pipeline.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>P/B 1.91, P/Sales 2.05, FCF yield 19.36%, 26% net cash position</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Pitolisant GR NDA Q2 2026 (PDUFA Q1 2027); BP-205 Phase 1 PK mid-2026</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Market: single-product cliff. Smart money: Lilly's $6.3B Centessa (Q3 2026 close) validated orexin space + IP estate.</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>M&amp;A buyers: Jazz Pharma, Lundbeck, Otsuka; Catalyst Pharma precedent</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>INMD</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Israeli aesthetic device leader (Morpheus8, BodyTite). 85% recurring consumables. Steel Partners +155% Q1 2026 = 25.5% of their book; founder Mizrahy bought 800k sh ($10.7M) Feb 2026.</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>P/B 1.32, FCF $537M cash = $8.47/sh (62% of price), 77.8% gross margin</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026 earnings ~Aug 5 + potential Steel renewed bid ($18 prior)</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Market: Israeli geopolitical + aesthetic cycle. Smart money: $11-12 floor on cash alone; Steel implied $20+ takeout.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Steel Partners 25.5% of book; Mizrahy +800k sh ($10.7M)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>MTY.TO</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Multi-brand Canadian QSR franchisor (90 banners incl Cold Stone, Mucho Burrito, Papa Murphy's). 7,000+ locations, 98%+ franchised. Q1 EPS C$0.98 BEAT vs C$0.80 cons.</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>P/B 1.04 (trading at book!), EV/EBITDA 7.5x (vs QSR peer 14-18x), 16.7% FCF yield</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026 earnings test SSS stabilization + NCIB 5% of float through July</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Market: melting ice cube. Variant: SSS troughing + debt paying down + M&amp;A pool (RBI, Inspire at 12-14x EBITDA).</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>CEO Lefebvre open-market buy at C$30.54 (+33% stake)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>NRP</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Royalty trust on 13M mineral acres + 49% Sisecam soda ash JV. Near-zero debt by mid-2026 after $109M paydown + preferred retirement. Distribution increase guided for November 2026 (delayed from prior guide due to Sisecam capital call).</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>P/B 2.26 (B/M 0.47), 14.5% FCF yield, ROA 10.5%, 6.6x P/FCF</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Nov 2026 distribution step-up + preferreds retire; Q3 2026 Sisecam recovery sig</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Market: dying coal MLP. Smart money: debt-free royalty with 12% FCF yield, comparable to TPL at 25x P/CF (NRP at 6x).</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Saber/Huber 17.75%, Greystone top, Right Tail NEW Q1 2026, Berkowitz/Fairholme</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>OPRX</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Digital health POC pharma messaging to 60%+ US prescribers. May 21 2026 DeepIntent integration = first DSP accessing OPRX EHR network (Q3 2026 launch) opens &gt;80% of digital pharma budgets.</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>P/B 0.70 (sub-book), P/FCF 4.89, 15.7% FCF yield, EV/Sales 0.88, Adj EBITDA 4.4x EV</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Q4 2026 DSP integration revenue start + Q2 2026 earnings Aug 14</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Market: MFN victim; Smart money: profitable ($19M FCF) at 0.7x book, target $11.50 (138% upside).</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Insider 14.82%; $10M buyback through March 2027; Doximity exec Presti to board April 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>ROCK</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3-segment industrial (Residential 80%, Renewables, Agtech). OmniMax acquisition closed Feb 2026 ($1.335B) = #1 in residential roofing accessories. FY26 guide $1.76-1.83B rev, $3.65-4.05 EPS.</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>P/B 1.34, FCF yield 6.5%, ROA 2.95%, EV/Sales 1.0x vs peer 1.5x</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026 earnings = first clean OmniMax quarter; aluminum normalization; Q3 reroofing season</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Market: busted SPAC with 1.56 D/E. Variant: one-time integration year; FY27 EPS $5+ at 15x = $75-90.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Director Metcalf bought $502k March 2026; Vanguard 5.24% 13G</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>TREE</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Three-segment marketplace (Insurance 68%, Consumer 20%, Home 12%) at Q1 2026 inflection: rev +37%, VMM +28%, EBITDA +71%, Insurance +51%. Net leverage falling 3.4x→2.1x; S&amp;P upgraded.</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>P/E 2.92, P/FCF 7.2, ROE 88.6%, B/M 0.60</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026 print + $575M July 2025 converts retired + Fed rate cuts unlock Home/Consumer</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Street disbelieves Insurance durability. Variant: insurance carriers in year-2 of 5-7yr up-cycle = $200M+ EBITDA into 2027.</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Yartseva 7/7 + post-Q1 inflection demonstrated</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>VITL</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Pasture-raised egg category creator with brand moat. Walmart/Target/Whole Foods distribution. 11% ROA sustained THROUGH the avian flu crash = exceptional earnings power.</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>B/M 0.74, ROA 11% (BEST in 6/7 tier), -68.76% from peak</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Avian flu egg-supply normalization + summer pricing + M&amp;A speculation</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Market lumped premium VITL with commodity egg crash. Reality: brand pricing power retained. Strategic buyers: Kraft Heinz, Hain, General Mills.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>No major fund concentrated yet = entry preserved; Yartseva 6/7</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>10. Hedged / Special Structure</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>AAP CALL</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Cooper Creek's largest single call exposure. Overlaps with H Partners' AAP cash 46% concentration = double-conviction across two fund styles.</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>$158M call notional; +213% Q1 2026 (Cooper Creek)</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026 margin recovery proof + H Partners 13D escalation</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Catalyst-driven leverage on H Partners' AAP thesis.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Cooper Creek call stack ($518M total notional incl SIG/TTWO/DOCN/GXO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>10. Hedged / Special Structure</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>CTMX-WT</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>BVF Partners holds CTMX Tranche 2 warrants expiring 7/3/2026 (next 5 weeks). Embedded biotech IPO/crossover leverage near expiration creates urgency catalyst.</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5.77M shares warrants; group ownership equivalent ~3.5%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Warrant expiration 7/3/2026 = IMMINENT URGENCY</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>BVF's KYMR top conviction (14.6%) signals their biotech book has high conviction quality.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>BVF Partners 13G/A #5 (warrants exp 7/3/2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>10. Hedged / Special Structure</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>LQDA</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Yutrepia (treprostinil dry-powder inhaler) for PAH and PH-ILD. Q1 2026 product sales $129.9M (+44% QoQ); 4,500 unique patients; mgmt $1B+ 2027 target.</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>P/Sales 12x on $130M Q1 run-rate; cash $200M+ floor; M&amp;A premium 50-100%</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>'327 patent ruling pending (binary); Q2 print Aug 2026; UTHR Tresmi competitive launch</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Consensus PT $63.75 assumes flat share. Buckley's PUT-hedged structure suggests binary patent risk; UTHR M&amp;A target.</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Buckley Capital 32% LONG + PUT structure ($44.7M notional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>10. Hedged / Special Structure</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>XBI</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Stonepine $51M long + $51M short = $102M notional. Pure long-vol bet on biotech 2026-2027 FDA cycle dispersion.</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Biotech basket at multi-year low; straddle structure captures vol</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Biotech FDA cycle 2026-2027 (multiple catalysts driving dispersion)</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Long-vol thesis: biotech sector cycle creates dispersion that benefits straddle structure regardless of direction.</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Stonepine 40.9% of $250M book in XBI straddle</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2. Activist Board Catalyst</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>AAP</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>#3 aftermarket retailer post-WorldPac sale. Q1 +3.5% comps (Pro mid-single, DIY low-single). 700+ stores closed; ~1,300 strategic locations remain. Bridge to AZO-style 8-10% margins = $130-150/sh.</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>3.8% op margin (rising +410bps), FY26 guide $2.40-3.10 EPS; sub-1x sales; M&amp;A floor 0.8x sales = $80/sh</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026 earnings Aug = needs comps +2%+ and op margin &gt;5%; H Partners 13D escalation possible</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Consensus PT $57 (dead money). H Partners 46% concentration implies AAP returns to AZO margins.</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>H Partners 46.3% / $71.2M / +50% sh Q1 2026 (1.35M sh); Legion Partners precedent</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2. Activist Board Catalyst</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>ACHC</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Largest US behavioral health network (260+ facilities). DOJ Medicaid investigation overhang. Q1 2026 admissions stabilizing. Greenlight 4.1M activist; Sohn 5/12 pitch.</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>EV/EBITDA 6.5x (vs HCA 9x, UHS 8x); 29% short float; -70% drawdown</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>DOJ resolution + Q2 2026 earnings + 29% short squeeze potential</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Market: DOJ/Medicaid existential. Greenlight: provider necessity + facility footprint + de-rate captured = floor near current.</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Greenlight Capital 4.1M sh (David Einhorn); Sohn presentation 5/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>2. Activist Board Catalyst</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>FUN</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Post-Cedar Fair/Six Flags merger consolidation. 42 parks irreplaceable real estate. Q1 2026 rev +12%, attendance +4%, per-cap +6%. $200M synergy target ($120M cost + $80M growth).</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>$5.27B net debt = 7x leverage; EV/EBITDA 9x on $1.05B 2027 EBITDA</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>May 26 2026 AGM: Jaffer joins board (Class III through 2027, Audit&amp;Finance Cttee). Jana 9% pushing OUTRIGHT SALE.</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Street: broken merger story. Two-front activist pressure (governance + sale) + per-park RE floor $47M each.</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>H Partners 53.7% / $82.5M / 5.7% of class; Jana 9% + Travis Kelce co-invest</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2. Activist Board Catalyst</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>MRP</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Lennar 80%+ owner spinoff with 100k+ optioned lots at cost basis. Land bank trading below NAV with Lennar as guaranteed off-take partner. Housing-cycle recovery levered.</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>B/M 1.274 (DEEPEST in 6/7 tier; deeper than NRP's 0.47), pure NAV play</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026 print + Lennar volume scaling + housing cycle inflection</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Market priced spinoff orphan technical pressure. Smart money: pure land cash-cow at discount to NAV.</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Lennar 80%+ owner = patient capital lock-in; SITG multi-fund flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>2. Activist Board Catalyst</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>POSTBPB</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Nierenberg/D3 is LARGEST shareholder (~$16.4M / 7% of D3 book). Customer-traffic gains while peers don't (Q1 2026 letter thesis). Form 4 insider buying by Nierenberg at depressed levels.</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Sub-$300M micro restaurant chain; turnaround stage</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Restaurant turnaround + Nierenberg potential escalation</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Market: tier-2 restaurant chain. Activist soft-pressure thesis.</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Nierenberg/D3 largest shareholder; 13D/A active March 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2. Activist Board Catalyst</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>QRHC</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Wynnefield filed 13D 13.3% May 2025; Robert Lipstein joined board. Cooperation Agreement w/ standstill until 30 days before 2027 nomination window. Asset-light recurring waste mgmt.</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Sub-$200M micro; recurring waste services revenue model</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Operational improvements + Wynnefield additional buying if dips</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Market: small-cap value trap. Activist: board seat + potential value-unlock initiatives.</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Wynnefield 13.3% / 2.73M sh / 13D w/ board seat</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>3. Biotech Multi-Fund Convergence</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>ASND</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>TransCon prodrug platform: SKYTROFA (GHD), YORVIPATH (hypopara), YUVIWEL (achondroplasia approved Feb 2026). &gt;1,000 new US YORVIPATH enrollments Q1; 6,300+ patients across 2,700 prescribers.</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Profitable (22% non-IFRS op margin); €247M Q1 (2x YoY); peak rev YORVIPATH $4-5B</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>YUVIWEL ramp + Q2/Q3 YORVIPATH growth + TransCon CNP follow-on indications</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Sell-side: $15B endocrine specialty maturing. RA Capital: $30B+ at 70-90K addressable hypopara population. Analyst high $345 (Barclays).</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>RA Capital 24.9% of $9.44B = $2.35B = LARGEST single biotech crossover position; held since 2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>3. Biotech Multi-Fund Convergence</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>BNTC</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Gene therapy platform anchor position. Suvretta 44.1% 13D anchor stake (largest activist ownership in their portfolio). PIPE participation Nov 2025.</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Sub-$300M biotech; gene therapy platform optionality</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Multiple gene-therapy programs in development; clinical readouts upcoming</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>44.1% ownership creates board influence + asymmetric upside on clinical reads.</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Suvretta 44.1% 13D (Suvretta's LARGEST stake by % ownership)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>3. Biotech Multi-Fund Convergence</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>CELC</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Phase 3 VIKTORIA-1 PIK3CA-mut POSITIVE May 1 2026 (76% PFS hazard reduction). Gedatolisib pan-PI3K/mTOR oncology. Triplet vs alpelisib+fulvestrant. Multiple HR+/HER2- breast cancer cohorts.</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>$387M cash + accepted NDA + Priority Review = de-risked; 4-5x peak rev precedent</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>JUNE 2 ASCO LBA1008 oral + JULY 17 PDUFA goal date (2 catalysts in 8 weeks)</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Market: alpelisib-class peak ($1-2B). Baker Bros 19.99% 13D activist: $5-10B peak (triplet displaces alpelisib + captures WT segment).</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Baker Bros 19.99% ACTIVIST 13D = $904M / 5.48% of $17.4B book</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3. Biotech Multi-Fund Convergence</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>KYMR</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Targeted protein degradation platform. Lead KT-621 oral STAT6 degrader competes with injectable Dupixent ($14B+ franchise). IRAK4 partnered with Sanofi.</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>$1.55B cash (runway 2029); Dec 2025 follow-on $602M at $86</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>BROADEN2 AD mid-2027 (12+ months); BREADTH asthma late 2027; FDA Fast Track granted both</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Market: Phase 1b execution risk. Two top biotech specialists: oral Dupixent-disruptor with peak $5-10B.</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>BVF #1 position 14.6% of $3.14B book ($458M) + Baker Bros 4.1% / $721M; BOTH anchored $86 follow-on</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>3. Biotech Multi-Fund Convergence</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>PRLD</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Precision oncology / molecular glue / degrader platform. SMARCA2 discontinued 2025; pivot to JAK2V617F (PRT12396) + KAT6A (PRT13722). AbCellera partnership.</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>$175M cash vs $340M mcap = $2.20/sh net cash (51% of price); buyout floor near current</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>PRT12396 Phase 1 H2 2026; PRT13722 IND mid-2026; Incyte option agreement Nov 2025</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Market: broken story post-SMARCA2 fail. Smart money: April 2026 refunding = platform-validation thesis. JAK2 mutant-selective addresses 95% PV/60% ET/55% MF.</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Baker Bros 15.5% 13D/A + RA Capital 9.99% 13G; BOTH anchored SAME $90M April financing at $4.44</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>3. Biotech Multi-Fund Convergence</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>PVLA</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Rare-disease topical platform. QTORIN rapamycin gel for microcystic LMs (Breakthrough + Orphan + Fast Track). Phase 3 SELVA POSITIVE Feb 24 2026 (mLM-IGA +2.13, p&lt;0.001).</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>$261.9M cash = $25/sh (19% of price). Phase 3 derisked. M&amp;A floor 4-6x peak rev</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Pre-NDA FDA meeting Q2 2026; NDA H2 2026; PDUFA H1 2027</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Market: single-asset rare-disease (~$1.5B). Smart money: platform with &gt;$1B peak QTORIN + venous malformations/angiokeratomas/pitavastatin programs.</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>BVF 3.8% / $120M (8.5% of company) + Suvretta 3.67% / $144M (+29.3% Q1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>4. Sponsor-Anchored Holdco Transformation</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>HHH</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Ackman-led 'Modern Berkshire'. 3,813 acres residential MPC ($4.8B NAV) + 2,447 acres commercial ($2.0B) + Vantage specialty insurance ($2.2B 2027 premium). Marc Grandisson (ex-Arch Capital CEO) on board April 2026.</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>NAV $95-105/sh = 33-39% discount; $1.84B cash + $515M revolver liquidity</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Vantage close Q2 2026 (30-45 days); Park Ward Village condo closings Q2-Q3 (~$1B rev); first post-Vantage capital allocation</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Street: sub-scale RE dev with leverage. Ackman: insurance float + permanent capital. NAV $95-105 vs $63 = 50-67% margin of safety.</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Ackman 47% via $900M @ $100/sh + $1B preferred; Northern Right NEW Q1 +12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>5. Spinoff / SoTP Arbitrage</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>DLTR</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Post-divestiture clean Dollar Tree franchise (16k+ stores). Multi-fund deep-value consensus Q1 2026. Mayer M6 turnaround pattern.</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>B/M 0.20 (Yartseva 6/7); Family Dollar divestiture proceeds = $1B+ cash bolster</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Family Dollar sale completion + comparable sales recovery + multiple re-rate</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Market priced Family Dollar mistake. Smart money: post-divestiture clean franchise.</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Multi-fund deep-value funds Q1 2026 adds</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>5. Spinoff / SoTP Arbitrage</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>KBR</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Two segments: MTS (gov services 72%, $18.5B backlog, cleared workforce 20k) + STS (process tech + TerraPower Natrium nuclear EPC alliance, 22% EBITDA margin). FY26 $980M-1.04B EBITDA, $3.87-4.22 EPS.</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>SoTP: MTS at 11x EBITDA ($5.2B EV) + STS at 14x ($5.3B) = $55-65/sh combined</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>MTS spin January 4 2027 (board-approved Sept 2025); NRC Natrium safety eval mid-2026</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Market: broken post-HomeSafe termination + class action overhang. Variant: HomeSafe disposed; spin unlocks SoTP value.</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>D3/Nierenberg +425% Q1 (largest single add in entire universe); Irenic activist ~1%; Director Form 4 buys May 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>6. Deep Drawdown Mean Reversion</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>COTY</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Prestige/fragrance beauty (Burberry, Tiffany, CK, Calvin Klein brands). KKR overhang anchor. -37.5% drawdown extreme contrarian setup. Brand assets worth multiples of EV.</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>B/M 1.73 (DEEPEST in 6/7 tier), FCF yield 17.4%, but ROA -4.91% (Y3 fails)</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Debt restructuring + KKR exit dynamics + cost program execution</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Market: earnings deterioration. Smart: 6-year FCF payback floor with brand asset coverage.</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>KKR legacy anchor; deep-value funds incrementally adding</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>6. Deep Drawdown Mean Reversion</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>FRPT</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Premium fresh dog food brand leader. Manufacturing capacity coming online (Ennis plant). Margin inflection at 70%+ utilization. M&amp;A target for Nestle Purina / Mars / General Mills.</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>B/M 0.50 (borderline Yartseva 6/7), ROA 3.41%, -40% drawdown</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Capacity utilization + margin inflection + M&amp;A speculation</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Market: consumer weakness + capex burden. Smart: brand pricing power + post-capex FCF inflection.</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Marlowe Partners 39.8% in last 13F (highest single-fund signal)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>6. Deep Drawdown Mean Reversion</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>OPRX</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1]</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>P/B 0.70 sub-book, -65.4% 6mo drawdown</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>DSP integration Q4 2026 + MFN clarity</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1]</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Insider 14.82%; $10M buyback</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>6. Deep Drawdown Mean Reversion</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>VITL</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1 for full thesis]</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>B/M 0.74, ROA 11%, -68.76% from peak (DEEPEST drawdown in 6/7)</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Avian flu normalization + M&amp;A + summer pricing</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1]</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>No major fund concentrated yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>7. Hard Asset / Royalty</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>JOE</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Florida Panhandle landbank with 170k+ acres. GAAP B/M understates LIFO land basis vs market value. True NAV-based B/M likely &gt;1.0 even at current price.</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Land bank: 170k acres NW Florida; GAAP B/M understates LIFO land basis</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Florida population growth + master plan community development + Berkowitz anchor</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Yartseva fails on size + low GAAP B/M; correct framework is Lynch asset play.</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Berkowitz/Fairholme longstanding anchor</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>7. Hard Asset / Royalty</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>NRP</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1]</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1]</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Nov 2026 distribution + preferreds retire</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1]</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Saber 17.75% + Greystone top + Right Tail NEW + Berkowitz</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>7. Hard Asset / Royalty</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>TPL</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Permian water + royalty optionality. Same NAV-vs-GAAP-book issue as JOE. Pricing 'endless drilling' premium.</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Permian royalty trust at 25x P/CF (vs NRP at 6x)</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Permian production growth + water revenue optionality</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Yartseva captures FCF yield + ROA but understates B/M for land assets.</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Multi-fund quality holders; HRC anchor</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>8. Foreign / Underfollowed Value</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>BZU.IM</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Italian cement (€8.9B mcap). 52% of EBITDA from US. AI data-center concrete demand thesis. Trading at sector-discount multiple to LafargeHolcim/CRH peers.</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>6.8x EV/EBITDA (vs peer 9-11x); €85 PT = +73% upside</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>AI data-center capex translating to concrete orders; multiple re-rate to peer levels</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Italian listing + cement = institutional underweight. Kerrisdale Oct 2025 long thesis 73% upside.</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Kerrisdale Capital published long thesis Oct 2025 (€85 PT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>8. Foreign / Underfollowed Value</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>MGNI</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Independent CTV SSP. Netflix/Disney/Roku exclusive deals scaling. AI ad-buying integration. Last major non-Google scaled SSP.</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Yartseva 6/7 (sub-$2B), B/M 0.49, FCF yield positive, ROA positive</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>CTV ad spend doubling 2024-2028 + Netflix exclusive scaling + AI integration</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Market: ad-tech roadkill. Smart: winning independent CTV SSP that survived ad-tech wash-out.</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Nine Ten Capital (Bares) 13.1% of book / 3.48M sh / $41.4M</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>8. Foreign / Underfollowed Value</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>MTY.TO</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1]</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1]</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026 SSS test + NCIB</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>[See Archetype 1]</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>CEO open-market buy</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>9. Quality Compounder at Trough</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>CTSH</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Yartseva 6/7 IT services franchise. Multi-fund consensus Q1 2026. 300k+ delivery workforce moat. AI/IT services capex super-cycle 2026-2028.</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>P/B 1.66 (B/M 0.60), 9.88% FCF yield, ROA 10.44%, -27% 6mo</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>AI implementation winner via enterprise partners + Q2 2026 earnings</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Market: AI disrupts IT services. Smart: AI accelerator not disruptor.</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Multi-fund deep-value funds Q1 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>9. Quality Compounder at Trough</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>DHR</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Pure-play life sciences (Cytiva bioprocessing, Beckman Dx, Cepheid). Q1 EPS $2.06 beat by 6.2%; bioprocessing inflecting positive after destock; Cepheid respiratory comp resets Q4 2026.</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>19.7x forward P/E (trough vs 5yr avg 30x); ROA pos; B/M 0.43</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Bioprocessing book-to-bill durably &gt;1.0 + China VBP stabilization H2 2026 + Cepheid Q4 reset</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Consensus: show-me on growth post-destock. Sundheim/D1: same stock 2019-2021 (30%/yr) at trough multiple while H2 2026 comps inflect.</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>D1 Capital +312% Q1 ($107M→$437M, 4th-largest position)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>9. Quality Compounder at Trough</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>REGN</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Founder/CEO Schleifer + Yancopoulos R&amp;D-led. $31.4B book equity + EYLEA franchise + Linvoseltamab launching. Pipeline broad. Itepekimab Phase 3 readout potential catalyst.</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>B/M 0.48, FCF yield 6.33%, P/B 2.07; Yartseva 6/7 (size only fail)</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Itepekimab 2026-2027 data + Linvoseltamab ramp</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Market: fianlimab miss + Eylea biosimilar. Smart: broad pipeline + buyback + founder skin.</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Founder-led; multi-fund pharma specialist holds</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22502,7 +25439,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23926,7 +26863,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24688,7 +27625,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25430,7 +28367,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26552,7 +29489,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28364,610 +31301,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Archetype</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Mapped factor</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Base rate 12m</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Live T1</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Live T2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Demoted</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Graduated (rerated)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Dead</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Untracked</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Best surviving</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Best ER</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>1. Yartseva Pure Multibagger</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>smart_money_uw</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>+17%</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>ROCK</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>+66%</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>WEAKENED</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>10. Hedged / Special Structure</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>EXCLUDED-BY-MANDATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2. Activist Board Catalyst</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>activist_13d</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-26%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>EMPIRICALLY-WEAK</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>3. Biotech Multi-Fund Convergence</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>EXCLUDED-BY-MANDATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>4. Sponsor-Anchored Holdco Transformation</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>sponsor_anchor</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>+17%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>HHH</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>+7%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5. Spinoff / SoTP Arbitrage</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>spin_arb</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>+10%</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>KBR</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>+70%</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>WEAKENED</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>6. Deep Drawdown Mean Reversion</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>smart_money_uw</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>+17%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>WEAKENED</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>7. Hard Asset / Royalty</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>family_anchor</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>+17%</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>NRP</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>+7%</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>WEAKENED</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>8. Foreign / Underfollowed Value</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>deep_value</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>+0%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>EMPTIED</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>9. Quality Compounder at Trough</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>post_acquisition</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>+0%</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>EMPTIED</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>